--- a/TN/dataset/tennessee_public_data_centers.xlsx
+++ b/TN/dataset/tennessee_public_data_centers.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf9d9800af38a4a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R3574101214004509"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R5082f2aa05f24078"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="Ra9cfb7e8060e46dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="R23c9e5d603d24ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R1b39ba1c1ad440e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R50f1835ae13d4a7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="Rf51c3b862c0f44bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R251ed96a6c2f4629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R733927bef93b4ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R1f6490a475fc4beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Ree55e08506e54a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Rb96916fd01d84047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0d2aded890494020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R1cc297d0f7004afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R5813bdeb2eac46ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R3b25501127854222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="Rd134fd093d564f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R2090a52bcc934526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="Rf5dfaf003577423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="Rbd0d0e93089f4341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R016acd8d38e047c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R226e36a77a544718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R1acf0415faed407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rcd08d83c01af4cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Rf58b1f9db49d44a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1383,7 +1383,7 @@
         <x:v>Verification policy</x:v>
       </x:c>
       <x:c r="B22" s="85" t="str">
-        <x:v>2026-09-04 fifth-pass candidate-location research: Jackson physical street address resolved to 2342 North Parkway East via JEA + SEC ownership chain; Atmosphere receives only a low-confidence market pin, explicitly not the 38-acre parcel; Mountain City parcel identity is high-confidence but WGS84 remains unresolved; Scipio remains explicitly non-public.</x:v>
+        <x:v>2026-09-07 review-queue resolution: Cielo remains in Master only for source traceability with analysis_scope=unconfirmed_candidate and is excluded from confirmed spatial training; the Atmosphere market pin was removed; linked and address discrepancies are documented in Review_Queue and model/data/metadata/review_queue_research_ledger.csv.</x:v>
       </x:c>
       <x:c r="C22" s="85" t="str">
         <x:v>Uncertain status, scope, or identity stays in Candidate_Sites</x:v>
@@ -4742,6 +4742,292 @@
         <x:v>Parcel identity strengthened; no textual WGS84 point found.</x:v>
       </x:c>
     </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>TNDC-006</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>analysis_scope</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>core_data_center</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>unconfirmed_candidate</x:v>
+      </x:c>
+      <x:c r="G135" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H135" t="str">
+        <x:v>Local reporting conflicts with market listings; retain traceability but exclude from confirmed spatial presence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>TNDC-023</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>verification_note</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>Local vicinity note</x:v>
+      </x:c>
+      <x:c r="F136" t="str">
+        <x:v>Approximate-vicinity decision</x:v>
+      </x:c>
+      <x:c r="G136" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H136" t="str">
+        <x:v>Official developer page lacks a parcel; prevent false exact-site interpretation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>Retired TNDC-025</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>Review_Pairs rationale</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>blank</x:v>
+      </x:c>
+      <x:c r="F137" t="str">
+        <x:v>No forced Colossus merge</x:v>
+      </x:c>
+      <x:c r="G137" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H137" t="str">
+        <x:v>Generic source cannot be assigned safely to either xAI campus.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>TNDC-037</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>address</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>2992 Sidco Drive</x:v>
+      </x:c>
+      <x:c r="F138" t="str">
+        <x:v>2990 Sidco Drive</x:v>
+      </x:c>
+      <x:c r="G138" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H138" t="str">
+        <x:v>Use current Lumen route-list address; retain legacy discrepancy in note.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>TNDC-039</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>operator</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>Fisk University</x:v>
+      </x:c>
+      <x:c r="F139" t="str">
+        <x:v>blank; Fisk retained as project sponsor</x:v>
+      </x:c>
+      <x:c r="G139" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H139" t="str">
+        <x:v>Operating partner is not publicly identified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>TNDC-002|TNDC-009</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>facility mapping</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>queue ambiguity</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>two distinct SEC-mapped properties</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>SEC evidence confirms both Crossville addresses and no merge.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>TNDC-059</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>verification_class</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>review</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>Facility-facing 4280 address and broader-site 4300 permit address are explicitly distinguished.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>TNCAND-005</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>review_note</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>prior note</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>current evidence limit recorded</x:v>
+      </x:c>
+      <x:c r="G142" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H142" t="str">
+        <x:v>Not promoted without current operating confirmation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>TNCAND-006</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>latitude|longitude</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>market pin</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>blank</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H143" t="str">
+        <x:v>No public parcel; remove physically inconsistent point from spatial use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>TNCAND-012</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>candidate_type</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>unresolved_duplicate_or_new_facility</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>linked_master_evidence</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>Shared address links this evidence to TNDC-038.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>TNCAND-013–016</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>review_note</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>legacy status unclear</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>primary-evidence requirement recorded</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>../model/data/metadata/review_queue_research_ledger.csv</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>Retained as candidates; do not promote from directory evidence alone.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5090,19 +5376,19 @@
         <x:v>Cielo Montgomery County AI Campus</x:v>
       </x:c>
       <x:c r="C2" s="85" t="str">
-        <x:v>verification</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D2" s="85" t="str">
-        <x:v>Candidate/unverified market listing; local June 2026 reporting said no data-center proposal was under discussion.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNDC-006</x:v>
       </x:c>
       <x:c r="E2" s="85" t="str">
-        <x:v>Keep as candidate; do not use as confirmed treatment unless new local evidence appears.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F2" s="85" t="str">
         <x:v>multiple public sources; local contradiction</x:v>
       </x:c>
       <x:c r="G2" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5113,19 +5399,19 @@
         <x:v>Hixson Data Center (McMinnville)</x:v>
       </x:c>
       <x:c r="C3" s="85" t="str">
-        <x:v>coordinate</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D3" s="85" t="str">
-        <x:v>Coordinate disagreement exceeds 7 km; only area/city-level point is defensible.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNDC-023</x:v>
       </x:c>
       <x:c r="E3" s="85" t="str">
-        <x:v>Resolve parcel/site before parcel-distance analysis.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F3" s="85" t="str">
         <x:v>source coordinate conflict retained</x:v>
       </x:c>
       <x:c r="G3" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5136,19 +5422,19 @@
         <x:v>Generic Colossus source identity</x:v>
       </x:c>
       <x:c r="C4" s="85" t="str">
-        <x:v>entity_resolution_retired</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D4" s="85" t="str">
-        <x:v>Removed from Master because it necessarily overlaps TNDC-030 or TNDC-031 but cannot be assigned safely.</x:v>
+        <x:v>Resolved in 2026-09-07 review: Retired TNDC-025</x:v>
       </x:c>
       <x:c r="E4" s="85" t="str">
-        <x:v>Resolve only if new source evidence identifies the matching campus; otherwise retain in Raw_Aligned and Review_Pairs.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F4" s="85" t="str">
         <x:v>all source records and URLs retained</x:v>
       </x:c>
       <x:c r="G4" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5159,19 +5445,19 @@
         <x:v>Level(3)/Lumen Nashville (Sidco)</x:v>
       </x:c>
       <x:c r="C5" s="85" t="str">
-        <x:v>address</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D5" s="85" t="str">
-        <x:v>Master has 2992 Sidco Drive while independent confirmed list reports 2990 Sidco Drive.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNDC-037</x:v>
       </x:c>
       <x:c r="E5" s="85" t="str">
-        <x:v>Resolve parcel/address before exact geospatial joins.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F5" s="85" t="str">
         <x:v>address contradiction</x:v>
       </x:c>
       <x:c r="G5" s="85" t="str">
-        <x:v>medium</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5182,19 +5468,19 @@
         <x:v>Quantum Leap Data Center / Fisk University</x:v>
       </x:c>
       <x:c r="C6" s="85" t="str">
-        <x:v>operator</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D6" s="85" t="str">
-        <x:v>Fisk confirms project/campus but operating data-center partner is not publicly identified.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNDC-039</x:v>
       </x:c>
       <x:c r="E6" s="85" t="str">
-        <x:v>Leave operator null until public operator evidence exists.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F6" s="85" t="str">
         <x:v>project verified; operator unresolved</x:v>
       </x:c>
       <x:c r="G6" s="85" t="str">
-        <x:v>medium</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5205,19 +5491,19 @@
         <x:v>CleanSpark Crossville pair</x:v>
       </x:c>
       <x:c r="C7" s="85" t="str">
-        <x:v>address</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D7" s="85" t="str">
-        <x:v>Two public Crossville addresses cannot be reliably assigned to TNDC-002 versus TNDC-009.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNDC-002</x:v>
       </x:c>
       <x:c r="E7" s="85" t="str">
-        <x:v>Leave both Master addresses null until facility-name mapping is sourced.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F7" s="85" t="str">
         <x:v>DataCenterMap market page retained in both records</x:v>
       </x:c>
       <x:c r="G7" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5228,19 +5514,19 @@
         <x:v>5C MEM01</x:v>
       </x:c>
       <x:c r="C8" s="85" t="str">
-        <x:v>address</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D8" s="85" t="str">
-        <x:v>County/public-health records use 4300 Getwell Rd; some directories use 4280 Getwell Rd.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNDC-059</x:v>
       </x:c>
       <x:c r="E8" s="85" t="str">
-        <x:v>Use 4300 as the official public-record address and retain the discrepancy.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F8" s="85" t="str">
         <x:v>official and industry sources retained</x:v>
       </x:c>
       <x:c r="G8" s="85" t="str">
-        <x:v>medium</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5251,19 +5537,19 @@
         <x:v>GRIID Jackson 60 MW Project</x:v>
       </x:c>
       <x:c r="C9" s="85" t="str">
-        <x:v>project_status</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D9" s="85" t="str">
-        <x:v>Announcement predates CleanSpark acquisition; no current site-level confirmation found.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNCAND-005</x:v>
       </x:c>
       <x:c r="E9" s="85" t="str">
-        <x:v>Do not promote until parcel and current status are confirmed.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F9" s="85" t="str">
         <x:v>announcement, acquisition, and SEC records retained</x:v>
       </x:c>
       <x:c r="G9" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5274,19 +5560,19 @@
         <x:v>Atmosphere Nashville Campus</x:v>
       </x:c>
       <x:c r="C10" s="85" t="str">
-        <x:v>location</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D10" s="85" t="str">
-        <x:v>Developer discloses scale but not an exact site.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNCAND-006</x:v>
       </x:c>
       <x:c r="E10" s="85" t="str">
-        <x:v>Keep as candidate until permitting or parcel evidence appears.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F10" s="85" t="str">
         <x:v>developer and trade reporting retained</x:v>
       </x:c>
       <x:c r="G10" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5297,19 +5583,19 @@
         <x:v>Scipio NREP Listing</x:v>
       </x:c>
       <x:c r="C11" s="85" t="str">
-        <x:v>entity_resolution</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D11" s="85" t="str">
-        <x:v>Could be TNDC-038 or a distinct Nashville site.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNCAND-012</x:v>
       </x:c>
       <x:c r="E11" s="85" t="str">
-        <x:v>Do not create another Master row without a distinct street address.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F11" s="85" t="str">
         <x:v>market directory and operator support page retained</x:v>
       </x:c>
       <x:c r="G11" s="85" t="str">
-        <x:v>high</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5320,19 +5606,19 @@
         <x:v>Legacy operational listings</x:v>
       </x:c>
       <x:c r="C12" s="85" t="str">
-        <x:v>current_status</x:v>
+        <x:v>closed_with_evidence</x:v>
       </x:c>
       <x:c r="D12" s="85" t="str">
-        <x:v>Historic/current directories identify physical sites, but present data-center operations are not explicit enough.</x:v>
+        <x:v>Resolved in 2026-09-07 review: TNCAND-013–016</x:v>
       </x:c>
       <x:c r="E12" s="85" t="str">
-        <x:v>Confirm current operator service before promotion to Master.</x:v>
+        <x:v>No open action for this dataset version. Evidence and disposition: ../model/data/metadata/review_queue_research_ledger.csv</x:v>
       </x:c>
       <x:c r="F12" s="85" t="str">
         <x:v>all supporting URLs retained in Candidate_Sites</x:v>
       </x:c>
       <x:c r="G12" s="85" t="str">
-        <x:v>medium</x:v>
+        <x:v>closed</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5603,13 +5889,13 @@
         <x:v>low</x:v>
       </x:c>
       <x:c r="J7" s="85" t="str">
-        <x:v>address | postal_code</x:v>
+        <x:v>unconfirmed_project_and_exact_site</x:v>
       </x:c>
       <x:c r="K7" s="85" t="str">
-        <x:v>COMPLIANT_PARTIAL</x:v>
+        <x:v>EXCLUDED_UNCONFIRMED</x:v>
       </x:c>
       <x:c r="L7" s="85" t="str">
-        <x:v>Coordinate populated with explicit non-exact precision/confidence and provenance.</x:v>
+        <x:v>Cielo is retained for source traceability only; local reporting conflicts with market listings. Excluded from confirmed spatial presence.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6216,12 +6502,14 @@
       <x:c r="I24" s="85" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J24" s="85" t="str"/>
+      <x:c r="J24" s="85" t="str">
+        <x:v>exact_parcel</x:v>
+      </x:c>
       <x:c r="K24" s="85" t="str">
-        <x:v>COMPLIANT_PARTIAL</x:v>
+        <x:v>APPROXIMATE_VICINITY</x:v>
       </x:c>
       <x:c r="L24" s="85" t="str">
-        <x:v>Coordinate populated with explicit non-exact precision/confidence and provenance.</x:v>
+        <x:v>Hixson confirms McMinnville/Warren County but has not published a parcel. 191 Industrial Dr is a local-reporting vicinity only.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -6670,7 +6958,7 @@
         <x:v>Nashville</x:v>
       </x:c>
       <x:c r="E37" s="85" t="str">
-        <x:v>2992 Sidco Drive</x:v>
+        <x:v>2990 Sidco Drive</x:v>
       </x:c>
       <x:c r="F37" s="85" t="n">
         <x:v>36.102726</x:v>
@@ -6686,10 +6974,10 @@
       </x:c>
       <x:c r="J37" s="85" t="str"/>
       <x:c r="K37" s="85" t="str">
-        <x:v>RESOLVED</x:v>
+        <x:v>ADDRESS_CANONICALIZED</x:v>
       </x:c>
       <x:c r="L37" s="85" t="str">
-        <x:v>Address/site-level location fully populated at high confidence.</x:v>
+        <x:v>Lumen current route list uses 2990 Sidco Drive; 2992 is retained as an adjacent legacy-directory discrepancy.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -7478,10 +7766,10 @@
       </x:c>
       <x:c r="J59" s="85" t="str"/>
       <x:c r="K59" s="85" t="str">
-        <x:v>COMPLIANT_PARTIAL</x:v>
+        <x:v>ADDRESS_CONTEXT_RESOLVED</x:v>
       </x:c>
       <x:c r="L59" s="85" t="str">
-        <x:v>Coordinate populated with explicit non-exact precision/confidence and provenance.</x:v>
+        <x:v>4280 Getwell Rd remains the facility-facing address; 4300 Getwell Rd is related broader-site permit/property evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -7748,12 +8036,8 @@
         <x:v>Nashville</x:v>
       </x:c>
       <x:c r="E67" s="85"/>
-      <x:c r="F67" s="85" t="n">
-        <x:v>36.16488198</x:v>
-      </x:c>
-      <x:c r="G67" s="85" t="n">
-        <x:v>-86.78088767</x:v>
-      </x:c>
+      <x:c r="F67" s="85" t="str"/>
+      <x:c r="G67" s="85" t="str"/>
       <x:c r="H67" s="85" t="str">
         <x:v>area_or_city</x:v>
       </x:c>
@@ -7761,13 +8045,13 @@
         <x:v>low</x:v>
       </x:c>
       <x:c r="J67" s="85" t="str">
-        <x:v>address | county | postal_code</x:v>
+        <x:v>exact_site|latitude|longitude</x:v>
       </x:c>
       <x:c r="K67" s="85" t="str">
-        <x:v>MARKET_PIN_ONLY</x:v>
+        <x:v>MARKET_ONLY</x:v>
       </x:c>
       <x:c r="L67" s="85" t="str">
-        <x:v>Coordinate is a low-confidence directory/market pin and must not be used as the 38-acre campus parcel.</x:v>
+        <x:v>Developer discloses Nashville project but no site. Removed the physically inconsistent market pin from spatial use.</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -7963,23 +8247,25 @@
       <x:c r="D73" s="85" t="str">
         <x:v>Nashville</x:v>
       </x:c>
-      <x:c r="E73" s="85"/>
+      <x:c r="E73" s="85" t="str">
+        <x:v>1661 Murfreesboro Pike</x:v>
+      </x:c>
       <x:c r="F73" s="85"/>
       <x:c r="G73" s="85"/>
       <x:c r="H73" s="85" t="str">
-        <x:v>area_or_city</x:v>
+        <x:v>address_or_site</x:v>
       </x:c>
       <x:c r="I73" s="85" t="str">
-        <x:v>low</x:v>
+        <x:v>high</x:v>
       </x:c>
       <x:c r="J73" s="85" t="str">
-        <x:v>address | latitude | longitude</x:v>
+        <x:v>none_linked_duplicate</x:v>
       </x:c>
       <x:c r="K73" s="85" t="str">
-        <x:v>EXPLICIT_NON_PUBLIC</x:v>
+        <x:v>LINKED_TO_MASTER</x:v>
       </x:c>
       <x:c r="L73" s="85" t="str">
-        <x:v>Current facility directory explicitly states the exact location is not public.</x:v>
+        <x:v>Shared public address links Scipio evidence to TNDC-038; not a distinct facility point.</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -8287,7 +8573,7 @@
       </x:c>
       <x:c r="B7" s="131" t="n">
         <x:f>COUNTIF(Master!V2:V1000,"core_data_center")</x:f>
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C7" s="67" t="str">
         <x:v>50 core entities after adding the independently verified Bristol facility; building-level records within existing campuses remain deduplicated.</x:v>
@@ -8422,7 +8708,7 @@
       </x:c>
       <x:c r="B13" s="131" t="n">
         <x:f>COUNTBLANK('Master'!C2:C61)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
         <x:v>Missing operators have explicit operator_status; unknown values are not fabricated.</x:v>
@@ -8824,7 +9110,7 @@
         <x:v>https://www.prnewswire.com/news-releases/cleanspark-to-add-5-ehs-and-increase-2024-guidance-with-acquisition-of-seven-additional-bitcoin-mining-facilities-in-tennessee-302244673.html | https://www.sec.gov/Archives/edgar/data/827876/000119312525297510/clsk-20250930.htm | https://www.datacentermap.com/usa/tennessee/crossville/ | https://www.sec.gov/Archives/edgar/data/827876/000095017024105354/clsk-ex10_4.htm</x:v>
       </x:c>
       <x:c r="AF3" s="128" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG3" s="85" t="str">
         <x:v>confirmed</x:v>
@@ -8845,7 +9131,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="AM3" s="85" t="str">
-        <x:v>SEC filing identifies the Campbell Junction Property at this address; existing approximate GPS retained.</x:v>
+        <x:v>CleanSpark SEC evidence maps Campbell Junction Property to 5784 Plateau Rd. The separate West Crossville property is 268 Sparta Hwy (TNDC-009); retain two facilities and do not merge.</x:v>
       </x:c>
       <x:c r="AN3" s="85" t="str">
         <x:v>1.1</x:v>
@@ -9264,7 +9550,7 @@
         <x:v>data_center</x:v>
       </x:c>
       <x:c r="V7" s="17" t="str">
-        <x:v>core_data_center</x:v>
+        <x:v>unconfirmed_candidate</x:v>
       </x:c>
       <x:c r="W7" s="91" t="n">
         <x:v>350</x:v>
@@ -9275,7 +9561,7 @@
       </x:c>
       <x:c r="Z7" s="35"/>
       <x:c r="AA7" s="17" t="str">
-        <x:v>compute_atlas | fractracker | server_country | datacenterwatch | fractracker_arcgis | servercountry.org | datacenterwatch.ai | services1.arcgis.com</x:v>
+        <x:v>compute_atlas | fractracker | server_country | datacenterwatch | fractracker_arcgis | servercountry.org | datacenterwatch.ai | services1.arcgis.com | clarksvillenow</x:v>
       </x:c>
       <x:c r="AB7" s="94" t="n">
         <x:v>8</x:v>
@@ -9287,10 +9573,10 @@
         <x:v>compute_atlas:cielo-clarksville-tn | fractracker:495</x:v>
       </x:c>
       <x:c r="AE7" s="23" t="str">
-        <x:v>https://cieloinfra.com/ | https://cleanview.co/data-centers/tennessee/2037/cielo-clarksville-data-center | https://www.arcgis.com/home/item.html?id=597555ce8e4a4892a030784a7c657fdd | https://www.datacenterdynamics.com/en/news/cielo-digital-infrastructure-plans-300mw-data-center-campus-in-south-carolina/ | https://www.servercountry.org/policy/tennessee/ | https://datacenterwatch.ai/proposals/fractracker-tn-unknown-operator-cielo-digital-infrastructure-686 | https://services1.arcgis.com/4yjifSiIG17X0gW4/arcgis/rest/services/Data_Centers/FeatureServer/0/query?where=OBJECTID%3D5239&amp;outFields=*&amp;returnGeometry=true&amp;f=json | https://registry.deploy.report/datacenters/facilities/cielo-clarksville-data-center-tn</x:v>
+        <x:v>https://cieloinfra.com/ | https://cleanview.co/data-centers/tennessee/2037/cielo-clarksville-data-center | https://www.arcgis.com/home/item.html?id=597555ce8e4a4892a030784a7c657fdd | https://www.datacenterdynamics.com/en/news/cielo-digital-infrastructure-plans-300mw-data-center-campus-in-south-carolina/ | https://www.servercountry.org/policy/tennessee/ | https://datacenterwatch.ai/proposals/fractracker-tn-unknown-operator-cielo-digital-infrastructure-686 | https://services1.arcgis.com/4yjifSiIG17X0gW4/arcgis/rest/services/Data_Centers/FeatureServer/0/query?where=OBJECTID%3D5239&amp;outFields=*&amp;returnGeometry=true&amp;f=json | https://registry.deploy.report/datacenters/facilities/cielo-clarksville-data-center-tn | https://clarksvillenow.com/local/council-discusses-data-center-concerns-but-no-proposal-is-on-the-table/</x:v>
       </x:c>
       <x:c r="AF7" s="128" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG7" s="85" t="str">
         <x:v>candidate</x:v>
@@ -9305,13 +9591,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AK7" s="96" t="n">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AL7" s="85" t="str">
-        <x:v>medium</x:v>
+        <x:v>low</x:v>
       </x:c>
       <x:c r="AM7" s="85" t="str">
-        <x:v>Current reviewed sources support Clarksville/Montgomery County but no public parcel/street address; broad coordinate is intentionally area_or_city / low.</x:v>
+        <x:v>Public market directories list a planned 350 MW Clarksville project, while June 2026 local reporting said the planning commission had no proposal under discussion. No primary local filing was identified. Retained for source traceability only as an unconfirmed candidate and excluded from confirmed-presence spatial training.</x:v>
       </x:c>
       <x:c r="AN7" s="85" t="str">
         <x:v>1.1</x:v>
@@ -9643,7 +9929,7 @@
         <x:v>https://www.prnewswire.com/news-releases/cleanspark-to-add-5-ehs-and-increase-2024-guidance-with-acquisition-of-seven-additional-bitcoin-mining-facilities-in-tennessee-302244673.html | https://www.sec.gov/Archives/edgar/data/827876/000119312525297510/clsk-20250930.htm | https://www.datacentermap.com/usa/tennessee/crossville/ | https://www.sec.gov/Archives/edgar/data/827876/000095017024105354/clsk-ex10_4.htm</x:v>
       </x:c>
       <x:c r="AF10" s="128" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG10" s="85" t="str">
         <x:v>confirmed</x:v>
@@ -9664,7 +9950,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="AM10" s="85" t="str">
-        <x:v>SEC filing identifies the West Crossville property at this address; existing approximate GPS retained.</x:v>
+        <x:v>CleanSpark SEC evidence maps West Crossville Property to 268 Sparta Hwy. The separate Campbell Junction property is 5784 Plateau Rd (TNDC-002); retain two facilities and do not merge.</x:v>
       </x:c>
       <x:c r="AN10" s="85" t="str">
         <x:v>1.1</x:v>
@@ -11273,7 +11559,7 @@
         <x:v>https://baxtel.com/news/25mw-ai-data-center-planned-for-mcminnville | https://www.wsmv.com/2026/06/01/amid-plans-new-high-density-ai-data-center-campus-middle-tennessee-city-locals-push-moratorium-such-facilities/ | https://hixsondc.com/ | https://warrencountyecd.com/site/mcminnville-warren-digital-site/ | https://www.datacenterdynamics.com/en/news/25mw-ai-data-center-to-be-built-in-mcminnville-tennessee/ | https://warrencountyway.com/hixson-data-center-development-project/</x:v>
       </x:c>
       <x:c r="AF24" s="128" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG24" s="85" t="str">
         <x:v>confirmed</x:v>
@@ -11294,7 +11580,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="AM24" s="85" t="str">
-        <x:v>Local reporting places the proposed site near 191 Industrial Dr; recorded as vicinity rather than exact parcel.</x:v>
+        <x:v>Hixson's current site confirms a planned 25 MW McMinnville/Warren County project but does not publish a parcel or street address. Local reporting supports only a vicinity near 191 Industrial Dr; retain this point solely as approximate_site, not as an exact parcel.</x:v>
       </x:c>
       <x:c r="AN24" s="85" t="str">
         <x:v>1.1</x:v>
@@ -12723,7 +13009,7 @@
         <x:v>Lumen Technologies Inc</x:v>
       </x:c>
       <x:c r="E37" s="23" t="str">
-        <x:v>2992 Sidco Drive</x:v>
+        <x:v>2990 Sidco Drive</x:v>
       </x:c>
       <x:c r="F37" s="17" t="str">
         <x:v>Nashville</x:v>
@@ -12779,7 +13065,7 @@
       <x:c r="Y37" s="91"/>
       <x:c r="Z37" s="35"/>
       <x:c r="AA37" s="17" t="str">
-        <x:v>peeringdb | wsmv</x:v>
+        <x:v>peeringdb | wsmv | lumen</x:v>
       </x:c>
       <x:c r="AB37" s="94" t="n">
         <x:v>2</x:v>
@@ -12788,13 +13074,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AD37" s="23" t="str">
-        <x:v>peeringdb:311 | wsmv:nashville-list-sidco</x:v>
+        <x:v>peeringdb:311 | wsmv:nashville-list-sidco | lumen:wavelength-site-list</x:v>
       </x:c>
       <x:c r="AE37" s="23" t="str">
-        <x:v>http://www.level3.com | https://www.wsmv.com/2026/06/04/how-many-data-centers-are-there-nashville-heres-map-where-theyre-located/</x:v>
+        <x:v>http://www.level3.com | https://www.wsmv.com/2026/06/04/how-many-data-centers-are-there-nashville-heres-map-where-theyre-located/ | https://assets.lumen.com/is/content/Lumen/waves-rapid-routes-site-list</x:v>
       </x:c>
       <x:c r="AF37" s="128" t="str">
-        <x:v>2026-09-03</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG37" s="85" t="str">
         <x:v>confirmed</x:v>
@@ -12815,7 +13101,7 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="AM37" s="85" t="str">
-        <x:v>Address discrepancy: existing record uses 2992 Sidco Drive; independent confirmed list reports 2990 Sidco Drive. Review before parcel join.</x:v>
+        <x:v>Canonical current address is 2990 Sidco Drive from Lumen's current route list. PeeringDB's 2992 Sidco Drive is retained as an adjacent legacy-directory discrepancy; the site point remains address_or_site rather than parcel-verified.</x:v>
       </x:c>
       <x:c r="AN37" s="85" t="str">
         <x:v>1.1</x:v>
@@ -12946,10 +13232,10 @@
       <x:c r="B39" s="23" t="str">
         <x:v>Quantum Leap Data Center/ Fisk University</x:v>
       </x:c>
-      <x:c r="C39" s="23" t="str">
-        <x:v>Fisk University</x:v>
-      </x:c>
-      <x:c r="D39" s="23"/>
+      <x:c r="C39" s="23" t="str"/>
+      <x:c r="D39" s="23" t="str">
+        <x:v>Fisk University (project sponsor); operating partner not publicly identified</x:v>
+      </x:c>
       <x:c r="E39" s="23" t="str">
         <x:v>1000 17th Ave N</x:v>
       </x:c>
@@ -13028,7 +13314,7 @@
         <x:v>https://www.datacenterdynamics.com/en/news/fisk-university-looks-to-build-data-center-in-nashville-tennessee/ | https://www.fisk.edu/quantumleap/ | https://www.fisk.edu/main-featured/fisk-university-unveils-1-billion-master-plan-launching-new-era-of-innovation-and-sustainability/ | https://www.datacentermap.com/usa/tennessee/nashville/quantum-leap-data-center/ | https://www.whereorg.com/fisk-university-15250808</x:v>
       </x:c>
       <x:c r="AF39" s="128" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG39" s="85" t="str">
         <x:v>confirmed</x:v>
@@ -13049,7 +13335,7 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="AM39" s="85" t="str">
-        <x:v>Address-level coordinate for 1000 17th Ave N; operator is Fisk University.</x:v>
+        <x:v>Fisk is the landowner and project sponsor. Fisk's August 2026 announcement describes the data-center corporate partner as yet to be determined, so no facility operator is attributed in this field.</x:v>
       </x:c>
       <x:c r="AN39" s="85" t="str">
         <x:v>1.1</x:v>
@@ -15354,10 +15640,10 @@
         <x:v>https://5c.ai/datacenters | https://5c.ai/ | https://5c.ai/news/5c-secures-more-than-usd-1-4-billion-to-power-north-americas-ai-infrastructure | https://www.assessormelvinburgess.com/propertyDetails?IR=true&amp;parcelid=073101++00119 | https://www.shelbytnhealth.com/DocumentCenter/View/7588 | https://www.datacenterdynamics.com/en/news/5c-plots-data-center-at-former-freds-site-in-memphis-tennessee/ | https://www.datacentermap.com/usa/tennessee/memphis/5cdc-memphis-mem01/ | https://baxtel.com/data-center/5cdc-memphis-tn | https://registry.deploy.report/datacenters/facilities/5c-memphis-getwell-road-tn</x:v>
       </x:c>
       <x:c r="AF59" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="AG59" s="85" t="str">
-        <x:v>review</x:v>
+        <x:v>confirmed</x:v>
       </x:c>
       <x:c r="AH59" s="85" t="str">
         <x:v>identified</x:v>
@@ -15375,7 +15661,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="AM59" s="85" t="str">
-        <x:v>Current DataCenterMap facility-facing address is 4280 Getwell Rd. Derived approximate-site coordinate from distances to Lumen Memphis 1 (0.38 mi), EdgeConneX Memphis (2.82 mi), and Connect Memphis (2.95 mi); residuals are effectively zero (&lt;0.001 km). Existing 4300 Getwell Rd assessor/permit evidence is preserved as related broader-site construction/property evidence, but the normalized facility address is updated to 4280 Getwell Rd.</x:v>
+        <x:v>Retain 4280 Getwell Rd as the facility-facing address supported by the current facility directory and the existing distance-derived site point. Shelby County's 4300 Getwell Rd notice is retained as related broader-site permit/property evidence, not silently substituted as the facility address.</x:v>
       </x:c>
       <x:c r="AN59" t="str">
         <x:v>1.1</x:v>
@@ -15799,7 +16085,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbad42c0300574707"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd675d4dec05a456f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36662,7 +36948,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9a37ae698d3491a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36dc408234cd43f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38704,7 +38990,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d57bebf2cb74bd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0c57e6acce4c93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38827,7 +39113,9 @@
       <x:c r="O2" s="46" t="str">
         <x:v>manual_review</x:v>
       </x:c>
-      <x:c r="P2" s="43" t="str"/>
+      <x:c r="P2" s="43" t="str">
+        <x:v>xAI confirms a South Memphis Colossus facility but the generic Compute Atlas source lacks a campus identifier. Do not merge it into Colossus 1 or Colossus 2 without source-specific evidence.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="34" hidden="0" customHeight="1">
       <x:c r="A3" s="39" t="str">
@@ -38875,12 +39163,14 @@
       <x:c r="O3" s="47" t="str">
         <x:v>manual_review</x:v>
       </x:c>
-      <x:c r="P3" s="45" t="str"/>
+      <x:c r="P3" s="45" t="str">
+        <x:v>xAI confirms a South Memphis Colossus facility but the generic Compute Atlas source lacks a campus identifier. Do not merge it into Colossus 1 or Colossus 2 without source-specific evidence.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37fb29ffda0440c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d5fb96826674ecd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39256,7 +39546,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74aa13d3b7114f44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa8b44e27e54611"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39441,7 +39731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4266988d073e438c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86bb6349a0ac436e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39753,10 +40043,10 @@
         <x:v>https://www.globenewswire.com/news-release/2024/02/06/2824158/0/en/GRIID-Infrastructure-to-Add-60-MW-with-New-Bitcoin-Mining-Facility-in-Tennessee.html | https://www.prnewswire.com/news-releases/cleanspark-announces-agreement-to-acquire-griid-infrastructure-based-on-an-enterprise-value-of-155-million-and-expansion-plans-of-over-400-mw-in-tennessee-302184116.html | https://www.sec.gov/Archives/edgar/data/1830029/000119312524223759/d888816ddefm14a.htm | https://baxtel.com/data-center/cleanspark-jackson-tn | https://tpucdockets.tn.gov/archive/filings/2003/0300438ar.pdf | https://www.sec.gov/Archives/edgar/data/1830029/000119312524000728/d941597dex211.htm</x:v>
       </x:c>
       <x:c r="P5" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q5" s="85" t="str">
-        <x:v>Jackson Energy Authority's audited filing states that Jones Creek Substation was built to serve Jackson Data, LLC located at 2342 North Parkway East and that the site would draw 60 MW of data-center load. SEC Exhibit 21.1 identifies Jackson Data LLC as a 100%-owned GRIID subsidiary; current Baxtel identifies the CleanSpark Jackson facility as operational, built 2025, on 15 acres with Jackson Energy Authority. This resolves the street address with high confidence. A defensible textual WGS84 point for 2342 North Parkway East was not found, so latitude/longitude remain blank rather than using a road-segment or nearby-business coordinate.</x:v>
+        <x:v>Public evidence supports prior GRIID/CleanSpark Jackson development and property ownership, but does not independently confirm the stated 60 MW facility is currently operating or energized. Retained as an unpromoted candidate.</x:v>
       </x:c>
       <x:c r="R5" s="85" t="str">
         <x:v>address_or_site</x:v>
@@ -39789,12 +40079,8 @@
         <x:v>TN</x:v>
       </x:c>
       <x:c r="J6"/>
-      <x:c r="K6" t="n">
-        <x:v>36.16488198</x:v>
-      </x:c>
-      <x:c r="L6" t="n">
-        <x:v>-86.78088767</x:v>
-      </x:c>
+      <x:c r="K6" t="str"/>
+      <x:c r="L6" t="str"/>
       <x:c r="M6" s="85" t="str">
         <x:v>Developer materials describe a 120 MW, 38-acre Nashville campus in development, but the exact site and county are not public.</x:v>
       </x:c>
@@ -39805,10 +40091,10 @@
         <x:v>https://atmosphere-dc.com/data-centers/nashville-tn/ | https://www.datacenterdynamics.com/en/news/atmosphere-dc-secures-investment-from-agc-equity-partners/ | https://baxtel.com/data-center/h5-data-centers-nashville-tn01 | https://baxtel.com/data-center/h5-data-centers-nashville-tn02 | https://baxtel.com/data-center/edgeconnex-nashville | https://baxtel.com/data-center/dc-blox-nashville | https://baxtel.com/data-center/lumen-nashville-2</x:v>
       </x:c>
       <x:c r="P6" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q6" s="85" t="str">
-        <x:v>Atmosphere officially discloses only Nashville, 120 MW, and a 38-acre campus. Baxtel nearest-facility distances can be multilaterated to approximately 36.16488198, -86.78088767 with sub-0.02-mile residuals, but that point lies in the downtown carrier-hotel cluster and is physically inconsistent with a 38-acre campus. It is therefore retained only as an area_or_city / low-confidence directory market pin, NOT as the development parcel. Exclude this point from parcel/site-level spatial analyses until the actual 38-acre site is disclosed.</x:v>
+        <x:v>Atmosphere publicly discloses Nashville, 120 MW, and a 38-acre campus but no street address, county, or parcel. The previous directory-derived market pin is removed because it is physically inconsistent with a 38-acre campus. Retain as a market-level candidate only.</x:v>
       </x:c>
       <x:c r="R6" s="85" t="str">
         <x:v>area_or_city</x:v>
@@ -39816,9 +40102,7 @@
       <x:c r="S6" s="85" t="str">
         <x:v>low</x:v>
       </x:c>
-      <x:c r="T6" s="85" t="str">
-        <x:v>baxtel-derived:atmosphere-market-pin</x:v>
-      </x:c>
+      <x:c r="T6" s="85" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -40129,12 +40413,14 @@
         <x:v>Scipio Technologies NREP Listing</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>unresolved_duplicate_or_new_facility</x:v>
+        <x:v>linked_master_evidence</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>low</x:v>
-      </x:c>
-      <x:c r="F12"/>
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>1661 Murfreesboro Pike</x:v>
+      </x:c>
       <x:c r="G12" t="str">
         <x:v>Nashville</x:v>
       </x:c>
@@ -40150,7 +40436,7 @@
       <x:c r="K12"/>
       <x:c r="L12"/>
       <x:c r="M12" s="85" t="str">
-        <x:v>A current market directory lists Scipio NREP in Nashville, but the public evidence does not establish whether it is distinct from TNDC-038 at 1661 Murfreesboro Pike.</x:v>
+        <x:v>Scipio's public support address is 1661 Murfreesboro Pike, matching TNDC-038. It is retained as linked supporting evidence, not a distinct spatial candidate.</x:v>
       </x:c>
       <x:c r="N12" s="85" t="str">
         <x:v>datacentermap.com | scipiotech.com</x:v>
@@ -40159,16 +40445,16 @@
         <x:v>https://www.datacentermap.com/usa/tennessee/nashville/ | https://scipiotech.com/support/ | https://www.datacentermap.com/usa/tennessee/nashville/nexus-nrep/</x:v>
       </x:c>
       <x:c r="P12" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q12" s="85" t="str">
-        <x:v>Explicit non-public exception: current DataCenterMap record states that the exact location is not public. Only Nashville/ZIP 37217 is public; coordinates intentionally remain blank.</x:v>
+        <x:v>Resolved as linked evidence for TNDC-038 by the shared 1661 Murfreesboro Pike address. Coordinates remain blank because this row is not a distinct site.</x:v>
       </x:c>
       <x:c r="R12" s="85" t="str">
-        <x:v>area_or_city</x:v>
+        <x:v>address_or_site</x:v>
       </x:c>
       <x:c r="S12" s="85" t="str">
-        <x:v>low</x:v>
+        <x:v>high</x:v>
       </x:c>
       <x:c r="T12" s="85"/>
     </x:row>
@@ -40217,10 +40503,10 @@
         <x:v>https://www.dataprise.com/get-in-touch/location/chattanooga/ | https://www.datacentermap.com/usa/tennessee/chattanooga/ | https://tnecd.com/wp-content/uploads/2018/10/business-services.pdf | https://www.whereorg.com/attorney-referral-service-15170587</x:v>
       </x:c>
       <x:c r="P13" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q13" s="85" t="str">
-        <x:v>Address-level coordinate for 801 Broad St, Chattanooga.</x:v>
+        <x:v>Current directory evidence lists the Airnet/Dataprise facility at 801 Broad Street, but no primary operator page confirms current data-center operations there. Retained as a candidate pending primary operational confirmation.</x:v>
       </x:c>
       <x:c r="R13" s="85" t="str">
         <x:v>address_or_site</x:v>
@@ -40275,10 +40561,10 @@
         <x:v>https://www.datacentermap.com/usa/tennessee/nashville/nuvox-nashville/ | https://tnecd.com/wp-content/uploads/2018/10/business-services.pdf | https://www.cityfeet.com/cont/listing/940-3rd-ave-n-nashville-tn-37201/cs39837774 | https://github.com/cmusatyalab/elijah-discovery-basic/blob/master/elijah/discovery/emulation/gps</x:v>
       </x:c>
       <x:c r="P14" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q14" s="85" t="str">
-        <x:v>DataCenterMap identifies Windstream Nashville at 940 3rd Ave North; a public geocoded GPS dataset gives 36.173667, -86.7835769 for the same address.</x:v>
+        <x:v>Current directory evidence lists the former Windstream/NuVox facility at 940 3rd Ave N. Corporate ownership naming changed after the Uniti transaction, but no primary operator page confirms current data-center operations. Retained as a candidate.</x:v>
       </x:c>
       <x:c r="R14" s="85" t="str">
         <x:v>address_or_site</x:v>
@@ -40335,10 +40621,10 @@
         <x:v>https://www.datacentermap.com/usa/tennessee/memphis/ | https://tnecd.com/wp-content/uploads/2018/10/business-services.pdf | https://www.shelbycountytn.gov/Archive/ViewFile/Item/13459 | https://promos.telarus.com/promo_docs/Q1-2011-XO-Colocation-and-DIA-Promo-Sales-Summary.pdf | https://www.whereorg.com/directv-15064353</x:v>
       </x:c>
       <x:c r="P15" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q15" s="85" t="str">
-        <x:v>Address-level coordinate for 5127 Truse Rd, Memphis.</x:v>
+        <x:v>Current directory evidence lists a Verizon facility at 5127 Truse Rd, but no primary current facility page confirms active data-center service. Retained as a candidate.</x:v>
       </x:c>
       <x:c r="R15" s="85" t="str">
         <x:v>address_or_site</x:v>
@@ -40393,10 +40679,10 @@
         <x:v>https://tnecd.com/wp-content/uploads/2018/10/business-services.pdf | https://businessinternet.com/tennessee/memphis | https://baxtel.com/data-center/memphis | https://www.whereorg.com/conference-technologies-15266003</x:v>
       </x:c>
       <x:c r="P16" s="123" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="Q16" s="85" t="str">
-        <x:v>Address-level coordinate for 5425 E Raines Rd, Memphis.</x:v>
+        <x:v>Current sources conflict: one directory labels the former tw telecom/Lumen listing inactive, while another labels it operational. Retained as a candidate with unresolved operating status.</x:v>
       </x:c>
       <x:c r="R16" s="85" t="str">
         <x:v>address_or_site</x:v>
@@ -40485,7 +40771,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11744bc9de1844c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44533988b8334e40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TN/dataset/tennessee_public_data_centers.xlsx
+++ b/TN/dataset/tennessee_public_data_centers.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0d2aded890494020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R1cc297d0f7004afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R5813bdeb2eac46ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R3b25501127854222"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="Rd134fd093d564f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R2090a52bcc934526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="Rf5dfaf003577423a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="Rbd0d0e93089f4341"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R016acd8d38e047c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R226e36a77a544718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R1acf0415faed407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rcd08d83c01af4cd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Rf58b1f9db49d44a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0512b60b15d34410"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R8b59c3c957a445fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Re6a0ad065e0e48a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R2b9315484dc44675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="R60c38f80d7ce44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="Rc7af1a06c20c4b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R1a066b5be4d04cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R6e67a17ff8784117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="Rf7cf617051f04f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="Ra5f3e93c3eb14f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R8d516726ec1f4a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="R94c7471464a44965"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Recaf2ccdc22149f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="10">
+  <x:numFmts count="12">
     <x:numFmt numFmtId="200" formatCode="#,##0.0"/>
     <x:numFmt numFmtId="201" formatCode="0.000000"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
@@ -36,8 +36,10 @@
     <x:numFmt numFmtId="207" formatCode="0.00"/>
     <x:numFmt numFmtId="208" formatCode="0"/>
     <x:numFmt numFmtId="209" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="210" formatCode="@"/>
+    <x:numFmt numFmtId="211" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -89,8 +91,24 @@
       <x:color rgb="FF7A4E00"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -182,8 +200,28 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF153B5B"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -319,11 +357,29 @@
         <x:color rgb="FFD9E1E8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="144">
+  <x:cellXfs count="230">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -716,6 +772,216 @@
     <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="9" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="9" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="9" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="9" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="208" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -741,8 +1007,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="MasterTable" displayName="MasterTable" ref="A1:AO62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="41">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="MasterTable" displayName="MasterTable" ref="A1:BQ62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="69">
     <x:tableColumn id="1" name="facility_id"/>
     <x:tableColumn id="2" name="facility_name"/>
     <x:tableColumn id="3" name="operator"/>
@@ -784,6 +1050,34 @@
     <x:tableColumn id="39" name="verification_note"/>
     <x:tableColumn id="40" name="schema_version"/>
     <x:tableColumn id="41" name="dataset_version"/>
+    <x:tableColumn id="42" name="dataset_version"/>
+    <x:tableColumn id="43" name="dataset_version"/>
+    <x:tableColumn id="44" name="dataset_version"/>
+    <x:tableColumn id="45" name="dataset_version"/>
+    <x:tableColumn id="46" name="dataset_version"/>
+    <x:tableColumn id="47" name="dataset_version"/>
+    <x:tableColumn id="48" name="dataset_version"/>
+    <x:tableColumn id="49" name="dataset_version"/>
+    <x:tableColumn id="50" name="dataset_version"/>
+    <x:tableColumn id="51" name="dataset_version"/>
+    <x:tableColumn id="52" name="dataset_version"/>
+    <x:tableColumn id="53" name="dataset_version"/>
+    <x:tableColumn id="54" name="dataset_version"/>
+    <x:tableColumn id="55" name="dataset_version"/>
+    <x:tableColumn id="56" name="dataset_version"/>
+    <x:tableColumn id="57" name="dataset_version"/>
+    <x:tableColumn id="58" name="dataset_version"/>
+    <x:tableColumn id="59" name="dataset_version"/>
+    <x:tableColumn id="60" name="dataset_version"/>
+    <x:tableColumn id="61" name="dataset_version"/>
+    <x:tableColumn id="62" name="dataset_version"/>
+    <x:tableColumn id="63" name="dataset_version"/>
+    <x:tableColumn id="64" name="dataset_version"/>
+    <x:tableColumn id="65" name="dataset_version"/>
+    <x:tableColumn id="66" name="dataset_version"/>
+    <x:tableColumn id="67" name="dataset_version"/>
+    <x:tableColumn id="68" name="dataset_version"/>
+    <x:tableColumn id="69" name="dataset_version"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -960,8 +1254,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="CandidateSitesTable" displayName="CandidateSitesTable" ref="A1:T17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="20">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CandidateSitesTable" displayName="CandidateSitesTable" ref="A1:AW17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="49">
     <x:tableColumn id="1" name="candidate_id"/>
     <x:tableColumn id="2" name="master_facility_id"/>
     <x:tableColumn id="3" name="candidate_site_name"/>
@@ -982,6 +1276,35 @@
     <x:tableColumn id="18" name="location_precision"/>
     <x:tableColumn id="19" name="location_confidence"/>
     <x:tableColumn id="20" name="coordinate_source"/>
+    <x:tableColumn id="21" name="phase1_feature_status"/>
+    <x:tableColumn id="22" name="nearest_neighbor_km"/>
+    <x:tableColumn id="23" name="cluster"/>
+    <x:tableColumn id="24" name="dist_transmission_any_km"/>
+    <x:tableColumn id="25" name="dist_transmission_100kv_km"/>
+    <x:tableColumn id="26" name="dist_transmission_230kv_km"/>
+    <x:tableColumn id="27" name="max_voltage_within_25km_kv"/>
+    <x:tableColumn id="28" name="transmission_owner_count_25km"/>
+    <x:tableColumn id="29" name="dist_major_road_km"/>
+    <x:tableColumn id="30" name="dist_interstate_km"/>
+    <x:tableColumn id="31" name="dist_surface_water_flowline_km"/>
+    <x:tableColumn id="32" name="named_flowlines_within_25km"/>
+    <x:tableColumn id="33" name="county_geoid"/>
+    <x:tableColumn id="34" name="county_name"/>
+    <x:tableColumn id="35" name="degree_institutions_50km"/>
+    <x:tableColumn id="36" name="cip11_completions_50km"/>
+    <x:tableColumn id="37" name="cip14_completions_50km"/>
+    <x:tableColumn id="38" name="degree_institutions_100km"/>
+    <x:tableColumn id="39" name="cip11_completions_100km"/>
+    <x:tableColumn id="40" name="cip14_completions_100km"/>
+    <x:tableColumn id="41" name="county_total_employment"/>
+    <x:tableColumn id="42" name="county_total_establishments"/>
+    <x:tableColumn id="43" name="county_total_employment_flag"/>
+    <x:tableColumn id="44" name="information_sector_employment"/>
+    <x:tableColumn id="45" name="information_sector_establishments"/>
+    <x:tableColumn id="46" name="information_sector_employment_flag"/>
+    <x:tableColumn id="47" name="professional_scientific_employment"/>
+    <x:tableColumn id="48" name="professional_scientific_establishments"/>
+    <x:tableColumn id="49" name="professional_scientific_employment_flag"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -8781,9 +9104,37 @@
     <x:col min="39" max="39" width="54" hidden="0" customWidth="1"/>
     <x:col min="40" max="40" width="14" hidden="0" customWidth="1"/>
     <x:col min="41" max="41" width="14" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="21" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="18" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="26" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="28" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="28" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="28" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="31" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="20" hidden="0" customWidth="1"/>
+    <x:col min="50" max="50" width="20" hidden="0" customWidth="1"/>
+    <x:col min="51" max="51" width="32" hidden="0" customWidth="1"/>
+    <x:col min="52" max="52" width="29" hidden="0" customWidth="1"/>
+    <x:col min="53" max="53" width="18" hidden="0" customWidth="1"/>
+    <x:col min="54" max="54" width="18" hidden="0" customWidth="1"/>
+    <x:col min="55" max="55" width="26" hidden="0" customWidth="1"/>
+    <x:col min="56" max="56" width="24" hidden="0" customWidth="1"/>
+    <x:col min="57" max="57" width="24" hidden="0" customWidth="1"/>
+    <x:col min="58" max="58" width="27" hidden="0" customWidth="1"/>
+    <x:col min="59" max="59" width="25" hidden="0" customWidth="1"/>
+    <x:col min="60" max="60" width="25" hidden="0" customWidth="1"/>
+    <x:col min="61" max="61" width="25" hidden="0" customWidth="1"/>
+    <x:col min="62" max="62" width="29" hidden="0" customWidth="1"/>
+    <x:col min="63" max="63" width="30" hidden="0" customWidth="1"/>
+    <x:col min="64" max="64" width="31" hidden="0" customWidth="1"/>
+    <x:col min="65" max="65" width="34" hidden="0" customWidth="1"/>
+    <x:col min="66" max="66" width="34" hidden="0" customWidth="1"/>
+    <x:col min="67" max="67" width="34" hidden="0" customWidth="1"/>
+    <x:col min="68" max="68" width="34" hidden="0" customWidth="1"/>
+    <x:col min="69" max="69" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
+    <x:row r="1" ht="58" customHeight="1">
       <x:c r="A1" s="9" t="str">
         <x:v>facility_id</x:v>
       </x:c>
@@ -8906,6 +9257,90 @@
       </x:c>
       <x:c r="AO1" s="84" t="str">
         <x:v>dataset_version</x:v>
+      </x:c>
+      <x:c r="AP1" s="211" t="str">
+        <x:v>nearest_neighbor_km</x:v>
+      </x:c>
+      <x:c r="AQ1" s="85" t="str">
+        <x:v>cluster</x:v>
+      </x:c>
+      <x:c r="AR1" s="211" t="str">
+        <x:v>dist_transmission_any_km</x:v>
+      </x:c>
+      <x:c r="AS1" s="211" t="str">
+        <x:v>dist_transmission_100kv_km</x:v>
+      </x:c>
+      <x:c r="AT1" s="211" t="str">
+        <x:v>dist_transmission_230kv_km</x:v>
+      </x:c>
+      <x:c r="AU1" s="96" t="str">
+        <x:v>max_voltage_within_25km_kv</x:v>
+      </x:c>
+      <x:c r="AV1" s="212" t="str">
+        <x:v>transmission_owner_count_25km</x:v>
+      </x:c>
+      <x:c r="AW1" s="211" t="str">
+        <x:v>dist_major_road_km</x:v>
+      </x:c>
+      <x:c r="AX1" s="211" t="str">
+        <x:v>dist_interstate_km</x:v>
+      </x:c>
+      <x:c r="AY1" s="211" t="str">
+        <x:v>dist_surface_water_flowline_km</x:v>
+      </x:c>
+      <x:c r="AZ1" s="85" t="str">
+        <x:v>named_flowlines_within_25km</x:v>
+      </x:c>
+      <x:c r="BA1" s="212" t="str">
+        <x:v>county_geoid</x:v>
+      </x:c>
+      <x:c r="BB1" s="212" t="str">
+        <x:v>county_name</x:v>
+      </x:c>
+      <x:c r="BC1" s="85" t="str">
+        <x:v>degree_institutions_50km</x:v>
+      </x:c>
+      <x:c r="BD1" s="212" t="str">
+        <x:v>cip11_completions_50km</x:v>
+      </x:c>
+      <x:c r="BE1" s="212" t="str">
+        <x:v>cip14_completions_50km</x:v>
+      </x:c>
+      <x:c r="BF1" s="85" t="str">
+        <x:v>degree_institutions_100km</x:v>
+      </x:c>
+      <x:c r="BG1" s="212" t="str">
+        <x:v>cip11_completions_100km</x:v>
+      </x:c>
+      <x:c r="BH1" s="212" t="str">
+        <x:v>cip14_completions_100km</x:v>
+      </x:c>
+      <x:c r="BI1" s="212" t="str">
+        <x:v>county_total_employment</x:v>
+      </x:c>
+      <x:c r="BJ1" s="212" t="str">
+        <x:v>county_total_establishments</x:v>
+      </x:c>
+      <x:c r="BK1" s="212" t="str">
+        <x:v>county_total_employment_flag</x:v>
+      </x:c>
+      <x:c r="BL1" s="212" t="str">
+        <x:v>information_sector_employment</x:v>
+      </x:c>
+      <x:c r="BM1" s="212" t="str">
+        <x:v>information_sector_establishments</x:v>
+      </x:c>
+      <x:c r="BN1" s="212" t="str">
+        <x:v>information_sector_employment_flag</x:v>
+      </x:c>
+      <x:c r="BO1" s="212" t="str">
+        <x:v>professional_scientific_employment</x:v>
+      </x:c>
+      <x:c r="BP1" s="212" t="str">
+        <x:v>professional_scientific_establishments</x:v>
+      </x:c>
+      <x:c r="BQ1" s="212" t="str">
+        <x:v>professional_scientific_employment_flag</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" hidden="0" customHeight="1">
@@ -9024,6 +9459,90 @@
       <x:c r="AO2" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP2" s="207" t="n">
+        <x:v>3.2412571929598153</x:v>
+      </x:c>
+      <x:c r="AQ2" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR2" s="207" t="n">
+        <x:v>0.1651959221897847</x:v>
+      </x:c>
+      <x:c r="AS2" s="207" t="n">
+        <x:v>0.1651959221897847</x:v>
+      </x:c>
+      <x:c r="AT2" s="207" t="n">
+        <x:v>0.1651959221897847</x:v>
+      </x:c>
+      <x:c r="AU2" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV2" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW2" s="207" t="n">
+        <x:v>0.2659630033542631</x:v>
+      </x:c>
+      <x:c r="AX2" s="207" t="n">
+        <x:v>0.2659630033542631</x:v>
+      </x:c>
+      <x:c r="AY2" s="207" t="n">
+        <x:v>0.6961163647055927</x:v>
+      </x:c>
+      <x:c r="AZ2" t="n">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="BA2" s="209" t="str">
+        <x:v>47187</x:v>
+      </x:c>
+      <x:c r="BB2" s="209" t="str">
+        <x:v>Williamson County</x:v>
+      </x:c>
+      <x:c r="BC2" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD2" s="209" t="n">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="BE2" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF2" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="BG2" s="209" t="n">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="BH2" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI2" s="209" t="n">
+        <x:v>149544</x:v>
+      </x:c>
+      <x:c r="BJ2" s="209" t="n">
+        <x:v>8707</x:v>
+      </x:c>
+      <x:c r="BK2" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL2" s="209" t="n">
+        <x:v>4817</x:v>
+      </x:c>
+      <x:c r="BM2" s="209" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="BN2" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO2" s="209" t="n">
+        <x:v>12710</x:v>
+      </x:c>
+      <x:c r="BP2" s="209" t="n">
+        <x:v>1322</x:v>
+      </x:c>
+      <x:c r="BQ2" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="30" hidden="0" customHeight="1">
       <x:c r="A3" s="16" t="str">
@@ -9139,6 +9658,90 @@
       <x:c r="AO3" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP3" s="207" t="n">
+        <x:v>16.5903008348662</x:v>
+      </x:c>
+      <x:c r="AQ3" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR3" s="207" t="n">
+        <x:v>2.396606264573128</x:v>
+      </x:c>
+      <x:c r="AS3" s="207" t="n">
+        <x:v>2.396606264573128</x:v>
+      </x:c>
+      <x:c r="AT3" s="207" t="n">
+        <x:v>2.396606264573128</x:v>
+      </x:c>
+      <x:c r="AU3" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV3" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW3" s="207" t="n">
+        <x:v>0.0469503578292588</x:v>
+      </x:c>
+      <x:c r="AX3" s="207" t="n">
+        <x:v>1.4075061718544764</x:v>
+      </x:c>
+      <x:c r="AY3" s="207" t="n">
+        <x:v>0.0181632993983025</x:v>
+      </x:c>
+      <x:c r="AZ3" t="n">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="BA3" s="209" t="str">
+        <x:v>47035</x:v>
+      </x:c>
+      <x:c r="BB3" s="209" t="str">
+        <x:v>Cumberland County</x:v>
+      </x:c>
+      <x:c r="BC3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BD3" s="209" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="BE3" s="209" t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="BF3" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="BG3" s="209" t="n">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="BH3" s="209" t="n">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="BI3" s="209" t="n">
+        <x:v>16494</x:v>
+      </x:c>
+      <x:c r="BJ3" s="209" t="n">
+        <x:v>1153</x:v>
+      </x:c>
+      <x:c r="BK3" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL3" s="209" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="BM3" s="209" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="BN3" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO3" s="209" t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="BP3" s="209" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="BQ3" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="30" hidden="0" customHeight="1">
       <x:c r="A4" s="16" t="str">
@@ -9256,6 +9859,90 @@
       <x:c r="AO4" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP4" s="207" t="n">
+        <x:v>0.7537456534095243</x:v>
+      </x:c>
+      <x:c r="AQ4" t="str">
+        <x:v>C3 Chattanooga area</x:v>
+      </x:c>
+      <x:c r="AR4" s="207" t="n">
+        <x:v>2.6067565059703095</x:v>
+      </x:c>
+      <x:c r="AS4" s="207" t="n">
+        <x:v>2.6067565059703095</x:v>
+      </x:c>
+      <x:c r="AT4" s="207" t="n">
+        <x:v>7.342171143213216</x:v>
+      </x:c>
+      <x:c r="AU4" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV4" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW4" s="207" t="n">
+        <x:v>0.0742319652923255</x:v>
+      </x:c>
+      <x:c r="AX4" s="207" t="n">
+        <x:v>0.8175356506839869</x:v>
+      </x:c>
+      <x:c r="AY4" s="207" t="n">
+        <x:v>1.0531543701566626</x:v>
+      </x:c>
+      <x:c r="AZ4" t="n">
+        <x:v>1150</x:v>
+      </x:c>
+      <x:c r="BA4" s="209" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="BB4" s="209" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="BC4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BD4" s="209" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="BE4" s="209" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="BF4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BG4" s="209" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="BH4" s="209" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="BI4" s="209" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="BJ4" s="209" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="BK4" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL4" s="209" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="BM4" s="209" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="BN4" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO4" s="209" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="BP4" s="209" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="BQ4" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" hidden="0" customHeight="1">
       <x:c r="A5" s="16" t="str">
@@ -9373,6 +10060,90 @@
       <x:c r="AO5" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP5" s="207" t="n">
+        <x:v>0.4108468813552908</x:v>
+      </x:c>
+      <x:c r="AQ5" t="str">
+        <x:v>C3 Chattanooga area</x:v>
+      </x:c>
+      <x:c r="AR5" s="207" t="n">
+        <x:v>2.40924676682399</x:v>
+      </x:c>
+      <x:c r="AS5" s="207" t="n">
+        <x:v>2.40924676682399</x:v>
+      </x:c>
+      <x:c r="AT5" s="207" t="n">
+        <x:v>6.044236499979038</x:v>
+      </x:c>
+      <x:c r="AU5" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV5" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW5" s="207" t="n">
+        <x:v>0.1349667724668807</x:v>
+      </x:c>
+      <x:c r="AX5" s="207" t="n">
+        <x:v>2.135441369400803</x:v>
+      </x:c>
+      <x:c r="AY5" s="207" t="n">
+        <x:v>0.95167681158497</x:v>
+      </x:c>
+      <x:c r="AZ5" t="n">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="BA5" s="209" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="BB5" s="209" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="BC5" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BD5" s="209" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="BE5" s="209" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="BF5" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BG5" s="209" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="BH5" s="209" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="BI5" s="209" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="BJ5" s="209" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="BK5" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL5" s="209" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="BM5" s="209" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="BN5" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO5" s="209" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="BP5" s="209" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="BQ5" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="30" hidden="0" customHeight="1">
       <x:c r="A6" s="16" t="str">
@@ -9488,6 +10259,90 @@
       <x:c r="AO6" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP6" s="207" t="n">
+        <x:v>0.7537456534095243</x:v>
+      </x:c>
+      <x:c r="AQ6" t="str">
+        <x:v>C3 Chattanooga area</x:v>
+      </x:c>
+      <x:c r="AR6" s="207" t="n">
+        <x:v>2.481827490296379</x:v>
+      </x:c>
+      <x:c r="AS6" s="207" t="n">
+        <x:v>2.481827490296379</x:v>
+      </x:c>
+      <x:c r="AT6" s="207" t="n">
+        <x:v>7.546223544674594</x:v>
+      </x:c>
+      <x:c r="AU6" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV6" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW6" s="207" t="n">
+        <x:v>0.2765433748031277</x:v>
+      </x:c>
+      <x:c r="AX6" s="207" t="n">
+        <x:v>1.5657424262598074</x:v>
+      </x:c>
+      <x:c r="AY6" s="207" t="n">
+        <x:v>1.7716781310704195</x:v>
+      </x:c>
+      <x:c r="AZ6" t="n">
+        <x:v>1158</x:v>
+      </x:c>
+      <x:c r="BA6" s="209" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="BB6" s="209" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="BC6" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BD6" s="209" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="BE6" s="209" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="BF6" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BG6" s="209" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="BH6" s="209" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="BI6" s="209" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="BJ6" s="209" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="BK6" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL6" s="209" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="BM6" s="209" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="BN6" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO6" s="209" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="BP6" s="209" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="BQ6" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="30" hidden="0" customHeight="1">
       <x:c r="A7" s="16" t="str">
@@ -9604,6 +10459,90 @@
       </x:c>
       <x:c r="AO7" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP7" s="207" t="n">
+        <x:v>13.34786983412424</x:v>
+      </x:c>
+      <x:c r="AQ7" t="str">
+        <x:v>Excluded / not clustered</x:v>
+      </x:c>
+      <x:c r="AR7" s="207" t="n">
+        <x:v>2.1435460189939812</x:v>
+      </x:c>
+      <x:c r="AS7" s="207" t="n">
+        <x:v>2.1435460189939812</x:v>
+      </x:c>
+      <x:c r="AT7" s="207" t="n">
+        <x:v>11.261366122590772</x:v>
+      </x:c>
+      <x:c r="AU7" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV7" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW7" s="207" t="n">
+        <x:v>0.0060403520815811</x:v>
+      </x:c>
+      <x:c r="AX7" s="207" t="n">
+        <x:v>9.953355261375314</x:v>
+      </x:c>
+      <x:c r="AY7" s="207" t="n">
+        <x:v>0.5019963529216311</x:v>
+      </x:c>
+      <x:c r="AZ7" t="n">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="BA7" s="209" t="str">
+        <x:v>47125</x:v>
+      </x:c>
+      <x:c r="BB7" s="209" t="str">
+        <x:v>Montgomery County</x:v>
+      </x:c>
+      <x:c r="BC7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BD7" s="209" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="BE7" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BF7" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BG7" s="209" t="n">
+        <x:v>1611</x:v>
+      </x:c>
+      <x:c r="BH7" s="209" t="n">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="BI7" s="209" t="n">
+        <x:v>53777</x:v>
+      </x:c>
+      <x:c r="BJ7" s="209" t="n">
+        <x:v>3428</x:v>
+      </x:c>
+      <x:c r="BK7" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL7" s="209" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="BM7" s="209" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="BN7" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO7" s="209" t="n">
+        <x:v>1647</x:v>
+      </x:c>
+      <x:c r="BP7" s="209" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="BQ7" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" hidden="0" customHeight="1">
@@ -9724,6 +10663,90 @@
       <x:c r="AO8" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP8" s="207" t="n">
+        <x:v>13.34786983412424</x:v>
+      </x:c>
+      <x:c r="AQ8" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR8" s="207" t="n">
+        <x:v>0.3528111168096206</x:v>
+      </x:c>
+      <x:c r="AS8" s="207" t="n">
+        <x:v>0.3528111168096206</x:v>
+      </x:c>
+      <x:c r="AT8" s="207" t="n">
+        <x:v>1.02987984886077</x:v>
+      </x:c>
+      <x:c r="AU8" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV8" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW8" s="207" t="n">
+        <x:v>0.8444641826026208</x:v>
+      </x:c>
+      <x:c r="AX8" s="207" t="n">
+        <x:v>2.803918570052872</x:v>
+      </x:c>
+      <x:c r="AY8" s="207" t="n">
+        <x:v>0.585738817548979</x:v>
+      </x:c>
+      <x:c r="AZ8" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="BA8" s="209" t="str">
+        <x:v>47125</x:v>
+      </x:c>
+      <x:c r="BB8" s="209" t="str">
+        <x:v>Montgomery County</x:v>
+      </x:c>
+      <x:c r="BC8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BD8" s="209" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="BE8" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BF8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BG8" s="209" t="n">
+        <x:v>1617</x:v>
+      </x:c>
+      <x:c r="BH8" s="209" t="n">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="BI8" s="209" t="n">
+        <x:v>53777</x:v>
+      </x:c>
+      <x:c r="BJ8" s="209" t="n">
+        <x:v>3428</x:v>
+      </x:c>
+      <x:c r="BK8" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL8" s="209" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="BM8" s="209" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="BN8" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO8" s="209" t="n">
+        <x:v>1647</x:v>
+      </x:c>
+      <x:c r="BP8" s="209" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="BQ8" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="30" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -9842,6 +10865,90 @@
       </x:c>
       <x:c r="AO9" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP9" s="207" t="n">
+        <x:v>11.311970674520817</x:v>
+      </x:c>
+      <x:c r="AQ9" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR9" s="207" t="n">
+        <x:v>2.0522271452302165</x:v>
+      </x:c>
+      <x:c r="AS9" s="207" t="n">
+        <x:v>2.0522271452302165</x:v>
+      </x:c>
+      <x:c r="AT9" s="207" t="n">
+        <x:v>9.978601417977911</x:v>
+      </x:c>
+      <x:c r="AU9" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV9" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW9" s="207" t="n">
+        <x:v>0.3713223977361833</x:v>
+      </x:c>
+      <x:c r="AX9" s="207" t="n">
+        <x:v>19.534397163993575</x:v>
+      </x:c>
+      <x:c r="AY9" s="207" t="n">
+        <x:v>0.6770377186021165</x:v>
+      </x:c>
+      <x:c r="AZ9" t="n">
+        <x:v>1353</x:v>
+      </x:c>
+      <x:c r="BA9" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB9" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC9" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BD9" s="209" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="BE9" s="209" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="BF9" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BG9" s="209" t="n">
+        <x:v>1218</x:v>
+      </x:c>
+      <x:c r="BH9" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI9" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ9" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK9" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL9" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM9" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN9" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO9" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP9" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ9" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" hidden="0" customHeight="1">
@@ -9958,6 +11065,90 @@
       <x:c r="AO10" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP10" s="207" t="n">
+        <x:v>16.5903008348662</x:v>
+      </x:c>
+      <x:c r="AQ10" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR10" s="207" t="n">
+        <x:v>1.991610443751144</x:v>
+      </x:c>
+      <x:c r="AS10" s="207" t="n">
+        <x:v>2.4886131922255355</x:v>
+      </x:c>
+      <x:c r="AT10" s="207" t="n">
+        <x:v>5.785272400934065</x:v>
+      </x:c>
+      <x:c r="AU10" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV10" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW10" s="207" t="n">
+        <x:v>0.0151785025615956</x:v>
+      </x:c>
+      <x:c r="AX10" s="207" t="n">
+        <x:v>3.666392601986651</x:v>
+      </x:c>
+      <x:c r="AY10" s="207" t="n">
+        <x:v>0.289985419117226</x:v>
+      </x:c>
+      <x:c r="AZ10" t="n">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="BA10" s="209" t="str">
+        <x:v>47035</x:v>
+      </x:c>
+      <x:c r="BB10" s="209" t="str">
+        <x:v>Cumberland County</x:v>
+      </x:c>
+      <x:c r="BC10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="BD10" s="209" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="BE10" s="209" t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="BF10" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="BG10" s="209" t="n">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="BH10" s="209" t="n">
+        <x:v>1330</x:v>
+      </x:c>
+      <x:c r="BI10" s="209" t="n">
+        <x:v>16494</x:v>
+      </x:c>
+      <x:c r="BJ10" s="209" t="n">
+        <x:v>1153</x:v>
+      </x:c>
+      <x:c r="BK10" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL10" s="209" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="BM10" s="209" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="BN10" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO10" s="209" t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="BP10" s="209" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="BQ10" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="30" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
@@ -10069,6 +11260,90 @@
       <x:c r="AO11" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP11" s="207" t="n">
+        <x:v>52.76647745819776</x:v>
+      </x:c>
+      <x:c r="AQ11" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR11" s="207" t="n">
+        <x:v>1.2587975694286953</x:v>
+      </x:c>
+      <x:c r="AS11" s="207" t="n">
+        <x:v>1.2587975694286953</x:v>
+      </x:c>
+      <x:c r="AT11" s="207" t="n">
+        <x:v>1.8509732506021557</x:v>
+      </x:c>
+      <x:c r="AU11" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV11" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW11" s="207" t="n">
+        <x:v>0.0045748522133634</x:v>
+      </x:c>
+      <x:c r="AX11" s="207" t="n">
+        <x:v>13.37638277901819</x:v>
+      </x:c>
+      <x:c r="AY11" s="207" t="n">
+        <x:v>0.2170490894246995</x:v>
+      </x:c>
+      <x:c r="AZ11" t="n">
+        <x:v>1180</x:v>
+      </x:c>
+      <x:c r="BA11" s="209" t="str">
+        <x:v>47121</x:v>
+      </x:c>
+      <x:c r="BB11" s="209" t="str">
+        <x:v>Meigs County</x:v>
+      </x:c>
+      <x:c r="BC11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="BD11" s="209" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="BE11" s="209" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="BF11" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="BG11" s="209" t="n">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c r="BH11" s="209" t="n">
+        <x:v>1469</x:v>
+      </x:c>
+      <x:c r="BI11" s="209" t="n">
+        <x:v>1839</x:v>
+      </x:c>
+      <x:c r="BJ11" s="209" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="BK11" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BL11" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BM11" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BN11" s="209" t="str">
+        <x:v>NO_PUBLISHED_ROW</x:v>
+      </x:c>
+      <x:c r="BO11" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BP11" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BQ11" s="209" t="str">
+        <x:v>NO_PUBLISHED_ROW</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="30" hidden="0" customHeight="1">
       <x:c r="A12" s="16" t="str">
@@ -10186,6 +11461,90 @@
       <x:c r="AO12" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP12" s="207" t="n">
+        <x:v>3.2412571929598153</x:v>
+      </x:c>
+      <x:c r="AQ12" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR12" s="207" t="n">
+        <x:v>1.1489252392323943</x:v>
+      </x:c>
+      <x:c r="AS12" s="207" t="n">
+        <x:v>1.1489252392323943</x:v>
+      </x:c>
+      <x:c r="AT12" s="207" t="n">
+        <x:v>3.211250079234238</x:v>
+      </x:c>
+      <x:c r="AU12" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV12" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW12" s="207" t="n">
+        <x:v>1.2128289754225414</x:v>
+      </x:c>
+      <x:c r="AX12" s="207" t="n">
+        <x:v>1.7489654321643044</x:v>
+      </x:c>
+      <x:c r="AY12" s="207" t="n">
+        <x:v>0.2093664616764297</x:v>
+      </x:c>
+      <x:c r="AZ12" t="n">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="BA12" s="209" t="str">
+        <x:v>47187</x:v>
+      </x:c>
+      <x:c r="BB12" s="209" t="str">
+        <x:v>Williamson County</x:v>
+      </x:c>
+      <x:c r="BC12" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD12" s="209" t="n">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="BE12" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF12" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="BG12" s="209" t="n">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="BH12" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI12" s="209" t="n">
+        <x:v>149544</x:v>
+      </x:c>
+      <x:c r="BJ12" s="209" t="n">
+        <x:v>8707</x:v>
+      </x:c>
+      <x:c r="BK12" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL12" s="209" t="n">
+        <x:v>4817</x:v>
+      </x:c>
+      <x:c r="BM12" s="209" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="BN12" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO12" s="209" t="n">
+        <x:v>12710</x:v>
+      </x:c>
+      <x:c r="BP12" s="209" t="n">
+        <x:v>1322</x:v>
+      </x:c>
+      <x:c r="BQ12" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="30" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
@@ -10303,6 +11662,90 @@
       <x:c r="AO13" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP13" s="207" t="n">
+        <x:v>3.65144110529003</x:v>
+      </x:c>
+      <x:c r="AQ13" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR13" s="207" t="n">
+        <x:v>0.1564264696118872</x:v>
+      </x:c>
+      <x:c r="AS13" s="207" t="n">
+        <x:v>0.1564264696118872</x:v>
+      </x:c>
+      <x:c r="AT13" s="207" t="n">
+        <x:v>5.722274609053078</x:v>
+      </x:c>
+      <x:c r="AU13" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV13" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW13" s="207" t="n">
+        <x:v>0.6342379741208156</x:v>
+      </x:c>
+      <x:c r="AX13" s="207" t="n">
+        <x:v>0.6342379741208156</x:v>
+      </x:c>
+      <x:c r="AY13" s="207" t="n">
+        <x:v>0.1821857162638619</x:v>
+      </x:c>
+      <x:c r="AZ13" t="n">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="BA13" s="209" t="str">
+        <x:v>47187</x:v>
+      </x:c>
+      <x:c r="BB13" s="209" t="str">
+        <x:v>Williamson County</x:v>
+      </x:c>
+      <x:c r="BC13" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BD13" s="209" t="n">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="BE13" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF13" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="BG13" s="209" t="n">
+        <x:v>1202</x:v>
+      </x:c>
+      <x:c r="BH13" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI13" s="209" t="n">
+        <x:v>149544</x:v>
+      </x:c>
+      <x:c r="BJ13" s="209" t="n">
+        <x:v>8707</x:v>
+      </x:c>
+      <x:c r="BK13" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL13" s="209" t="n">
+        <x:v>4817</x:v>
+      </x:c>
+      <x:c r="BM13" s="209" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="BN13" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO13" s="209" t="n">
+        <x:v>12710</x:v>
+      </x:c>
+      <x:c r="BP13" s="209" t="n">
+        <x:v>1322</x:v>
+      </x:c>
+      <x:c r="BQ13" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="30" hidden="0" customHeight="1">
       <x:c r="A14" s="16" t="str">
@@ -10423,6 +11866,90 @@
       </x:c>
       <x:c r="AO14" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP14" s="207" t="n">
+        <x:v>3.580764672121382</x:v>
+      </x:c>
+      <x:c r="AQ14" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR14" s="207" t="n">
+        <x:v>0.1963708261707566</x:v>
+      </x:c>
+      <x:c r="AS14" s="207" t="n">
+        <x:v>0.1963708261707566</x:v>
+      </x:c>
+      <x:c r="AT14" s="207" t="n">
+        <x:v>6.691251651484206</x:v>
+      </x:c>
+      <x:c r="AU14" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV14" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW14" s="207" t="n">
+        <x:v>0.5817709748863257</x:v>
+      </x:c>
+      <x:c r="AX14" s="207" t="n">
+        <x:v>2.973406278764428</x:v>
+      </x:c>
+      <x:c r="AY14" s="207" t="n">
+        <x:v>0.397530656515906</x:v>
+      </x:c>
+      <x:c r="AZ14" t="n">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="BA14" s="209" t="str">
+        <x:v>47187</x:v>
+      </x:c>
+      <x:c r="BB14" s="209" t="str">
+        <x:v>Williamson County</x:v>
+      </x:c>
+      <x:c r="BC14" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD14" s="209" t="n">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="BE14" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF14" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="BG14" s="209" t="n">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="BH14" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI14" s="209" t="n">
+        <x:v>149544</x:v>
+      </x:c>
+      <x:c r="BJ14" s="209" t="n">
+        <x:v>8707</x:v>
+      </x:c>
+      <x:c r="BK14" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL14" s="209" t="n">
+        <x:v>4817</x:v>
+      </x:c>
+      <x:c r="BM14" s="209" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="BN14" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO14" s="209" t="n">
+        <x:v>12710</x:v>
+      </x:c>
+      <x:c r="BP14" s="209" t="n">
+        <x:v>1322</x:v>
+      </x:c>
+      <x:c r="BQ14" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" hidden="0" customHeight="1">
@@ -10543,6 +12070,90 @@
       <x:c r="AO15" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP15" s="207" t="n">
+        <x:v>2.3980314314913542</x:v>
+      </x:c>
+      <x:c r="AQ15" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR15" s="207" t="n">
+        <x:v>1.541822644321149</x:v>
+      </x:c>
+      <x:c r="AS15" s="207" t="n">
+        <x:v>1.541822644321149</x:v>
+      </x:c>
+      <x:c r="AT15" s="207" t="n">
+        <x:v>12.415479711967578</x:v>
+      </x:c>
+      <x:c r="AU15" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV15" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW15" s="207" t="n">
+        <x:v>0.7719361137903836</x:v>
+      </x:c>
+      <x:c r="AX15" s="207" t="n">
+        <x:v>24.206824773615864</x:v>
+      </x:c>
+      <x:c r="AY15" s="207" t="n">
+        <x:v>1.2778095465339745</x:v>
+      </x:c>
+      <x:c r="AZ15" t="n">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="BA15" s="209" t="str">
+        <x:v>47165</x:v>
+      </x:c>
+      <x:c r="BB15" s="209" t="str">
+        <x:v>Sumner County</x:v>
+      </x:c>
+      <x:c r="BC15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BD15" s="209" t="n">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="BE15" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF15" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="BG15" s="209" t="n">
+        <x:v>1692</x:v>
+      </x:c>
+      <x:c r="BH15" s="209" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="BI15" s="209" t="n">
+        <x:v>56402</x:v>
+      </x:c>
+      <x:c r="BJ15" s="209" t="n">
+        <x:v>3875</x:v>
+      </x:c>
+      <x:c r="BK15" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL15" s="209" t="n">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="BM15" s="209" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="BN15" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO15" s="209" t="n">
+        <x:v>1911</x:v>
+      </x:c>
+      <x:c r="BP15" s="209" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="BQ15" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="16" t="str">
@@ -10665,6 +12276,90 @@
       </x:c>
       <x:c r="AO16" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP16" s="207" t="n">
+        <x:v>2.3980314314913542</x:v>
+      </x:c>
+      <x:c r="AQ16" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR16" s="207" t="n">
+        <x:v>3.91959956912533</x:v>
+      </x:c>
+      <x:c r="AS16" s="207" t="n">
+        <x:v>3.91959956912533</x:v>
+      </x:c>
+      <x:c r="AT16" s="207" t="n">
+        <x:v>14.790394818910544</x:v>
+      </x:c>
+      <x:c r="AU16" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV16" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW16" s="207" t="n">
+        <x:v>1.6581578932936945</x:v>
+      </x:c>
+      <x:c r="AX16" s="207" t="n">
+        <x:v>24.948091855395333</x:v>
+      </x:c>
+      <x:c r="AY16" s="207" t="n">
+        <x:v>0.4422402921235759</x:v>
+      </x:c>
+      <x:c r="AZ16" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="BA16" s="209" t="str">
+        <x:v>47165</x:v>
+      </x:c>
+      <x:c r="BB16" s="209" t="str">
+        <x:v>Sumner County</x:v>
+      </x:c>
+      <x:c r="BC16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="BD16" s="209" t="n">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="BE16" s="209" t="n">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="BF16" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="BG16" s="209" t="n">
+        <x:v>1692</x:v>
+      </x:c>
+      <x:c r="BH16" s="209" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="BI16" s="209" t="n">
+        <x:v>56402</x:v>
+      </x:c>
+      <x:c r="BJ16" s="209" t="n">
+        <x:v>3875</x:v>
+      </x:c>
+      <x:c r="BK16" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL16" s="209" t="n">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="BM16" s="209" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="BN16" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO16" s="209" t="n">
+        <x:v>1911</x:v>
+      </x:c>
+      <x:c r="BP16" s="209" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="BQ16" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" hidden="0" customHeight="1">
@@ -10783,6 +12478,90 @@
       <x:c r="AO17" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP17" s="207" t="n">
+        <x:v>28.99347267843897</x:v>
+      </x:c>
+      <x:c r="AQ17" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR17" s="207" t="n">
+        <x:v>1.1978992125192136</x:v>
+      </x:c>
+      <x:c r="AS17" s="207" t="n">
+        <x:v>1.1978992125192136</x:v>
+      </x:c>
+      <x:c r="AT17" s="207" t="n">
+        <x:v>31.896433653443474</x:v>
+      </x:c>
+      <x:c r="AU17" s="208" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AV17" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW17" s="207" t="n">
+        <x:v>0.1124495739899919</x:v>
+      </x:c>
+      <x:c r="AX17" s="207" t="n">
+        <x:v>1.4793724136890174</x:v>
+      </x:c>
+      <x:c r="AY17" s="207" t="n">
+        <x:v>0.3235840952448916</x:v>
+      </x:c>
+      <x:c r="AZ17" t="n">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="BA17" s="209" t="str">
+        <x:v>47013</x:v>
+      </x:c>
+      <x:c r="BB17" s="209" t="str">
+        <x:v>Campbell County</x:v>
+      </x:c>
+      <x:c r="BC17" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BD17" s="209" t="n">
+        <x:v>1544</x:v>
+      </x:c>
+      <x:c r="BE17" s="209" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BF17" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="BG17" s="209" t="n">
+        <x:v>2138</x:v>
+      </x:c>
+      <x:c r="BH17" s="209" t="n">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="BI17" s="209" t="n">
+        <x:v>7285</x:v>
+      </x:c>
+      <x:c r="BJ17" s="209" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="BK17" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL17" s="209" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="BM17" s="209" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="BN17" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO17" s="209" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="BP17" s="209" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="BQ17" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="16" t="str">
@@ -10899,6 +12678,90 @@
       </x:c>
       <x:c r="AO18" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP18" s="207" t="n">
+        <x:v>7.584785746838801</x:v>
+      </x:c>
+      <x:c r="AQ18" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR18" s="207" t="n">
+        <x:v>0.2313865857682145</x:v>
+      </x:c>
+      <x:c r="AS18" s="207" t="n">
+        <x:v>1.7093783161502618</x:v>
+      </x:c>
+      <x:c r="AT18" s="207" t="n">
+        <x:v>18.81818062745676</x:v>
+      </x:c>
+      <x:c r="AU18" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV18" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW18" s="207" t="n">
+        <x:v>1.048316797114264</x:v>
+      </x:c>
+      <x:c r="AX18" s="207" t="n">
+        <x:v>7.503498068760646</x:v>
+      </x:c>
+      <x:c r="AY18" s="207" t="n">
+        <x:v>0.2826796179112065</x:v>
+      </x:c>
+      <x:c r="AZ18" t="n">
+        <x:v>1210</x:v>
+      </x:c>
+      <x:c r="BA18" s="209" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BB18" s="209" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BC18" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="BD18" s="209" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="BE18" s="209" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BF18" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BG18" s="209" t="n">
+        <x:v>1989</x:v>
+      </x:c>
+      <x:c r="BH18" s="209" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="BI18" s="209" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="BJ18" s="209" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="BK18" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL18" s="209" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="BM18" s="209" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="BN18" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO18" s="209" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="BP18" s="209" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="BQ18" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" hidden="0" customHeight="1">
@@ -11015,6 +12878,90 @@
       <x:c r="AO19" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP19" s="207" t="n">
+        <x:v>0.992513351398504</x:v>
+      </x:c>
+      <x:c r="AQ19" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR19" s="207" t="n">
+        <x:v>0.4268084066683132</x:v>
+      </x:c>
+      <x:c r="AS19" s="207" t="n">
+        <x:v>2.859111353593593</x:v>
+      </x:c>
+      <x:c r="AT19" s="207" t="n">
+        <x:v>14.090986329547407</x:v>
+      </x:c>
+      <x:c r="AU19" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV19" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW19" s="207" t="n">
+        <x:v>0.2191797735874382</x:v>
+      </x:c>
+      <x:c r="AX19" s="207" t="n">
+        <x:v>0.5679865991787838</x:v>
+      </x:c>
+      <x:c r="AY19" s="207" t="n">
+        <x:v>0.355008815222425</x:v>
+      </x:c>
+      <x:c r="AZ19" t="n">
+        <x:v>1220</x:v>
+      </x:c>
+      <x:c r="BA19" s="209" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BB19" s="209" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BC19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BD19" s="209" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="BE19" s="209" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BF19" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BG19" s="209" t="n">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="BH19" s="209" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="BI19" s="209" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="BJ19" s="209" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="BK19" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL19" s="209" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="BM19" s="209" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="BN19" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO19" s="209" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="BP19" s="209" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="BQ19" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="30" hidden="0" customHeight="1">
       <x:c r="A20" s="16" t="str">
@@ -11131,6 +13078,90 @@
       </x:c>
       <x:c r="AO20" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP20" s="207" t="n">
+        <x:v>4.917109437996493</x:v>
+      </x:c>
+      <x:c r="AQ20" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR20" s="207" t="n">
+        <x:v>0.1749519251604409</x:v>
+      </x:c>
+      <x:c r="AS20" s="207" t="n">
+        <x:v>0.7331509214128205</x:v>
+      </x:c>
+      <x:c r="AT20" s="207" t="n">
+        <x:v>7.003961137321444</x:v>
+      </x:c>
+      <x:c r="AU20" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV20" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW20" s="207" t="n">
+        <x:v>0.0156475901485648</x:v>
+      </x:c>
+      <x:c r="AX20" s="207" t="n">
+        <x:v>3.9786798846338463</x:v>
+      </x:c>
+      <x:c r="AY20" s="207" t="n">
+        <x:v>0.4660022321881332</x:v>
+      </x:c>
+      <x:c r="AZ20" t="n">
+        <x:v>1210</x:v>
+      </x:c>
+      <x:c r="BA20" s="209" t="str">
+        <x:v>47105</x:v>
+      </x:c>
+      <x:c r="BB20" s="209" t="str">
+        <x:v>Loudon County</x:v>
+      </x:c>
+      <x:c r="BC20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BD20" s="209" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="BE20" s="209" t="n">
+        <x:v>969</x:v>
+      </x:c>
+      <x:c r="BF20" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BG20" s="209" t="n">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="BH20" s="209" t="n">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="BI20" s="209" t="n">
+        <x:v>14920</x:v>
+      </x:c>
+      <x:c r="BJ20" s="209" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="BK20" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL20" s="209" t="n">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="BM20" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BN20" s="209" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="BO20" s="209" t="n">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="BP20" s="209" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="BQ20" s="209" t="str">
+        <x:v>H</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" hidden="0" customHeight="1">
@@ -11243,6 +13274,90 @@
       <x:c r="AO21" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP21" s="207" t="n">
+        <x:v>57.045255277578455</x:v>
+      </x:c>
+      <x:c r="AQ21" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR21" s="207" t="n">
+        <x:v>0.190786926193177</x:v>
+      </x:c>
+      <x:c r="AS21" s="207" t="n">
+        <x:v>2.1251177094146807</x:v>
+      </x:c>
+      <x:c r="AT21" s="207" t="n">
+        <x:v>17.66443363436844</x:v>
+      </x:c>
+      <x:c r="AU21" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV21" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW21" s="207" t="n">
+        <x:v>1.474933927023007</x:v>
+      </x:c>
+      <x:c r="AX21" s="207" t="n">
+        <x:v>16.368752508779316</x:v>
+      </x:c>
+      <x:c r="AY21" s="207" t="n">
+        <x:v>0.495141034497529</x:v>
+      </x:c>
+      <x:c r="AZ21" t="n">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c r="BA21" s="209" t="str">
+        <x:v>47179</x:v>
+      </x:c>
+      <x:c r="BB21" s="209" t="str">
+        <x:v>Washington County</x:v>
+      </x:c>
+      <x:c r="BC21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BD21" s="209" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="BE21" s="209" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BF21" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="BG21" s="209" t="n">
+        <x:v>749</x:v>
+      </x:c>
+      <x:c r="BH21" s="209" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="BI21" s="209" t="n">
+        <x:v>56072</x:v>
+      </x:c>
+      <x:c r="BJ21" s="209" t="n">
+        <x:v>3076</x:v>
+      </x:c>
+      <x:c r="BK21" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL21" s="209" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="BM21" s="209" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="BN21" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO21" s="209" t="n">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="BP21" s="209" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="BQ21" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="30" hidden="0" customHeight="1">
       <x:c r="A22" s="16" t="str">
@@ -11355,6 +13470,90 @@
       </x:c>
       <x:c r="AO22" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP22" s="207" t="n">
+        <x:v>43.6773958414442</x:v>
+      </x:c>
+      <x:c r="AQ22" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR22" s="207" t="n">
+        <x:v>1.4658739374691323</x:v>
+      </x:c>
+      <x:c r="AS22" s="207" t="n">
+        <x:v>1.4658739374691323</x:v>
+      </x:c>
+      <x:c r="AT22" s="207" t="n">
+        <x:v>3.778594864329164</x:v>
+      </x:c>
+      <x:c r="AU22" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV22" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW22" s="207" t="n">
+        <x:v>5.375552404498445</x:v>
+      </x:c>
+      <x:c r="AX22" s="207" t="n">
+        <x:v>6.896218127128046</x:v>
+      </x:c>
+      <x:c r="AY22" s="207" t="n">
+        <x:v>0.1760684700295366</x:v>
+      </x:c>
+      <x:c r="AZ22" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="BA22" s="209" t="str">
+        <x:v>47031</x:v>
+      </x:c>
+      <x:c r="BB22" s="209" t="str">
+        <x:v>Coffee County</x:v>
+      </x:c>
+      <x:c r="BC22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BD22" s="209" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="BE22" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF22" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BG22" s="209" t="n">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="BH22" s="209" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="BI22" s="209" t="n">
+        <x:v>21060</x:v>
+      </x:c>
+      <x:c r="BJ22" s="209" t="n">
+        <x:v>1308</x:v>
+      </x:c>
+      <x:c r="BK22" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL22" s="209" t="n">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="BM22" s="209" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="BN22" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO22" s="209" t="n">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="BP22" s="209" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="BQ22" s="209" t="str">
+        <x:v>H</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" hidden="0" customHeight="1">
@@ -11467,6 +13666,90 @@
       <x:c r="AO23" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP23" s="207" t="n">
+        <x:v>27.74221155274318</x:v>
+      </x:c>
+      <x:c r="AQ23" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR23" s="207" t="n">
+        <x:v>0.0349440603714979</x:v>
+      </x:c>
+      <x:c r="AS23" s="207" t="n">
+        <x:v>10.264845416036176</x:v>
+      </x:c>
+      <x:c r="AT23" s="207" t="n">
+        <x:v>11.767292743393927</x:v>
+      </x:c>
+      <x:c r="AU23" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV23" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW23" s="207" t="n">
+        <x:v>0.1754402631891888</x:v>
+      </x:c>
+      <x:c r="AX23" s="207" t="n">
+        <x:v>25.255352267090117</x:v>
+      </x:c>
+      <x:c r="AY23" s="207" t="n">
+        <x:v>0.1102396338194165</x:v>
+      </x:c>
+      <x:c r="AZ23" t="n">
+        <x:v>985</x:v>
+      </x:c>
+      <x:c r="BA23" s="209" t="str">
+        <x:v>47173</x:v>
+      </x:c>
+      <x:c r="BB23" s="209" t="str">
+        <x:v>Union County</x:v>
+      </x:c>
+      <x:c r="BC23" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="BD23" s="209" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="BE23" s="209" t="n">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="BF23" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BG23" s="209" t="n">
+        <x:v>1973</x:v>
+      </x:c>
+      <x:c r="BH23" s="209" t="n">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="BI23" s="209" t="n">
+        <x:v>1971</x:v>
+      </x:c>
+      <x:c r="BJ23" s="209" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="BK23" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL23" s="209" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="BM23" s="209" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="BN23" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO23" s="209" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="BP23" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BQ23" s="209" t="str">
+        <x:v>J</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="30" hidden="0" customHeight="1">
       <x:c r="A24" s="16" t="str">
@@ -11587,6 +13870,90 @@
       </x:c>
       <x:c r="AO24" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP24" s="207" t="n">
+        <x:v>7.55864423304588</x:v>
+      </x:c>
+      <x:c r="AQ24" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR24" s="207" t="n">
+        <x:v>3.670810269189298</x:v>
+      </x:c>
+      <x:c r="AS24" s="207" t="n">
+        <x:v>3.670810269189298</x:v>
+      </x:c>
+      <x:c r="AT24" s="207" t="n">
+        <x:v>43.05319069901394</x:v>
+      </x:c>
+      <x:c r="AU24" s="208" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AV24" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW24" s="207" t="n">
+        <x:v>1.639881477326324</x:v>
+      </x:c>
+      <x:c r="AX24" s="207" t="n">
+        <x:v>32.901569856081274</x:v>
+      </x:c>
+      <x:c r="AY24" s="207" t="n">
+        <x:v>0.685404786228203</x:v>
+      </x:c>
+      <x:c r="AZ24" t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="BA24" s="209" t="str">
+        <x:v>47177</x:v>
+      </x:c>
+      <x:c r="BB24" s="209" t="str">
+        <x:v>Warren County</x:v>
+      </x:c>
+      <x:c r="BC24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BD24" s="209" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="BE24" s="209" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="BF24" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="BG24" s="209" t="n">
+        <x:v>1307</x:v>
+      </x:c>
+      <x:c r="BH24" s="209" t="n">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="BI24" s="209" t="n">
+        <x:v>9738</x:v>
+      </x:c>
+      <x:c r="BJ24" s="209" t="n">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="BK24" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BL24" s="209" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="BM24" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BN24" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO24" s="209" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="BP24" s="209" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="BQ24" s="209" t="str">
+        <x:v>H</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="30" hidden="0" customHeight="1">
@@ -11703,6 +14070,90 @@
       <x:c r="AO25" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP25" s="207" t="n">
+        <x:v>7.55864423304588</x:v>
+      </x:c>
+      <x:c r="AQ25" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR25" s="207" t="n">
+        <x:v>2.132477135416224</x:v>
+      </x:c>
+      <x:c r="AS25" s="207" t="n">
+        <x:v>2.132477135416224</x:v>
+      </x:c>
+      <x:c r="AT25" s="207" t="n">
+        <x:v>38.88347996553414</x:v>
+      </x:c>
+      <x:c r="AU25" s="208" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AV25" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW25" s="207" t="n">
+        <x:v>0.4944864850989494</x:v>
+      </x:c>
+      <x:c r="AX25" s="207" t="n">
+        <x:v>35.95161008183839</x:v>
+      </x:c>
+      <x:c r="AY25" s="207" t="n">
+        <x:v>0.7994885219051292</x:v>
+      </x:c>
+      <x:c r="AZ25" t="n">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="BA25" s="209" t="str">
+        <x:v>47177</x:v>
+      </x:c>
+      <x:c r="BB25" s="209" t="str">
+        <x:v>Warren County</x:v>
+      </x:c>
+      <x:c r="BC25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD25" s="209" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BE25" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF25" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="BG25" s="209" t="n">
+        <x:v>935</x:v>
+      </x:c>
+      <x:c r="BH25" s="209" t="n">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="BI25" s="209" t="n">
+        <x:v>9738</x:v>
+      </x:c>
+      <x:c r="BJ25" s="209" t="n">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="BK25" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BL25" s="209" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="BM25" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BN25" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO25" s="209" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="BP25" s="209" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="BQ25" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="30" hidden="0" customHeight="1">
       <x:c r="A26" s="16" t="str">
@@ -11820,6 +14271,90 @@
       <x:c r="AO26" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP26" s="207" t="n">
+        <x:v>6.5393152771957945</x:v>
+      </x:c>
+      <x:c r="AQ26" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR26" s="207" t="n">
+        <x:v>1.801478760362311</x:v>
+      </x:c>
+      <x:c r="AS26" s="207" t="n">
+        <x:v>1.801478760362311</x:v>
+      </x:c>
+      <x:c r="AT26" s="207" t="n">
+        <x:v>6.51808905597597</x:v>
+      </x:c>
+      <x:c r="AU26" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV26" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW26" s="207" t="n">
+        <x:v>0.1614199250776193</x:v>
+      </x:c>
+      <x:c r="AX26" s="207" t="n">
+        <x:v>1.4795104512074932</x:v>
+      </x:c>
+      <x:c r="AY26" s="207" t="n">
+        <x:v>0.4020932115671458</x:v>
+      </x:c>
+      <x:c r="AZ26" t="n">
+        <x:v>1606</x:v>
+      </x:c>
+      <x:c r="BA26" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB26" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC26" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BD26" s="209" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="BE26" s="209" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="BF26" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BG26" s="209" t="n">
+        <x:v>1218</x:v>
+      </x:c>
+      <x:c r="BH26" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI26" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ26" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK26" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL26" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM26" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN26" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO26" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP26" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ26" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="30" hidden="0" customHeight="1">
       <x:c r="A27" s="16" t="str">
@@ -11935,6 +14470,90 @@
       <x:c r="AO27" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP27" s="207" t="n">
+        <x:v>0.3454071544348475</x:v>
+      </x:c>
+      <x:c r="AQ27" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR27" s="207" t="n">
+        <x:v>0.4488855567176492</x:v>
+      </x:c>
+      <x:c r="AS27" s="207" t="n">
+        <x:v>3.197151023892995</x:v>
+      </x:c>
+      <x:c r="AT27" s="207" t="n">
+        <x:v>3.197151023892995</x:v>
+      </x:c>
+      <x:c r="AU27" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV27" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW27" s="207" t="n">
+        <x:v>2.045267858764466</x:v>
+      </x:c>
+      <x:c r="AX27" s="207" t="n">
+        <x:v>4.738141350151713</x:v>
+      </x:c>
+      <x:c r="AY27" s="207" t="n">
+        <x:v>0.1410492800953825</x:v>
+      </x:c>
+      <x:c r="AZ27" t="n">
+        <x:v>1240</x:v>
+      </x:c>
+      <x:c r="BA27" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB27" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC27" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="BD27" s="209" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="BE27" s="209" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="BF27" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BG27" s="209" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="BH27" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI27" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ27" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK27" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL27" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM27" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN27" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO27" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP27" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ27" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="30" hidden="0" customHeight="1">
       <x:c r="A28" s="16" t="str">
@@ -12055,6 +14674,90 @@
       </x:c>
       <x:c r="AO28" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP28" s="207" t="n">
+        <x:v>9.26082548446652</x:v>
+      </x:c>
+      <x:c r="AQ28" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR28" s="207" t="n">
+        <x:v>2.743864322292094</x:v>
+      </x:c>
+      <x:c r="AS28" s="207" t="n">
+        <x:v>2.743864322292094</x:v>
+      </x:c>
+      <x:c r="AT28" s="207" t="n">
+        <x:v>4.203553032602433</x:v>
+      </x:c>
+      <x:c r="AU28" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV28" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW28" s="207" t="n">
+        <x:v>1.7586309331365042</x:v>
+      </x:c>
+      <x:c r="AX28" s="207" t="n">
+        <x:v>8.267327931912364</x:v>
+      </x:c>
+      <x:c r="AY28" s="207" t="n">
+        <x:v>0.2850046653473752</x:v>
+      </x:c>
+      <x:c r="AZ28" t="n">
+        <x:v>1366</x:v>
+      </x:c>
+      <x:c r="BA28" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB28" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC28" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BD28" s="209" t="n">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="BE28" s="209" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="BF28" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BG28" s="209" t="n">
+        <x:v>1235</x:v>
+      </x:c>
+      <x:c r="BH28" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI28" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ28" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK28" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL28" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM28" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN28" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO28" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP28" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ28" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" hidden="0" customHeight="1">
@@ -12171,6 +14874,90 @@
       <x:c r="AO29" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP29" s="207" t="n">
+        <x:v>0.6115269873530994</x:v>
+      </x:c>
+      <x:c r="AQ29" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR29" s="207" t="n">
+        <x:v>0.3074476694115916</x:v>
+      </x:c>
+      <x:c r="AS29" s="207" t="n">
+        <x:v>3.465447418191996</x:v>
+      </x:c>
+      <x:c r="AT29" s="207" t="n">
+        <x:v>3.465447418191996</x:v>
+      </x:c>
+      <x:c r="AU29" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV29" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW29" s="207" t="n">
+        <x:v>0.5701825438554421</x:v>
+      </x:c>
+      <x:c r="AX29" s="207" t="n">
+        <x:v>5.5848875252100845</x:v>
+      </x:c>
+      <x:c r="AY29" s="207" t="n">
+        <x:v>0.4033270583573426</x:v>
+      </x:c>
+      <x:c r="AZ29" t="n">
+        <x:v>1185</x:v>
+      </x:c>
+      <x:c r="BA29" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB29" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC29" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BD29" s="209" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="BE29" s="209" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="BF29" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BG29" s="209" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="BH29" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI29" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ29" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK29" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL29" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM29" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN29" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO29" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP29" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ29" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="30" hidden="0" customHeight="1">
       <x:c r="A30" s="16" t="str">
@@ -12288,6 +15075,90 @@
       <x:c r="AO30" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP30" s="207" t="n">
+        <x:v>12.992330991063133</x:v>
+      </x:c>
+      <x:c r="AQ30" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR30" s="207" t="n">
+        <x:v>0.3825056426327811</x:v>
+      </x:c>
+      <x:c r="AS30" s="207" t="n">
+        <x:v>0.3825056426327811</x:v>
+      </x:c>
+      <x:c r="AT30" s="207" t="n">
+        <x:v>0.6164401627809571</x:v>
+      </x:c>
+      <x:c r="AU30" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV30" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW30" s="207" t="n">
+        <x:v>7.504371525109421</x:v>
+      </x:c>
+      <x:c r="AX30" s="207" t="n">
+        <x:v>7.836205367039168</x:v>
+      </x:c>
+      <x:c r="AY30" s="207" t="n">
+        <x:v>1.966385380374673</x:v>
+      </x:c>
+      <x:c r="AZ30" t="n">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="BA30" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB30" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC30" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BD30" s="209" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="BE30" s="209" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="BF30" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BG30" s="209" t="n">
+        <x:v>1231</x:v>
+      </x:c>
+      <x:c r="BH30" s="209" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="BI30" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ30" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK30" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL30" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM30" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN30" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO30" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP30" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ30" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="30" hidden="0" customHeight="1">
       <x:c r="A31" s="16" t="str">
@@ -12408,6 +15279,90 @@
       </x:c>
       <x:c r="AO31" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP31" s="207" t="n">
+        <x:v>9.853330615022765</x:v>
+      </x:c>
+      <x:c r="AQ31" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR31" s="207" t="n">
+        <x:v>0.331100853314858</x:v>
+      </x:c>
+      <x:c r="AS31" s="207" t="n">
+        <x:v>0.5450873034591647</x:v>
+      </x:c>
+      <x:c r="AT31" s="207" t="n">
+        <x:v>0.5450873034591647</x:v>
+      </x:c>
+      <x:c r="AU31" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV31" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW31" s="207" t="n">
+        <x:v>0.9131365437319892</x:v>
+      </x:c>
+      <x:c r="AX31" s="207" t="n">
+        <x:v>2.9605312398261776</x:v>
+      </x:c>
+      <x:c r="AY31" s="207" t="n">
+        <x:v>0.5167153407544153</x:v>
+      </x:c>
+      <x:c r="AZ31" t="n">
+        <x:v>1127</x:v>
+      </x:c>
+      <x:c r="BA31" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB31" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC31" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BD31" s="209" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="BE31" s="209" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="BF31" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="BG31" s="209" t="n">
+        <x:v>1174</x:v>
+      </x:c>
+      <x:c r="BH31" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI31" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ31" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK31" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL31" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM31" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN31" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO31" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP31" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ31" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="30" hidden="0" customHeight="1">
@@ -12527,6 +15482,90 @@
       </x:c>
       <x:c r="AO32" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP32" s="207" t="n">
+        <x:v>1.5634296886992427</x:v>
+      </x:c>
+      <x:c r="AQ32" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR32" s="207" t="n">
+        <x:v>0.115983122705762</x:v>
+      </x:c>
+      <x:c r="AS32" s="207" t="n">
+        <x:v>0.6606674404981177</x:v>
+      </x:c>
+      <x:c r="AT32" s="207" t="n">
+        <x:v>11.2366852000021</x:v>
+      </x:c>
+      <x:c r="AU32" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV32" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW32" s="207" t="n">
+        <x:v>1.0324548896531869</x:v>
+      </x:c>
+      <x:c r="AX32" s="207" t="n">
+        <x:v>1.3766893607197908</x:v>
+      </x:c>
+      <x:c r="AY32" s="207" t="n">
+        <x:v>0.5877614886412902</x:v>
+      </x:c>
+      <x:c r="AZ32" t="n">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="BA32" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB32" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC32" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD32" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE32" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF32" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="BG32" s="209" t="n">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="BH32" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI32" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ32" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK32" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL32" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM32" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN32" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO32" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP32" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ32" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="30" hidden="0" customHeight="1">
@@ -12643,6 +15682,90 @@
       <x:c r="AO33" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP33" s="207" t="n">
+        <x:v>1.976314023135052</x:v>
+      </x:c>
+      <x:c r="AQ33" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR33" s="207" t="n">
+        <x:v>0.121071942828338</x:v>
+      </x:c>
+      <x:c r="AS33" s="207" t="n">
+        <x:v>0.121071942828338</x:v>
+      </x:c>
+      <x:c r="AT33" s="207" t="n">
+        <x:v>13.534945397120635</x:v>
+      </x:c>
+      <x:c r="AU33" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV33" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW33" s="207" t="n">
+        <x:v>0.1172400237093578</x:v>
+      </x:c>
+      <x:c r="AX33" s="207" t="n">
+        <x:v>0.1172400237093578</x:v>
+      </x:c>
+      <x:c r="AY33" s="207" t="n">
+        <x:v>0.6475982838099955</x:v>
+      </x:c>
+      <x:c r="AZ33" t="n">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="BA33" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB33" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC33" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD33" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE33" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF33" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG33" s="209" t="n">
+        <x:v>1623</x:v>
+      </x:c>
+      <x:c r="BH33" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI33" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ33" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK33" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL33" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM33" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN33" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO33" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP33" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ33" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="30" hidden="0" customHeight="1">
       <x:c r="A34" s="16" t="str">
@@ -12761,6 +15884,90 @@
       </x:c>
       <x:c r="AO34" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP34" s="207" t="n">
+        <x:v>0.2086854803185778</x:v>
+      </x:c>
+      <x:c r="AQ34" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR34" s="207" t="n">
+        <x:v>0.3316205949751729</x:v>
+      </x:c>
+      <x:c r="AS34" s="207" t="n">
+        <x:v>1.5872554210648755</x:v>
+      </x:c>
+      <x:c r="AT34" s="207" t="n">
+        <x:v>19.647452385720698</x:v>
+      </x:c>
+      <x:c r="AU34" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV34" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW34" s="207" t="n">
+        <x:v>0.2355441969279202</x:v>
+      </x:c>
+      <x:c r="AX34" s="207" t="n">
+        <x:v>1.2137968750288166</x:v>
+      </x:c>
+      <x:c r="AY34" s="207" t="n">
+        <x:v>0.4253171342582417</x:v>
+      </x:c>
+      <x:c r="AZ34" t="n">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="BA34" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB34" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC34" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD34" s="209" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="BE34" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF34" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="BG34" s="209" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="BH34" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI34" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ34" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK34" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL34" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM34" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN34" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO34" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP34" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ34" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="30" hidden="0" customHeight="1">
@@ -12879,6 +16086,90 @@
       <x:c r="AO35" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP35" s="207" t="n">
+        <x:v>0.2086854803185778</x:v>
+      </x:c>
+      <x:c r="AQ35" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR35" s="207" t="n">
+        <x:v>0.1640777880258871</x:v>
+      </x:c>
+      <x:c r="AS35" s="207" t="n">
+        <x:v>1.4811008140686903</x:v>
+      </x:c>
+      <x:c r="AT35" s="207" t="n">
+        <x:v>19.542920530071527</x:v>
+      </x:c>
+      <x:c r="AU35" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV35" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW35" s="207" t="n">
+        <x:v>0.1203295080290079</x:v>
+      </x:c>
+      <x:c r="AX35" s="207" t="n">
+        <x:v>1.10915247143415</x:v>
+      </x:c>
+      <x:c r="AY35" s="207" t="n">
+        <x:v>0.2693965447065286</x:v>
+      </x:c>
+      <x:c r="AZ35" t="n">
+        <x:v>934</x:v>
+      </x:c>
+      <x:c r="BA35" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB35" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC35" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD35" s="209" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="BE35" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF35" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="BG35" s="209" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="BH35" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI35" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ35" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK35" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL35" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM35" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN35" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO35" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP35" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ35" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="30" hidden="0" customHeight="1">
       <x:c r="A36" s="16" t="str">
@@ -12994,6 +16285,90 @@
       <x:c r="AO36" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP36" s="207" t="n">
+        <x:v>2.3989227738591374</x:v>
+      </x:c>
+      <x:c r="AQ36" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR36" s="207" t="n">
+        <x:v>0.2273852455170062</x:v>
+      </x:c>
+      <x:c r="AS36" s="207" t="n">
+        <x:v>2.113753637504367</x:v>
+      </x:c>
+      <x:c r="AT36" s="207" t="n">
+        <x:v>19.6969167183482</x:v>
+      </x:c>
+      <x:c r="AU36" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV36" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW36" s="207" t="n">
+        <x:v>0.2266622130345049</x:v>
+      </x:c>
+      <x:c r="AX36" s="207" t="n">
+        <x:v>0.747404067564151</x:v>
+      </x:c>
+      <x:c r="AY36" s="207" t="n">
+        <x:v>1.4459045910957635</x:v>
+      </x:c>
+      <x:c r="AZ36" t="n">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="BA36" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB36" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC36" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="BD36" s="209" t="n">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="BE36" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF36" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG36" s="209" t="n">
+        <x:v>1667</x:v>
+      </x:c>
+      <x:c r="BH36" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI36" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ36" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK36" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL36" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM36" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN36" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO36" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP36" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ36" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="30" hidden="0" customHeight="1">
       <x:c r="A37" s="16" t="str">
@@ -13109,6 +16484,90 @@
       <x:c r="AO37" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP37" s="207" t="n">
+        <x:v>1.5634296886992427</x:v>
+      </x:c>
+      <x:c r="AQ37" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR37" s="207" t="n">
+        <x:v>0.0719328320559844</x:v>
+      </x:c>
+      <x:c r="AS37" s="207" t="n">
+        <x:v>0.0719328320559844</x:v>
+      </x:c>
+      <x:c r="AT37" s="207" t="n">
+        <x:v>12.79322332420262</x:v>
+      </x:c>
+      <x:c r="AU37" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV37" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW37" s="207" t="n">
+        <x:v>0.8043017565536495</x:v>
+      </x:c>
+      <x:c r="AX37" s="207" t="n">
+        <x:v>0.8043017565536495</x:v>
+      </x:c>
+      <x:c r="AY37" s="207" t="n">
+        <x:v>1.042069394443569</x:v>
+      </x:c>
+      <x:c r="AZ37" t="n">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="BA37" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB37" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC37" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD37" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE37" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF37" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BG37" s="209" t="n">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="BH37" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI37" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ37" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK37" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL37" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM37" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN37" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO37" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP37" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ37" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="30" hidden="0" customHeight="1">
       <x:c r="A38" s="16" t="str">
@@ -13224,6 +16683,90 @@
       <x:c r="AO38" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP38" s="207" t="n">
+        <x:v>5.053066150501399</x:v>
+      </x:c>
+      <x:c r="AQ38" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR38" s="207" t="n">
+        <x:v>0.0707119478126202</x:v>
+      </x:c>
+      <x:c r="AS38" s="207" t="n">
+        <x:v>1.0205936549853298</x:v>
+      </x:c>
+      <x:c r="AT38" s="207" t="n">
+        <x:v>8.266680964276182</x:v>
+      </x:c>
+      <x:c r="AU38" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV38" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW38" s="207" t="n">
+        <x:v>0.101192712090354</x:v>
+      </x:c>
+      <x:c r="AX38" s="207" t="n">
+        <x:v>3.367226120148101</x:v>
+      </x:c>
+      <x:c r="AY38" s="207" t="n">
+        <x:v>0.216468617040965</x:v>
+      </x:c>
+      <x:c r="AZ38" t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="BA38" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB38" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC38" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD38" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE38" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF38" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG38" s="209" t="n">
+        <x:v>1623</x:v>
+      </x:c>
+      <x:c r="BH38" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI38" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ38" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK38" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL38" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM38" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN38" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO38" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP38" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ38" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="30" hidden="0" customHeight="1">
       <x:c r="A39" s="16" t="str">
@@ -13342,6 +16885,90 @@
       </x:c>
       <x:c r="AO39" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP39" s="207" t="n">
+        <x:v>1.735944713176277</x:v>
+      </x:c>
+      <x:c r="AQ39" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR39" s="207" t="n">
+        <x:v>0.3583329681780802</x:v>
+      </x:c>
+      <x:c r="AS39" s="207" t="n">
+        <x:v>1.2702551176752837</x:v>
+      </x:c>
+      <x:c r="AT39" s="207" t="n">
+        <x:v>19.413290132561848</x:v>
+      </x:c>
+      <x:c r="AU39" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV39" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW39" s="207" t="n">
+        <x:v>0.3489538946991903</x:v>
+      </x:c>
+      <x:c r="AX39" s="207" t="n">
+        <x:v>0.3489538946991903</x:v>
+      </x:c>
+      <x:c r="AY39" s="207" t="n">
+        <x:v>1.3238321098183508</x:v>
+      </x:c>
+      <x:c r="AZ39" t="n">
+        <x:v>963</x:v>
+      </x:c>
+      <x:c r="BA39" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB39" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC39" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BD39" s="209" t="n">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="BE39" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF39" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG39" s="209" t="n">
+        <x:v>1588</x:v>
+      </x:c>
+      <x:c r="BH39" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI39" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ39" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK39" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL39" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM39" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN39" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO39" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP39" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ39" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="30" hidden="0" customHeight="1">
@@ -13459,6 +17086,90 @@
       </x:c>
       <x:c r="AO40" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP40" s="207" t="n">
+        <x:v>10.252603292630416</x:v>
+      </x:c>
+      <x:c r="AQ40" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR40" s="207" t="n">
+        <x:v>0.9431874961031312</x:v>
+      </x:c>
+      <x:c r="AS40" s="207" t="n">
+        <x:v>0.9431874961031312</x:v>
+      </x:c>
+      <x:c r="AT40" s="207" t="n">
+        <x:v>17.882198943230637</x:v>
+      </x:c>
+      <x:c r="AU40" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV40" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW40" s="207" t="n">
+        <x:v>0.0351958031727906</x:v>
+      </x:c>
+      <x:c r="AX40" s="207" t="n">
+        <x:v>1.3327258192916658</x:v>
+      </x:c>
+      <x:c r="AY40" s="207" t="n">
+        <x:v>0.142918790272357</x:v>
+      </x:c>
+      <x:c r="AZ40" t="n">
+        <x:v>953</x:v>
+      </x:c>
+      <x:c r="BA40" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB40" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC40" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="BD40" s="209" t="n">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="BE40" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF40" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="BG40" s="209" t="n">
+        <x:v>1667</x:v>
+      </x:c>
+      <x:c r="BH40" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI40" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ40" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK40" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL40" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM40" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN40" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO40" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP40" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ40" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="30" hidden="0" customHeight="1">
@@ -13575,6 +17286,90 @@
       <x:c r="AO41" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP41" s="207" t="n">
+        <x:v>0.5416832532175047</x:v>
+      </x:c>
+      <x:c r="AQ41" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR41" s="207" t="n">
+        <x:v>0.2114381637319143</x:v>
+      </x:c>
+      <x:c r="AS41" s="207" t="n">
+        <x:v>0.979748508254938</x:v>
+      </x:c>
+      <x:c r="AT41" s="207" t="n">
+        <x:v>19.02158182459572</x:v>
+      </x:c>
+      <x:c r="AU41" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV41" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW41" s="207" t="n">
+        <x:v>0.0221684540655779</x:v>
+      </x:c>
+      <x:c r="AX41" s="207" t="n">
+        <x:v>0.8721446837344404</x:v>
+      </x:c>
+      <x:c r="AY41" s="207" t="n">
+        <x:v>0.3177463534475093</x:v>
+      </x:c>
+      <x:c r="AZ41" t="n">
+        <x:v>922</x:v>
+      </x:c>
+      <x:c r="BA41" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB41" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC41" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD41" s="209" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="BE41" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF41" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="BG41" s="209" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="BH41" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI41" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ41" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK41" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL41" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM41" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN41" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO41" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP41" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ41" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="30" hidden="0" customHeight="1">
       <x:c r="A42" s="16" t="str">
@@ -13690,6 +17485,90 @@
       <x:c r="AO42" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP42" s="207" t="n">
+        <x:v>0.919336050690768</x:v>
+      </x:c>
+      <x:c r="AQ42" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR42" s="207" t="n">
+        <x:v>0.7363645579344529</x:v>
+      </x:c>
+      <x:c r="AS42" s="207" t="n">
+        <x:v>1.238191763901084</x:v>
+      </x:c>
+      <x:c r="AT42" s="207" t="n">
+        <x:v>19.042220946222173</x:v>
+      </x:c>
+      <x:c r="AU42" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV42" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW42" s="207" t="n">
+        <x:v>0.2262446919391716</x:v>
+      </x:c>
+      <x:c r="AX42" s="207" t="n">
+        <x:v>0.4932669783149543</x:v>
+      </x:c>
+      <x:c r="AY42" s="207" t="n">
+        <x:v>1.21434260846641</x:v>
+      </x:c>
+      <x:c r="AZ42" t="n">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="BA42" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB42" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC42" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BD42" s="209" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="BE42" s="209" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="BF42" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="BG42" s="209" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="BH42" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI42" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ42" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK42" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL42" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM42" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN42" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO42" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP42" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ42" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="30" hidden="0" customHeight="1">
       <x:c r="A43" s="16" t="str">
@@ -13806,6 +17685,90 @@
       </x:c>
       <x:c r="AO43" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP43" s="207" t="n">
+        <x:v>27.74221155274318</x:v>
+      </x:c>
+      <x:c r="AQ43" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR43" s="207" t="n">
+        <x:v>2.0152424357641316</x:v>
+      </x:c>
+      <x:c r="AS43" s="207" t="n">
+        <x:v>2.0152424357641316</x:v>
+      </x:c>
+      <x:c r="AT43" s="207" t="n">
+        <x:v>25.06971285347489</x:v>
+      </x:c>
+      <x:c r="AU43" s="208" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AV43" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW43" s="207" t="n">
+        <x:v>0.5694106398496785</x:v>
+      </x:c>
+      <x:c r="AX43" s="207" t="n">
+        <x:v>43.67052319965182</x:v>
+      </x:c>
+      <x:c r="AY43" s="207" t="n">
+        <x:v>1.849218320891234</x:v>
+      </x:c>
+      <x:c r="AZ43" t="n">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="BA43" s="209" t="str">
+        <x:v>47025</x:v>
+      </x:c>
+      <x:c r="BB43" s="209" t="str">
+        <x:v>Claiborne County</x:v>
+      </x:c>
+      <x:c r="BC43" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BD43" s="209" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="BE43" s="209" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BF43" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BG43" s="209" t="n">
+        <x:v>2241</x:v>
+      </x:c>
+      <x:c r="BH43" s="209" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="BI43" s="209" t="n">
+        <x:v>7084</x:v>
+      </x:c>
+      <x:c r="BJ43" s="209" t="n">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="BK43" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL43" s="209" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BM43" s="209" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BN43" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO43" s="209" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="BP43" s="209" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="BQ43" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="30" hidden="0" customHeight="1">
@@ -13918,6 +17881,90 @@
       <x:c r="AO44" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP44" s="207" t="n">
+        <x:v>7.65235803152038</x:v>
+      </x:c>
+      <x:c r="AQ44" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR44" s="207" t="n">
+        <x:v>1.7243463363400615</x:v>
+      </x:c>
+      <x:c r="AS44" s="207" t="n">
+        <x:v>1.7243463363400615</x:v>
+      </x:c>
+      <x:c r="AT44" s="207" t="n">
+        <x:v>51.34799871300031</x:v>
+      </x:c>
+      <x:c r="AU44" s="208" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AV44" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW44" s="207" t="n">
+        <x:v>0.2027920201141038</x:v>
+      </x:c>
+      <x:c r="AX44" s="207" t="n">
+        <x:v>20.897119695906408</x:v>
+      </x:c>
+      <x:c r="AY44" s="207" t="n">
+        <x:v>0.2302877542446328</x:v>
+      </x:c>
+      <x:c r="AZ44" t="n">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="BA44" s="209" t="str">
+        <x:v>47151</x:v>
+      </x:c>
+      <x:c r="BB44" s="209" t="str">
+        <x:v>Scott County</x:v>
+      </x:c>
+      <x:c r="BC44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BD44" s="209" t="n">
+        <x:v>1484</x:v>
+      </x:c>
+      <x:c r="BE44" s="209" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BF44" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="BG44" s="209" t="n">
+        <x:v>2869</x:v>
+      </x:c>
+      <x:c r="BH44" s="209" t="n">
+        <x:v>1335</x:v>
+      </x:c>
+      <x:c r="BI44" s="209" t="n">
+        <x:v>4173</x:v>
+      </x:c>
+      <x:c r="BJ44" s="209" t="n">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="BK44" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL44" s="209" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BM44" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BN44" s="209" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="BO44" s="209" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BP44" s="209" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BQ44" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="30" hidden="0" customHeight="1">
       <x:c r="A45" s="16" t="str">
@@ -14033,6 +18080,90 @@
       <x:c r="AO45" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP45" s="207" t="n">
+        <x:v>7.65235803152038</x:v>
+      </x:c>
+      <x:c r="AQ45" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR45" s="207" t="n">
+        <x:v>0.1251214503645664</x:v>
+      </x:c>
+      <x:c r="AS45" s="207" t="n">
+        <x:v>0.1251214503645664</x:v>
+      </x:c>
+      <x:c r="AT45" s="207" t="n">
+        <x:v>43.99028734704144</x:v>
+      </x:c>
+      <x:c r="AU45" s="208" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AV45" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW45" s="207" t="n">
+        <x:v>0.744571894380068</x:v>
+      </x:c>
+      <x:c r="AX45" s="207" t="n">
+        <x:v>18.88814560524287</x:v>
+      </x:c>
+      <x:c r="AY45" s="207" t="n">
+        <x:v>0.1155601680918731</x:v>
+      </x:c>
+      <x:c r="AZ45" t="n">
+        <x:v>967</x:v>
+      </x:c>
+      <x:c r="BA45" s="209" t="str">
+        <x:v>47151</x:v>
+      </x:c>
+      <x:c r="BB45" s="209" t="str">
+        <x:v>Scott County</x:v>
+      </x:c>
+      <x:c r="BC45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BD45" s="209" t="n">
+        <x:v>1484</x:v>
+      </x:c>
+      <x:c r="BE45" s="209" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BF45" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BG45" s="209" t="n">
+        <x:v>2746</x:v>
+      </x:c>
+      <x:c r="BH45" s="209" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="BI45" s="209" t="n">
+        <x:v>4173</x:v>
+      </x:c>
+      <x:c r="BJ45" s="209" t="n">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="BK45" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL45" s="209" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="BM45" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BN45" s="209" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="BO45" s="209" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BP45" s="209" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BQ45" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="30" hidden="0" customHeight="1">
       <x:c r="A46" s="19" t="str">
@@ -14148,6 +18279,90 @@
       <x:c r="AO46" s="85" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP46" s="207" t="n">
+        <x:v>4.917109437996493</x:v>
+      </x:c>
+      <x:c r="AQ46" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR46" s="207" t="n">
+        <x:v>0.3175809708941679</x:v>
+      </x:c>
+      <x:c r="AS46" s="207" t="n">
+        <x:v>0.3175809708941679</x:v>
+      </x:c>
+      <x:c r="AT46" s="207" t="n">
+        <x:v>11.011105990163353</x:v>
+      </x:c>
+      <x:c r="AU46" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV46" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW46" s="207" t="n">
+        <x:v>0.4505027023461488</x:v>
+      </x:c>
+      <x:c r="AX46" s="207" t="n">
+        <x:v>0.5301486747649652</x:v>
+      </x:c>
+      <x:c r="AY46" s="207" t="n">
+        <x:v>0.2583308641238066</x:v>
+      </x:c>
+      <x:c r="AZ46" t="n">
+        <x:v>1234</x:v>
+      </x:c>
+      <x:c r="BA46" s="209" t="str">
+        <x:v>47105</x:v>
+      </x:c>
+      <x:c r="BB46" s="209" t="str">
+        <x:v>Loudon County</x:v>
+      </x:c>
+      <x:c r="BC46" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="BD46" s="209" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="BE46" s="209" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BF46" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BG46" s="209" t="n">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="BH46" s="209" t="n">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="BI46" s="209" t="n">
+        <x:v>14920</x:v>
+      </x:c>
+      <x:c r="BJ46" s="209" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="BK46" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL46" s="209" t="n">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="BM46" s="209" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BN46" s="209" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="BO46" s="209" t="n">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="BP46" s="209" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="BQ46" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
@@ -14264,6 +18479,90 @@
       </x:c>
       <x:c r="AO47" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP47" s="207" t="n">
+        <x:v>0.992513351398504</x:v>
+      </x:c>
+      <x:c r="AQ47" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR47" s="207" t="n">
+        <x:v>0.0486728763684856</x:v>
+      </x:c>
+      <x:c r="AS47" s="207" t="n">
+        <x:v>3.7947914042191337</x:v>
+      </x:c>
+      <x:c r="AT47" s="207" t="n">
+        <x:v>14.190962703158428</x:v>
+      </x:c>
+      <x:c r="AU47" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV47" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW47" s="207" t="n">
+        <x:v>0.3630747475924</x:v>
+      </x:c>
+      <x:c r="AX47" s="207" t="n">
+        <x:v>0.7699289531659047</x:v>
+      </x:c>
+      <x:c r="AY47" s="207" t="n">
+        <x:v>0.112354637998837</x:v>
+      </x:c>
+      <x:c r="AZ47" t="n">
+        <x:v>1231</x:v>
+      </x:c>
+      <x:c r="BA47" s="209" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BB47" s="209" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BC47" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BD47" s="209" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="BE47" s="209" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BF47" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="BG47" s="209" t="n">
+        <x:v>1967</x:v>
+      </x:c>
+      <x:c r="BH47" s="209" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="BI47" s="209" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="BJ47" s="209" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="BK47" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL47" s="209" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="BM47" s="209" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="BN47" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO47" s="209" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="BP47" s="209" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="BQ47" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -14380,6 +18679,90 @@
       <x:c r="AO48" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP48" s="207" t="n">
+        <x:v>1.4454623860169304</x:v>
+      </x:c>
+      <x:c r="AQ48" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR48" s="207" t="n">
+        <x:v>1.3598517309135123</x:v>
+      </x:c>
+      <x:c r="AS48" s="207" t="n">
+        <x:v>1.378281471825916</x:v>
+      </x:c>
+      <x:c r="AT48" s="207" t="n">
+        <x:v>1.6120211739270764</x:v>
+      </x:c>
+      <x:c r="AU48" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV48" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW48" s="207" t="n">
+        <x:v>1.169009252566629</x:v>
+      </x:c>
+      <x:c r="AX48" s="207" t="n">
+        <x:v>5.338593636801503</x:v>
+      </x:c>
+      <x:c r="AY48" s="207" t="n">
+        <x:v>0.0259528255880626</x:v>
+      </x:c>
+      <x:c r="AZ48" t="n">
+        <x:v>1177</x:v>
+      </x:c>
+      <x:c r="BA48" s="209" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BB48" s="209" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BC48" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BD48" s="209" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="BE48" s="209" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BF48" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BG48" s="209" t="n">
+        <x:v>1928</x:v>
+      </x:c>
+      <x:c r="BH48" s="209" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="BI48" s="209" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="BJ48" s="209" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="BK48" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL48" s="209" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="BM48" s="209" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="BN48" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO48" s="209" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="BP48" s="209" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="BQ48" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
@@ -14495,6 +18878,90 @@
       <x:c r="AO49" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP49" s="207" t="n">
+        <x:v>1.4454623860169304</x:v>
+      </x:c>
+      <x:c r="AQ49" t="str">
+        <x:v>C4 Knoxville area</x:v>
+      </x:c>
+      <x:c r="AR49" s="207" t="n">
+        <x:v>1.403542243702083</x:v>
+      </x:c>
+      <x:c r="AS49" s="207" t="n">
+        <x:v>1.403542243702083</x:v>
+      </x:c>
+      <x:c r="AT49" s="207" t="n">
+        <x:v>1.403542243702083</x:v>
+      </x:c>
+      <x:c r="AU49" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV49" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW49" s="207" t="n">
+        <x:v>0.1525331462117285</x:v>
+      </x:c>
+      <x:c r="AX49" s="207" t="n">
+        <x:v>4.421398391309641</x:v>
+      </x:c>
+      <x:c r="AY49" s="207" t="n">
+        <x:v>0.1244458600637066</x:v>
+      </x:c>
+      <x:c r="AZ49" t="n">
+        <x:v>1194</x:v>
+      </x:c>
+      <x:c r="BA49" s="209" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BB49" s="209" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BC49" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BD49" s="209" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="BE49" s="209" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BF49" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BG49" s="209" t="n">
+        <x:v>1936</x:v>
+      </x:c>
+      <x:c r="BH49" s="209" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="BI49" s="209" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="BJ49" s="209" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="BK49" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL49" s="209" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="BM49" s="209" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="BN49" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO49" s="209" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="BP49" s="209" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="BQ49" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -14610,6 +19077,90 @@
       <x:c r="AO50" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP50" s="207" t="n">
+        <x:v>4.365935265331043</x:v>
+      </x:c>
+      <x:c r="AQ50" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR50" s="207" t="n">
+        <x:v>2.8590383758194164</x:v>
+      </x:c>
+      <x:c r="AS50" s="207" t="n">
+        <x:v>2.8590383758194164</x:v>
+      </x:c>
+      <x:c r="AT50" s="207" t="n">
+        <x:v>9.40933125627591</x:v>
+      </x:c>
+      <x:c r="AU50" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV50" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW50" s="207" t="n">
+        <x:v>0.3051082522058725</x:v>
+      </x:c>
+      <x:c r="AX50" s="207" t="n">
+        <x:v>6.10578479026357</x:v>
+      </x:c>
+      <x:c r="AY50" s="207" t="n">
+        <x:v>1.1704272775317783</x:v>
+      </x:c>
+      <x:c r="AZ50" t="n">
+        <x:v>1376</x:v>
+      </x:c>
+      <x:c r="BA50" s="209" t="str">
+        <x:v>47113</x:v>
+      </x:c>
+      <x:c r="BB50" s="209" t="str">
+        <x:v>Madison County</x:v>
+      </x:c>
+      <x:c r="BC50" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="BD50" s="209" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="BE50" s="209" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BF50" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="BG50" s="209" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="BH50" s="209" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BI50" s="209" t="n">
+        <x:v>55344</x:v>
+      </x:c>
+      <x:c r="BJ50" s="209" t="n">
+        <x:v>2598</x:v>
+      </x:c>
+      <x:c r="BK50" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL50" s="209" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="BM50" s="209" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="BN50" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO50" s="209" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="BP50" s="209" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="BQ50" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -14729,6 +19280,90 @@
       <x:c r="AO51" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP51" s="207" t="n">
+        <x:v>10.771741932562746</x:v>
+      </x:c>
+      <x:c r="AQ51" t="str">
+        <x:v>C3 Chattanooga area</x:v>
+      </x:c>
+      <x:c r="AR51" s="207" t="n">
+        <x:v>0.3477659403392347</x:v>
+      </x:c>
+      <x:c r="AS51" s="207" t="n">
+        <x:v>0.3477659403392347</x:v>
+      </x:c>
+      <x:c r="AT51" s="207" t="n">
+        <x:v>9.002526174550091</x:v>
+      </x:c>
+      <x:c r="AU51" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV51" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW51" s="207" t="n">
+        <x:v>0.2179821528089125</x:v>
+      </x:c>
+      <x:c r="AX51" s="207" t="n">
+        <x:v>4.440412587403477</x:v>
+      </x:c>
+      <x:c r="AY51" s="207" t="n">
+        <x:v>0.220688502890341</x:v>
+      </x:c>
+      <x:c r="AZ51" t="n">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="BA51" s="209" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="BB51" s="209" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="BC51" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BD51" s="209" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="BE51" s="209" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="BF51" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BG51" s="209" t="n">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="BH51" s="209" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="BI51" s="209" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="BJ51" s="209" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="BK51" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL51" s="209" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="BM51" s="209" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="BN51" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO51" s="209" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="BP51" s="209" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="BQ51" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
@@ -14848,6 +19483,90 @@
       <x:c r="AO52" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP52" s="207" t="n">
+        <x:v>17.477420413451394</x:v>
+      </x:c>
+      <x:c r="AQ52" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR52" s="207" t="n">
+        <x:v>1.7083487826864354</x:v>
+      </x:c>
+      <x:c r="AS52" s="207" t="n">
+        <x:v>1.7083487826864354</x:v>
+      </x:c>
+      <x:c r="AT52" s="207" t="n">
+        <x:v>17.320638167725356</x:v>
+      </x:c>
+      <x:c r="AU52" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV52" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW52" s="207" t="n">
+        <x:v>0.1272572601694827</x:v>
+      </x:c>
+      <x:c r="AX52" s="207" t="n">
+        <x:v>2.646802318868086</x:v>
+      </x:c>
+      <x:c r="AY52" s="207" t="n">
+        <x:v>0.4438700880493592</x:v>
+      </x:c>
+      <x:c r="AZ52" t="n">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="BA52" s="209" t="str">
+        <x:v>47149</x:v>
+      </x:c>
+      <x:c r="BB52" s="209" t="str">
+        <x:v>Rutherford County</x:v>
+      </x:c>
+      <x:c r="BC52" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BD52" s="209" t="n">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="BE52" s="209" t="n">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="BF52" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="BG52" s="209" t="n">
+        <x:v>1215</x:v>
+      </x:c>
+      <x:c r="BH52" s="209" t="n">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="BI52" s="209" t="n">
+        <x:v>128935</x:v>
+      </x:c>
+      <x:c r="BJ52" s="209" t="n">
+        <x:v>6285</x:v>
+      </x:c>
+      <x:c r="BK52" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL52" s="209" t="n">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="BM52" s="209" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="BN52" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO52" s="209" t="n">
+        <x:v>5057</x:v>
+      </x:c>
+      <x:c r="BP52" s="209" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="BQ52" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
@@ -14965,6 +19684,90 @@
       <x:c r="AO53" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP53" s="207" t="n">
+        <x:v>7.201622189296421</x:v>
+      </x:c>
+      <x:c r="AQ53" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR53" s="207" t="n">
+        <x:v>1.8279218635089325</x:v>
+      </x:c>
+      <x:c r="AS53" s="207" t="n">
+        <x:v>1.8279218635089325</x:v>
+      </x:c>
+      <x:c r="AT53" s="207" t="n">
+        <x:v>6.530205327468523</x:v>
+      </x:c>
+      <x:c r="AU53" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV53" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW53" s="207" t="n">
+        <x:v>0.169894974354871</x:v>
+      </x:c>
+      <x:c r="AX53" s="207" t="n">
+        <x:v>2.076589381175805</x:v>
+      </x:c>
+      <x:c r="AY53" s="207" t="n">
+        <x:v>0.0755279788635552</x:v>
+      </x:c>
+      <x:c r="AZ53" t="n">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="BA53" s="209" t="str">
+        <x:v>47187</x:v>
+      </x:c>
+      <x:c r="BB53" s="209" t="str">
+        <x:v>Williamson County</x:v>
+      </x:c>
+      <x:c r="BC53" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD53" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE53" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF53" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="BG53" s="209" t="n">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="BH53" s="209" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="BI53" s="209" t="n">
+        <x:v>149544</x:v>
+      </x:c>
+      <x:c r="BJ53" s="209" t="n">
+        <x:v>8707</x:v>
+      </x:c>
+      <x:c r="BK53" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL53" s="209" t="n">
+        <x:v>4817</x:v>
+      </x:c>
+      <x:c r="BM53" s="209" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="BN53" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="BO53" s="209" t="n">
+        <x:v>12710</x:v>
+      </x:c>
+      <x:c r="BP53" s="209" t="n">
+        <x:v>1322</x:v>
+      </x:c>
+      <x:c r="BQ53" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
@@ -15082,6 +19885,90 @@
       <x:c r="AO54" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP54" s="207" t="n">
+        <x:v>1.976314023135052</x:v>
+      </x:c>
+      <x:c r="AQ54" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR54" s="207" t="n">
+        <x:v>0.5359714148150394</x:v>
+      </x:c>
+      <x:c r="AS54" s="207" t="n">
+        <x:v>0.5359714148150394</x:v>
+      </x:c>
+      <x:c r="AT54" s="207" t="n">
+        <x:v>12.30715632663763</x:v>
+      </x:c>
+      <x:c r="AU54" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV54" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW54" s="207" t="n">
+        <x:v>0.5647373518848544</x:v>
+      </x:c>
+      <x:c r="AX54" s="207" t="n">
+        <x:v>0.5647373518848544</x:v>
+      </x:c>
+      <x:c r="AY54" s="207" t="n">
+        <x:v>0.1422154514615573</x:v>
+      </x:c>
+      <x:c r="AZ54" t="n">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="BA54" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB54" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC54" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD54" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE54" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF54" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG54" s="209" t="n">
+        <x:v>1623</x:v>
+      </x:c>
+      <x:c r="BH54" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI54" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ54" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK54" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL54" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM54" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN54" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO54" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP54" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ54" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
@@ -15199,6 +20086,90 @@
       <x:c r="AO55" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP55" s="207" t="n">
+        <x:v>1.510841476707156</x:v>
+      </x:c>
+      <x:c r="AQ55" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR55" s="207" t="n">
+        <x:v>0.6092041304101868</x:v>
+      </x:c>
+      <x:c r="AS55" s="207" t="n">
+        <x:v>0.6092041304101868</x:v>
+      </x:c>
+      <x:c r="AT55" s="207" t="n">
+        <x:v>14.781532831661425</x:v>
+      </x:c>
+      <x:c r="AU55" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV55" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW55" s="207" t="n">
+        <x:v>0.0294158088330879</x:v>
+      </x:c>
+      <x:c r="AX55" s="207" t="n">
+        <x:v>0.0294158088330879</x:v>
+      </x:c>
+      <x:c r="AY55" s="207" t="n">
+        <x:v>0.8057133630999617</x:v>
+      </x:c>
+      <x:c r="AZ55" t="n">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="BA55" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB55" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC55" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD55" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE55" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF55" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG55" s="209" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="BH55" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI55" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ55" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK55" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL55" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM55" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN55" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO55" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP55" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ55" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
@@ -15317,6 +20288,90 @@
       </x:c>
       <x:c r="AO56" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP56" s="207" t="n">
+        <x:v>1.510841476707156</x:v>
+      </x:c>
+      <x:c r="AQ56" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="AR56" s="207" t="n">
+        <x:v>0.2987076008641238</x:v>
+      </x:c>
+      <x:c r="AS56" s="207" t="n">
+        <x:v>0.2987076008641238</x:v>
+      </x:c>
+      <x:c r="AT56" s="207" t="n">
+        <x:v>15.577122714327889</x:v>
+      </x:c>
+      <x:c r="AU56" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV56" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW56" s="207" t="n">
+        <x:v>0.224520073306856</x:v>
+      </x:c>
+      <x:c r="AX56" s="207" t="n">
+        <x:v>0.9650322224514756</x:v>
+      </x:c>
+      <x:c r="AY56" s="207" t="n">
+        <x:v>0.6129462036681714</x:v>
+      </x:c>
+      <x:c r="AZ56" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="BA56" s="209" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BB56" s="209" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BC56" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BD56" s="209" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BE56" s="209" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BF56" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="BG56" s="209" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="BH56" s="209" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="BI56" s="209" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="BJ56" s="209" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="BK56" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL56" s="209" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="BM56" s="209" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="BN56" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO56" s="209" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="BP56" s="209" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="BQ56" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -15433,6 +20488,90 @@
       <x:c r="AO57" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP57" s="207" t="n">
+        <x:v>0.536086088636087</x:v>
+      </x:c>
+      <x:c r="AQ57" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR57" s="207" t="n">
+        <x:v>0.2021176968700708</x:v>
+      </x:c>
+      <x:c r="AS57" s="207" t="n">
+        <x:v>0.2021176968700708</x:v>
+      </x:c>
+      <x:c r="AT57" s="207" t="n">
+        <x:v>5.958812171188375</x:v>
+      </x:c>
+      <x:c r="AU57" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV57" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW57" s="207" t="n">
+        <x:v>0.1674602325282303</x:v>
+      </x:c>
+      <x:c r="AX57" s="207" t="n">
+        <x:v>2.111826646225866</x:v>
+      </x:c>
+      <x:c r="AY57" s="207" t="n">
+        <x:v>0.5067458598584822</x:v>
+      </x:c>
+      <x:c r="AZ57" t="n">
+        <x:v>1359</x:v>
+      </x:c>
+      <x:c r="BA57" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB57" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC57" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BD57" s="209" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="BE57" s="209" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="BF57" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BG57" s="209" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="BH57" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI57" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ57" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK57" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL57" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM57" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN57" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO57" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP57" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ57" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
@@ -15550,6 +20689,90 @@
       <x:c r="AO58" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP58" s="207" t="n">
+        <x:v>0.3454071544348475</x:v>
+      </x:c>
+      <x:c r="AQ58" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR58" s="207" t="n">
+        <x:v>0.6310822975962274</x:v>
+      </x:c>
+      <x:c r="AS58" s="207" t="n">
+        <x:v>3.437632206786213</x:v>
+      </x:c>
+      <x:c r="AT58" s="207" t="n">
+        <x:v>3.437632206786213</x:v>
+      </x:c>
+      <x:c r="AU58" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV58" s="209" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW58" s="207" t="n">
+        <x:v>2.353354596410896</x:v>
+      </x:c>
+      <x:c r="AX58" s="207" t="n">
+        <x:v>4.514833120388392</x:v>
+      </x:c>
+      <x:c r="AY58" s="207" t="n">
+        <x:v>0.0972216616329214</x:v>
+      </x:c>
+      <x:c r="AZ58" t="n">
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="BA58" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB58" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC58" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="BD58" s="209" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="BE58" s="209" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="BF58" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BG58" s="209" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="BH58" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI58" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ58" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK58" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL58" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM58" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN58" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO58" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP58" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ58" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
@@ -15668,6 +20891,90 @@
       </x:c>
       <x:c r="AO59" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP59" s="207" t="n">
+        <x:v>0.6115269873530994</x:v>
+      </x:c>
+      <x:c r="AQ59" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR59" s="207" t="n">
+        <x:v>0.8973628978282975</x:v>
+      </x:c>
+      <x:c r="AS59" s="207" t="n">
+        <x:v>4.027798856933369</x:v>
+      </x:c>
+      <x:c r="AT59" s="207" t="n">
+        <x:v>4.027798856933369</x:v>
+      </x:c>
+      <x:c r="AU59" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV59" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW59" s="207" t="n">
+        <x:v>0.1258764639860509</x:v>
+      </x:c>
+      <x:c r="AX59" s="207" t="n">
+        <x:v>5.205206220710836</x:v>
+      </x:c>
+      <x:c r="AY59" s="207" t="n">
+        <x:v>0.2826489190682394</x:v>
+      </x:c>
+      <x:c r="AZ59" t="n">
+        <x:v>1192</x:v>
+      </x:c>
+      <x:c r="BA59" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB59" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC59" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BD59" s="209" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="BE59" s="209" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="BF59" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BG59" s="209" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="BH59" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI59" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ59" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK59" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL59" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM59" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN59" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO59" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP59" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ59" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -15788,6 +21095,90 @@
       <x:c r="AO60" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP60" s="207" t="n">
+        <x:v>6.183699762877351</x:v>
+      </x:c>
+      <x:c r="AQ60" t="str">
+        <x:v>C1 Memphis area</x:v>
+      </x:c>
+      <x:c r="AR60" s="207" t="n">
+        <x:v>1.3226434909323577</x:v>
+      </x:c>
+      <x:c r="AS60" s="207" t="n">
+        <x:v>1.3226434909323577</x:v>
+      </x:c>
+      <x:c r="AT60" s="207" t="n">
+        <x:v>7.118945210680754</x:v>
+      </x:c>
+      <x:c r="AU60" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV60" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW60" s="207" t="n">
+        <x:v>0.3797875155960548</x:v>
+      </x:c>
+      <x:c r="AX60" s="207" t="n">
+        <x:v>0.3797875155960548</x:v>
+      </x:c>
+      <x:c r="AY60" s="207" t="n">
+        <x:v>0.8328101602034235</x:v>
+      </x:c>
+      <x:c r="AZ60" t="n">
+        <x:v>1423</x:v>
+      </x:c>
+      <x:c r="BA60" s="209" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="BB60" s="209" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="BC60" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="BD60" s="209" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="BE60" s="209" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="BF60" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="BG60" s="209" t="n">
+        <x:v>1235</x:v>
+      </x:c>
+      <x:c r="BH60" s="209" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="BI60" s="209" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="BJ60" s="209" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="BK60" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL60" s="209" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="BM60" s="209" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="BN60" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO60" s="209" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="BP60" s="209" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="BQ60" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
@@ -15905,6 +21296,90 @@
       <x:c r="AO61" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
       </x:c>
+      <x:c r="AP61" s="207" t="n">
+        <x:v>23.739097663615286</x:v>
+      </x:c>
+      <x:c r="AQ61" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR61" s="207" t="n">
+        <x:v>4.485592853711683</x:v>
+      </x:c>
+      <x:c r="AS61" s="207" t="n">
+        <x:v>7.9269330290775875</x:v>
+      </x:c>
+      <x:c r="AT61" s="207" t="n">
+        <x:v>16.95648787706169</x:v>
+      </x:c>
+      <x:c r="AU61" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV61" s="209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW61" s="207" t="n">
+        <x:v>0.6314902866766976</x:v>
+      </x:c>
+      <x:c r="AX61" s="207" t="n">
+        <x:v>20.670084890856504</x:v>
+      </x:c>
+      <x:c r="AY61" s="207" t="n">
+        <x:v>0.3366153606477722</x:v>
+      </x:c>
+      <x:c r="AZ61" t="n">
+        <x:v>1459</x:v>
+      </x:c>
+      <x:c r="BA61" s="209" t="str">
+        <x:v>47053</x:v>
+      </x:c>
+      <x:c r="BB61" s="209" t="str">
+        <x:v>Gibson County</x:v>
+      </x:c>
+      <x:c r="BC61" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="BD61" s="209" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="BE61" s="209" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BF61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="BG61" s="209" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="BH61" s="209" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="BI61" s="209" t="n">
+        <x:v>12656</x:v>
+      </x:c>
+      <x:c r="BJ61" s="209" t="n">
+        <x:v>951</x:v>
+      </x:c>
+      <x:c r="BK61" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL61" s="209" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="BM61" s="209" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="BN61" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO61" s="209" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="BP61" s="209" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="BQ61" s="209" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
@@ -16025,6 +21500,90 @@
       </x:c>
       <x:c r="AO62" t="str">
         <x:v>2026-09-03-deduplicated</x:v>
+      </x:c>
+      <x:c r="AP62" s="207" t="n">
+        <x:v>37.94409711967336</x:v>
+      </x:c>
+      <x:c r="AQ62" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="AR62" s="207" t="n">
+        <x:v>0.4012387576353779</x:v>
+      </x:c>
+      <x:c r="AS62" s="207" t="n">
+        <x:v>3.116653456205808</x:v>
+      </x:c>
+      <x:c r="AT62" s="207" t="n">
+        <x:v>6.207202653955594</x:v>
+      </x:c>
+      <x:c r="AU62" s="208" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AV62" s="209" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW62" s="207" t="n">
+        <x:v>0.1535730440308025</x:v>
+      </x:c>
+      <x:c r="AX62" s="207" t="n">
+        <x:v>5.356146431785924</x:v>
+      </x:c>
+      <x:c r="AY62" s="207" t="n">
+        <x:v>0.2212782102181217</x:v>
+      </x:c>
+      <x:c r="AZ62" t="n">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c r="BA62" s="209" t="str">
+        <x:v>47163</x:v>
+      </x:c>
+      <x:c r="BB62" s="209" t="str">
+        <x:v>Sullivan County</x:v>
+      </x:c>
+      <x:c r="BC62" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="BD62" s="209" t="n">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="BE62" s="209" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BF62" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="BG62" s="209" t="n">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="BH62" s="209" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="BI62" s="209" t="n">
+        <x:v>60008</x:v>
+      </x:c>
+      <x:c r="BJ62" s="209" t="n">
+        <x:v>3382</x:v>
+      </x:c>
+      <x:c r="BK62" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BL62" s="209" t="n">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="BM62" s="209" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="BN62" s="209" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="BO62" s="209" t="n">
+        <x:v>1436</x:v>
+      </x:c>
+      <x:c r="BP62" s="209" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="BQ62" s="209" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16085,7 +21644,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd675d4dec05a456f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36774806f8c84305"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36948,7 +42507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36dc408234cd43f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa50700318684d03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38990,7 +44549,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0c57e6acce4c93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R425b4b3ecadb40c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39170,7 +44729,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d5fb96826674ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c237ebd7bfa4ad6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39546,7 +45105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaa8b44e27e54611"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd208a7c1e3cd49e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39731,7 +45290,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86bb6349a0ac436e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cea2fdd68ae42bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39760,9 +45319,38 @@
     <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="38" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="23" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="21" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="26" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="28" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="28" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="28" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="31" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="20" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="20" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="32" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="29" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="18" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="18" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="26" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="24" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="24" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="27" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="25" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="25" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="25" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="29" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="30" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="31" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="34" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="34" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="34" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="34" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="58" customHeight="1">
       <x:c r="A1" s="84" t="str">
         <x:v>candidate_id</x:v>
       </x:c>
@@ -39822,6 +45410,93 @@
       </x:c>
       <x:c r="T1" s="121" t="str">
         <x:v>coordinate_source</x:v>
+      </x:c>
+      <x:c r="U1" s="217" t="str">
+        <x:v>phase1_feature_status</x:v>
+      </x:c>
+      <x:c r="V1" s="221" t="str">
+        <x:v>nearest_neighbor_km</x:v>
+      </x:c>
+      <x:c r="W1" s="217" t="str">
+        <x:v>cluster</x:v>
+      </x:c>
+      <x:c r="X1" s="221" t="str">
+        <x:v>dist_transmission_any_km</x:v>
+      </x:c>
+      <x:c r="Y1" s="221" t="str">
+        <x:v>dist_transmission_100kv_km</x:v>
+      </x:c>
+      <x:c r="Z1" s="221" t="str">
+        <x:v>dist_transmission_230kv_km</x:v>
+      </x:c>
+      <x:c r="AA1" s="223" t="str">
+        <x:v>max_voltage_within_25km_kv</x:v>
+      </x:c>
+      <x:c r="AB1" s="225" t="str">
+        <x:v>transmission_owner_count_25km</x:v>
+      </x:c>
+      <x:c r="AC1" s="221" t="str">
+        <x:v>dist_major_road_km</x:v>
+      </x:c>
+      <x:c r="AD1" s="221" t="str">
+        <x:v>dist_interstate_km</x:v>
+      </x:c>
+      <x:c r="AE1" s="221" t="str">
+        <x:v>dist_surface_water_flowline_km</x:v>
+      </x:c>
+      <x:c r="AF1" s="217" t="str">
+        <x:v>named_flowlines_within_25km</x:v>
+      </x:c>
+      <x:c r="AG1" s="225" t="str">
+        <x:v>county_geoid</x:v>
+      </x:c>
+      <x:c r="AH1" s="225" t="str">
+        <x:v>county_name</x:v>
+      </x:c>
+      <x:c r="AI1" s="217" t="str">
+        <x:v>degree_institutions_50km</x:v>
+      </x:c>
+      <x:c r="AJ1" s="225" t="str">
+        <x:v>cip11_completions_50km</x:v>
+      </x:c>
+      <x:c r="AK1" s="225" t="str">
+        <x:v>cip14_completions_50km</x:v>
+      </x:c>
+      <x:c r="AL1" s="217" t="str">
+        <x:v>degree_institutions_100km</x:v>
+      </x:c>
+      <x:c r="AM1" s="225" t="str">
+        <x:v>cip11_completions_100km</x:v>
+      </x:c>
+      <x:c r="AN1" s="225" t="str">
+        <x:v>cip14_completions_100km</x:v>
+      </x:c>
+      <x:c r="AO1" s="225" t="str">
+        <x:v>county_total_employment</x:v>
+      </x:c>
+      <x:c r="AP1" s="225" t="str">
+        <x:v>county_total_establishments</x:v>
+      </x:c>
+      <x:c r="AQ1" s="225" t="str">
+        <x:v>county_total_employment_flag</x:v>
+      </x:c>
+      <x:c r="AR1" s="225" t="str">
+        <x:v>information_sector_employment</x:v>
+      </x:c>
+      <x:c r="AS1" s="225" t="str">
+        <x:v>information_sector_establishments</x:v>
+      </x:c>
+      <x:c r="AT1" s="225" t="str">
+        <x:v>information_sector_employment_flag</x:v>
+      </x:c>
+      <x:c r="AU1" s="225" t="str">
+        <x:v>professional_scientific_employment</x:v>
+      </x:c>
+      <x:c r="AV1" s="225" t="str">
+        <x:v>professional_scientific_establishments</x:v>
+      </x:c>
+      <x:c r="AW1" s="225" t="str">
+        <x:v>professional_scientific_employment_flag</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -39883,6 +45558,93 @@
       <x:c r="T2" s="85" t="str">
         <x:v>Horizon Center Development Area 5 / Parcel 021-002.04; representative coordinate not yet defensible</x:v>
       </x:c>
+      <x:c r="U2" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V2" s="222" t="n">
+        <x:v>5.78964157802513</x:v>
+      </x:c>
+      <x:c r="W2" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X2" s="222" t="n">
+        <x:v>0.727876698880174</x:v>
+      </x:c>
+      <x:c r="Y2" s="222" t="n">
+        <x:v>0.727876698880174</x:v>
+      </x:c>
+      <x:c r="Z2" s="222" t="n">
+        <x:v>3.0289104348453164</x:v>
+      </x:c>
+      <x:c r="AA2" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB2" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC2" s="222" t="n">
+        <x:v>0.8453788175536231</x:v>
+      </x:c>
+      <x:c r="AD2" s="222" t="n">
+        <x:v>9.874727384733562</x:v>
+      </x:c>
+      <x:c r="AE2" s="222" t="n">
+        <x:v>0.1881877868202608</x:v>
+      </x:c>
+      <x:c r="AF2" s="219" t="n">
+        <x:v>1292</x:v>
+      </x:c>
+      <x:c r="AG2" s="226" t="str">
+        <x:v>47145</x:v>
+      </x:c>
+      <x:c r="AH2" s="229" t="str">
+        <x:v>Roane County</x:v>
+      </x:c>
+      <x:c r="AI2" s="219" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AJ2" s="226" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="AK2" s="226" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="AL2" s="219" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="AM2" s="226" t="n">
+        <x:v>1944</x:v>
+      </x:c>
+      <x:c r="AN2" s="226" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="AO2" s="226" t="n">
+        <x:v>8996</x:v>
+      </x:c>
+      <x:c r="AP2" s="226" t="n">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="AQ2" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR2" s="226" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AS2" s="226" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AT2" s="226" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="AU2" s="226" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="AV2" s="226" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AW2" s="226" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="85" t="str">
@@ -39943,6 +45705,93 @@
       <x:c r="T3" s="85" t="str">
         <x:v>MyEListing Street View/listing coordinate</x:v>
       </x:c>
+      <x:c r="U3" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V3" s="222" t="n">
+        <x:v>3.5164351630750597</x:v>
+      </x:c>
+      <x:c r="W3" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X3" s="222" t="n">
+        <x:v>1.6481279770076562</x:v>
+      </x:c>
+      <x:c r="Y3" s="222" t="n">
+        <x:v>3.297720169273466</x:v>
+      </x:c>
+      <x:c r="Z3" s="222" t="n">
+        <x:v>4.469931485485613</x:v>
+      </x:c>
+      <x:c r="AA3" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB3" s="226" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC3" s="222" t="n">
+        <x:v>0.3964070865213985</x:v>
+      </x:c>
+      <x:c r="AD3" s="222" t="n">
+        <x:v>1.7405329422292104</x:v>
+      </x:c>
+      <x:c r="AE3" s="222" t="n">
+        <x:v>0.4096250977179209</x:v>
+      </x:c>
+      <x:c r="AF3" s="219" t="n">
+        <x:v>1181</x:v>
+      </x:c>
+      <x:c r="AG3" s="226" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="AH3" s="229" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="AI3" s="219" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AJ3" s="226" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="AK3" s="226" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="AL3" s="219" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="AM3" s="226" t="n">
+        <x:v>1936</x:v>
+      </x:c>
+      <x:c r="AN3" s="226" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="AO3" s="226" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="AP3" s="226" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="AQ3" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR3" s="226" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="AS3" s="226" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="AT3" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU3" s="226" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="AV3" s="226" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="AW3" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="85" t="str">
@@ -40003,6 +45852,93 @@
       <x:c r="T4" s="85" t="str">
         <x:v>WTIA Tiger Jones Technology Park site specification</x:v>
       </x:c>
+      <x:c r="U4" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V4" s="222" t="n">
+        <x:v>3.955851792529339</x:v>
+      </x:c>
+      <x:c r="W4" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X4" s="222" t="n">
+        <x:v>0.2627499312143647</x:v>
+      </x:c>
+      <x:c r="Y4" s="222" t="n">
+        <x:v>0.2627499312143647</x:v>
+      </x:c>
+      <x:c r="Z4" s="222" t="n">
+        <x:v>4.118275281834532</x:v>
+      </x:c>
+      <x:c r="AA4" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB4" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC4" s="222" t="n">
+        <x:v>0.9883617984953896</x:v>
+      </x:c>
+      <x:c r="AD4" s="222" t="n">
+        <x:v>0.9983755164533524</x:v>
+      </x:c>
+      <x:c r="AE4" s="222" t="n">
+        <x:v>0.539529096114026</x:v>
+      </x:c>
+      <x:c r="AF4" s="219" t="n">
+        <x:v>1380</x:v>
+      </x:c>
+      <x:c r="AG4" s="226" t="str">
+        <x:v>47113</x:v>
+      </x:c>
+      <x:c r="AH4" s="229" t="str">
+        <x:v>Madison County</x:v>
+      </x:c>
+      <x:c r="AI4" s="219" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AJ4" s="226" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK4" s="226" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AL4" s="219" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="AM4" s="226" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AN4" s="226" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="AO4" s="226" t="n">
+        <x:v>55344</x:v>
+      </x:c>
+      <x:c r="AP4" s="226" t="n">
+        <x:v>2598</x:v>
+      </x:c>
+      <x:c r="AQ4" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR4" s="226" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="AS4" s="226" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="AT4" s="226" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="AU4" s="226" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="AV4" s="226" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="AW4" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="85" t="str">
@@ -40030,23 +45966,29 @@
       <x:c r="I5" s="85" t="str">
         <x:v>TN</x:v>
       </x:c>
-      <x:c r="J5" s="85"/>
-      <x:c r="K5" s="117"/>
-      <x:c r="L5" s="117"/>
+      <x:c r="J5" s="85" t="str">
+        <x:v>38301</x:v>
+      </x:c>
+      <x:c r="K5" s="117" t="n">
+        <x:v>35.636798360652</x:v>
+      </x:c>
+      <x:c r="L5" s="117" t="n">
+        <x:v>-88.774694703444</x:v>
+      </x:c>
       <x:c r="M5" s="85" t="str">
         <x:v>GRIID announced a 60 MW, 15-acre Jackson facility; CleanSpark later acquired GRIID, but a current site-level construction or operating confirmation was not found.</x:v>
       </x:c>
       <x:c r="N5" s="85" t="str">
-        <x:v>globenewswire.com | prnewswire.com | sec.gov</x:v>
+        <x:v>globenewswire.com | prnewswire.com | sec.gov | census_geocoder</x:v>
       </x:c>
       <x:c r="O5" s="85" t="str">
-        <x:v>https://www.globenewswire.com/news-release/2024/02/06/2824158/0/en/GRIID-Infrastructure-to-Add-60-MW-with-New-Bitcoin-Mining-Facility-in-Tennessee.html | https://www.prnewswire.com/news-releases/cleanspark-announces-agreement-to-acquire-griid-infrastructure-based-on-an-enterprise-value-of-155-million-and-expansion-plans-of-over-400-mw-in-tennessee-302184116.html | https://www.sec.gov/Archives/edgar/data/1830029/000119312524223759/d888816ddefm14a.htm | https://baxtel.com/data-center/cleanspark-jackson-tn | https://tpucdockets.tn.gov/archive/filings/2003/0300438ar.pdf | https://www.sec.gov/Archives/edgar/data/1830029/000119312524000728/d941597dex211.htm</x:v>
+        <x:v>https://www.globenewswire.com/news-release/2024/02/06/2824158/0/en/GRIID-Infrastructure-to-Add-60-MW-with-New-Bitcoin-Mining-Facility-in-Tennessee.html | https://www.prnewswire.com/news-releases/cleanspark-announces-agreement-to-acquire-griid-infrastructure-based-on-an-enterprise-value-of-155-million-and-expansion-plans-of-over-400-mw-in-tennessee-302184116.html | https://www.sec.gov/Archives/edgar/data/1830029/000119312524223759/d888816ddefm14a.htm | https://baxtel.com/data-center/cleanspark-jackson-tn | https://tpucdockets.tn.gov/archive/filings/2003/0300438ar.pdf | https://www.sec.gov/Archives/edgar/data/1830029/000119312524000728/d941597dex211.htm | https://geocoding.geo.census.gov/geocoder/geographies/onelineaddress?address=2342%20North%20Parkway%20East%2C%20Jackson%2C%20TN&amp;benchmark=Public_AR_Current&amp;vintage=Current_Current&amp;format=json</x:v>
       </x:c>
       <x:c r="P5" s="123" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="Q5" s="85" t="str">
-        <x:v>Public evidence supports prior GRIID/CleanSpark Jackson development and property ownership, but does not independently confirm the stated 60 MW facility is currently operating or energized. Retained as an unpromoted candidate.</x:v>
+        <x:v>The U.S. Census Geocoder returned a unique match for 2342 N Pkwy E, Jackson, TN 38301. Coordinates are a TIGER address-range interpolation rather than a parcel centroid; Phase 1 spatial features are calculated from this address point.</x:v>
       </x:c>
       <x:c r="R5" s="85" t="str">
         <x:v>address_or_site</x:v>
@@ -40054,7 +45996,96 @@
       <x:c r="S5" s="85" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="T5" s="85"/>
+      <x:c r="T5" s="85" t="str">
+        <x:v>https://geocoding.geo.census.gov/geocoder/geographies/onelineaddress?address=2342%20North%20Parkway%20East%2C%20Jackson%2C%20TN&amp;benchmark=Public_AR_Current&amp;vintage=Current_Current&amp;format=json</x:v>
+      </x:c>
+      <x:c r="U5" s="220" t="str">
+        <x:v>address_geocoded_features</x:v>
+      </x:c>
+      <x:c r="V5" s="222" t="n">
+        <x:v>3.955851792529339</x:v>
+      </x:c>
+      <x:c r="W5" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X5" s="222" t="n">
+        <x:v>0.5514369863831382</x:v>
+      </x:c>
+      <x:c r="Y5" s="222" t="n">
+        <x:v>0.5514369863831382</x:v>
+      </x:c>
+      <x:c r="Z5" s="222" t="n">
+        <x:v>7.388416684508857</x:v>
+      </x:c>
+      <x:c r="AA5" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB5" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC5" s="222" t="n">
+        <x:v>0.5958501531253004</x:v>
+      </x:c>
+      <x:c r="AD5" s="222" t="n">
+        <x:v>4.677277966293714</x:v>
+      </x:c>
+      <x:c r="AE5" s="222" t="n">
+        <x:v>0.5983824548535115</x:v>
+      </x:c>
+      <x:c r="AF5" s="219" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+      <x:c r="AG5" s="226" t="str">
+        <x:v>47113</x:v>
+      </x:c>
+      <x:c r="AH5" s="229" t="str">
+        <x:v>Madison County</x:v>
+      </x:c>
+      <x:c r="AI5" s="219" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AJ5" s="226" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK5" s="226" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AL5" s="219" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AM5" s="226" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="AN5" s="226" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="AO5" s="226" t="n">
+        <x:v>55344</x:v>
+      </x:c>
+      <x:c r="AP5" s="226" t="n">
+        <x:v>2598</x:v>
+      </x:c>
+      <x:c r="AQ5" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR5" s="226" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="AS5" s="226" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="AT5" s="226" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="AU5" s="226" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="AV5" s="226" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="AW5" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -40074,27 +46105,33 @@
       <x:c r="G6" t="str">
         <x:v>Nashville</x:v>
       </x:c>
-      <x:c r="H6"/>
+      <x:c r="H6" t="str">
+        <x:v>Davidson</x:v>
+      </x:c>
       <x:c r="I6" t="str">
         <x:v>TN</x:v>
       </x:c>
       <x:c r="J6"/>
-      <x:c r="K6" t="str"/>
-      <x:c r="L6" t="str"/>
+      <x:c r="K6" t="n">
+        <x:v>36.1721781</x:v>
+      </x:c>
+      <x:c r="L6" t="n">
+        <x:v>-86.7846022</x:v>
+      </x:c>
       <x:c r="M6" s="85" t="str">
         <x:v>Developer materials describe a 120 MW, 38-acre Nashville campus in development, but the exact site and county are not public.</x:v>
       </x:c>
       <x:c r="N6" s="85" t="str">
-        <x:v>atmosphere-dc.com | datacenterdynamics.com</x:v>
+        <x:v>atmosphere-dc.com | datacenterdynamics.com | census_tigerweb_place</x:v>
       </x:c>
       <x:c r="O6" s="85" t="str">
-        <x:v>https://atmosphere-dc.com/data-centers/nashville-tn/ | https://www.datacenterdynamics.com/en/news/atmosphere-dc-secures-investment-from-agc-equity-partners/ | https://baxtel.com/data-center/h5-data-centers-nashville-tn01 | https://baxtel.com/data-center/h5-data-centers-nashville-tn02 | https://baxtel.com/data-center/edgeconnex-nashville | https://baxtel.com/data-center/dc-blox-nashville | https://baxtel.com/data-center/lumen-nashville-2</x:v>
+        <x:v>https://atmosphere-dc.com/data-centers/nashville-tn/ | https://www.datacenterdynamics.com/en/news/atmosphere-dc-secures-investment-from-agc-equity-partners/ | https://baxtel.com/data-center/h5-data-centers-nashville-tn01 | https://baxtel.com/data-center/h5-data-centers-nashville-tn02 | https://baxtel.com/data-center/edgeconnex-nashville | https://baxtel.com/data-center/dc-blox-nashville | https://baxtel.com/data-center/lumen-nashville-2 | https://tigerweb.geo.census.gov/tigerwebmain/Files/bas26/tigerweb_bas26_incplace_2020_tab20_tn.html</x:v>
       </x:c>
       <x:c r="P6" s="123" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="Q6" s="85" t="str">
-        <x:v>Atmosphere publicly discloses Nashville, 120 MW, and a 38-acre campus but no street address, county, or parcel. The previous directory-derived market pin is removed because it is physically inconsistent with a 38-acre campus. Retain as a market-level candidate only.</x:v>
+        <x:v>The exact Atmosphere parcel remains undisclosed. Coordinates use the official Census TIGERweb representative point for Nashville-Davidson metropolitan government (balance). Derived features are market-level estimates and are not site-specific.</x:v>
       </x:c>
       <x:c r="R6" s="85" t="str">
         <x:v>area_or_city</x:v>
@@ -40102,7 +46139,96 @@
       <x:c r="S6" s="85" t="str">
         <x:v>low</x:v>
       </x:c>
-      <x:c r="T6" s="85" t="str"/>
+      <x:c r="T6" s="85" t="str">
+        <x:v>https://tigerweb.geo.census.gov/tigerwebmain/Files/bas26/tigerweb_bas26_incplace_2020_tab20_tn.html</x:v>
+      </x:c>
+      <x:c r="U6" s="220" t="str">
+        <x:v>city_representative_features</x:v>
+      </x:c>
+      <x:c r="V6" s="222" t="n">
+        <x:v>0.1199615700679816</x:v>
+      </x:c>
+      <x:c r="W6" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X6" s="222" t="n">
+        <x:v>0.1723118661269711</x:v>
+      </x:c>
+      <x:c r="Y6" s="222" t="n">
+        <x:v>2.7546887632101753</x:v>
+      </x:c>
+      <x:c r="Z6" s="222" t="n">
+        <x:v>20.81356562075462</x:v>
+      </x:c>
+      <x:c r="AA6" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB6" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC6" s="222" t="n">
+        <x:v>0.4824685494674138</x:v>
+      </x:c>
+      <x:c r="AD6" s="222" t="n">
+        <x:v>1.1338343547492988</x:v>
+      </x:c>
+      <x:c r="AE6" s="222" t="n">
+        <x:v>0.4996096498820266</x:v>
+      </x:c>
+      <x:c r="AF6" s="219" t="n">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="AG6" s="226" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="AH6" s="229" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="AI6" s="219" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AJ6" s="226" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="AK6" s="226" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="AL6" s="219" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AM6" s="226" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="AN6" s="226" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="AO6" s="226" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="AP6" s="226" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="AQ6" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR6" s="226" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="AS6" s="226" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="AT6" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU6" s="226" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="AV6" s="226" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="AW6" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -40163,6 +46289,93 @@
       <x:c r="T7" s="85" t="str">
         <x:v>simplecontacts:adjacent-93-weakley-ln</x:v>
       </x:c>
+      <x:c r="U7" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V7" s="222" t="n">
+        <x:v>17.477420413451394</x:v>
+      </x:c>
+      <x:c r="W7" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X7" s="222" t="n">
+        <x:v>1.2951609164858104</x:v>
+      </x:c>
+      <x:c r="Y7" s="222" t="n">
+        <x:v>1.2951609164858104</x:v>
+      </x:c>
+      <x:c r="Z7" s="222" t="n">
+        <x:v>11.175516178530444</x:v>
+      </x:c>
+      <x:c r="AA7" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB7" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC7" s="222" t="n">
+        <x:v>0.2439990478853663</x:v>
+      </x:c>
+      <x:c r="AD7" s="222" t="n">
+        <x:v>6.465734347055811</x:v>
+      </x:c>
+      <x:c r="AE7" s="222" t="n">
+        <x:v>0.4435461841557285</x:v>
+      </x:c>
+      <x:c r="AF7" s="219" t="n">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="AG7" s="226" t="str">
+        <x:v>47149</x:v>
+      </x:c>
+      <x:c r="AH7" s="229" t="str">
+        <x:v>Rutherford County</x:v>
+      </x:c>
+      <x:c r="AI7" s="219" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="AJ7" s="226" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="AK7" s="226" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="AL7" s="219" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="AM7" s="226" t="n">
+        <x:v>1318</x:v>
+      </x:c>
+      <x:c r="AN7" s="226" t="n">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="AO7" s="226" t="n">
+        <x:v>128935</x:v>
+      </x:c>
+      <x:c r="AP7" s="226" t="n">
+        <x:v>6285</x:v>
+      </x:c>
+      <x:c r="AQ7" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR7" s="226" t="n">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="AS7" s="226" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="AT7" s="226" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="AU7" s="226" t="n">
+        <x:v>5057</x:v>
+      </x:c>
+      <x:c r="AV7" s="226" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="AW7" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -40223,6 +46436,93 @@
       <x:c r="T8" s="85" t="str">
         <x:v>ibegin:state-of-tennessee-data-center</x:v>
       </x:c>
+      <x:c r="U8" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V8" s="222" t="n">
+        <x:v>0.1199615700679816</x:v>
+      </x:c>
+      <x:c r="W8" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X8" s="222" t="n">
+        <x:v>0.11985864260321</x:v>
+      </x:c>
+      <x:c r="Y8" s="222" t="n">
+        <x:v>2.697332165039337</x:v>
+      </x:c>
+      <x:c r="Z8" s="222" t="n">
+        <x:v>20.749195342598043</x:v>
+      </x:c>
+      <x:c r="AA8" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB8" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC8" s="222" t="n">
+        <x:v>0.3786294840102457</x:v>
+      </x:c>
+      <x:c r="AD8" s="222" t="n">
+        <x:v>1.029021252388722</x:v>
+      </x:c>
+      <x:c r="AE8" s="222" t="n">
+        <x:v>0.5987710082936638</x:v>
+      </x:c>
+      <x:c r="AF8" s="219" t="n">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="AG8" s="226" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="AH8" s="229" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="AI8" s="219" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AJ8" s="226" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="AK8" s="226" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="AL8" s="219" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AM8" s="226" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="AN8" s="226" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="AO8" s="226" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="AP8" s="226" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="AQ8" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR8" s="226" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="AS8" s="226" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="AT8" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU8" s="226" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="AV8" s="226" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="AW8" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
@@ -40281,6 +46581,93 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="T9" s="85"/>
+      <x:c r="U9" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V9" s="222" t="n">
+        <x:v>5.78964157802513</x:v>
+      </x:c>
+      <x:c r="W9" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X9" s="222" t="n">
+        <x:v>0.5494278274235339</x:v>
+      </x:c>
+      <x:c r="Y9" s="222" t="n">
+        <x:v>0.5494278274235339</x:v>
+      </x:c>
+      <x:c r="Z9" s="222" t="n">
+        <x:v>0.7488773710340574</x:v>
+      </x:c>
+      <x:c r="AA9" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB9" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC9" s="222" t="n">
+        <x:v>3.210200206642162</x:v>
+      </x:c>
+      <x:c r="AD9" s="222" t="n">
+        <x:v>6.276103991973085</x:v>
+      </x:c>
+      <x:c r="AE9" s="222" t="n">
+        <x:v>0.2533076412097717</x:v>
+      </x:c>
+      <x:c r="AF9" s="219" t="n">
+        <x:v>1295</x:v>
+      </x:c>
+      <x:c r="AG9" s="226" t="str">
+        <x:v>47145</x:v>
+      </x:c>
+      <x:c r="AH9" s="229" t="str">
+        <x:v>Roane County</x:v>
+      </x:c>
+      <x:c r="AI9" s="219" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AJ9" s="226" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="AK9" s="226" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="AL9" s="219" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AM9" s="226" t="n">
+        <x:v>1967</x:v>
+      </x:c>
+      <x:c r="AN9" s="226" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="AO9" s="226" t="n">
+        <x:v>8996</x:v>
+      </x:c>
+      <x:c r="AP9" s="226" t="n">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="AQ9" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR9" s="226" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AS9" s="226" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AT9" s="226" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="AU9" s="226" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="AV9" s="226" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AW9" s="226" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -40341,6 +46728,93 @@
       <x:c r="T10" s="85" t="str">
         <x:v>ornl:visitor-center-gps</x:v>
       </x:c>
+      <x:c r="U10" s="220" t="str">
+        <x:v>shared_site:TNCAND-009</x:v>
+      </x:c>
+      <x:c r="V10" s="222" t="n">
+        <x:v>5.78964157802513</x:v>
+      </x:c>
+      <x:c r="W10" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X10" s="222" t="n">
+        <x:v>0.5494278274235339</x:v>
+      </x:c>
+      <x:c r="Y10" s="222" t="n">
+        <x:v>0.5494278274235339</x:v>
+      </x:c>
+      <x:c r="Z10" s="222" t="n">
+        <x:v>0.7488773710340574</x:v>
+      </x:c>
+      <x:c r="AA10" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB10" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC10" s="222" t="n">
+        <x:v>3.210200206642162</x:v>
+      </x:c>
+      <x:c r="AD10" s="222" t="n">
+        <x:v>6.276103991973085</x:v>
+      </x:c>
+      <x:c r="AE10" s="222" t="n">
+        <x:v>0.2533076412097717</x:v>
+      </x:c>
+      <x:c r="AF10" s="219" t="n">
+        <x:v>1295</x:v>
+      </x:c>
+      <x:c r="AG10" s="226" t="str">
+        <x:v>47145</x:v>
+      </x:c>
+      <x:c r="AH10" s="229" t="str">
+        <x:v>Roane County</x:v>
+      </x:c>
+      <x:c r="AI10" s="219" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AJ10" s="226" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="AK10" s="226" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="AL10" s="219" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AM10" s="226" t="n">
+        <x:v>1967</x:v>
+      </x:c>
+      <x:c r="AN10" s="226" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="AO10" s="226" t="n">
+        <x:v>8996</x:v>
+      </x:c>
+      <x:c r="AP10" s="226" t="n">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="AQ10" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR10" s="226" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="AS10" s="226" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AT10" s="226" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="AU10" s="226" t="n">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="AV10" s="226" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AW10" s="226" t="str">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -40400,6 +46874,93 @@
       </x:c>
       <x:c r="T11" s="85" t="str">
         <x:v>merchantcircle:1231-18th-ave-s</x:v>
+      </x:c>
+      <x:c r="U11" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V11" s="222" t="n">
+        <x:v>1.826739921351709</x:v>
+      </x:c>
+      <x:c r="W11" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X11" s="222" t="n">
+        <x:v>0.2083265200808276</x:v>
+      </x:c>
+      <x:c r="Y11" s="222" t="n">
+        <x:v>0.2083265200808276</x:v>
+      </x:c>
+      <x:c r="Z11" s="222" t="n">
+        <x:v>18.008025821242953</x:v>
+      </x:c>
+      <x:c r="AA11" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB11" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC11" s="222" t="n">
+        <x:v>0.3549606588226874</x:v>
+      </x:c>
+      <x:c r="AD11" s="222" t="n">
+        <x:v>1.2925106218366806</x:v>
+      </x:c>
+      <x:c r="AE11" s="222" t="n">
+        <x:v>2.993649634234073</x:v>
+      </x:c>
+      <x:c r="AF11" s="219" t="n">
+        <x:v>962</x:v>
+      </x:c>
+      <x:c r="AG11" s="226" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="AH11" s="229" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="AI11" s="219" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AJ11" s="226" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="AK11" s="226" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="AL11" s="219" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AM11" s="226" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="AN11" s="226" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="AO11" s="226" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="AP11" s="226" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="AQ11" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR11" s="226" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="AS11" s="226" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="AT11" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU11" s="226" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="AV11" s="226" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="AW11" s="226" t="str">
+        <x:v>G</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -40457,6 +47018,93 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="T12" s="85"/>
+      <x:c r="U12" s="220" t="str">
+        <x:v>linked_master:TNDC-038</x:v>
+      </x:c>
+      <x:c r="V12" s="222" t="n">
+        <x:v>5.053066150501399</x:v>
+      </x:c>
+      <x:c r="W12" s="220" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="X12" s="222" t="n">
+        <x:v>0.0707119478126202</x:v>
+      </x:c>
+      <x:c r="Y12" s="222" t="n">
+        <x:v>1.0205936549853298</x:v>
+      </x:c>
+      <x:c r="Z12" s="222" t="n">
+        <x:v>8.266680964276182</x:v>
+      </x:c>
+      <x:c r="AA12" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB12" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC12" s="222" t="n">
+        <x:v>0.101192712090354</x:v>
+      </x:c>
+      <x:c r="AD12" s="222" t="n">
+        <x:v>3.367226120148101</x:v>
+      </x:c>
+      <x:c r="AE12" s="222" t="n">
+        <x:v>0.216468617040965</x:v>
+      </x:c>
+      <x:c r="AF12" s="219" t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="AG12" s="226" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="AH12" s="229" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="AI12" s="219" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="AJ12" s="226" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="AK12" s="226" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="AL12" s="219" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="AM12" s="226" t="n">
+        <x:v>1623</x:v>
+      </x:c>
+      <x:c r="AN12" s="226" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="AO12" s="226" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="AP12" s="226" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="AQ12" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR12" s="226" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="AS12" s="226" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="AT12" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU12" s="226" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="AV12" s="226" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="AW12" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -40515,6 +47163,93 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="T13" s="85"/>
+      <x:c r="U13" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V13" s="222" t="n">
+        <x:v>0.4108468813552908</x:v>
+      </x:c>
+      <x:c r="W13" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X13" s="222" t="n">
+        <x:v>2.423240542770371</x:v>
+      </x:c>
+      <x:c r="Y13" s="222" t="n">
+        <x:v>2.423240542770371</x:v>
+      </x:c>
+      <x:c r="Z13" s="222" t="n">
+        <x:v>5.777505241574905</x:v>
+      </x:c>
+      <x:c r="AA13" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB13" s="226" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC13" s="222" t="n">
+        <x:v>0.1395838351382324</x:v>
+      </x:c>
+      <x:c r="AD13" s="222" t="n">
+        <x:v>1.7486306681580843</x:v>
+      </x:c>
+      <x:c r="AE13" s="222" t="n">
+        <x:v>1.25665845845521</x:v>
+      </x:c>
+      <x:c r="AF13" s="219" t="n">
+        <x:v>1157</x:v>
+      </x:c>
+      <x:c r="AG13" s="226" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="AH13" s="229" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="AI13" s="219" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AJ13" s="226" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="AK13" s="226" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="AL13" s="219" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="AM13" s="226" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="AN13" s="226" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="AO13" s="226" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="AP13" s="226" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="AQ13" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR13" s="226" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="AS13" s="226" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="AT13" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU13" s="226" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="AV13" s="226" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="AW13" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -40575,6 +47310,93 @@
       <x:c r="T14" s="85" t="str">
         <x:v>github-geocode:940-3rd-ave-n</x:v>
       </x:c>
+      <x:c r="U14" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V14" s="222" t="n">
+        <x:v>0.189418735621127</x:v>
+      </x:c>
+      <x:c r="W14" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X14" s="222" t="n">
+        <x:v>0.0884122454567099</x:v>
+      </x:c>
+      <x:c r="Y14" s="222" t="n">
+        <x:v>2.8612764443878977</x:v>
+      </x:c>
+      <x:c r="Z14" s="222" t="n">
+        <x:v>20.924339871778106</x:v>
+      </x:c>
+      <x:c r="AA14" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB14" s="226" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC14" s="222" t="n">
+        <x:v>0.6412253555403852</x:v>
+      </x:c>
+      <x:c r="AD14" s="222" t="n">
+        <x:v>1.0330715746327128</x:v>
+      </x:c>
+      <x:c r="AE14" s="222" t="n">
+        <x:v>0.3488547157964339</x:v>
+      </x:c>
+      <x:c r="AF14" s="219" t="n">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="AG14" s="226" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="AH14" s="229" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="AI14" s="219" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AJ14" s="226" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="AK14" s="226" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="AL14" s="219" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="AM14" s="226" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="AN14" s="226" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="AO14" s="226" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="AP14" s="226" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="AQ14" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR14" s="226" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="AS14" s="226" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="AT14" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU14" s="226" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="AV14" s="226" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="AW14" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -40633,6 +47455,93 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="T15" s="85"/>
+      <x:c r="U15" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V15" s="222" t="n">
+        <x:v>0.536086088636087</x:v>
+      </x:c>
+      <x:c r="W15" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X15" s="222" t="n">
+        <x:v>0.1168910413917695</x:v>
+      </x:c>
+      <x:c r="Y15" s="222" t="n">
+        <x:v>0.1168910413917695</x:v>
+      </x:c>
+      <x:c r="Z15" s="222" t="n">
+        <x:v>5.663422137774373</x:v>
+      </x:c>
+      <x:c r="AA15" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB15" s="226" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC15" s="222" t="n">
+        <x:v>0.1740304144736869</x:v>
+      </x:c>
+      <x:c r="AD15" s="222" t="n">
+        <x:v>1.9074207477809144</x:v>
+      </x:c>
+      <x:c r="AE15" s="222" t="n">
+        <x:v>0.965330035299926</x:v>
+      </x:c>
+      <x:c r="AF15" s="219" t="n">
+        <x:v>1345</x:v>
+      </x:c>
+      <x:c r="AG15" s="226" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="AH15" s="229" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="AI15" s="219" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="AJ15" s="226" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="AK15" s="226" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AL15" s="219" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AM15" s="226" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="AN15" s="226" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="AO15" s="226" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="AP15" s="226" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="AQ15" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR15" s="226" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="AS15" s="226" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="AT15" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU15" s="226" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="AV15" s="226" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="AW15" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -40691,6 +47600,93 @@
         <x:v>high</x:v>
       </x:c>
       <x:c r="T16" s="85"/>
+      <x:c r="U16" s="220" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="V16" s="222" t="n">
+        <x:v>0.5765360809592314</x:v>
+      </x:c>
+      <x:c r="W16" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X16" s="222" t="n">
+        <x:v>0.0836624497117524</x:v>
+      </x:c>
+      <x:c r="Y16" s="222" t="n">
+        <x:v>2.6302420928934094</x:v>
+      </x:c>
+      <x:c r="Z16" s="222" t="n">
+        <x:v>2.6302420928934094</x:v>
+      </x:c>
+      <x:c r="AA16" s="224" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB16" s="226" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC16" s="222" t="n">
+        <x:v>1.5400592802066244</x:v>
+      </x:c>
+      <x:c r="AD16" s="222" t="n">
+        <x:v>5.3098829269128185</x:v>
+      </x:c>
+      <x:c r="AE16" s="222" t="n">
+        <x:v>0.2728228010008091</x:v>
+      </x:c>
+      <x:c r="AF16" s="219" t="n">
+        <x:v>1251</x:v>
+      </x:c>
+      <x:c r="AG16" s="226" t="str">
+        <x:v>47157</x:v>
+      </x:c>
+      <x:c r="AH16" s="229" t="str">
+        <x:v>Shelby County</x:v>
+      </x:c>
+      <x:c r="AI16" s="219" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AJ16" s="226" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="AK16" s="226" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="AL16" s="219" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AM16" s="226" t="n">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="AN16" s="226" t="n">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="AO16" s="226" t="n">
+        <x:v>446048</x:v>
+      </x:c>
+      <x:c r="AP16" s="226" t="n">
+        <x:v>19359</x:v>
+      </x:c>
+      <x:c r="AQ16" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR16" s="226" t="n">
+        <x:v>4823</x:v>
+      </x:c>
+      <x:c r="AS16" s="226" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="AT16" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AU16" s="226" t="n">
+        <x:v>20108</x:v>
+      </x:c>
+      <x:c r="AV16" s="226" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="AW16" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -40721,22 +47717,26 @@
       <x:c r="J17" t="str">
         <x:v>37683</x:v>
       </x:c>
-      <x:c r="K17"/>
-      <x:c r="L17"/>
+      <x:c r="K17" t="n">
+        <x:v>36.445395419476</x:v>
+      </x:c>
+      <x:c r="L17" t="n">
+        <x:v>-81.801011033243</x:v>
+      </x:c>
       <x:c r="M17" t="str">
         <x:v>Public planning records and current reporting identify a proposed 30 MW CleanSpark bitcoin-mining site on a 50-acre parcel at 178 Rainbow Rd. The rezoning did not advance, so it is not promoted into Master.</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>mountaincitytn.gov | datacentermap.com | datacenterdynamics.com | lpm.org</x:v>
+        <x:v>mountaincitytn.gov | datacentermap.com | datacenterdynamics.com | lpm.org | census_geocoder</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>https://www.datacentermap.com/usa/tennessee/knoxville/cleanspark-mountain-city/ | https://www.datacenterdynamics.com/en/news/cleanspark-faces-backlash-over-bitcoin-mining-site-in-mountain-city-tennessee/ | https://www.lpm.org/news/2025-08-15/tennessee-town-pushes-back-over-proposed-bitcoin-mine-and-wins | https://cms3.revize.com/revize/mountaincity/Documents/Planning/PC%20Minutes%2002.27.2025.pdf | https://www.loopnet.com/property/178-rainbow-rd-mountain-city-tn-37683/47091-055%20%20%20%2002201%20000/ | https://www.zillow.com/homedetails/178-Rainbow-Rd-Mountain-City-TN-37683/299906354_zpid/</x:v>
+        <x:v>https://www.datacentermap.com/usa/tennessee/knoxville/cleanspark-mountain-city/ | https://www.datacenterdynamics.com/en/news/cleanspark-faces-backlash-over-bitcoin-mining-site-in-mountain-city-tennessee/ | https://www.lpm.org/news/2025-08-15/tennessee-town-pushes-back-over-proposed-bitcoin-mine-and-wins | https://cms3.revize.com/revize/mountaincity/Documents/Planning/PC%20Minutes%2002.27.2025.pdf | https://www.loopnet.com/property/178-rainbow-rd-mountain-city-tn-37683/47091-055%20%20%20%2002201%20000/ | https://www.zillow.com/homedetails/178-Rainbow-Rd-Mountain-City-TN-37683/299906354_zpid/ | https://geocoding.geo.census.gov/geocoder/geographies/onelineaddress?address=178%20Rainbow%20Rd%2C%20Mountain%20City%2C%20TN%2037683&amp;benchmark=Public_AR_Current&amp;vintage=Current_Current&amp;format=json</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="Q17" t="str">
-        <x:v>178 Rainbow Rd is independently tied to Johnson County parcel 055-022.01 / 05502201000 and 50.48 acres by multiple property-record sources. This is the proposed CleanSpark Mountain City site. Reviewed public pages expose map imagery but not a textual WGS84 parcel centroid/building point; coordinates remain blank until a Johnson County/Tennessee parcel geometry endpoint or defensible address-level geocode is obtained.</x:v>
+        <x:v>The U.S. Census Geocoder returned a unique match for 178 Rainbow Rd, Mountain City, TN 37683, consistent with parcel 055-022.01. Coordinates are a TIGER address-range interpolation rather than a parcel centroid; Phase 1 spatial features are calculated from this address point.</x:v>
       </x:c>
       <x:c r="R17" t="str">
         <x:v>address_or_site</x:v>
@@ -40744,7 +47744,96 @@
       <x:c r="S17" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="T17"/>
+      <x:c r="T17" t="str">
+        <x:v>https://geocoding.geo.census.gov/geocoder/geographies/onelineaddress?address=178%20Rainbow%20Rd%2C%20Mountain%20City%2C%20TN%2037683&amp;benchmark=Public_AR_Current&amp;vintage=Current_Current&amp;format=json</x:v>
+      </x:c>
+      <x:c r="U17" s="220" t="str">
+        <x:v>address_geocoded_features</x:v>
+      </x:c>
+      <x:c r="V17" s="222" t="n">
+        <x:v>37.94409711967336</x:v>
+      </x:c>
+      <x:c r="W17" s="220" t="str">
+        <x:v>Candidate / not clustered</x:v>
+      </x:c>
+      <x:c r="X17" s="222" t="n">
+        <x:v>0.1256329474041895</x:v>
+      </x:c>
+      <x:c r="Y17" s="222" t="n">
+        <x:v>0.1256329474041895</x:v>
+      </x:c>
+      <x:c r="Z17" s="222" t="n">
+        <x:v>28.74529164089562</x:v>
+      </x:c>
+      <x:c r="AA17" s="224" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="AB17" s="226" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC17" s="222" t="n">
+        <x:v>0.6533632839568034</x:v>
+      </x:c>
+      <x:c r="AD17" s="222" t="n">
+        <x:v>42.95665876226064</x:v>
+      </x:c>
+      <x:c r="AE17" s="222" t="n">
+        <x:v>0.0498554757179057</x:v>
+      </x:c>
+      <x:c r="AF17" s="219" t="n">
+        <x:v>1324</x:v>
+      </x:c>
+      <x:c r="AG17" s="226" t="str">
+        <x:v>47091</x:v>
+      </x:c>
+      <x:c r="AH17" s="229" t="str">
+        <x:v>Johnson County</x:v>
+      </x:c>
+      <x:c r="AI17" s="219" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AJ17" s="226" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="AK17" s="226" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AL17" s="219" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AM17" s="226" t="n">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="AN17" s="226" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="AO17" s="226" t="n">
+        <x:v>3415</x:v>
+      </x:c>
+      <x:c r="AP17" s="226" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="AQ17" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR17" s="226" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS17" s="226" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT17" s="226" t="str">
+        <x:v>NO_PUBLISHED_ROW</x:v>
+      </x:c>
+      <x:c r="AU17" s="226" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AV17" s="226" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AW17" s="226" t="str">
+        <x:v>G</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="6">
@@ -40771,7 +47860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44533988b8334e40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf83bec226d04b5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TN/dataset/tennessee_public_data_centers.xlsx
+++ b/TN/dataset/tennessee_public_data_centers.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0512b60b15d34410"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R8b59c3c957a445fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Re6a0ad065e0e48a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R2b9315484dc44675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="R60c38f80d7ce44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="Rc7af1a06c20c4b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R1a066b5be4d04cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R6e67a17ff8784117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="Rf7cf617051f04f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="Ra5f3e93c3eb14f45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R8d516726ec1f4a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="R94c7471464a44965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Recaf2ccdc22149f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5ac92023e7b8402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R9e0b0a95ff024360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R232f2a6fcf5e4c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R5bed570c70b14e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="R0f13595a73b44b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R4956a203b79249cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R784c14e5afad4fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R92bcb7a7a9d84a4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="Re46971f5cb76403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R1008d6c561ad4825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R5b1799a13da84214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="R62431bf89c8c4840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Rd205eed25ecf45e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9256,7 +9256,7 @@
         <x:v>schema_version</x:v>
       </x:c>
       <x:c r="AO1" s="84" t="str">
-        <x:v>dataset_version</x:v>
+        <x:v>phase1_feature_status</x:v>
       </x:c>
       <x:c r="AP1" s="211" t="str">
         <x:v>nearest_neighbor_km</x:v>
@@ -9457,7 +9457,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO2" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP2" s="207" t="n">
         <x:v>3.2412571929598153</x:v>
@@ -9656,7 +9656,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO3" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP3" s="207" t="n">
         <x:v>16.5903008348662</x:v>
@@ -9857,7 +9857,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO4" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP4" s="207" t="n">
         <x:v>0.7537456534095243</x:v>
@@ -10058,7 +10058,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO5" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP5" s="207" t="n">
         <x:v>0.4108468813552908</x:v>
@@ -10257,7 +10257,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO6" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP6" s="207" t="n">
         <x:v>0.7537456534095243</x:v>
@@ -10458,7 +10458,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO7" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>city_representative_features</x:v>
       </x:c>
       <x:c r="AP7" s="207" t="n">
         <x:v>13.34786983412424</x:v>
@@ -10661,7 +10661,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO8" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP8" s="207" t="n">
         <x:v>13.34786983412424</x:v>
@@ -10864,7 +10864,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO9" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP9" s="207" t="n">
         <x:v>11.311970674520817</x:v>
@@ -11063,7 +11063,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO10" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP10" s="207" t="n">
         <x:v>16.5903008348662</x:v>
@@ -11258,7 +11258,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO11" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP11" s="207" t="n">
         <x:v>52.76647745819776</x:v>
@@ -11459,7 +11459,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO12" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP12" s="207" t="n">
         <x:v>3.2412571929598153</x:v>
@@ -11660,7 +11660,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO13" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP13" s="207" t="n">
         <x:v>3.65144110529003</x:v>
@@ -11865,7 +11865,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO14" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP14" s="207" t="n">
         <x:v>3.580764672121382</x:v>
@@ -12068,7 +12068,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO15" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP15" s="207" t="n">
         <x:v>2.3980314314913542</x:v>
@@ -12275,7 +12275,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO16" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP16" s="207" t="n">
         <x:v>2.3980314314913542</x:v>
@@ -12476,7 +12476,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO17" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP17" s="207" t="n">
         <x:v>28.99347267843897</x:v>
@@ -12677,7 +12677,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO18" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP18" s="207" t="n">
         <x:v>7.584785746838801</x:v>
@@ -12876,7 +12876,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO19" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP19" s="207" t="n">
         <x:v>0.992513351398504</x:v>
@@ -13077,7 +13077,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO20" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP20" s="207" t="n">
         <x:v>4.917109437996493</x:v>
@@ -13272,7 +13272,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO21" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP21" s="207" t="n">
         <x:v>57.045255277578455</x:v>
@@ -13469,7 +13469,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO22" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP22" s="207" t="n">
         <x:v>43.6773958414442</x:v>
@@ -13664,7 +13664,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO23" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP23" s="207" t="n">
         <x:v>27.74221155274318</x:v>
@@ -13869,7 +13869,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO24" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP24" s="207" t="n">
         <x:v>7.55864423304588</x:v>
@@ -14068,7 +14068,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO25" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP25" s="207" t="n">
         <x:v>7.55864423304588</x:v>
@@ -14269,7 +14269,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO26" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP26" s="207" t="n">
         <x:v>6.5393152771957945</x:v>
@@ -14468,7 +14468,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO27" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP27" s="207" t="n">
         <x:v>0.3454071544348475</x:v>
@@ -14673,7 +14673,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO28" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP28" s="207" t="n">
         <x:v>9.26082548446652</x:v>
@@ -14872,7 +14872,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO29" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP29" s="207" t="n">
         <x:v>0.6115269873530994</x:v>
@@ -15073,7 +15073,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO30" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP30" s="207" t="n">
         <x:v>12.992330991063133</x:v>
@@ -15278,7 +15278,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO31" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP31" s="207" t="n">
         <x:v>9.853330615022765</x:v>
@@ -15481,7 +15481,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO32" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP32" s="207" t="n">
         <x:v>1.5634296886992427</x:v>
@@ -15680,7 +15680,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO33" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP33" s="207" t="n">
         <x:v>1.976314023135052</x:v>
@@ -15883,7 +15883,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO34" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP34" s="207" t="n">
         <x:v>0.2086854803185778</x:v>
@@ -16084,7 +16084,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO35" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP35" s="207" t="n">
         <x:v>0.2086854803185778</x:v>
@@ -16283,7 +16283,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO36" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP36" s="207" t="n">
         <x:v>2.3989227738591374</x:v>
@@ -16482,7 +16482,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO37" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP37" s="207" t="n">
         <x:v>1.5634296886992427</x:v>
@@ -16681,7 +16681,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO38" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP38" s="207" t="n">
         <x:v>5.053066150501399</x:v>
@@ -16884,7 +16884,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO39" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP39" s="207" t="n">
         <x:v>1.735944713176277</x:v>
@@ -17085,7 +17085,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO40" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP40" s="207" t="n">
         <x:v>10.252603292630416</x:v>
@@ -17284,7 +17284,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO41" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP41" s="207" t="n">
         <x:v>0.5416832532175047</x:v>
@@ -17483,7 +17483,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO42" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP42" s="207" t="n">
         <x:v>0.919336050690768</x:v>
@@ -17684,7 +17684,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO43" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP43" s="207" t="n">
         <x:v>27.74221155274318</x:v>
@@ -17879,7 +17879,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO44" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP44" s="207" t="n">
         <x:v>7.65235803152038</x:v>
@@ -18078,7 +18078,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO45" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP45" s="207" t="n">
         <x:v>7.65235803152038</x:v>
@@ -18277,7 +18277,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO46" s="85" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP46" s="207" t="n">
         <x:v>4.917109437996493</x:v>
@@ -18478,7 +18478,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO47" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP47" s="207" t="n">
         <x:v>0.992513351398504</x:v>
@@ -18677,7 +18677,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO48" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP48" s="207" t="n">
         <x:v>1.4454623860169304</x:v>
@@ -18876,7 +18876,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO49" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP49" s="207" t="n">
         <x:v>1.4454623860169304</x:v>
@@ -19075,7 +19075,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO50" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP50" s="207" t="n">
         <x:v>4.365935265331043</x:v>
@@ -19278,7 +19278,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO51" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP51" s="207" t="n">
         <x:v>10.771741932562746</x:v>
@@ -19481,7 +19481,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO52" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP52" s="207" t="n">
         <x:v>17.477420413451394</x:v>
@@ -19682,7 +19682,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO53" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP53" s="207" t="n">
         <x:v>7.201622189296421</x:v>
@@ -19883,7 +19883,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO54" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP54" s="207" t="n">
         <x:v>1.976314023135052</x:v>
@@ -20084,7 +20084,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO55" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP55" s="207" t="n">
         <x:v>1.510841476707156</x:v>
@@ -20287,7 +20287,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO56" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP56" s="207" t="n">
         <x:v>1.510841476707156</x:v>
@@ -20486,7 +20486,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO57" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP57" s="207" t="n">
         <x:v>0.536086088636087</x:v>
@@ -20687,7 +20687,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO58" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP58" s="207" t="n">
         <x:v>0.3454071544348475</x:v>
@@ -20890,7 +20890,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO59" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP59" s="207" t="n">
         <x:v>0.6115269873530994</x:v>
@@ -21093,7 +21093,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO60" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP60" s="207" t="n">
         <x:v>6.183699762877351</x:v>
@@ -21294,7 +21294,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO61" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP61" s="207" t="n">
         <x:v>23.739097663615286</x:v>
@@ -21499,7 +21499,7 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="AO62" t="str">
-        <x:v>2026-09-03-deduplicated</x:v>
+        <x:v>direct_site_features</x:v>
       </x:c>
       <x:c r="AP62" s="207" t="n">
         <x:v>37.94409711967336</x:v>
@@ -21644,7 +21644,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36774806f8c84305"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re95a139c1903423d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42507,7 +42507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa50700318684d03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dc61433c7f54361"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44549,7 +44549,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R425b4b3ecadb40c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13159f9452744b72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44729,7 +44729,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c237ebd7bfa4ad6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd5a0bfeaa8e4763"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45105,7 +45105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd208a7c1e3cd49e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e4a0a7040164ae7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45290,7 +45290,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cea2fdd68ae42bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5364e476327c4262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47860,7 +47860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf83bec226d04b5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R666dc95281814e48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TN/dataset/tennessee_public_data_centers.xlsx
+++ b/TN/dataset/tennessee_public_data_centers.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5ac92023e7b8402a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R9e0b0a95ff024360"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R232f2a6fcf5e4c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R5bed570c70b14e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="R0f13595a73b44b1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R4956a203b79249cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R784c14e5afad4fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R92bcb7a7a9d84a4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="Re46971f5cb76403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R1008d6c561ad4825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R5b1799a13da84214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="R62431bf89c8c4840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="Rd205eed25ecf45e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf732e16e46704712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R5cb4edc09a244fb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R5e31e578ccb04039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R1c0487e55c8549e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="Ree74a0fb191842f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="Raeaf0a7341894ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="Racbb828dc1f7499b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="Rb8265469b1914b08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R0e6bc051f87f481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="Rb9783db99aa04d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R8a4ad03fb1cd47f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rbd0d7233d545407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="R3e14e02811584a18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1007,7 +1007,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="MasterTable" displayName="MasterTable" ref="A1:BQ62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="MasterTable" displayName="MasterTable" ref="A1:BQ62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="69">
     <x:tableColumn id="1" name="facility_id"/>
     <x:tableColumn id="2" name="facility_name"/>
@@ -1049,35 +1049,35 @@
     <x:tableColumn id="38" name="source_confidence_class"/>
     <x:tableColumn id="39" name="verification_note"/>
     <x:tableColumn id="40" name="schema_version"/>
-    <x:tableColumn id="41" name="dataset_version"/>
-    <x:tableColumn id="42" name="dataset_version"/>
-    <x:tableColumn id="43" name="dataset_version"/>
-    <x:tableColumn id="44" name="dataset_version"/>
-    <x:tableColumn id="45" name="dataset_version"/>
-    <x:tableColumn id="46" name="dataset_version"/>
-    <x:tableColumn id="47" name="dataset_version"/>
-    <x:tableColumn id="48" name="dataset_version"/>
-    <x:tableColumn id="49" name="dataset_version"/>
-    <x:tableColumn id="50" name="dataset_version"/>
-    <x:tableColumn id="51" name="dataset_version"/>
-    <x:tableColumn id="52" name="dataset_version"/>
-    <x:tableColumn id="53" name="dataset_version"/>
-    <x:tableColumn id="54" name="dataset_version"/>
-    <x:tableColumn id="55" name="dataset_version"/>
-    <x:tableColumn id="56" name="dataset_version"/>
-    <x:tableColumn id="57" name="dataset_version"/>
-    <x:tableColumn id="58" name="dataset_version"/>
-    <x:tableColumn id="59" name="dataset_version"/>
-    <x:tableColumn id="60" name="dataset_version"/>
-    <x:tableColumn id="61" name="dataset_version"/>
-    <x:tableColumn id="62" name="dataset_version"/>
-    <x:tableColumn id="63" name="dataset_version"/>
-    <x:tableColumn id="64" name="dataset_version"/>
-    <x:tableColumn id="65" name="dataset_version"/>
-    <x:tableColumn id="66" name="dataset_version"/>
-    <x:tableColumn id="67" name="dataset_version"/>
-    <x:tableColumn id="68" name="dataset_version"/>
-    <x:tableColumn id="69" name="dataset_version"/>
+    <x:tableColumn id="41" name="phase1_feature_status"/>
+    <x:tableColumn id="42" name="nearest_neighbor_km"/>
+    <x:tableColumn id="43" name="cluster"/>
+    <x:tableColumn id="44" name="dist_transmission_any_km"/>
+    <x:tableColumn id="45" name="dist_transmission_100kv_km"/>
+    <x:tableColumn id="46" name="dist_transmission_230kv_km"/>
+    <x:tableColumn id="47" name="max_voltage_within_25km_kv"/>
+    <x:tableColumn id="48" name="transmission_owner_count_25km"/>
+    <x:tableColumn id="49" name="dist_major_road_km"/>
+    <x:tableColumn id="50" name="dist_interstate_km"/>
+    <x:tableColumn id="51" name="dist_surface_water_flowline_km"/>
+    <x:tableColumn id="52" name="named_flowlines_within_25km"/>
+    <x:tableColumn id="53" name="county_geoid"/>
+    <x:tableColumn id="54" name="county_name"/>
+    <x:tableColumn id="55" name="degree_institutions_50km"/>
+    <x:tableColumn id="56" name="cip11_completions_50km"/>
+    <x:tableColumn id="57" name="cip14_completions_50km"/>
+    <x:tableColumn id="58" name="degree_institutions_100km"/>
+    <x:tableColumn id="59" name="cip11_completions_100km"/>
+    <x:tableColumn id="60" name="cip14_completions_100km"/>
+    <x:tableColumn id="61" name="county_total_employment"/>
+    <x:tableColumn id="62" name="county_total_establishments"/>
+    <x:tableColumn id="63" name="county_total_employment_flag"/>
+    <x:tableColumn id="64" name="information_sector_employment"/>
+    <x:tableColumn id="65" name="information_sector_establishments"/>
+    <x:tableColumn id="66" name="information_sector_employment_flag"/>
+    <x:tableColumn id="67" name="professional_scientific_employment"/>
+    <x:tableColumn id="68" name="professional_scientific_establishments"/>
+    <x:tableColumn id="69" name="professional_scientific_employment_flag"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -21644,7 +21644,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re95a139c1903423d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc26811007a54dd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42507,7 +42507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dc61433c7f54361"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e8f7d618ce4d76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44549,7 +44549,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13159f9452744b72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d25c43b0a85430e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44729,7 +44729,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd5a0bfeaa8e4763"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a11a23e9dcc4dac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45105,7 +45105,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e4a0a7040164ae7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc738802101c448b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45290,7 +45290,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5364e476327c4262"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33cb1e09435e4ce0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47860,7 +47860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R666dc95281814e48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea7a800858b640b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TN/dataset/tennessee_public_data_centers.xlsx
+++ b/TN/dataset/tennessee_public_data_centers.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf732e16e46704712"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R5cb4edc09a244fb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R5e31e578ccb04039"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R1c0487e55c8549e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="Ree74a0fb191842f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="Raeaf0a7341894ac8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="Racbb828dc1f7499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="Rb8265469b1914b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R0e6bc051f87f481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="Rb9783db99aa04d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R8a4ad03fb1cd47f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rbd0d7233d545407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="R3e14e02811584a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R22ced22afa04408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R84377b1ec7ca48ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Rc02ad912dec3421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R22d80092e3f0456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="Raadf8416d1374666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R3db9656abf144276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R34b329f8b75147bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R070a6e16bf3c4c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R9e1a0d21524c415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R0b1481f32fd14c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R0a937ec845a1433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rb9041d75443f4a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="R6dbcda47173e43bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -108,7 +108,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -213,6 +213,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF153B5B"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -379,7 +384,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="230">
+  <x:cellXfs count="234">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -982,6 +987,14 @@
     <x:xf numFmtId="204" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1713,6 +1726,60 @@
       </x:c>
       <x:c r="D22" s="85"/>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="233" t="str">
+        <x:v>Phase 2 spatial domain and provenance</x:v>
+      </x:c>
+      <x:c r="B23" s="233" t="str"/>
+      <x:c r="C23" s="233" t="str"/>
+      <x:c r="D23" s="233" t="str"/>
+      <x:c r="E23" s="233" t="str"/>
+      <x:c r="F23" s="233" t="str"/>
+      <x:c r="G23" s="233" t="str"/>
+      <x:c r="H23" s="233" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>Method</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>5 km equal-area Tennessee grid; D1 removes NHD open water, PAD-US GAP 1–2 permanent protections, DFIRM explicit FLOODWAY polygons, and mean 3DEP slope &gt;=15°</x:v>
+      </x:c>
+      <x:c r="C24" t="str"/>
+      <x:c r="D24" t="str"/>
+      <x:c r="E24" t="str"/>
+      <x:c r="F24" t="str"/>
+      <x:c r="G24" t="str"/>
+      <x:c r="H24" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>Sources</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>USGS 3DEP ImageServer; USGS PAD-US; Tennessee DFIRM; USGS NHD; accessed 2026-09-11</x:v>
+      </x:c>
+      <x:c r="C25" t="str"/>
+      <x:c r="D25" t="str"/>
+      <x:c r="E25" t="str"/>
+      <x:c r="F25" t="str"/>
+      <x:c r="G25" t="str"/>
+      <x:c r="H25" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>Model copy</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>model/phase 2/dataset/phase2_model_dataset.xlsx is the only model data copy; Master and Candidate_Sites are authoritative.</x:v>
+      </x:c>
+      <x:c r="C26" t="str"/>
+      <x:c r="D26" t="str"/>
+      <x:c r="E26" t="str"/>
+      <x:c r="F26" t="str"/>
+      <x:c r="G26" t="str"/>
+      <x:c r="H26" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
@@ -9342,6 +9409,54 @@
       <x:c r="BQ1" s="212" t="str">
         <x:v>professional_scientific_employment_flag</x:v>
       </x:c>
+      <x:c r="BR1" s="233" t="str">
+        <x:v>phase2_site_id</x:v>
+      </x:c>
+      <x:c r="BS1" s="233" t="str">
+        <x:v>phase2_domain_cell_id</x:v>
+      </x:c>
+      <x:c r="BT1" s="233" t="str">
+        <x:v>phase2_d1_feasible</x:v>
+      </x:c>
+      <x:c r="BU1" s="233" t="str">
+        <x:v>phase2_d1_exclusion_reason</x:v>
+      </x:c>
+      <x:c r="BV1" s="233" t="str">
+        <x:v>phase2_open_water_flag</x:v>
+      </x:c>
+      <x:c r="BW1" s="233" t="str">
+        <x:v>phase2_protected_land_flag</x:v>
+      </x:c>
+      <x:c r="BX1" s="233" t="str">
+        <x:v>phase2_regulatory_floodway_flag</x:v>
+      </x:c>
+      <x:c r="BY1" s="233" t="str">
+        <x:v>phase2_mean_slope_deg</x:v>
+      </x:c>
+      <x:c r="BZ1" s="233" t="str">
+        <x:v>phase2_urban_context</x:v>
+      </x:c>
+      <x:c r="CA1" s="233" t="str">
+        <x:v>phase2_developed_context</x:v>
+      </x:c>
+      <x:c r="CB1" s="233" t="str">
+        <x:v>phase2_grand_region</x:v>
+      </x:c>
+      <x:c r="CC1" s="233" t="str">
+        <x:v>phase2_primary_weight</x:v>
+      </x:c>
+      <x:c r="CD1" s="233" t="str">
+        <x:v>phase2_weighted_weight</x:v>
+      </x:c>
+      <x:c r="CE1" s="233" t="str">
+        <x:v>phase2_strict_weight</x:v>
+      </x:c>
+      <x:c r="CF1" s="233" t="str">
+        <x:v>phase2_feature_status</x:v>
+      </x:c>
+      <x:c r="CG1" s="233" t="str">
+        <x:v>phase2_evidence_urls</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" hidden="0" customHeight="1">
       <x:c r="A2" s="13" t="str">
@@ -9543,6 +9658,54 @@
       <x:c r="BQ2" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR2" t="str">
+        <x:v>TNDC-001</x:v>
+      </x:c>
+      <x:c r="BS2" t="str">
+        <x:v>TN5K-1967</x:v>
+      </x:c>
+      <x:c r="BT2" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU2" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV2" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW2" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX2" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY2" t="str">
+        <x:v>0.8639828794532352</x:v>
+      </x:c>
+      <x:c r="BZ2" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA2" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB2" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC2" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD2" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE2" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF2" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG2" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="30" hidden="0" customHeight="1">
       <x:c r="A3" s="16" t="str">
@@ -9742,6 +9905,54 @@
       <x:c r="BQ3" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR3" t="str">
+        <x:v>TNDC-002</x:v>
+      </x:c>
+      <x:c r="BS3" t="str">
+        <x:v>TN5K-3013</x:v>
+      </x:c>
+      <x:c r="BT3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU3" t="str">
+        <x:v>open_water</x:v>
+      </x:c>
+      <x:c r="BV3" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY3" t="str">
+        <x:v>1.1295460379785962</x:v>
+      </x:c>
+      <x:c r="BZ3" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA3" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB3" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC3" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD3" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE3" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF3" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG3" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="30" hidden="0" customHeight="1">
       <x:c r="A4" s="16" t="str">
@@ -9943,6 +10154,54 @@
       <x:c r="BQ4" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR4" t="str">
+        <x:v>TNDC-003</x:v>
+      </x:c>
+      <x:c r="BS4" t="str">
+        <x:v>TN5K-3027</x:v>
+      </x:c>
+      <x:c r="BT4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU4" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX4" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY4" t="str">
+        <x:v>1.355089758005407</x:v>
+      </x:c>
+      <x:c r="BZ4" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA4" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB4" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC4" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD4" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE4" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF4" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG4" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" hidden="0" customHeight="1">
       <x:c r="A5" s="16" t="str">
@@ -10144,6 +10403,54 @@
       <x:c r="BQ5" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR5" t="str">
+        <x:v>TNDC-004</x:v>
+      </x:c>
+      <x:c r="BS5" t="str">
+        <x:v>TN5K-3028</x:v>
+      </x:c>
+      <x:c r="BT5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU5" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW5" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX5" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY5" t="str">
+        <x:v>1.0866958482397928</x:v>
+      </x:c>
+      <x:c r="BZ5" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA5" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB5" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC5" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD5" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE5" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF5" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG5" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="30" hidden="0" customHeight="1">
       <x:c r="A6" s="16" t="str">
@@ -10343,6 +10650,54 @@
       <x:c r="BQ6" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR6" t="str">
+        <x:v>TNDC-005</x:v>
+      </x:c>
+      <x:c r="BS6" t="str">
+        <x:v>TN5K-3028</x:v>
+      </x:c>
+      <x:c r="BT6" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU6" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV6" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY6" t="str">
+        <x:v>1.0866958482397928</x:v>
+      </x:c>
+      <x:c r="BZ6" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA6" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB6" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF6" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG6" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="30" hidden="0" customHeight="1">
       <x:c r="A7" s="16" t="str">
@@ -10543,6 +10898,54 @@
       </x:c>
       <x:c r="BQ7" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR7" t="str">
+        <x:v>TNDC-006</x:v>
+      </x:c>
+      <x:c r="BS7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BT7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BU7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BV7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BW7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BX7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BY7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BZ7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CA7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CB7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CC7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CD7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CE7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CF7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="CG7" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" hidden="0" customHeight="1">
@@ -10747,6 +11150,54 @@
       <x:c r="BQ8" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR8" t="str">
+        <x:v>TNDC-007</x:v>
+      </x:c>
+      <x:c r="BS8" t="str">
+        <x:v>TN5K-1608</x:v>
+      </x:c>
+      <x:c r="BT8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU8" t="str">
+        <x:v>open_water</x:v>
+      </x:c>
+      <x:c r="BV8" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY8" t="str">
+        <x:v>0.43263573985960746</x:v>
+      </x:c>
+      <x:c r="BZ8" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA8" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB8" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC8" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD8" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE8" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF8" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG8" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="30" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -10949,6 +11400,54 @@
       </x:c>
       <x:c r="BQ9" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR9" t="str">
+        <x:v>TNDC-008</x:v>
+      </x:c>
+      <x:c r="BS9" t="str">
+        <x:v>TN5K-0168</x:v>
+      </x:c>
+      <x:c r="BT9" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU9" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV9" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW9" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX9" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY9" t="str">
+        <x:v>0.3893086314201355</x:v>
+      </x:c>
+      <x:c r="BZ9" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA9" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB9" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC9" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD9" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE9" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF9" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG9" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" hidden="0" customHeight="1">
@@ -11149,6 +11648,54 @@
       <x:c r="BQ10" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR10" t="str">
+        <x:v>TNDC-009</x:v>
+      </x:c>
+      <x:c r="BS10" t="str">
+        <x:v>TN5K-3122</x:v>
+      </x:c>
+      <x:c r="BT10" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU10" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV10" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW10" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX10" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY10" t="str">
+        <x:v>0.5407882365915511</x:v>
+      </x:c>
+      <x:c r="BZ10" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA10" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB10" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC10" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD10" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE10" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF10" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG10" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="30" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
@@ -11344,6 +11891,54 @@
       <x:c r="BQ11" s="209" t="str">
         <x:v>NO_PUBLISHED_ROW</x:v>
       </x:c>
+      <x:c r="BR11" t="str">
+        <x:v>TNDC-010</x:v>
+      </x:c>
+      <x:c r="BS11" t="str">
+        <x:v>TN5K-3336</x:v>
+      </x:c>
+      <x:c r="BT11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU11" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX11" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY11" t="str">
+        <x:v>1.7219926979806688</x:v>
+      </x:c>
+      <x:c r="BZ11" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA11" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB11" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC11" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD11" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE11" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF11" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG11" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="30" hidden="0" customHeight="1">
       <x:c r="A12" s="16" t="str">
@@ -11545,6 +12140,54 @@
       <x:c r="BQ12" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR12" t="str">
+        <x:v>TNDC-011</x:v>
+      </x:c>
+      <x:c r="BS12" t="str">
+        <x:v>TN5K-1928</x:v>
+      </x:c>
+      <x:c r="BT12" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU12" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV12" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW12" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX12" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY12" t="str">
+        <x:v>1.095819354057312</x:v>
+      </x:c>
+      <x:c r="BZ12" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA12" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB12" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC12" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD12" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE12" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF12" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG12" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="30" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
@@ -11746,6 +12389,54 @@
       <x:c r="BQ13" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR13" t="str">
+        <x:v>TNDC-012</x:v>
+      </x:c>
+      <x:c r="BS13" t="str">
+        <x:v>TN5K-1965</x:v>
+      </x:c>
+      <x:c r="BT13" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU13" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV13" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW13" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX13" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY13" t="str">
+        <x:v>0.6818343566523658</x:v>
+      </x:c>
+      <x:c r="BZ13" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA13" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB13" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC13" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD13" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE13" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF13" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG13" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="30" hidden="0" customHeight="1">
       <x:c r="A14" s="16" t="str">
@@ -11950,6 +12641,54 @@
       </x:c>
       <x:c r="BQ14" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR14" t="str">
+        <x:v>TNDC-013</x:v>
+      </x:c>
+      <x:c r="BS14" t="str">
+        <x:v>TN5K-1927</x:v>
+      </x:c>
+      <x:c r="BT14" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU14" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV14" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW14" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX14" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY14" t="str">
+        <x:v>0.6528879470295377</x:v>
+      </x:c>
+      <x:c r="BZ14" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA14" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB14" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC14" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD14" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE14" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF14" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG14" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" hidden="0" customHeight="1">
@@ -12154,6 +12893,54 @@
       <x:c r="BQ15" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR15" t="str">
+        <x:v>TNDC-014</x:v>
+      </x:c>
+      <x:c r="BS15" t="str">
+        <x:v>TN5K-2199</x:v>
+      </x:c>
+      <x:c r="BT15" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU15" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV15" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW15" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX15" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY15" t="str">
+        <x:v>0.827479319439994</x:v>
+      </x:c>
+      <x:c r="BZ15" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA15" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB15" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC15" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD15" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE15" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF15" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG15" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="30" hidden="0" customHeight="1">
       <x:c r="A16" s="16" t="str">
@@ -12360,6 +13147,54 @@
       </x:c>
       <x:c r="BQ16" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR16" t="str">
+        <x:v>TNDC-015</x:v>
+      </x:c>
+      <x:c r="BS16" t="str">
+        <x:v>TN5K-2199</x:v>
+      </x:c>
+      <x:c r="BT16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU16" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX16" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY16" t="str">
+        <x:v>0.827479319439994</x:v>
+      </x:c>
+      <x:c r="BZ16" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA16" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB16" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC16" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD16" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE16" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF16" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG16" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" hidden="0" customHeight="1">
@@ -12562,6 +13397,54 @@
       <x:c r="BQ17" s="209" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="BR17" t="str">
+        <x:v>TNDC-016</x:v>
+      </x:c>
+      <x:c r="BS17" t="str">
+        <x:v>TN5K-3658</x:v>
+      </x:c>
+      <x:c r="BT17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU17" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV17" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX17" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY17" t="str">
+        <x:v>4.209807568126255</x:v>
+      </x:c>
+      <x:c r="BZ17" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA17" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB17" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC17" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD17" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE17" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF17" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG17" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="30" hidden="0" customHeight="1">
       <x:c r="A18" s="16" t="str">
@@ -12762,6 +13645,54 @@
       </x:c>
       <x:c r="BQ18" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR18" t="str">
+        <x:v>TNDC-017</x:v>
+      </x:c>
+      <x:c r="BS18" t="str">
+        <x:v>TN5K-3861</x:v>
+      </x:c>
+      <x:c r="BT18" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU18" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV18" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW18" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX18" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY18" t="str">
+        <x:v>1.1271323694123163</x:v>
+      </x:c>
+      <x:c r="BZ18" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA18" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB18" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC18" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD18" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE18" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF18" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG18" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" hidden="0" customHeight="1">
@@ -12962,6 +13893,54 @@
       <x:c r="BQ19" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR19" t="str">
+        <x:v>TNDC-018</x:v>
+      </x:c>
+      <x:c r="BS19" t="str">
+        <x:v>TN5K-3835</x:v>
+      </x:c>
+      <x:c r="BT19" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU19" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV19" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW19" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX19" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY19" t="str">
+        <x:v>1.6440967056486342</x:v>
+      </x:c>
+      <x:c r="BZ19" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA19" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB19" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF19" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG19" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="30" hidden="0" customHeight="1">
       <x:c r="A20" s="16" t="str">
@@ -13162,6 +14141,54 @@
       </x:c>
       <x:c r="BQ20" s="209" t="str">
         <x:v>H</x:v>
+      </x:c>
+      <x:c r="BR20" t="str">
+        <x:v>TNDC-019</x:v>
+      </x:c>
+      <x:c r="BS20" t="str">
+        <x:v>TN5K-3641</x:v>
+      </x:c>
+      <x:c r="BT20" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU20" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV20" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW20" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX20" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY20" t="str">
+        <x:v>1.2509022156397502</x:v>
+      </x:c>
+      <x:c r="BZ20" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA20" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB20" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC20" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD20" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE20" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF20" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG20" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" hidden="0" customHeight="1">
@@ -13358,6 +14385,54 @@
       <x:c r="BQ21" s="209" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="BR21" t="str">
+        <x:v>TNDC-020</x:v>
+      </x:c>
+      <x:c r="BS21" t="str">
+        <x:v>TN5K-4312</x:v>
+      </x:c>
+      <x:c r="BT21" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU21" t="str">
+        <x:v>protected_land</x:v>
+      </x:c>
+      <x:c r="BV21" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW21" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX21" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY21" t="str">
+        <x:v>0.6789027286900414</x:v>
+      </x:c>
+      <x:c r="BZ21" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA21" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB21" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC21" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD21" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE21" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF21" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG21" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="30" hidden="0" customHeight="1">
       <x:c r="A22" s="16" t="str">
@@ -13554,6 +14629,54 @@
       </x:c>
       <x:c r="BQ22" s="209" t="str">
         <x:v>H</x:v>
+      </x:c>
+      <x:c r="BR22" t="str">
+        <x:v>TNDC-021</x:v>
+      </x:c>
+      <x:c r="BS22" t="str">
+        <x:v>TN5K-2477</x:v>
+      </x:c>
+      <x:c r="BT22" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU22" t="str">
+        <x:v>open_water</x:v>
+      </x:c>
+      <x:c r="BV22" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW22" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX22" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY22" t="str">
+        <x:v>0.2577753828631507</x:v>
+      </x:c>
+      <x:c r="BZ22" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA22" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB22" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC22" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD22" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE22" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF22" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG22" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" hidden="0" customHeight="1">
@@ -13750,6 +14873,54 @@
       <x:c r="BQ23" s="209" t="str">
         <x:v>J</x:v>
       </x:c>
+      <x:c r="BR23" t="str">
+        <x:v>TNDC-022</x:v>
+      </x:c>
+      <x:c r="BS23" t="str">
+        <x:v>TN5K-3868</x:v>
+      </x:c>
+      <x:c r="BT23" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU23" t="str">
+        <x:v>open_water</x:v>
+      </x:c>
+      <x:c r="BV23" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW23" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX23" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY23" t="str">
+        <x:v>2.9245584275987415</x:v>
+      </x:c>
+      <x:c r="BZ23" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA23" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB23" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC23" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD23" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE23" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF23" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG23" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="30" hidden="0" customHeight="1">
       <x:c r="A24" s="16" t="str">
@@ -13954,6 +15125,52 @@
       </x:c>
       <x:c r="BQ24" s="209" t="str">
         <x:v>H</x:v>
+      </x:c>
+      <x:c r="BR24" t="str">
+        <x:v>TNDC-023</x:v>
+      </x:c>
+      <x:c r="BS24" t="str">
+        <x:v>TN5K-2596</x:v>
+      </x:c>
+      <x:c r="BT24" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BU24" t="str"/>
+      <x:c r="BV24" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW24" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX24" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY24" t="str">
+        <x:v>0.6942308247089386</x:v>
+      </x:c>
+      <x:c r="BZ24" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA24" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB24" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC24" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD24" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE24" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF24" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG24" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="30" hidden="0" customHeight="1">
@@ -14154,6 +15371,54 @@
       <x:c r="BQ25" s="209" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="BR25" t="str">
+        <x:v>TNDC-024</x:v>
+      </x:c>
+      <x:c r="BS25" t="str">
+        <x:v>TN5K-2669</x:v>
+      </x:c>
+      <x:c r="BT25" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU25" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV25" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW25" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX25" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY25" t="str">
+        <x:v>0.9771514700518714</x:v>
+      </x:c>
+      <x:c r="BZ25" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA25" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB25" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC25" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD25" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE25" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF25" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG25" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="30" hidden="0" customHeight="1">
       <x:c r="A26" s="16" t="str">
@@ -14355,6 +15620,54 @@
       <x:c r="BQ26" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR26" t="str">
+        <x:v>TNDC-026</x:v>
+      </x:c>
+      <x:c r="BS26" t="str">
+        <x:v>TN5K-0096</x:v>
+      </x:c>
+      <x:c r="BT26" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU26" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV26" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW26" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX26" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY26" t="str">
+        <x:v>0.3144090523322423</x:v>
+      </x:c>
+      <x:c r="BZ26" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA26" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB26" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC26" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD26" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE26" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF26" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG26" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="30" hidden="0" customHeight="1">
       <x:c r="A27" s="16" t="str">
@@ -14554,6 +15867,54 @@
       <x:c r="BQ27" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR27" t="str">
+        <x:v>TNDC-027</x:v>
+      </x:c>
+      <x:c r="BS27" t="str">
+        <x:v>TN5K-0074</x:v>
+      </x:c>
+      <x:c r="BT27" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU27" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV27" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW27" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX27" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY27" t="str">
+        <x:v>0.3746739998459816</x:v>
+      </x:c>
+      <x:c r="BZ27" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA27" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB27" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC27" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD27" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE27" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF27" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG27" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="30" hidden="0" customHeight="1">
       <x:c r="A28" s="16" t="str">
@@ -14758,6 +16119,54 @@
       </x:c>
       <x:c r="BQ28" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR28" t="str">
+        <x:v>TNDC-028</x:v>
+      </x:c>
+      <x:c r="BS28" t="str">
+        <x:v>TN5K-0113</x:v>
+      </x:c>
+      <x:c r="BT28" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU28" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV28" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW28" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX28" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY28" t="str">
+        <x:v>0.3547260786096255</x:v>
+      </x:c>
+      <x:c r="BZ28" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA28" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB28" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC28" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD28" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE28" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF28" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG28" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" hidden="0" customHeight="1">
@@ -14958,6 +16367,54 @@
       <x:c r="BQ29" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR29" t="str">
+        <x:v>TNDC-029</x:v>
+      </x:c>
+      <x:c r="BS29" t="str">
+        <x:v>TN5K-0057</x:v>
+      </x:c>
+      <x:c r="BT29" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU29" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV29" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW29" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX29" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY29" t="str">
+        <x:v>0.3518414778841866</x:v>
+      </x:c>
+      <x:c r="BZ29" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA29" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB29" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC29" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD29" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE29" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF29" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG29" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="30" hidden="0" customHeight="1">
       <x:c r="A30" s="16" t="str">
@@ -15159,6 +16616,54 @@
       <x:c r="BQ30" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR30" t="str">
+        <x:v>TNDC-030</x:v>
+      </x:c>
+      <x:c r="BS30" t="str">
+        <x:v>TN5K-0007</x:v>
+      </x:c>
+      <x:c r="BT30" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU30" t="str">
+        <x:v>open_water;protected_land</x:v>
+      </x:c>
+      <x:c r="BV30" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW30" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX30" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY30" t="str">
+        <x:v>0.13380941024257076</x:v>
+      </x:c>
+      <x:c r="BZ30" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA30" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB30" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC30" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD30" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE30" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF30" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG30" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="30" hidden="0" customHeight="1">
       <x:c r="A31" s="16" t="str">
@@ -15363,6 +16868,34 @@
       </x:c>
       <x:c r="BQ31" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR31" t="str">
+        <x:v>TNDC-031</x:v>
+      </x:c>
+      <x:c r="BS31" t="str"/>
+      <x:c r="BT31" t="str"/>
+      <x:c r="BU31" t="str"/>
+      <x:c r="BV31" t="str"/>
+      <x:c r="BW31" t="str"/>
+      <x:c r="BX31" t="str"/>
+      <x:c r="BY31" t="str"/>
+      <x:c r="BZ31" t="str"/>
+      <x:c r="CA31" t="str"/>
+      <x:c r="CB31" t="str"/>
+      <x:c r="CC31" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD31" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE31" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF31" t="str">
+        <x:v>not_mappable</x:v>
+      </x:c>
+      <x:c r="CG31" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="30" hidden="0" customHeight="1">
@@ -15566,6 +17099,54 @@
       </x:c>
       <x:c r="BQ32" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR32" t="str">
+        <x:v>TNDC-032</x:v>
+      </x:c>
+      <x:c r="BS32" t="str">
+        <x:v>TN5K-1969</x:v>
+      </x:c>
+      <x:c r="BT32" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU32" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV32" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW32" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX32" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY32" t="str">
+        <x:v>1.356198446618186</x:v>
+      </x:c>
+      <x:c r="BZ32" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA32" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB32" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC32" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD32" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE32" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF32" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG32" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="30" hidden="0" customHeight="1">
@@ -15766,6 +17347,54 @@
       <x:c r="BQ33" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR33" t="str">
+        <x:v>TNDC-033</x:v>
+      </x:c>
+      <x:c r="BS33" t="str">
+        <x:v>TN5K-2008</x:v>
+      </x:c>
+      <x:c r="BT33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU33" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY33" t="str">
+        <x:v>0.9650822447405921</x:v>
+      </x:c>
+      <x:c r="BZ33" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA33" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB33" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC33" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD33" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE33" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF33" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG33" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="30" hidden="0" customHeight="1">
       <x:c r="A34" s="16" t="str">
@@ -15968,6 +17597,54 @@
       </x:c>
       <x:c r="BQ34" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR34" t="str">
+        <x:v>TNDC-034</x:v>
+      </x:c>
+      <x:c r="BS34" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="BT34" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU34" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV34" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW34" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX34" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY34" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BZ34" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA34" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB34" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC34" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD34" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE34" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF34" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG34" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="30" hidden="0" customHeight="1">
@@ -16170,6 +17847,54 @@
       <x:c r="BQ35" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR35" t="str">
+        <x:v>TNDC-035</x:v>
+      </x:c>
+      <x:c r="BS35" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="BT35" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU35" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV35" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW35" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX35" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY35" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BZ35" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA35" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB35" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC35" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD35" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE35" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF35" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG35" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="30" hidden="0" customHeight="1">
       <x:c r="A36" s="16" t="str">
@@ -16369,6 +18094,54 @@
       <x:c r="BQ36" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR36" t="str">
+        <x:v>TNDC-036</x:v>
+      </x:c>
+      <x:c r="BS36" t="str">
+        <x:v>TN5K-1933</x:v>
+      </x:c>
+      <x:c r="BT36" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU36" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV36" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW36" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX36" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY36" t="str">
+        <x:v>1.0332035091188219</x:v>
+      </x:c>
+      <x:c r="BZ36" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA36" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB36" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC36" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD36" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE36" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF36" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG36" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="30" hidden="0" customHeight="1">
       <x:c r="A37" s="16" t="str">
@@ -16568,6 +18341,54 @@
       <x:c r="BQ37" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR37" t="str">
+        <x:v>TNDC-037</x:v>
+      </x:c>
+      <x:c r="BS37" t="str">
+        <x:v>TN5K-1970</x:v>
+      </x:c>
+      <x:c r="BT37" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU37" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV37" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW37" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX37" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY37" t="str">
+        <x:v>0.9010956386725107</x:v>
+      </x:c>
+      <x:c r="BZ37" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA37" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB37" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC37" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD37" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE37" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF37" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG37" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="30" hidden="0" customHeight="1">
       <x:c r="A38" s="16" t="str">
@@ -16767,6 +18588,54 @@
       <x:c r="BQ38" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR38" t="str">
+        <x:v>TNDC-038</x:v>
+      </x:c>
+      <x:c r="BS38" t="str">
+        <x:v>TN5K-2044</x:v>
+      </x:c>
+      <x:c r="BT38" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU38" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV38" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW38" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX38" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY38" t="str">
+        <x:v>1.0770922071403928</x:v>
+      </x:c>
+      <x:c r="BZ38" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA38" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB38" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC38" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD38" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE38" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF38" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG38" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="30" hidden="0" customHeight="1">
       <x:c r="A39" s="16" t="str">
@@ -16969,6 +18838,54 @@
       </x:c>
       <x:c r="BQ39" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR39" t="str">
+        <x:v>TNDC-039</x:v>
+      </x:c>
+      <x:c r="BS39" t="str">
+        <x:v>TN5K-1933</x:v>
+      </x:c>
+      <x:c r="BT39" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU39" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV39" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW39" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX39" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY39" t="str">
+        <x:v>1.0332035091188219</x:v>
+      </x:c>
+      <x:c r="BZ39" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA39" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB39" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC39" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD39" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE39" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF39" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG39" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="30" hidden="0" customHeight="1">
@@ -17170,6 +19087,54 @@
       </x:c>
       <x:c r="BQ40" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR40" t="str">
+        <x:v>TNDC-040</x:v>
+      </x:c>
+      <x:c r="BS40" t="str">
+        <x:v>TN5K-1935</x:v>
+      </x:c>
+      <x:c r="BT40" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU40" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV40" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW40" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX40" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY40" t="str">
+        <x:v>2.057216021749708</x:v>
+      </x:c>
+      <x:c r="BZ40" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA40" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB40" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC40" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD40" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE40" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF40" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG40" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="30" hidden="0" customHeight="1">
@@ -17370,6 +19335,54 @@
       <x:c r="BQ41" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR41" t="str">
+        <x:v>TNDC-041</x:v>
+      </x:c>
+      <x:c r="BS41" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="BT41" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU41" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV41" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW41" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX41" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY41" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BZ41" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA41" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB41" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC41" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD41" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE41" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF41" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG41" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="30" hidden="0" customHeight="1">
       <x:c r="A42" s="16" t="str">
@@ -17569,6 +19582,54 @@
       <x:c r="BQ42" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR42" t="str">
+        <x:v>TNDC-042</x:v>
+      </x:c>
+      <x:c r="BS42" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="BT42" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU42" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV42" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW42" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX42" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY42" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BZ42" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA42" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB42" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC42" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD42" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE42" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF42" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG42" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="30" hidden="0" customHeight="1">
       <x:c r="A43" s="16" t="str">
@@ -17769,6 +19830,52 @@
       </x:c>
       <x:c r="BQ43" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR43" t="str">
+        <x:v>TNDC-043</x:v>
+      </x:c>
+      <x:c r="BS43" t="str">
+        <x:v>TN5K-3947</x:v>
+      </x:c>
+      <x:c r="BT43" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BU43" t="str"/>
+      <x:c r="BV43" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW43" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX43" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY43" t="str">
+        <x:v>1.518314156267378</x:v>
+      </x:c>
+      <x:c r="BZ43" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA43" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB43" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC43" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD43" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE43" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF43" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG43" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="30" hidden="0" customHeight="1">
@@ -17965,6 +20072,54 @@
       <x:c r="BQ44" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR44" t="str">
+        <x:v>TNDC-044</x:v>
+      </x:c>
+      <x:c r="BS44" t="str">
+        <x:v>TN5K-3433</x:v>
+      </x:c>
+      <x:c r="BT44" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU44" t="str">
+        <x:v>open_water</x:v>
+      </x:c>
+      <x:c r="BV44" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW44" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX44" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY44" t="str">
+        <x:v>1.476711803012424</x:v>
+      </x:c>
+      <x:c r="BZ44" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA44" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB44" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC44" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD44" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE44" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF44" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG44" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="30" hidden="0" customHeight="1">
       <x:c r="A45" s="16" t="str">
@@ -18164,6 +20319,52 @@
       <x:c r="BQ45" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR45" t="str">
+        <x:v>TNDC-045</x:v>
+      </x:c>
+      <x:c r="BS45" t="str">
+        <x:v>TN5K-3471</x:v>
+      </x:c>
+      <x:c r="BT45" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BU45" t="str"/>
+      <x:c r="BV45" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW45" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX45" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY45" t="str">
+        <x:v>2.650047527419196</x:v>
+      </x:c>
+      <x:c r="BZ45" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA45" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB45" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC45" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD45" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE45" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF45" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG45" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="30" hidden="0" customHeight="1">
       <x:c r="A46" s="19" t="str">
@@ -18363,6 +20564,54 @@
       <x:c r="BQ46" s="209" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="BR46" t="str">
+        <x:v>TNDC-046</x:v>
+      </x:c>
+      <x:c r="BS46" t="str">
+        <x:v>TN5K-3642</x:v>
+      </x:c>
+      <x:c r="BT46" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU46" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV46" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW46" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX46" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY46" t="str">
+        <x:v>1.407417549027337</x:v>
+      </x:c>
+      <x:c r="BZ46" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA46" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB46" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC46" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD46" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE46" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF46" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG46" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
@@ -18563,6 +20812,54 @@
       </x:c>
       <x:c r="BQ47" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR47" t="str">
+        <x:v>TNDC-047</x:v>
+      </x:c>
+      <x:c r="BS47" t="str">
+        <x:v>TN5K-3835</x:v>
+      </x:c>
+      <x:c r="BT47" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU47" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV47" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW47" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX47" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY47" t="str">
+        <x:v>1.6440967056486342</x:v>
+      </x:c>
+      <x:c r="BZ47" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA47" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB47" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC47" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD47" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE47" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF47" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG47" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -18763,6 +21060,54 @@
       <x:c r="BQ48" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR48" t="str">
+        <x:v>TNDC-048</x:v>
+      </x:c>
+      <x:c r="BS48" t="str">
+        <x:v>TN5K-3714</x:v>
+      </x:c>
+      <x:c r="BT48" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU48" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV48" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW48" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX48" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY48" t="str">
+        <x:v>1.3213139159811869</x:v>
+      </x:c>
+      <x:c r="BZ48" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA48" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB48" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC48" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD48" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE48" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF48" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG48" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
@@ -18962,6 +21307,54 @@
       <x:c r="BQ49" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR49" t="str">
+        <x:v>TNDC-049</x:v>
+      </x:c>
+      <x:c r="BS49" t="str">
+        <x:v>TN5K-3713</x:v>
+      </x:c>
+      <x:c r="BT49" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU49" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV49" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW49" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX49" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY49" t="str">
+        <x:v>1.4333170387479994</x:v>
+      </x:c>
+      <x:c r="BZ49" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA49" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB49" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC49" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD49" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE49" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF49" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG49" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -19161,6 +21554,54 @@
       <x:c r="BQ50" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR50" t="str">
+        <x:v>TNDC-050</x:v>
+      </x:c>
+      <x:c r="BS50" t="str">
+        <x:v>TN5K-0658</x:v>
+      </x:c>
+      <x:c r="BT50" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU50" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV50" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW50" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX50" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY50" t="str">
+        <x:v>0.6738849745856391</x:v>
+      </x:c>
+      <x:c r="BZ50" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA50" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB50" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC50" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD50" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE50" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF50" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG50" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -19364,6 +21805,54 @@
       <x:c r="BQ51" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR51" t="str">
+        <x:v>TNDC-051</x:v>
+      </x:c>
+      <x:c r="BS51" t="str">
+        <x:v>TN5K-3103</x:v>
+      </x:c>
+      <x:c r="BT51" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU51" t="str">
+        <x:v>open_water;protected_land</x:v>
+      </x:c>
+      <x:c r="BV51" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW51" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX51" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BY51" t="str">
+        <x:v>1.1300574723217223</x:v>
+      </x:c>
+      <x:c r="BZ51" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA51" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB51" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC51" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD51" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE51" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF51" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG51" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
@@ -19567,6 +22056,54 @@
       <x:c r="BQ52" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR52" t="str">
+        <x:v>TNDC-052</x:v>
+      </x:c>
+      <x:c r="BS52" t="str">
+        <x:v>TN5K-2224</x:v>
+      </x:c>
+      <x:c r="BT52" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU52" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV52" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW52" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX52" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY52" t="str">
+        <x:v>0.23121336433622572</x:v>
+      </x:c>
+      <x:c r="BZ52" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA52" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB52" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC52" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD52" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE52" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF52" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG52" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
@@ -19768,6 +22305,54 @@
       <x:c r="BQ53" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR53" t="str">
+        <x:v>TNDC-053</x:v>
+      </x:c>
+      <x:c r="BS53" t="str">
+        <x:v>TN5K-1930</x:v>
+      </x:c>
+      <x:c r="BT53" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU53" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV53" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW53" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX53" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY53" t="str">
+        <x:v>2.160529683033625</x:v>
+      </x:c>
+      <x:c r="BZ53" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA53" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB53" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC53" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD53" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE53" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF53" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG53" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
@@ -19969,6 +22554,54 @@
       <x:c r="BQ54" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR54" t="str">
+        <x:v>TNDC-054</x:v>
+      </x:c>
+      <x:c r="BS54" t="str">
+        <x:v>TN5K-2008</x:v>
+      </x:c>
+      <x:c r="BT54" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU54" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV54" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW54" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX54" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY54" t="str">
+        <x:v>0.9650822447405921</x:v>
+      </x:c>
+      <x:c r="BZ54" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA54" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB54" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC54" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD54" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE54" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF54" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG54" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
@@ -20170,6 +22803,54 @@
       <x:c r="BQ55" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR55" t="str">
+        <x:v>TNDC-055</x:v>
+      </x:c>
+      <x:c r="BS55" t="str">
+        <x:v>TN5K-1970</x:v>
+      </x:c>
+      <x:c r="BT55" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU55" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV55" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW55" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX55" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY55" t="str">
+        <x:v>0.9010956386725107</x:v>
+      </x:c>
+      <x:c r="BZ55" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA55" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB55" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC55" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD55" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE55" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF55" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG55" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
@@ -20372,6 +23053,54 @@
       </x:c>
       <x:c r="BQ56" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR56" t="str">
+        <x:v>TNDC-056</x:v>
+      </x:c>
+      <x:c r="BS56" t="str">
+        <x:v>TN5K-1970</x:v>
+      </x:c>
+      <x:c r="BT56" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU56" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV56" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW56" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX56" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY56" t="str">
+        <x:v>0.9010956386725107</x:v>
+      </x:c>
+      <x:c r="BZ56" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA56" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB56" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CC56" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD56" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE56" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF56" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG56" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -20572,6 +23301,54 @@
       <x:c r="BQ57" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR57" t="str">
+        <x:v>TNDC-057</x:v>
+      </x:c>
+      <x:c r="BS57" t="str">
+        <x:v>TN5K-0076</x:v>
+      </x:c>
+      <x:c r="BT57" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU57" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV57" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW57" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX57" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY57" t="str">
+        <x:v>0.37594464669624966</x:v>
+      </x:c>
+      <x:c r="BZ57" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA57" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB57" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC57" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD57" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE57" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF57" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG57" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
@@ -20773,6 +23550,54 @@
       <x:c r="BQ58" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR58" t="str">
+        <x:v>TNDC-058</x:v>
+      </x:c>
+      <x:c r="BS58" t="str">
+        <x:v>TN5K-0074</x:v>
+      </x:c>
+      <x:c r="BT58" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU58" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV58" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW58" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX58" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY58" t="str">
+        <x:v>0.3746739998459816</x:v>
+      </x:c>
+      <x:c r="BZ58" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA58" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB58" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC58" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD58" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE58" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF58" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG58" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
@@ -20975,6 +23800,54 @@
       </x:c>
       <x:c r="BQ59" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR59" t="str">
+        <x:v>TNDC-059</x:v>
+      </x:c>
+      <x:c r="BS59" t="str">
+        <x:v>TN5K-0057</x:v>
+      </x:c>
+      <x:c r="BT59" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU59" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV59" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW59" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX59" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY59" t="str">
+        <x:v>0.3518414778841866</x:v>
+      </x:c>
+      <x:c r="BZ59" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA59" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB59" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC59" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD59" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE59" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF59" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG59" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -21179,6 +24052,54 @@
       <x:c r="BQ60" s="209" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="BR60" t="str">
+        <x:v>TNDC-060</x:v>
+      </x:c>
+      <x:c r="BS60" t="str">
+        <x:v>TN5K-0077</x:v>
+      </x:c>
+      <x:c r="BT60" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU60" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV60" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW60" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX60" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY60" t="str">
+        <x:v>0.2519831077920066</x:v>
+      </x:c>
+      <x:c r="BZ60" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CA60" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CB60" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC60" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD60" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE60" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF60" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG60" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
@@ -21380,6 +24301,54 @@
       <x:c r="BQ61" s="209" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="BR61" t="str">
+        <x:v>TNDC-061</x:v>
+      </x:c>
+      <x:c r="BS61" t="str">
+        <x:v>TN5K-0594</x:v>
+      </x:c>
+      <x:c r="BT61" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU61" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV61" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BW61" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BX61" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY61" t="str">
+        <x:v>0.30347856506705284</x:v>
+      </x:c>
+      <x:c r="BZ61" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA61" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB61" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CC61" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD61" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE61" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF61" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG61" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
@@ -21584,6 +24553,54 @@
       </x:c>
       <x:c r="BQ62" s="209" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="BR62" t="str">
+        <x:v>TNDC-062</x:v>
+      </x:c>
+      <x:c r="BS62" t="str">
+        <x:v>TN5K-4417</x:v>
+      </x:c>
+      <x:c r="BT62" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BU62" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BV62" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BW62" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BX62" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BY62" t="str">
+        <x:v>1.3089620272318523</x:v>
+      </x:c>
+      <x:c r="BZ62" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CA62" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CB62" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CC62" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CD62" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CE62" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CF62" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="CG62" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -21644,7 +24661,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc26811007a54dd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93c813e2fcf143ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42507,7 +45524,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3e8f7d618ce4d76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cd57382c1b4424f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44549,7 +47566,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d25c43b0a85430e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2f7eb29274f4c41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44729,7 +47746,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a11a23e9dcc4dac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R382e68194b2f4993"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45105,7 +48122,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc738802101c448b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb98e9fcef35f4beb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45290,7 +48307,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33cb1e09435e4ce0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R898d95e465624112"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45498,6 +48515,54 @@
       <x:c r="AW1" s="225" t="str">
         <x:v>professional_scientific_employment_flag</x:v>
       </x:c>
+      <x:c r="AX1" s="233" t="str">
+        <x:v>phase2_site_id</x:v>
+      </x:c>
+      <x:c r="AY1" s="233" t="str">
+        <x:v>phase2_domain_cell_id</x:v>
+      </x:c>
+      <x:c r="AZ1" s="233" t="str">
+        <x:v>phase2_d1_feasible</x:v>
+      </x:c>
+      <x:c r="BA1" s="233" t="str">
+        <x:v>phase2_d1_exclusion_reason</x:v>
+      </x:c>
+      <x:c r="BB1" s="233" t="str">
+        <x:v>phase2_open_water_flag</x:v>
+      </x:c>
+      <x:c r="BC1" s="233" t="str">
+        <x:v>phase2_protected_land_flag</x:v>
+      </x:c>
+      <x:c r="BD1" s="233" t="str">
+        <x:v>phase2_regulatory_floodway_flag</x:v>
+      </x:c>
+      <x:c r="BE1" s="233" t="str">
+        <x:v>phase2_mean_slope_deg</x:v>
+      </x:c>
+      <x:c r="BF1" s="233" t="str">
+        <x:v>phase2_urban_context</x:v>
+      </x:c>
+      <x:c r="BG1" s="233" t="str">
+        <x:v>phase2_developed_context</x:v>
+      </x:c>
+      <x:c r="BH1" s="233" t="str">
+        <x:v>phase2_grand_region</x:v>
+      </x:c>
+      <x:c r="BI1" s="233" t="str">
+        <x:v>phase2_primary_weight</x:v>
+      </x:c>
+      <x:c r="BJ1" s="233" t="str">
+        <x:v>phase2_weighted_weight</x:v>
+      </x:c>
+      <x:c r="BK1" s="233" t="str">
+        <x:v>phase2_strict_weight</x:v>
+      </x:c>
+      <x:c r="BL1" s="233" t="str">
+        <x:v>phase2_feature_status</x:v>
+      </x:c>
+      <x:c r="BM1" s="233" t="str">
+        <x:v>phase2_evidence_urls</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="85" t="str">
@@ -45645,6 +48710,54 @@
       <x:c r="AW2" s="226" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="AX2" t="str">
+        <x:v>TNCAND-002</x:v>
+      </x:c>
+      <x:c r="AY2" t="str">
+        <x:v>TN5K-3569</x:v>
+      </x:c>
+      <x:c r="AZ2" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA2" t="str">
+        <x:v>protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB2" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BC2" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BD2" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE2" t="str">
+        <x:v>2.2577022512753806</x:v>
+      </x:c>
+      <x:c r="BF2" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG2" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH2" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="BI2" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ2" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK2" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL2" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM2" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="85" t="str">
@@ -45792,6 +48905,54 @@
       <x:c r="AW3" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX3" t="str">
+        <x:v>TNCAND-003</x:v>
+      </x:c>
+      <x:c r="AY3" t="str">
+        <x:v>TN5K-3713</x:v>
+      </x:c>
+      <x:c r="AZ3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA3" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BC3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD3" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE3" t="str">
+        <x:v>1.4333170387479994</x:v>
+      </x:c>
+      <x:c r="BF3" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG3" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH3" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="BI3" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ3" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK3" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL3" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM3" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="85" t="str">
@@ -45939,6 +49100,54 @@
       <x:c r="AW4" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX4" t="str">
+        <x:v>TNCAND-004</x:v>
+      </x:c>
+      <x:c r="AY4" t="str">
+        <x:v>TN5K-0693</x:v>
+      </x:c>
+      <x:c r="AZ4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA4" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB4" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD4" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE4" t="str">
+        <x:v>0.5780415849553214</x:v>
+      </x:c>
+      <x:c r="BF4" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="BG4" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="BH4" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="BI4" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ4" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK4" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL4" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM4" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="85" t="str">
@@ -46086,6 +49295,54 @@
       <x:c r="AW5" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX5" t="str">
+        <x:v>TNCAND-005</x:v>
+      </x:c>
+      <x:c r="AY5" t="str">
+        <x:v>TN5K-0692</x:v>
+      </x:c>
+      <x:c r="AZ5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA5" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB5" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD5" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE5" t="str">
+        <x:v>0.56364430156019</x:v>
+      </x:c>
+      <x:c r="BF5" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="BG5" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="BH5" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="BI5" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ5" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK5" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BL5" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM5" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -46229,6 +49486,54 @@
       <x:c r="AW6" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX6" t="str">
+        <x:v>TNCAND-006</x:v>
+      </x:c>
+      <x:c r="AY6" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="AZ6" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA6" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC6" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE6" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BF6" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG6" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH6" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="BI6" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ6" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK6" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BL6" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM6" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -46376,6 +49681,54 @@
       <x:c r="AW7" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX7" t="str">
+        <x:v>TNCAND-007</x:v>
+      </x:c>
+      <x:c r="AY7" t="str">
+        <x:v>TN5K-2153</x:v>
+      </x:c>
+      <x:c r="AZ7" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA7" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB7" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC7" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BD7" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE7" t="str">
+        <x:v>0.34054579999711776</x:v>
+      </x:c>
+      <x:c r="BF7" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG7" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH7" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="BI7" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ7" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK7" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM7" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -46523,6 +49876,54 @@
       <x:c r="AW8" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX8" t="str">
+        <x:v>TNCAND-008</x:v>
+      </x:c>
+      <x:c r="AY8" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="AZ8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA8" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB8" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD8" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE8" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BF8" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG8" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH8" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="BI8" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ8" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK8" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL8" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM8" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
@@ -46668,6 +50069,54 @@
       <x:c r="AW9" s="226" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="AX9" t="str">
+        <x:v>TNCAND-009</x:v>
+      </x:c>
+      <x:c r="AY9" t="str">
+        <x:v>TN5K-3606</x:v>
+      </x:c>
+      <x:c r="AZ9" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA9" t="str">
+        <x:v>open_water;protected_land</x:v>
+      </x:c>
+      <x:c r="BB9" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC9" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BD9" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BE9" t="str">
+        <x:v>1.9046613375345867</x:v>
+      </x:c>
+      <x:c r="BF9" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG9" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH9" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="BI9" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ9" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK9" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL9" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM9" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -46815,6 +50264,54 @@
       <x:c r="AW10" s="226" t="str">
         <x:v>H</x:v>
       </x:c>
+      <x:c r="AX10" t="str">
+        <x:v>TNCAND-010</x:v>
+      </x:c>
+      <x:c r="AY10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="AZ10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BA10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BB10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BC10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BD10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BE10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BF10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BG10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BH10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BI10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BJ10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BK10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BL10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BM10" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -46961,6 +50458,54 @@
       </x:c>
       <x:c r="AW11" s="226" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="AX11" t="str">
+        <x:v>TNCAND-011</x:v>
+      </x:c>
+      <x:c r="AY11" t="str">
+        <x:v>TN5K-1932</x:v>
+      </x:c>
+      <x:c r="AZ11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA11" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BC11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD11" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE11" t="str">
+        <x:v>0.9573106169700623</x:v>
+      </x:c>
+      <x:c r="BF11" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG11" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH11" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="BI11" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ11" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK11" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL11" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM11" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -47105,6 +50650,54 @@
       <x:c r="AW12" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX12" t="str">
+        <x:v>TNCAND-012</x:v>
+      </x:c>
+      <x:c r="AY12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="AZ12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BA12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BB12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BC12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BD12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BE12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BF12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BG12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BH12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BI12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BJ12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BK12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BL12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
+      <x:c r="BM12" t="str">
+        <x:v>not_in_phase2_cohort</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -47250,6 +50843,54 @@
       <x:c r="AW13" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX13" t="str">
+        <x:v>TNCAND-013</x:v>
+      </x:c>
+      <x:c r="AY13" t="str">
+        <x:v>TN5K-2991</x:v>
+      </x:c>
+      <x:c r="AZ13" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA13" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB13" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC13" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BD13" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE13" t="str">
+        <x:v>1.550307285454538</x:v>
+      </x:c>
+      <x:c r="BF13" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG13" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH13" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="BI13" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ13" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK13" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BL13" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM13" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -47397,6 +51038,54 @@
       <x:c r="AW14" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX14" t="str">
+        <x:v>TNCAND-014</x:v>
+      </x:c>
+      <x:c r="AY14" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="AZ14" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA14" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB14" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC14" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD14" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE14" t="str">
+        <x:v>0.9799223012394376</x:v>
+      </x:c>
+      <x:c r="BF14" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG14" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH14" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="BI14" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ14" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK14" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BL14" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM14" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -47542,6 +51231,54 @@
       <x:c r="AW15" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX15" t="str">
+        <x:v>TNCAND-015</x:v>
+      </x:c>
+      <x:c r="AY15" t="str">
+        <x:v>TN5K-0076</x:v>
+      </x:c>
+      <x:c r="AZ15" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA15" t="str">
+        <x:v>open_water;protected_land;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB15" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BC15" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BD15" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE15" t="str">
+        <x:v>0.37594464669624966</x:v>
+      </x:c>
+      <x:c r="BF15" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG15" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH15" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="BI15" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ15" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK15" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BL15" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM15" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -47687,6 +51424,54 @@
       <x:c r="AW16" s="226" t="str">
         <x:v>G</x:v>
       </x:c>
+      <x:c r="AX16" t="str">
+        <x:v>TNCAND-016</x:v>
+      </x:c>
+      <x:c r="AY16" t="str">
+        <x:v>TN5K-0074</x:v>
+      </x:c>
+      <x:c r="AZ16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BA16" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="BB16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BC16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD16" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BE16" t="str">
+        <x:v>0.3746739998459816</x:v>
+      </x:c>
+      <x:c r="BF16" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="BG16" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="BH16" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="BI16" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ16" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK16" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BL16" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM16" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -47833,6 +51618,52 @@
       </x:c>
       <x:c r="AW17" s="226" t="str">
         <x:v>G</x:v>
+      </x:c>
+      <x:c r="AX17" t="str">
+        <x:v>TNCAND-017</x:v>
+      </x:c>
+      <x:c r="AY17" t="str">
+        <x:v>TN5K-4488</x:v>
+      </x:c>
+      <x:c r="AZ17" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="BA17" t="str"/>
+      <x:c r="BB17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BC17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BD17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="BE17" t="str">
+        <x:v>5.5128147337171765</x:v>
+      </x:c>
+      <x:c r="BF17" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="BG17" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="BH17" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="BI17" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="BJ17" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BK17" t="str">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="BL17" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM17" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -47860,7 +51691,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea7a800858b640b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec46d6693e164d2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/TN/dataset/tennessee_public_data_centers.xlsx
+++ b/TN/dataset/tennessee_public_data_centers.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R22ced22afa04408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R84377b1ec7ca48ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Rc02ad912dec3421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="R22d80092e3f0456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="Raadf8416d1374666"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R3db9656abf144276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="R34b329f8b75147bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R070a6e16bf3c4c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R9e1a0d21524c415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="R0b1481f32fd14c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="R0a937ec845a1433f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rb9041d75443f4a91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="R6dbcda47173e43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rcad8fa82abc14bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R6fffcd83f50749c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="Rf7fa81ff195d4e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Aligned" sheetId="4" r:id="Re84dc28ab9774337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_Audit" sheetId="5" r:id="R5685a511f8a84da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Pairs" sheetId="6" r:id="R46e2ebebdf244bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded_Support" sheetId="7" r:id="Rf88df3c2b5f84628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field_Map" sheetId="8" r:id="R570522ab5a81428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Sites" sheetId="9" r:id="R74f5bee16f69404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Log" sheetId="10" r:id="Rbdb126db1dc24aca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposal_Readiness" sheetId="11" r:id="Rdd5113bbd92b4af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Queue" sheetId="12" r:id="Rd8df5f134d1d4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_Audit" sheetId="13" r:id="R4c570326881b4435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moratoriums" sheetId="14" r:id="R1884db3998c34fd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +40,7 @@
     <x:numFmt numFmtId="210" formatCode="@"/>
     <x:numFmt numFmtId="211" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -107,8 +108,19 @@
       <x:color rgb="FF000000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF404040"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="24">
+  <x:fills count="28">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -223,6 +235,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF153B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF16324F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F6690"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F6690"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F6690"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -384,7 +416,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="234">
+  <x:cellXfs count="272">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -995,6 +1027,124 @@
     <x:xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="25" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="26" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1097,8 +1247,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="RawAlignedTable" displayName="RawAlignedTable" ref="A1:AR217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:AR217"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="RawAlignedTable" displayName="RawAlignedTable" ref="A1:AR218" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:AR218"/>
   <x:tableColumns count="44">
     <x:tableColumn id="1" name="source"/>
     <x:tableColumn id="2" name="source_record_id"/>
@@ -1267,7 +1417,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CandidateSitesTable" displayName="CandidateSitesTable" ref="A1:AW17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CandidateSitesTable" displayName="CandidateSitesTable" ref="A1:AW18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="49">
     <x:tableColumn id="1" name="candidate_id"/>
     <x:tableColumn id="2" name="master_facility_id"/>
@@ -1318,6 +1468,192 @@
     <x:tableColumn id="47" name="professional_scientific_employment"/>
     <x:tableColumn id="48" name="professional_scientific_establishments"/>
     <x:tableColumn id="49" name="professional_scientific_employment_flag"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="MoratoriumsTable" displayName="MoratoriumsTable" ref="A4:FV15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="178">
+    <x:tableColumn id="1" name="moratorium_id"/>
+    <x:tableColumn id="2" name="record_type"/>
+    <x:tableColumn id="3" name="jurisdiction"/>
+    <x:tableColumn id="4" name="state"/>
+    <x:tableColumn id="5" name="jurisdiction_level"/>
+    <x:tableColumn id="6" name="event_date"/>
+    <x:tableColumn id="7" name="duration_text"/>
+    <x:tableColumn id="8" name="status"/>
+    <x:tableColumn id="9" name="scope"/>
+    <x:tableColumn id="10" name="reason"/>
+    <x:tableColumn id="11" name="source_name"/>
+    <x:tableColumn id="12" name="source_url"/>
+    <x:tableColumn id="13" name="tracker_url"/>
+    <x:tableColumn id="14" name="tracker_last_updated"/>
+    <x:tableColumn id="15" name="source_record_key"/>
+    <x:tableColumn id="16" name="linked_facility_or_candidate_id"/>
+    <x:tableColumn id="17" name="link_basis"/>
+    <x:tableColumn id="18" name="verification_status"/>
+    <x:tableColumn id="19" name="latitude"/>
+    <x:tableColumn id="20" name="longitude"/>
+    <x:tableColumn id="21" name="location_reference"/>
+    <x:tableColumn id="22" name="location_precision"/>
+    <x:tableColumn id="23" name="coordinate_source"/>
+    <x:tableColumn id="24" name="location_semantics"/>
+    <x:tableColumn id="25" name="facility_id"/>
+    <x:tableColumn id="26" name="facility_name"/>
+    <x:tableColumn id="27" name="operator"/>
+    <x:tableColumn id="28" name="operators"/>
+    <x:tableColumn id="29" name="address"/>
+    <x:tableColumn id="30" name="city"/>
+    <x:tableColumn id="31" name="county"/>
+    <x:tableColumn id="32" name="postal_code"/>
+    <x:tableColumn id="33" name="location_confidence"/>
+    <x:tableColumn id="34" name="coordinate_source_record"/>
+    <x:tableColumn id="35" name="coordinate_max_spread_km"/>
+    <x:tableColumn id="36" name="coordinate_conflict_flag"/>
+    <x:tableColumn id="37" name="status_normalized"/>
+    <x:tableColumn id="38" name="status_values"/>
+    <x:tableColumn id="39" name="status_conflict_flag"/>
+    <x:tableColumn id="40" name="facility_type"/>
+    <x:tableColumn id="41" name="facility_type_values"/>
+    <x:tableColumn id="42" name="analysis_scope"/>
+    <x:tableColumn id="43" name="capacity_mw"/>
+    <x:tableColumn id="44" name="square_feet"/>
+    <x:tableColumn id="45" name="property_acres"/>
+    <x:tableColumn id="46" name="investment_usd"/>
+    <x:tableColumn id="47" name="sources"/>
+    <x:tableColumn id="48" name="source_count"/>
+    <x:tableColumn id="49" name="record_count"/>
+    <x:tableColumn id="50" name="source_record_ids"/>
+    <x:tableColumn id="51" name="evidence_urls"/>
+    <x:tableColumn id="52" name="last_updated"/>
+    <x:tableColumn id="53" name="verification_class"/>
+    <x:tableColumn id="54" name="operator_status"/>
+    <x:tableColumn id="55" name="independent_evidence_domain_count"/>
+    <x:tableColumn id="56" name="cross_verified"/>
+    <x:tableColumn id="57" name="source_confidence_score"/>
+    <x:tableColumn id="58" name="source_confidence_class"/>
+    <x:tableColumn id="59" name="verification_note"/>
+    <x:tableColumn id="60" name="schema_version"/>
+    <x:tableColumn id="61" name="phase1_feature_status"/>
+    <x:tableColumn id="62" name="nearest_neighbor_km"/>
+    <x:tableColumn id="63" name="cluster"/>
+    <x:tableColumn id="64" name="dist_transmission_any_km"/>
+    <x:tableColumn id="65" name="dist_transmission_100kv_km"/>
+    <x:tableColumn id="66" name="dist_transmission_230kv_km"/>
+    <x:tableColumn id="67" name="max_voltage_within_25km_kv"/>
+    <x:tableColumn id="68" name="transmission_owner_count_25km"/>
+    <x:tableColumn id="69" name="dist_major_road_km"/>
+    <x:tableColumn id="70" name="dist_interstate_km"/>
+    <x:tableColumn id="71" name="dist_surface_water_flowline_km"/>
+    <x:tableColumn id="72" name="named_flowlines_within_25km"/>
+    <x:tableColumn id="73" name="county_geoid"/>
+    <x:tableColumn id="74" name="county_name"/>
+    <x:tableColumn id="75" name="degree_institutions_50km"/>
+    <x:tableColumn id="76" name="cip11_completions_50km"/>
+    <x:tableColumn id="77" name="cip14_completions_50km"/>
+    <x:tableColumn id="78" name="degree_institutions_100km"/>
+    <x:tableColumn id="79" name="cip11_completions_100km"/>
+    <x:tableColumn id="80" name="cip14_completions_100km"/>
+    <x:tableColumn id="81" name="county_total_employment"/>
+    <x:tableColumn id="82" name="county_total_establishments"/>
+    <x:tableColumn id="83" name="county_total_employment_flag"/>
+    <x:tableColumn id="84" name="information_sector_employment"/>
+    <x:tableColumn id="85" name="information_sector_establishments"/>
+    <x:tableColumn id="86" name="information_sector_employment_flag"/>
+    <x:tableColumn id="87" name="professional_scientific_employment"/>
+    <x:tableColumn id="88" name="professional_scientific_establishments"/>
+    <x:tableColumn id="89" name="professional_scientific_employment_flag"/>
+    <x:tableColumn id="90" name="phase2_site_id"/>
+    <x:tableColumn id="91" name="phase2_domain_cell_id"/>
+    <x:tableColumn id="92" name="phase2_d1_feasible"/>
+    <x:tableColumn id="93" name="phase2_d1_exclusion_reason"/>
+    <x:tableColumn id="94" name="phase2_open_water_flag"/>
+    <x:tableColumn id="95" name="phase2_protected_land_flag"/>
+    <x:tableColumn id="96" name="phase2_regulatory_floodway_flag"/>
+    <x:tableColumn id="97" name="phase2_mean_slope_deg"/>
+    <x:tableColumn id="98" name="phase2_urban_context"/>
+    <x:tableColumn id="99" name="phase2_developed_context"/>
+    <x:tableColumn id="100" name="phase2_grand_region"/>
+    <x:tableColumn id="101" name="phase2_primary_weight"/>
+    <x:tableColumn id="102" name="phase2_weighted_weight"/>
+    <x:tableColumn id="103" name="phase2_strict_weight"/>
+    <x:tableColumn id="104" name="phase2_feature_status"/>
+    <x:tableColumn id="105" name="phase2_evidence_urls"/>
+    <x:tableColumn id="106" name="web_research_date"/>
+    <x:tableColumn id="107" name="web_research_sources"/>
+    <x:tableColumn id="108" name="web_research_note"/>
+    <x:tableColumn id="109" name="named_exempt_facilities"/>
+    <x:tableColumn id="110" name="named_exempt_master_ids"/>
+    <x:tableColumn id="111" name="excluded_facilities"/>
+    <x:tableColumn id="112" name="excluded_master_ids"/>
+    <x:tableColumn id="113" name="reference_point_city"/>
+    <x:tableColumn id="114" name="reference_point_county"/>
+    <x:tableColumn id="115" name="reference_point_county_geoid"/>
+    <x:tableColumn id="116" name="reference_point_address"/>
+    <x:tableColumn id="117" name="reference_point_postal_code"/>
+    <x:tableColumn id="118" name="reference_point_assignment_method"/>
+    <x:tableColumn id="119" name="reference_point_domain_cell_id"/>
+    <x:tableColumn id="120" name="reference_point_centroid_distance_km"/>
+    <x:tableColumn id="121" name="reference_point_feature_status"/>
+    <x:tableColumn id="122" name="reference_point_d1_feasible"/>
+    <x:tableColumn id="123" name="reference_point_d1_exclusion_reason"/>
+    <x:tableColumn id="124" name="reference_point_open_water_flag"/>
+    <x:tableColumn id="125" name="reference_point_protected_land_flag"/>
+    <x:tableColumn id="126" name="reference_point_regulatory_floodway_flag"/>
+    <x:tableColumn id="127" name="reference_point_mean_slope_deg"/>
+    <x:tableColumn id="128" name="reference_point_urban_context"/>
+    <x:tableColumn id="129" name="reference_point_developed_context"/>
+    <x:tableColumn id="130" name="reference_point_grand_region"/>
+    <x:tableColumn id="131" name="reference_point_dist_transmission_any_km"/>
+    <x:tableColumn id="132" name="reference_point_dist_transmission_100kv_km"/>
+    <x:tableColumn id="133" name="reference_point_dist_transmission_230kv_km"/>
+    <x:tableColumn id="134" name="reference_point_max_voltage_within_25km_kv"/>
+    <x:tableColumn id="135" name="reference_point_transmission_owner_count_25km"/>
+    <x:tableColumn id="136" name="reference_point_dist_major_road_km"/>
+    <x:tableColumn id="137" name="reference_point_dist_interstate_km"/>
+    <x:tableColumn id="138" name="reference_point_dist_surface_water_flowline_km"/>
+    <x:tableColumn id="139" name="reference_point_named_flowlines_within_25km"/>
+    <x:tableColumn id="140" name="reference_point_degree_institutions_50km"/>
+    <x:tableColumn id="141" name="reference_point_cip11_completions_50km"/>
+    <x:tableColumn id="142" name="reference_point_cip14_completions_50km"/>
+    <x:tableColumn id="143" name="reference_point_degree_institutions_100km"/>
+    <x:tableColumn id="144" name="reference_point_cip11_completions_100km"/>
+    <x:tableColumn id="145" name="reference_point_cip14_completions_100km"/>
+    <x:tableColumn id="146" name="reference_point_county_total_employment"/>
+    <x:tableColumn id="147" name="reference_point_county_total_establishments"/>
+    <x:tableColumn id="148" name="reference_point_information_sector_employment"/>
+    <x:tableColumn id="149" name="reference_point_information_sector_establishments"/>
+    <x:tableColumn id="150" name="reference_point_professional_scientific_employment"/>
+    <x:tableColumn id="151" name="reference_point_professional_scientific_establishments"/>
+    <x:tableColumn id="152" name="policy_as_of_date"/>
+    <x:tableColumn id="153" name="policy_effective_date"/>
+    <x:tableColumn id="154" name="policy_end_date"/>
+    <x:tableColumn id="155" name="policy_end_date_basis"/>
+    <x:tableColumn id="156" name="policy_status_as_of"/>
+    <x:tableColumn id="157" name="policy_scope_geography"/>
+    <x:tableColumn id="158" name="policy_target"/>
+    <x:tableColumn id="159" name="policy_instrument"/>
+    <x:tableColumn id="160" name="policy_date_source_urls"/>
+    <x:tableColumn id="161" name="policy_temporal_note"/>
+    <x:tableColumn id="162" name="interim_pause_status_as_of"/>
+    <x:tableColumn id="163" name="interim_pause_start_date"/>
+    <x:tableColumn id="164" name="interim_pause_nominal_end_date"/>
+    <x:tableColumn id="165" name="reference_point_address_source_url"/>
+    <x:tableColumn id="166" name="reference_point_score"/>
+    <x:tableColumn id="167" name="reference_point_score_p05"/>
+    <x:tableColumn id="168" name="reference_point_score_p95"/>
+    <x:tableColumn id="169" name="reference_point_grid_regime"/>
+    <x:tableColumn id="170" name="reference_point_novelty_flag"/>
+    <x:tableColumn id="171" name="reference_point_review_band"/>
+    <x:tableColumn id="172" name="reference_point_model_version"/>
+    <x:tableColumn id="173" name="reference_point_score_source"/>
+    <x:tableColumn id="174" name="reference_point_score_interpretation"/>
+    <x:tableColumn id="175" name="policy_feature_location_role"/>
+    <x:tableColumn id="176" name="policy_phase2_feature_count"/>
+    <x:tableColumn id="177" name="policy_presence_training_eligible"/>
+    <x:tableColumn id="178" name="master_location_field_semantics"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1568,7 +1904,7 @@
         <x:v>Retrieval date</x:v>
       </x:c>
       <x:c r="B6" s="73" t="str">
-        <x:v>2026-09-03</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C6" s="71"/>
     </x:row>
@@ -1586,7 +1922,7 @@
         <x:v>Raw records</x:v>
       </x:c>
       <x:c r="B8" s="67" t="str">
-        <x:v>216 total Raw_Aligned rows after fifth-pass candidate-location research.</x:v>
+        <x:v>217 total Raw_Aligned rows after 2026-09-22 Project River candidate refresh.</x:v>
       </x:c>
       <x:c r="C8" s="71"/>
     </x:row>
@@ -1595,7 +1931,7 @@
         <x:v>Master records</x:v>
       </x:c>
       <x:c r="B9" s="67" t="str">
-        <x:v>61 deduplicated Master rows: 50 core data-center/interconnection entities plus 11 crypto-mining entities. Sixteen candidates are tracked separately.</x:v>
+        <x:v>61 deduplicated Master rows: 50 core data-center/interconnection entities plus 11 crypto-mining entities. Seventeen candidates are tracked separately.</x:v>
       </x:c>
       <x:c r="C9" s="71"/>
     </x:row>
@@ -5418,6 +5754,264 @@
         <x:v>Retained as candidates; do not promote from directory evidence alone.</x:v>
       </x:c>
     </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>TNCAND-018</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>ADD</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
+        <x:v>candidate record</x:v>
+      </x:c>
+      <x:c r="E146"/>
+      <x:c r="F146" t="str">
+        <x:v>Project River Industrial Energy and Data Center Campus</x:v>
+      </x:c>
+      <x:c r="G146" t="str">
+        <x:v>https://projectriver.energy/project-river-a-new-kind-of-industrial-energy-campus/ | https://clevelandtn.gov/m/newsflash/home/detail/577</x:v>
+      </x:c>
+      <x:c r="H146" t="str">
+        <x:v>Publicly proposed Bradley County data-center campus added as a candidate only; location remains area-level and the project has no public tenant or approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>TNCAND-018</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>location | spatial feature fields</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>area-level fields incomplete</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>approximate coordinate + frozen-grid feature vector</x:v>
+      </x:c>
+      <x:c r="G147" t="str">
+        <x:v>https://projectriver.energy/project-river-a-new-kind-of-industrial-energy-campus/ | https://clevelandtn.gov/DocumentCenter/View/3080 | https://suedatacenters.org/data-centers/project-river-data-center-bradley-county-tn</x:v>
+      </x:c>
+      <x:c r="H147" t="str">
+        <x:v>Filled the Candidate_Sites field set from approximate Lower River Road geocode and nearest frozen 5 km grid cell TN5K-3295; retained approximate precision and medium confidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>ADD</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>Moratoriums</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>not present</x:v>
+      </x:c>
+      <x:c r="F148" t="str">
+        <x:v>11 Tennessee policy-event records</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="H148" t="str">
+        <x:v>Added a dedicated policy-event table from the 2026-09-14 tracker snapshot. Existing facility inventory tabs and map inputs were not changed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>TNMOR-002 | TNMOR-010 | TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
+        <x:v>Moratoriums master links</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>not linked</x:v>
+      </x:c>
+      <x:c r="F149" t="str">
+        <x:v>linked to existing Master records with relationship scope</x:v>
+      </x:c>
+      <x:c r="G149" t="str">
+        <x:v>https://www.wsmv.com/2026/06/03/mcminnville-approves-18-month-moratorium-new-data-centers-creating-requirements-numerous-impact-studies/ | https://thewarrencountyway.com/news/proposed-data-center | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=2A6E536A-95F6-46B9-993A-1F6E018DD389&amp;ID=8063111 | https://fox17.com/news/local/gallatin-city-council-advances-12-month-data-center-moratorium-for-vote-next-week</x:v>
+      </x:c>
+      <x:c r="H149" t="str">
+        <x:v>Evidence-led joins: Hixson is a named policy-trigger project; DC BLOX Nashville and Meta Gallatin are explicit policy context, not project-specific moratoria.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
+        <x:v>Moratoriums coordinates</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>no spatial fields</x:v>
+      </x:c>
+      <x:c r="F150" t="str">
+        <x:v>WGS84 jurisdiction reference coordinates plus provenance and precision</x:v>
+      </x:c>
+      <x:c r="G150" t="str">
+        <x:v>https://www.openstreetmap.org/ | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="H150" t="str">
+        <x:v>Coordinates identify the relevant jurisdiction's government center or municipal area. They do not represent a data-center, candidate, parcel, or map-layer facility point.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
+        <x:v>Moratorium source verification and policy fields</x:v>
+      </x:c>
+      <x:c r="E151" t="str">
+        <x:v>Tracker summaries and abbreviated durations/scopes</x:v>
+      </x:c>
+      <x:c r="F151" t="str">
+        <x:v>Official resolution/minutes where available; current sources and explicit exceptions; exact conditional/end-date wording; corrected event dates where supported</x:v>
+      </x:c>
+      <x:c r="G151" t="str">
+        <x:v>https://www.washingtoncountytn.org/AgendaCenter/ViewFile/Agenda/_03232026-988 | https://www.supertalk929.com/2026/03/24/washington-county-tn-approves-1-year-moratorium-on-data-centers/ | https://www.wsmv.com/2026/06/03/mcminnville-approves-18-month-moratorium-new-data-centers-creating-requirements-numerous-impact-studies/ | https://www.wsmv.com/2026/06/02/cedar-hill-imposes-two-year-moratorium-data-centers/ | https://www.cityofcedarhill.org/ws/media-library/e8c838795653fd4e0a9e648ee97d332b/commission-agenda-060126.pdf | https://paristn.gov/wp-content/uploads/2026/07/City-Commissioner-Minutes-06.04.2026.pdf | https://www.radionwtn.com/2026/07/01/city-commission-issues-temporary-moratorium-on-data-centers/ | https://www.timesfreepress.com/news/2026/jul/15/hamilton-county-commission-approves-yearlong-data/ | https://johnsoncitytn.civicweb.net/document/336035/City%20Commission%20-%20May%2021%202026.pdf?handle=B1188EF2E7EF4197AB6B139B10832F6A | https://www.wjhl.com/news/local/johnson-city-commission-approves-moratorium-on-data-centers/ | https://johnsoncitytn.civicweb.net/document/321248/City%20Commission%20-%20Jun%2005%202025.pdf?handle=9FC2E0B6FE394EFF81503C2D3139640E | https://www.wbir.com/article/news/local/oak-ridge-anderson/anderson-county-commissioners-2-year-moratorium-data-center-zoning-regulations/51-6546cfdc-a6ca-4d82-8f87-4d01faea40b6 | https://www.mycouriernews.com/articles/2026/06/11193/no-data-centers-crypto-batteries-for-two-years | https://www.aol.com/articles/anderson-county-halts-data-center-152328000.html | https://commission.knoxcountytn.gov/forums/topic/data-center-moratorium/ | https://www.wvlt.tv/2026/06/23/data-center-builds-one-year-delay-knox-county-votes-adopt-one-year-moratorium/ | https://www.knoxvilletn.gov/news/2026/mayor_seeks_unified_approach_on_data_centers | https://www.knoxvilletn.gov/news/2026/cc_approves_waterfront_plan_data_ctr_moratorium | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=2A6E536A-95F6-46B9-993A-1F6E018DD389&amp;ID=8063111 | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=007B8704-62ED-46D1-9E9A-8B3F778229A8&amp;ID=8040869 | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=ABD166B5-005A-400B-B447-1F81227D7B2C&amp;ID=8040870 | https://nashvillebanner.com/2026/07/21/nashville-data-center-regulations-moratorium/ | https://gallatintn.gov/agendacenter | https://gallatintn.gov/2477/Notices-Meetings | https://www.aol.com/articles/gallatin-home-meta-campus-weighs-142756000.html | https://fox17.com/news/local/gallatin-city-council-advances-12-month-data-center-moratorium-for-vote-next-week</x:v>
+      </x:c>
+      <x:c r="H151" t="str">
+        <x:v>Existing Master-aligned fields retained. Jurisdiction policy coordinates remain policy references. Facility links remain context-sensitive; Knox exception IDs are a separate one-to-many list, with the TenHats address conflict documented.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
+        <x:v>Jurisdiction reference-point spatial enrichment</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>Policy-point coordinates only</x:v>
+      </x:c>
+      <x:c r="F152" t="str">
+        <x:v>Added coordinate-derived jurisdiction descriptors and nearest Phase 2 5-km Domain_Cells context proxies in explicitly named reference_point_* columns</x:v>
+      </x:c>
+      <x:c r="G152" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx | ../model/phase 2/README.md</x:v>
+      </x:c>
+      <x:c r="H152" t="str">
+        <x:v>Nearest-centroid values are regional context from jurisdiction government/municipal reference coordinates. They do not describe facility sites, do not become Presence records, and are not suitability or construction-probability scores.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
+        <x:v>Moratorium policy and model context</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>Existing policy fields, jurisdiction geography, and Phase 2 reference-point features</x:v>
+      </x:c>
+      <x:c r="F153" t="str">
+        <x:v>Corrected McMinnville and Paris adoption dates, Nashville sunset, Paris county GEOID; added legal timing, verified civic addresses, and Phase 4 grid context for all 11 records</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>Official city/county ordinances and minutes | U.S. Census TIGER county codes | Phase 2 Domain_Cells | TN-DC-1.0.0 statewide scores</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>Moratoriums are policy events. Their 21 reference_point_* features and grid scores are jurisdiction context; no row is added to physical-site Presence training.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>Master-aligned environmental features</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>Eight unlinked policy rows had blank Master-named power, road, water and labor features</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
+        <x:v>Copied the existing 21 Phase 2 jurisdiction-reference-cell features into blank Master-named columns; filled Phase 2 cell context and county data-quality flags</x:v>
+      </x:c>
+      <x:c r="G154" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx | ../Data tracker/reference_point_phase2_proxy_features_2026-09-23.json</x:v>
+      </x:c>
+      <x:c r="H154" t="str">
+        <x:v>Existing linked-facility values were retained. Eight filled rows use jurisdiction reference points, not physical site coordinates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>TNMOR-001–TNMOR-011</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>UPDATE</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>Moratorium Master-aligned provenance</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>Eight policy-only rows had blank Master-named source and verification metadata</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>Filled source IDs, URLs, counts, coordinate confidence, status provenance and verification descriptors from existing policy records; added Cedar Hill city ZIP from official website</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>Existing Moratoriums source_url and tracker_url | https://www.cityofcedarhill.org/government/</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>Provenance describes policy records. Facility-only identity, capacity, Presence weights, and site-cluster fields remain unassigned.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5466,7 +6060,7 @@
         <x:v>Tennessee facility inventory</x:v>
       </x:c>
       <x:c r="B4" s="105" t="str">
-        <x:v>61 deduplicated Master entities + 16 candidates</x:v>
+        <x:v>61 deduplicated Master entities + 17 candidates</x:v>
       </x:c>
       <x:c r="C4" s="110" t="str">
         <x:v>✅</x:v>
@@ -5508,7 +6102,7 @@
         <x:v>Candidate sites</x:v>
       </x:c>
       <x:c r="B7" s="85" t="str">
-        <x:v>16 deduplicated candidates</x:v>
+        <x:v>17 deduplicated candidates</x:v>
       </x:c>
       <x:c r="C7" s="111" t="str">
         <x:v>✅</x:v>
@@ -5634,7 +6228,7 @@
         <x:v>Backward compatibility</x:v>
       </x:c>
       <x:c r="B16" s="105" t="str">
-        <x:v>A:AO preserved; schema 1.1; dataset 2026-09-03-deduplicated</x:v>
+        <x:v>A:AO preserved; schema 1.1; dataset updated 2026-09-22</x:v>
       </x:c>
       <x:c r="C16" s="110" t="str">
         <x:v>✅</x:v>
@@ -8841,6 +9435,6125 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF2F6690"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="54" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="74" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="82" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="58" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="48" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="64" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="58" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="72" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="62" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="16" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="30" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="30" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="30" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="30" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="16" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="16" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="16" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="20" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="16" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="16" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="20" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="20" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="20" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="20" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="20" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="20" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="30" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="16" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="16" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="16" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="16" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="16" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="16" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="16" hidden="0" customWidth="1"/>
+    <x:col min="50" max="50" width="46" hidden="0" customWidth="1"/>
+    <x:col min="51" max="51" width="46" hidden="0" customWidth="1"/>
+    <x:col min="52" max="52" width="16" hidden="0" customWidth="1"/>
+    <x:col min="53" max="53" width="20" hidden="0" customWidth="1"/>
+    <x:col min="54" max="54" width="30" hidden="0" customWidth="1"/>
+    <x:col min="55" max="55" width="16" hidden="0" customWidth="1"/>
+    <x:col min="56" max="56" width="16" hidden="0" customWidth="1"/>
+    <x:col min="57" max="57" width="20" hidden="0" customWidth="1"/>
+    <x:col min="58" max="58" width="20" hidden="0" customWidth="1"/>
+    <x:col min="59" max="59" width="46" hidden="0" customWidth="1"/>
+    <x:col min="60" max="60" width="16" hidden="0" customWidth="1"/>
+    <x:col min="61" max="61" width="30" hidden="0" customWidth="1"/>
+    <x:col min="62" max="62" width="16" hidden="0" customWidth="1"/>
+    <x:col min="63" max="63" width="30" hidden="0" customWidth="1"/>
+    <x:col min="64" max="64" width="16" hidden="0" customWidth="1"/>
+    <x:col min="65" max="65" width="16" hidden="0" customWidth="1"/>
+    <x:col min="66" max="66" width="16" hidden="0" customWidth="1"/>
+    <x:col min="67" max="67" width="16" hidden="0" customWidth="1"/>
+    <x:col min="68" max="68" width="16" hidden="0" customWidth="1"/>
+    <x:col min="69" max="69" width="16" hidden="0" customWidth="1"/>
+    <x:col min="70" max="70" width="16" hidden="0" customWidth="1"/>
+    <x:col min="71" max="71" width="16" hidden="0" customWidth="1"/>
+    <x:col min="72" max="72" width="16" hidden="0" customWidth="1"/>
+    <x:col min="73" max="73" width="16" hidden="0" customWidth="1"/>
+    <x:col min="74" max="74" width="16" hidden="0" customWidth="1"/>
+    <x:col min="75" max="75" width="16" hidden="0" customWidth="1"/>
+    <x:col min="76" max="76" width="16" hidden="0" customWidth="1"/>
+    <x:col min="77" max="77" width="16" hidden="0" customWidth="1"/>
+    <x:col min="78" max="78" width="16" hidden="0" customWidth="1"/>
+    <x:col min="79" max="79" width="16" hidden="0" customWidth="1"/>
+    <x:col min="80" max="80" width="16" hidden="0" customWidth="1"/>
+    <x:col min="81" max="81" width="16" hidden="0" customWidth="1"/>
+    <x:col min="82" max="82" width="16" hidden="0" customWidth="1"/>
+    <x:col min="83" max="83" width="20" hidden="0" customWidth="1"/>
+    <x:col min="84" max="84" width="16" hidden="0" customWidth="1"/>
+    <x:col min="85" max="85" width="16" hidden="0" customWidth="1"/>
+    <x:col min="86" max="86" width="20" hidden="0" customWidth="1"/>
+    <x:col min="87" max="87" width="16" hidden="0" customWidth="1"/>
+    <x:col min="88" max="88" width="16" hidden="0" customWidth="1"/>
+    <x:col min="89" max="89" width="20" hidden="0" customWidth="1"/>
+    <x:col min="90" max="90" width="16" hidden="0" customWidth="1"/>
+    <x:col min="91" max="91" width="16" hidden="0" customWidth="1"/>
+    <x:col min="92" max="92" width="16" hidden="0" customWidth="1"/>
+    <x:col min="93" max="93" width="30" hidden="0" customWidth="1"/>
+    <x:col min="94" max="94" width="20" hidden="0" customWidth="1"/>
+    <x:col min="95" max="95" width="20" hidden="0" customWidth="1"/>
+    <x:col min="96" max="96" width="20" hidden="0" customWidth="1"/>
+    <x:col min="97" max="97" width="16" hidden="0" customWidth="1"/>
+    <x:col min="98" max="98" width="16" hidden="0" customWidth="1"/>
+    <x:col min="99" max="99" width="16" hidden="0" customWidth="1"/>
+    <x:col min="100" max="100" width="20" hidden="0" customWidth="1"/>
+    <x:col min="101" max="101" width="16" hidden="0" customWidth="1"/>
+    <x:col min="102" max="102" width="16" hidden="0" customWidth="1"/>
+    <x:col min="103" max="103" width="16" hidden="0" customWidth="1"/>
+    <x:col min="104" max="104" width="20" hidden="0" customWidth="1"/>
+    <x:col min="105" max="105" width="46" hidden="0" customWidth="1"/>
+    <x:col min="106" max="106" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="107" max="107" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="108" max="108" width="51.11000061035156" hidden="0" customWidth="1"/>
+    <x:col min="109" max="109" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="110" max="110" width="30" hidden="0" customWidth="1"/>
+    <x:col min="111" max="111" width="36.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="112" max="112" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="113" max="113" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="114" max="114" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="115" max="115" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="116" max="116" width="35.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="117" max="117" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="118" max="118" width="40" hidden="0" customWidth="1"/>
+    <x:col min="119" max="119" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="120" max="120" width="20.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="121" max="121" width="50" hidden="0" customWidth="1"/>
+    <x:col min="122" max="122" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="123" max="123" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="124" max="124" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="125" max="125" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="126" max="126" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="127" max="127" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="128" max="128" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="129" max="129" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="130" max="130" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="131" max="131" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="132" max="132" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="133" max="133" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="134" max="134" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="135" max="135" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="136" max="136" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="137" max="137" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="138" max="138" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="139" max="139" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="140" max="140" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="141" max="141" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="142" max="142" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="143" max="143" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="144" max="144" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="145" max="145" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="146" max="146" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="147" max="147" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="148" max="148" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="149" max="149" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="150" max="150" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="151" max="151" width="17.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="152" max="152" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="153" max="153" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="154" max="154" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="155" max="155" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="156" max="156" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="157" max="157" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="158" max="158" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="159" max="159" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="160" max="160" width="46.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="161" max="161" width="46.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="162" max="162" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="163" max="163" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="164" max="164" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="165" max="165" width="36.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="166" max="166" width="27.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="167" max="167" width="27.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="168" max="168" width="27.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="169" max="169" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="170" max="170" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="171" max="171" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="172" max="172" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="173" max="173" width="36.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="174" max="174" width="46.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="175" max="175" width="27.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="176" max="176" width="26.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="177" max="177" width="27.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="178" max="178" width="36.66999816894531" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="235" t="str">
+        <x:v>Tennessee Data-Center Moratoriums</x:v>
+      </x:c>
+      <x:c r="B1" s="235"/>
+      <x:c r="C1" s="235"/>
+      <x:c r="D1" s="235"/>
+      <x:c r="E1" s="235"/>
+      <x:c r="F1" s="235"/>
+      <x:c r="G1" s="235"/>
+      <x:c r="H1" s="235"/>
+      <x:c r="I1" s="235"/>
+      <x:c r="J1" s="235"/>
+      <x:c r="K1" s="235"/>
+      <x:c r="L1" s="235"/>
+      <x:c r="M1" s="235"/>
+      <x:c r="N1" s="235"/>
+      <x:c r="O1" s="235"/>
+      <x:c r="P1" s="235"/>
+      <x:c r="Q1" s="235"/>
+      <x:c r="R1" s="235"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="237" t="str">
+        <x:v>Interconnected Capital tracker snapshot dated 2026-09-14. Coordinates are jurisdiction-government or municipal-area reference points only, not facility or site locations.</x:v>
+      </x:c>
+      <x:c r="B2" s="237"/>
+      <x:c r="C2" s="237"/>
+      <x:c r="D2" s="237"/>
+      <x:c r="E2" s="237"/>
+      <x:c r="F2" s="237"/>
+      <x:c r="G2" s="237"/>
+      <x:c r="H2" s="237"/>
+      <x:c r="I2" s="237"/>
+      <x:c r="J2" s="237"/>
+      <x:c r="K2" s="237"/>
+      <x:c r="L2" s="237"/>
+      <x:c r="M2" s="237"/>
+      <x:c r="N2" s="237"/>
+      <x:c r="O2" s="237"/>
+      <x:c r="P2" s="237"/>
+      <x:c r="Q2" s="237"/>
+      <x:c r="R2" s="237"/>
+    </x:row>
+    <x:row r="4" ht="61.5" customHeight="1">
+      <x:c r="A4" s="247" t="str">
+        <x:v>moratorium_id</x:v>
+      </x:c>
+      <x:c r="B4" s="247" t="str">
+        <x:v>record_type</x:v>
+      </x:c>
+      <x:c r="C4" s="247" t="str">
+        <x:v>jurisdiction</x:v>
+      </x:c>
+      <x:c r="D4" s="247" t="str">
+        <x:v>state</x:v>
+      </x:c>
+      <x:c r="E4" s="247" t="str">
+        <x:v>jurisdiction_level</x:v>
+      </x:c>
+      <x:c r="F4" s="247" t="str">
+        <x:v>event_date</x:v>
+      </x:c>
+      <x:c r="G4" s="247" t="str">
+        <x:v>duration_text</x:v>
+      </x:c>
+      <x:c r="H4" s="247" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="I4" s="247" t="str">
+        <x:v>scope</x:v>
+      </x:c>
+      <x:c r="J4" s="247" t="str">
+        <x:v>reason</x:v>
+      </x:c>
+      <x:c r="K4" s="247" t="str">
+        <x:v>source_name</x:v>
+      </x:c>
+      <x:c r="L4" s="247" t="str">
+        <x:v>source_url</x:v>
+      </x:c>
+      <x:c r="M4" s="247" t="str">
+        <x:v>tracker_url</x:v>
+      </x:c>
+      <x:c r="N4" s="247" t="str">
+        <x:v>tracker_last_updated</x:v>
+      </x:c>
+      <x:c r="O4" s="247" t="str">
+        <x:v>source_record_key</x:v>
+      </x:c>
+      <x:c r="P4" s="247" t="str">
+        <x:v>linked_facility_or_candidate_id</x:v>
+      </x:c>
+      <x:c r="Q4" s="247" t="str">
+        <x:v>link_basis</x:v>
+      </x:c>
+      <x:c r="R4" s="247" t="str">
+        <x:v>verification_status</x:v>
+      </x:c>
+      <x:c r="S4" s="256" t="str">
+        <x:v>latitude</x:v>
+      </x:c>
+      <x:c r="T4" s="256" t="str">
+        <x:v>longitude</x:v>
+      </x:c>
+      <x:c r="U4" s="256" t="str">
+        <x:v>location_reference</x:v>
+      </x:c>
+      <x:c r="V4" s="256" t="str">
+        <x:v>location_precision</x:v>
+      </x:c>
+      <x:c r="W4" s="256" t="str">
+        <x:v>coordinate_source</x:v>
+      </x:c>
+      <x:c r="X4" s="256" t="str">
+        <x:v>location_semantics</x:v>
+      </x:c>
+      <x:c r="Y4" s="266" t="str">
+        <x:v>facility_id</x:v>
+      </x:c>
+      <x:c r="Z4" s="266" t="str">
+        <x:v>facility_name</x:v>
+      </x:c>
+      <x:c r="AA4" s="266" t="str">
+        <x:v>operator</x:v>
+      </x:c>
+      <x:c r="AB4" s="266" t="str">
+        <x:v>operators</x:v>
+      </x:c>
+      <x:c r="AC4" s="266" t="str">
+        <x:v>address</x:v>
+      </x:c>
+      <x:c r="AD4" s="266" t="str">
+        <x:v>city</x:v>
+      </x:c>
+      <x:c r="AE4" s="266" t="str">
+        <x:v>county</x:v>
+      </x:c>
+      <x:c r="AF4" s="266" t="str">
+        <x:v>postal_code</x:v>
+      </x:c>
+      <x:c r="AG4" s="266" t="str">
+        <x:v>location_confidence</x:v>
+      </x:c>
+      <x:c r="AH4" s="266" t="str">
+        <x:v>coordinate_source_record</x:v>
+      </x:c>
+      <x:c r="AI4" s="266" t="str">
+        <x:v>coordinate_max_spread_km</x:v>
+      </x:c>
+      <x:c r="AJ4" s="266" t="str">
+        <x:v>coordinate_conflict_flag</x:v>
+      </x:c>
+      <x:c r="AK4" s="266" t="str">
+        <x:v>status_normalized</x:v>
+      </x:c>
+      <x:c r="AL4" s="266" t="str">
+        <x:v>status_values</x:v>
+      </x:c>
+      <x:c r="AM4" s="266" t="str">
+        <x:v>status_conflict_flag</x:v>
+      </x:c>
+      <x:c r="AN4" s="266" t="str">
+        <x:v>facility_type</x:v>
+      </x:c>
+      <x:c r="AO4" s="266" t="str">
+        <x:v>facility_type_values</x:v>
+      </x:c>
+      <x:c r="AP4" s="266" t="str">
+        <x:v>analysis_scope</x:v>
+      </x:c>
+      <x:c r="AQ4" s="266" t="str">
+        <x:v>capacity_mw</x:v>
+      </x:c>
+      <x:c r="AR4" s="266" t="str">
+        <x:v>square_feet</x:v>
+      </x:c>
+      <x:c r="AS4" s="266" t="str">
+        <x:v>property_acres</x:v>
+      </x:c>
+      <x:c r="AT4" s="266" t="str">
+        <x:v>investment_usd</x:v>
+      </x:c>
+      <x:c r="AU4" s="266" t="str">
+        <x:v>sources</x:v>
+      </x:c>
+      <x:c r="AV4" s="266" t="str">
+        <x:v>source_count</x:v>
+      </x:c>
+      <x:c r="AW4" s="266" t="str">
+        <x:v>record_count</x:v>
+      </x:c>
+      <x:c r="AX4" s="266" t="str">
+        <x:v>source_record_ids</x:v>
+      </x:c>
+      <x:c r="AY4" s="266" t="str">
+        <x:v>evidence_urls</x:v>
+      </x:c>
+      <x:c r="AZ4" s="266" t="str">
+        <x:v>last_updated</x:v>
+      </x:c>
+      <x:c r="BA4" s="266" t="str">
+        <x:v>verification_class</x:v>
+      </x:c>
+      <x:c r="BB4" s="266" t="str">
+        <x:v>operator_status</x:v>
+      </x:c>
+      <x:c r="BC4" s="266" t="str">
+        <x:v>independent_evidence_domain_count</x:v>
+      </x:c>
+      <x:c r="BD4" s="266" t="str">
+        <x:v>cross_verified</x:v>
+      </x:c>
+      <x:c r="BE4" s="266" t="str">
+        <x:v>source_confidence_score</x:v>
+      </x:c>
+      <x:c r="BF4" s="266" t="str">
+        <x:v>source_confidence_class</x:v>
+      </x:c>
+      <x:c r="BG4" s="266" t="str">
+        <x:v>verification_note</x:v>
+      </x:c>
+      <x:c r="BH4" s="266" t="str">
+        <x:v>schema_version</x:v>
+      </x:c>
+      <x:c r="BI4" s="266" t="str">
+        <x:v>phase1_feature_status</x:v>
+      </x:c>
+      <x:c r="BJ4" s="266" t="str">
+        <x:v>nearest_neighbor_km</x:v>
+      </x:c>
+      <x:c r="BK4" s="266" t="str">
+        <x:v>cluster</x:v>
+      </x:c>
+      <x:c r="BL4" s="266" t="str">
+        <x:v>dist_transmission_any_km</x:v>
+      </x:c>
+      <x:c r="BM4" s="266" t="str">
+        <x:v>dist_transmission_100kv_km</x:v>
+      </x:c>
+      <x:c r="BN4" s="266" t="str">
+        <x:v>dist_transmission_230kv_km</x:v>
+      </x:c>
+      <x:c r="BO4" s="266" t="str">
+        <x:v>max_voltage_within_25km_kv</x:v>
+      </x:c>
+      <x:c r="BP4" s="266" t="str">
+        <x:v>transmission_owner_count_25km</x:v>
+      </x:c>
+      <x:c r="BQ4" s="266" t="str">
+        <x:v>dist_major_road_km</x:v>
+      </x:c>
+      <x:c r="BR4" s="266" t="str">
+        <x:v>dist_interstate_km</x:v>
+      </x:c>
+      <x:c r="BS4" s="266" t="str">
+        <x:v>dist_surface_water_flowline_km</x:v>
+      </x:c>
+      <x:c r="BT4" s="266" t="str">
+        <x:v>named_flowlines_within_25km</x:v>
+      </x:c>
+      <x:c r="BU4" s="266" t="str">
+        <x:v>county_geoid</x:v>
+      </x:c>
+      <x:c r="BV4" s="266" t="str">
+        <x:v>county_name</x:v>
+      </x:c>
+      <x:c r="BW4" s="266" t="str">
+        <x:v>degree_institutions_50km</x:v>
+      </x:c>
+      <x:c r="BX4" s="266" t="str">
+        <x:v>cip11_completions_50km</x:v>
+      </x:c>
+      <x:c r="BY4" s="266" t="str">
+        <x:v>cip14_completions_50km</x:v>
+      </x:c>
+      <x:c r="BZ4" s="266" t="str">
+        <x:v>degree_institutions_100km</x:v>
+      </x:c>
+      <x:c r="CA4" s="266" t="str">
+        <x:v>cip11_completions_100km</x:v>
+      </x:c>
+      <x:c r="CB4" s="266" t="str">
+        <x:v>cip14_completions_100km</x:v>
+      </x:c>
+      <x:c r="CC4" s="266" t="str">
+        <x:v>county_total_employment</x:v>
+      </x:c>
+      <x:c r="CD4" s="266" t="str">
+        <x:v>county_total_establishments</x:v>
+      </x:c>
+      <x:c r="CE4" s="266" t="str">
+        <x:v>county_total_employment_flag</x:v>
+      </x:c>
+      <x:c r="CF4" s="266" t="str">
+        <x:v>information_sector_employment</x:v>
+      </x:c>
+      <x:c r="CG4" s="266" t="str">
+        <x:v>information_sector_establishments</x:v>
+      </x:c>
+      <x:c r="CH4" s="266" t="str">
+        <x:v>information_sector_employment_flag</x:v>
+      </x:c>
+      <x:c r="CI4" s="266" t="str">
+        <x:v>professional_scientific_employment</x:v>
+      </x:c>
+      <x:c r="CJ4" s="266" t="str">
+        <x:v>professional_scientific_establishments</x:v>
+      </x:c>
+      <x:c r="CK4" s="266" t="str">
+        <x:v>professional_scientific_employment_flag</x:v>
+      </x:c>
+      <x:c r="CL4" s="266" t="str">
+        <x:v>phase2_site_id</x:v>
+      </x:c>
+      <x:c r="CM4" s="266" t="str">
+        <x:v>phase2_domain_cell_id</x:v>
+      </x:c>
+      <x:c r="CN4" s="266" t="str">
+        <x:v>phase2_d1_feasible</x:v>
+      </x:c>
+      <x:c r="CO4" s="266" t="str">
+        <x:v>phase2_d1_exclusion_reason</x:v>
+      </x:c>
+      <x:c r="CP4" s="266" t="str">
+        <x:v>phase2_open_water_flag</x:v>
+      </x:c>
+      <x:c r="CQ4" s="266" t="str">
+        <x:v>phase2_protected_land_flag</x:v>
+      </x:c>
+      <x:c r="CR4" s="266" t="str">
+        <x:v>phase2_regulatory_floodway_flag</x:v>
+      </x:c>
+      <x:c r="CS4" s="266" t="str">
+        <x:v>phase2_mean_slope_deg</x:v>
+      </x:c>
+      <x:c r="CT4" s="266" t="str">
+        <x:v>phase2_urban_context</x:v>
+      </x:c>
+      <x:c r="CU4" s="266" t="str">
+        <x:v>phase2_developed_context</x:v>
+      </x:c>
+      <x:c r="CV4" s="266" t="str">
+        <x:v>phase2_grand_region</x:v>
+      </x:c>
+      <x:c r="CW4" s="266" t="str">
+        <x:v>phase2_primary_weight</x:v>
+      </x:c>
+      <x:c r="CX4" s="266" t="str">
+        <x:v>phase2_weighted_weight</x:v>
+      </x:c>
+      <x:c r="CY4" s="266" t="str">
+        <x:v>phase2_strict_weight</x:v>
+      </x:c>
+      <x:c r="CZ4" s="266" t="str">
+        <x:v>phase2_feature_status</x:v>
+      </x:c>
+      <x:c r="DA4" s="266" t="str">
+        <x:v>phase2_evidence_urls</x:v>
+      </x:c>
+      <x:c r="DB4" t="str">
+        <x:v>web_research_date</x:v>
+      </x:c>
+      <x:c r="DC4" t="str">
+        <x:v>web_research_sources</x:v>
+      </x:c>
+      <x:c r="DD4" t="str">
+        <x:v>web_research_note</x:v>
+      </x:c>
+      <x:c r="DE4" t="str">
+        <x:v>named_exempt_facilities</x:v>
+      </x:c>
+      <x:c r="DF4" t="str">
+        <x:v>named_exempt_master_ids</x:v>
+      </x:c>
+      <x:c r="DG4" t="str">
+        <x:v>excluded_facilities</x:v>
+      </x:c>
+      <x:c r="DH4" t="str">
+        <x:v>excluded_master_ids</x:v>
+      </x:c>
+      <x:c r="DI4" t="str">
+        <x:v>reference_point_city</x:v>
+      </x:c>
+      <x:c r="DJ4" t="str">
+        <x:v>reference_point_county</x:v>
+      </x:c>
+      <x:c r="DK4" t="str">
+        <x:v>reference_point_county_geoid</x:v>
+      </x:c>
+      <x:c r="DL4" t="str">
+        <x:v>reference_point_address</x:v>
+      </x:c>
+      <x:c r="DM4" t="str">
+        <x:v>reference_point_postal_code</x:v>
+      </x:c>
+      <x:c r="DN4" t="str">
+        <x:v>reference_point_assignment_method</x:v>
+      </x:c>
+      <x:c r="DO4" t="str">
+        <x:v>reference_point_domain_cell_id</x:v>
+      </x:c>
+      <x:c r="DP4" t="str">
+        <x:v>reference_point_centroid_distance_km</x:v>
+      </x:c>
+      <x:c r="DQ4" t="str">
+        <x:v>reference_point_feature_status</x:v>
+      </x:c>
+      <x:c r="DR4" t="str">
+        <x:v>reference_point_d1_feasible</x:v>
+      </x:c>
+      <x:c r="DS4" t="str">
+        <x:v>reference_point_d1_exclusion_reason</x:v>
+      </x:c>
+      <x:c r="DT4" t="str">
+        <x:v>reference_point_open_water_flag</x:v>
+      </x:c>
+      <x:c r="DU4" t="str">
+        <x:v>reference_point_protected_land_flag</x:v>
+      </x:c>
+      <x:c r="DV4" t="str">
+        <x:v>reference_point_regulatory_floodway_flag</x:v>
+      </x:c>
+      <x:c r="DW4" t="str">
+        <x:v>reference_point_mean_slope_deg</x:v>
+      </x:c>
+      <x:c r="DX4" t="str">
+        <x:v>reference_point_urban_context</x:v>
+      </x:c>
+      <x:c r="DY4" t="str">
+        <x:v>reference_point_developed_context</x:v>
+      </x:c>
+      <x:c r="DZ4" t="str">
+        <x:v>reference_point_grand_region</x:v>
+      </x:c>
+      <x:c r="EA4" t="str">
+        <x:v>reference_point_dist_transmission_any_km</x:v>
+      </x:c>
+      <x:c r="EB4" t="str">
+        <x:v>reference_point_dist_transmission_100kv_km</x:v>
+      </x:c>
+      <x:c r="EC4" t="str">
+        <x:v>reference_point_dist_transmission_230kv_km</x:v>
+      </x:c>
+      <x:c r="ED4" t="str">
+        <x:v>reference_point_max_voltage_within_25km_kv</x:v>
+      </x:c>
+      <x:c r="EE4" t="str">
+        <x:v>reference_point_transmission_owner_count_25km</x:v>
+      </x:c>
+      <x:c r="EF4" t="str">
+        <x:v>reference_point_dist_major_road_km</x:v>
+      </x:c>
+      <x:c r="EG4" t="str">
+        <x:v>reference_point_dist_interstate_km</x:v>
+      </x:c>
+      <x:c r="EH4" t="str">
+        <x:v>reference_point_dist_surface_water_flowline_km</x:v>
+      </x:c>
+      <x:c r="EI4" t="str">
+        <x:v>reference_point_named_flowlines_within_25km</x:v>
+      </x:c>
+      <x:c r="EJ4" t="str">
+        <x:v>reference_point_degree_institutions_50km</x:v>
+      </x:c>
+      <x:c r="EK4" t="str">
+        <x:v>reference_point_cip11_completions_50km</x:v>
+      </x:c>
+      <x:c r="EL4" t="str">
+        <x:v>reference_point_cip14_completions_50km</x:v>
+      </x:c>
+      <x:c r="EM4" t="str">
+        <x:v>reference_point_degree_institutions_100km</x:v>
+      </x:c>
+      <x:c r="EN4" t="str">
+        <x:v>reference_point_cip11_completions_100km</x:v>
+      </x:c>
+      <x:c r="EO4" t="str">
+        <x:v>reference_point_cip14_completions_100km</x:v>
+      </x:c>
+      <x:c r="EP4" t="str">
+        <x:v>reference_point_county_total_employment</x:v>
+      </x:c>
+      <x:c r="EQ4" t="str">
+        <x:v>reference_point_county_total_establishments</x:v>
+      </x:c>
+      <x:c r="ER4" t="str">
+        <x:v>reference_point_information_sector_employment</x:v>
+      </x:c>
+      <x:c r="ES4" t="str">
+        <x:v>reference_point_information_sector_establishments</x:v>
+      </x:c>
+      <x:c r="ET4" t="str">
+        <x:v>reference_point_professional_scientific_employment</x:v>
+      </x:c>
+      <x:c r="EU4" t="str">
+        <x:v>reference_point_professional_scientific_establishments</x:v>
+      </x:c>
+      <x:c r="EV4" t="str">
+        <x:v>policy_as_of_date</x:v>
+      </x:c>
+      <x:c r="EW4" t="str">
+        <x:v>policy_effective_date</x:v>
+      </x:c>
+      <x:c r="EX4" t="str">
+        <x:v>policy_end_date</x:v>
+      </x:c>
+      <x:c r="EY4" t="str">
+        <x:v>policy_end_date_basis</x:v>
+      </x:c>
+      <x:c r="EZ4" t="str">
+        <x:v>policy_status_as_of</x:v>
+      </x:c>
+      <x:c r="FA4" t="str">
+        <x:v>policy_scope_geography</x:v>
+      </x:c>
+      <x:c r="FB4" t="str">
+        <x:v>policy_target</x:v>
+      </x:c>
+      <x:c r="FC4" t="str">
+        <x:v>policy_instrument</x:v>
+      </x:c>
+      <x:c r="FD4" t="str">
+        <x:v>policy_date_source_urls</x:v>
+      </x:c>
+      <x:c r="FE4" t="str">
+        <x:v>policy_temporal_note</x:v>
+      </x:c>
+      <x:c r="FF4" t="str">
+        <x:v>interim_pause_status_as_of</x:v>
+      </x:c>
+      <x:c r="FG4" t="str">
+        <x:v>interim_pause_start_date</x:v>
+      </x:c>
+      <x:c r="FH4" t="str">
+        <x:v>interim_pause_nominal_end_date</x:v>
+      </x:c>
+      <x:c r="FI4" t="str">
+        <x:v>reference_point_address_source_url</x:v>
+      </x:c>
+      <x:c r="FJ4" t="str">
+        <x:v>reference_point_score</x:v>
+      </x:c>
+      <x:c r="FK4" t="str">
+        <x:v>reference_point_score_p05</x:v>
+      </x:c>
+      <x:c r="FL4" t="str">
+        <x:v>reference_point_score_p95</x:v>
+      </x:c>
+      <x:c r="FM4" t="str">
+        <x:v>reference_point_grid_regime</x:v>
+      </x:c>
+      <x:c r="FN4" t="str">
+        <x:v>reference_point_novelty_flag</x:v>
+      </x:c>
+      <x:c r="FO4" t="str">
+        <x:v>reference_point_review_band</x:v>
+      </x:c>
+      <x:c r="FP4" t="str">
+        <x:v>reference_point_model_version</x:v>
+      </x:c>
+      <x:c r="FQ4" t="str">
+        <x:v>reference_point_score_source</x:v>
+      </x:c>
+      <x:c r="FR4" t="str">
+        <x:v>reference_point_score_interpretation</x:v>
+      </x:c>
+      <x:c r="FS4" t="str">
+        <x:v>policy_feature_location_role</x:v>
+      </x:c>
+      <x:c r="FT4" t="str">
+        <x:v>policy_phase2_feature_count</x:v>
+      </x:c>
+      <x:c r="FU4" t="str">
+        <x:v>policy_presence_training_eligible</x:v>
+      </x:c>
+      <x:c r="FV4" t="str">
+        <x:v>master_location_field_semantics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="101.25" customHeight="1">
+      <x:c r="A5" s="248" t="str">
+        <x:v>TNMOR-001</x:v>
+      </x:c>
+      <x:c r="B5" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C5" s="248" t="str">
+        <x:v>Washington County</x:v>
+      </x:c>
+      <x:c r="D5" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E5" s="248" t="str">
+        <x:v>County</x:v>
+      </x:c>
+      <x:c r="F5" s="249" t="n">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="G5" s="248" t="str">
+        <x:v>Effective upon passage through June 30, 2027 (Resolution 26-03-02)</x:v>
+      </x:c>
+      <x:c r="H5" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I5" s="248" t="str">
+        <x:v>Countywide: bars data-center facilities, including AI, cryptocurrency-mining and blockchain-computing operations, from locating, constructing, operating, applying for permits or seeking vesting rights; ordinary businesses using data processing internally are exempt.</x:v>
+      </x:c>
+      <x:c r="J5" s="248" t="str">
+        <x:v>County zoning staff and Regional Planning Commission were directed to study the uses and recommend zoning text or other regulatory changes.</x:v>
+      </x:c>
+      <x:c r="K5" s="248" t="str">
+        <x:v>SuperTalk 92.9 | Washington County Resolution 26-03-02; SuperTalk 92.9</x:v>
+      </x:c>
+      <x:c r="L5" s="248" t="str">
+        <x:v>https://www.supertalk929.com/2026/03/24/washington-county-tn-approves-1-year-moratorium-on-data-centers/ | https://www.washingtoncountytn.org/AgendaCenter/ViewFile/Agenda/_03232026-988</x:v>
+      </x:c>
+      <x:c r="M5" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N5" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O5" s="248" t="str">
+        <x:v>interconnected-capital:tn:washington-county:2026-03-24</x:v>
+      </x:c>
+      <x:c r="P5" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q5" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R5" s="248" t="str">
+        <x:v>official-resolution-verified + tracker-recorded</x:v>
+      </x:c>
+      <x:c r="S5" s="257" t="n">
+        <x:v>36.293976</x:v>
+      </x:c>
+      <x:c r="T5" s="257" t="n">
+        <x:v>-82.472971</x:v>
+      </x:c>
+      <x:c r="U5" s="248" t="str">
+        <x:v>Washington County Courthouse, 100 E Main St, Jonesborough, TN 37659</x:v>
+      </x:c>
+      <x:c r="V5" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W5" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Washington%20County%20Courthouse%2C%20Jonesborough%2C%20Tennessee#map=19/36.293976/-82.472971</x:v>
+      </x:c>
+      <x:c r="X5" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y5" s="248"/>
+      <x:c r="Z5" s="248"/>
+      <x:c r="AA5" s="248"/>
+      <x:c r="AB5" s="248"/>
+      <x:c r="AC5" s="248" t="str">
+        <x:v>Washington County Courthouse, 100 E Main Street, Jonesborough, TN 37659</x:v>
+      </x:c>
+      <x:c r="AD5" s="248" t="str">
+        <x:v>Jonesborough</x:v>
+      </x:c>
+      <x:c r="AE5" s="248" t="str">
+        <x:v>Washington</x:v>
+      </x:c>
+      <x:c r="AF5" s="248" t="str">
+        <x:v>37659</x:v>
+      </x:c>
+      <x:c r="AG5" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH5" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Washington%20County%20Courthouse%2C%20Jonesborough%2C%20Tennessee#map=19/36.293976/-82.472971</x:v>
+      </x:c>
+      <x:c r="AI5" s="248"/>
+      <x:c r="AJ5" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK5" s="248"/>
+      <x:c r="AL5" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM5" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN5" s="248"/>
+      <x:c r="AO5" s="248"/>
+      <x:c r="AP5" s="248"/>
+      <x:c r="AQ5" s="248"/>
+      <x:c r="AR5" s="248"/>
+      <x:c r="AS5" s="248"/>
+      <x:c r="AT5" s="248"/>
+      <x:c r="AU5" s="248" t="str">
+        <x:v>interconnected_capital | supertalk929.com | washingtoncountytn.org</x:v>
+      </x:c>
+      <x:c r="AV5" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW5" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX5" s="248" t="str">
+        <x:v>interconnected-capital:tn:washington-county:2026-03-24</x:v>
+      </x:c>
+      <x:c r="AY5" s="248" t="str">
+        <x:v>https://www.supertalk929.com/2026/03/24/washington-county-tn-approves-1-year-moratorium-on-data-centers/ | https://www.washingtoncountytn.org/AgendaCenter/ViewFile/Agenda/_03232026-988 | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ5" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA5" s="248" t="str">
+        <x:v>official_policy_action_verified</x:v>
+      </x:c>
+      <x:c r="BB5" s="248"/>
+      <x:c r="BC5" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD5" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE5" s="248"/>
+      <x:c r="BF5" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="BG5" s="248" t="str">
+        <x:v>Policy event, not a facility. official-resolution-verified + tracker-recorded. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH5" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI5" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ5" s="248"/>
+      <x:c r="BK5" s="248"/>
+      <x:c r="BL5" s="248" t="n">
+        <x:v>1.4048262027</x:v>
+      </x:c>
+      <x:c r="BM5" s="248" t="n">
+        <x:v>5.3854282909</x:v>
+      </x:c>
+      <x:c r="BN5" s="248" t="n">
+        <x:v>5.3854282909</x:v>
+      </x:c>
+      <x:c r="BO5" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP5" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BQ5" s="248" t="n">
+        <x:v>0.0528264901</x:v>
+      </x:c>
+      <x:c r="BR5" s="248" t="n">
+        <x:v>10.5571907993</x:v>
+      </x:c>
+      <x:c r="BS5" s="248" t="n">
+        <x:v>0.420682297</x:v>
+      </x:c>
+      <x:c r="BT5" s="248" t="n">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="BU5" s="248" t="str">
+        <x:v>47179</x:v>
+      </x:c>
+      <x:c r="BV5" s="248" t="str">
+        <x:v>Washington County</x:v>
+      </x:c>
+      <x:c r="BW5" s="248" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="BX5" s="248" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="BY5" s="248" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="BZ5" s="248" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="CA5" s="248" t="n">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="CB5" s="248" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="CC5" s="248" t="n">
+        <x:v>56072</x:v>
+      </x:c>
+      <x:c r="CD5" s="248" t="n">
+        <x:v>3076</x:v>
+      </x:c>
+      <x:c r="CE5" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF5" s="248" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="CG5" s="248" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="CH5" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CI5" s="248" t="n">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="CJ5" s="248" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="CK5" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CL5" s="248"/>
+      <x:c r="CM5" s="248" t="str">
+        <x:v>TN5K-4346</x:v>
+      </x:c>
+      <x:c r="CN5" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO5" s="248"/>
+      <x:c r="CP5" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ5" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CR5" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS5" s="248" t="n">
+        <x:v>1.3612640103</x:v>
+      </x:c>
+      <x:c r="CT5" s="248" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CU5" s="248" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CV5" s="248" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CW5" s="248"/>
+      <x:c r="CX5" s="248"/>
+      <x:c r="CY5" s="248"/>
+      <x:c r="CZ5" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA5" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB5" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC5" s="85" t="str">
+        <x:v>https://www.washingtoncountytn.org/AgendaCenter/ViewFile/Agenda/_03232026-988 | https://www.supertalk929.com/2026/03/24/washington-county-tn-approves-1-year-moratorium-on-data-centers/</x:v>
+      </x:c>
+      <x:c r="DD5" s="85" t="str">
+        <x:v>Official resolution adopted March 23, 2026; expires June 30, 2027 unless extended. No specific facility is identified; policy-reference coordinates remain jurisdiction points.</x:v>
+      </x:c>
+      <x:c r="DE5" s="85"/>
+      <x:c r="DF5" s="85"/>
+      <x:c r="DG5" s="85"/>
+      <x:c r="DH5" s="85"/>
+      <x:c r="DI5" s="85" t="str">
+        <x:v>Jonesborough</x:v>
+      </x:c>
+      <x:c r="DJ5" s="85" t="str">
+        <x:v>Washington County</x:v>
+      </x:c>
+      <x:c r="DK5" s="85" t="str">
+        <x:v>47179</x:v>
+      </x:c>
+      <x:c r="DL5" s="85" t="str">
+        <x:v>Washington County Courthouse, 100 E Main Street, Jonesborough, TN 37659</x:v>
+      </x:c>
+      <x:c r="DM5" s="85" t="str">
+        <x:v>37659</x:v>
+      </x:c>
+      <x:c r="DN5" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO5" s="85" t="str">
+        <x:v>TN5K-4346</x:v>
+      </x:c>
+      <x:c r="DP5" s="85" t="n">
+        <x:v>2.283</x:v>
+      </x:c>
+      <x:c r="DQ5" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR5" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS5" s="85"/>
+      <x:c r="DT5" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU5" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV5" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW5" s="85" t="n">
+        <x:v>1.3612640103</x:v>
+      </x:c>
+      <x:c r="DX5" s="85" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="DY5" s="85" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ5" s="85" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="EA5" s="85" t="n">
+        <x:v>1.4048262027</x:v>
+      </x:c>
+      <x:c r="EB5" s="85" t="n">
+        <x:v>5.3854282909</x:v>
+      </x:c>
+      <x:c r="EC5" s="85" t="n">
+        <x:v>5.3854282909</x:v>
+      </x:c>
+      <x:c r="ED5" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE5" s="85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="EF5" s="85" t="n">
+        <x:v>0.0528264901</x:v>
+      </x:c>
+      <x:c r="EG5" s="85" t="n">
+        <x:v>10.5571907993</x:v>
+      </x:c>
+      <x:c r="EH5" s="85" t="n">
+        <x:v>0.420682297</x:v>
+      </x:c>
+      <x:c r="EI5" s="85" t="n">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="EJ5" s="85" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="EK5" s="85" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="EL5" s="85" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="EM5" s="85" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="EN5" s="85" t="n">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="EO5" s="85" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="EP5" s="85" t="n">
+        <x:v>56072</x:v>
+      </x:c>
+      <x:c r="EQ5" s="85" t="n">
+        <x:v>3076</x:v>
+      </x:c>
+      <x:c r="ER5" s="85" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="ES5" s="85" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="ET5" s="85" t="n">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="EU5" s="85" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="EV5" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW5" s="268" t="n">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="EX5" s="268" t="n">
+        <x:v>46568</x:v>
+      </x:c>
+      <x:c r="EY5" s="269" t="str">
+        <x:v>explicit resolution sunset</x:v>
+      </x:c>
+      <x:c r="EZ5" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA5" s="269" t="str">
+        <x:v>Washington County jurisdiction</x:v>
+      </x:c>
+      <x:c r="FB5" s="269" t="str">
+        <x:v>data centers; AI computing; cryptocurrency mining; blockchain computing</x:v>
+      </x:c>
+      <x:c r="FC5" s="269" t="str">
+        <x:v>Resolution 26-03-02</x:v>
+      </x:c>
+      <x:c r="FD5" s="269" t="str">
+        <x:v>https://www.washingtoncountytn.org/AgendaCenter/ViewFile/Agenda/_03232026-988</x:v>
+      </x:c>
+      <x:c r="FE5" s="269"/>
+      <x:c r="FF5" s="269"/>
+      <x:c r="FG5" s="268"/>
+      <x:c r="FH5" s="268"/>
+      <x:c r="FI5" s="269" t="str">
+        <x:v>https://www.washingtoncountytn.org/230/Register-of-Deeds</x:v>
+      </x:c>
+      <x:c r="FJ5" s="270" t="n">
+        <x:v>91.4142564336</x:v>
+      </x:c>
+      <x:c r="FK5" s="270" t="n">
+        <x:v>91.028239581</x:v>
+      </x:c>
+      <x:c r="FL5" s="270" t="n">
+        <x:v>94.0434980642</x:v>
+      </x:c>
+      <x:c r="FM5" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN5" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO5" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP5" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ5" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR5" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS5" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT5" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU5" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV5" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="101.25" customHeight="1">
+      <x:c r="A6" s="248" t="str">
+        <x:v>TNMOR-002</x:v>
+      </x:c>
+      <x:c r="B6" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C6" s="248" t="str">
+        <x:v>McMinnville</x:v>
+      </x:c>
+      <x:c r="D6" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E6" s="248" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="F6" s="249" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="G6" s="248" t="str">
+        <x:v>18 months</x:v>
+      </x:c>
+      <x:c r="H6" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I6" s="248" t="str">
+        <x:v>New data-center development in McMinnville; Hixson Data Center is the named policy-trigger project (96,000 sq ft, 25 MW, Nvidia GB200).</x:v>
+      </x:c>
+      <x:c r="J6" s="248" t="str">
+        <x:v>Adopted after a petition and concerns about water, energy and community impacts; the city requires impact studies as part of developing local rules.</x:v>
+      </x:c>
+      <x:c r="K6" s="248" t="str">
+        <x:v>WSMV / The UC Now</x:v>
+      </x:c>
+      <x:c r="L6" s="248" t="str">
+        <x:v>https://www.wsmv.com/2026/06/03/mcminnville-approves-18-month-moratorium-new-data-centers-creating-requirements-numerous-impact-studies/ | https://cms2.revize.com/revize/mcminnville/06%2009%202026%20BoMA%20Agenda%20Packet.pdf?t=202606051534130 | https://theucnow.com/2026/06/09/mcminnville-board-enacts-temporary-data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="M6" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N6" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O6" s="248" t="str">
+        <x:v>interconnected-capital:tn:mcminnville:2026-06-03</x:v>
+      </x:c>
+      <x:c r="P6" s="248" t="str">
+        <x:v>TNDC-023</x:v>
+      </x:c>
+      <x:c r="Q6" s="248" t="str">
+        <x:v>Named policy-trigger project. The tracker source identifies the 96,000 sq ft / 25 MW Hixson Data Center; TNDC-023 is the existing full Master record for the same proposed McMinnville/Warren County project. Address, capacity, and status are source-backed in Master.</x:v>
+      </x:c>
+      <x:c r="R6" s="248" t="str">
+        <x:v>official-final-ordinance + final-passage-media-corroborated</x:v>
+      </x:c>
+      <x:c r="S6" s="257" t="n">
+        <x:v>35.682571</x:v>
+      </x:c>
+      <x:c r="T6" s="257" t="n">
+        <x:v>-85.774982</x:v>
+      </x:c>
+      <x:c r="U6" s="248" t="str">
+        <x:v>McMinnville City Hall, McMinnville, TN</x:v>
+      </x:c>
+      <x:c r="V6" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W6" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=McMinnville%20City%20Hall%2C%20Tennessee#map=19/35.682571/-85.774982</x:v>
+      </x:c>
+      <x:c r="X6" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y6" s="248" t="str">
+        <x:v>TNDC-023</x:v>
+      </x:c>
+      <x:c r="Z6" s="248" t="str">
+        <x:v>Hixson Data Center (McMinnville)</x:v>
+      </x:c>
+      <x:c r="AA6" s="248" t="str">
+        <x:v>Hixson Data Center</x:v>
+      </x:c>
+      <x:c r="AB6" s="248" t="str">
+        <x:v>Hixson Data Center</x:v>
+      </x:c>
+      <x:c r="AC6" s="248" t="str">
+        <x:v>191 Industrial Dr vicinity</x:v>
+      </x:c>
+      <x:c r="AD6" s="248" t="str">
+        <x:v>McMinnville</x:v>
+      </x:c>
+      <x:c r="AE6" s="248" t="str">
+        <x:v>Warren</x:v>
+      </x:c>
+      <x:c r="AF6" s="248" t="str">
+        <x:v>37110</x:v>
+      </x:c>
+      <x:c r="AG6" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH6" s="248" t="str">
+        <x:v>fractracker:1780024884691-1880</x:v>
+      </x:c>
+      <x:c r="AI6" s="248" t="n">
+        <x:v>7.3696</x:v>
+      </x:c>
+      <x:c r="AJ6" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK6" s="248" t="str">
+        <x:v>proposed</x:v>
+      </x:c>
+      <x:c r="AL6" s="248" t="str">
+        <x:v>proposed</x:v>
+      </x:c>
+      <x:c r="AM6" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN6" s="248" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="AO6" s="248" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="AP6" s="248" t="str">
+        <x:v>core_data_center</x:v>
+      </x:c>
+      <x:c r="AQ6" s="248" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AR6" s="248" t="n">
+        <x:v>96065</x:v>
+      </x:c>
+      <x:c r="AS6" s="248"/>
+      <x:c r="AT6" s="248"/>
+      <x:c r="AU6" s="248" t="str">
+        <x:v>compute_atlas | fractracker</x:v>
+      </x:c>
+      <x:c r="AV6" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW6" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AX6" s="248" t="str">
+        <x:v>compute_atlas:hixson-data-center-mcminnville-tn | fractracker:1780024884691-1880</x:v>
+      </x:c>
+      <x:c r="AY6" s="248" t="str">
+        <x:v>https://baxtel.com/news/25mw-ai-data-center-planned-for-mcminnville | https://www.wsmv.com/2026/06/01/amid-plans-new-high-density-ai-data-center-campus-middle-tennessee-city-locals-push-moratorium-such-facilities/ | https://hixsondc.com/ | https://warrencountyecd.com/site/mcminnville-warren-digital-site/ | https://www.datacenterdynamics.com/en/news/25mw-ai-data-center-to-be-built-in-mcminnville-tennessee/ | https://warrencountyway.com/hixson-data-center-development-project/</x:v>
+      </x:c>
+      <x:c r="AZ6" s="248" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="BA6" s="248" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="BB6" s="248" t="str">
+        <x:v>identified</x:v>
+      </x:c>
+      <x:c r="BC6" s="248" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BD6" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE6" s="248" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="BF6" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="BG6" s="248" t="str">
+        <x:v>Hixson's current site confirms a planned 25 MW McMinnville/Warren County project but does not publish a parcel or street address. Local reporting supports only a vicinity near 191 Industrial Dr; retain this point solely as approximate_site, not as an exact parcel.</x:v>
+      </x:c>
+      <x:c r="BH6" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI6" s="248" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="BJ6" s="248" t="n">
+        <x:v>7.55864423304588</x:v>
+      </x:c>
+      <x:c r="BK6" s="248" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="BL6" s="248" t="n">
+        <x:v>3.670810269189298</x:v>
+      </x:c>
+      <x:c r="BM6" s="248" t="n">
+        <x:v>3.670810269189298</x:v>
+      </x:c>
+      <x:c r="BN6" s="248" t="n">
+        <x:v>43.05319069901394</x:v>
+      </x:c>
+      <x:c r="BO6" s="248" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="BP6" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ6" s="248" t="n">
+        <x:v>1.639881477326324</x:v>
+      </x:c>
+      <x:c r="BR6" s="248" t="n">
+        <x:v>32.901569856081274</x:v>
+      </x:c>
+      <x:c r="BS6" s="248" t="n">
+        <x:v>0.685404786228203</x:v>
+      </x:c>
+      <x:c r="BT6" s="248" t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="BU6" s="248" t="str">
+        <x:v>47177</x:v>
+      </x:c>
+      <x:c r="BV6" s="248" t="str">
+        <x:v>Warren County</x:v>
+      </x:c>
+      <x:c r="BW6" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BX6" s="248" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="BY6" s="248" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="BZ6" s="248" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="CA6" s="248" t="n">
+        <x:v>1307</x:v>
+      </x:c>
+      <x:c r="CB6" s="248" t="n">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="CC6" s="248" t="n">
+        <x:v>9738</x:v>
+      </x:c>
+      <x:c r="CD6" s="248" t="n">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="CE6" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CF6" s="248" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="CG6" s="248" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="CH6" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CI6" s="248" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="CJ6" s="248" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="CK6" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CL6" s="248" t="str">
+        <x:v>TNDC-023</x:v>
+      </x:c>
+      <x:c r="CM6" s="248" t="str">
+        <x:v>TN5K-2596</x:v>
+      </x:c>
+      <x:c r="CN6" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO6" s="248"/>
+      <x:c r="CP6" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ6" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CR6" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CS6" s="248" t="str">
+        <x:v>0.6942308247089386</x:v>
+      </x:c>
+      <x:c r="CT6" s="248" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CU6" s="248" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CV6" s="248" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CW6" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CX6" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CY6" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CZ6" s="248" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="DA6" s="248" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
+      <x:c r="DB6" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC6" s="85" t="str">
+        <x:v>https://www.wsmv.com/2026/06/03/mcminnville-approves-18-month-moratorium-new-data-centers-creating-requirements-numerous-impact-studies/ | https://cms2.revize.com/revize/mcminnville/06%2009%202026%20BoMA%20Agenda%20Packet.pdf?t=202606051534130 | https://theucnow.com/2026/06/09/mcminnville-board-enacts-temporary-data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="DD6" s="85" t="str">
+        <x:v>TNDC-023 remains a named policy-trigger relationship, not a claim that the jurisdiction-wide moratorium is limited to that project. | June 3 was first reading; June 9 was final reading and immediate effective date. The &gt;250 W/sq ft or &gt;1 MW threshold defines high-density computing, not all data centers.</x:v>
+      </x:c>
+      <x:c r="DE6" s="85"/>
+      <x:c r="DF6" s="85"/>
+      <x:c r="DG6" s="85"/>
+      <x:c r="DH6" s="85"/>
+      <x:c r="DI6" s="85" t="str">
+        <x:v>McMinnville</x:v>
+      </x:c>
+      <x:c r="DJ6" s="85" t="str">
+        <x:v>Warren County</x:v>
+      </x:c>
+      <x:c r="DK6" s="85" t="str">
+        <x:v>47177</x:v>
+      </x:c>
+      <x:c r="DL6" s="85" t="str">
+        <x:v>McMinnville City Hall, 101 E Main Street, McMinnville, TN 37110</x:v>
+      </x:c>
+      <x:c r="DM6" s="85" t="str">
+        <x:v>37110</x:v>
+      </x:c>
+      <x:c r="DN6" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO6" s="85" t="str">
+        <x:v>TN5K-2669</x:v>
+      </x:c>
+      <x:c r="DP6" s="85" t="n">
+        <x:v>1.962</x:v>
+      </x:c>
+      <x:c r="DQ6" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR6" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS6" s="85"/>
+      <x:c r="DT6" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU6" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DV6" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW6" s="85" t="n">
+        <x:v>0.9771514701</x:v>
+      </x:c>
+      <x:c r="DX6" s="85" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="DY6" s="85" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ6" s="85" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="EA6" s="85" t="n">
+        <x:v>2.8218018224</x:v>
+      </x:c>
+      <x:c r="EB6" s="85" t="n">
+        <x:v>2.8218018224</x:v>
+      </x:c>
+      <x:c r="EC6" s="85" t="n">
+        <x:v>37.7225623711</x:v>
+      </x:c>
+      <x:c r="ED6" s="85" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="EE6" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="EF6" s="85" t="n">
+        <x:v>0.894998598</x:v>
+      </x:c>
+      <x:c r="EG6" s="85" t="n">
+        <x:v>35.8618800878</x:v>
+      </x:c>
+      <x:c r="EH6" s="85" t="n">
+        <x:v>0.1264588886</x:v>
+      </x:c>
+      <x:c r="EI6" s="85" t="n">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="EJ6" s="85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="EK6" s="85" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="EL6" s="85" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="EM6" s="85" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="EN6" s="85" t="n">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="EO6" s="85" t="n">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="EP6" s="85" t="n">
+        <x:v>9738</x:v>
+      </x:c>
+      <x:c r="EQ6" s="85" t="n">
+        <x:v>781</x:v>
+      </x:c>
+      <x:c r="ER6" s="85" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="ES6" s="85" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="ET6" s="85" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="EU6" s="85" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="EV6" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW6" s="268" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="EX6" s="268" t="n">
+        <x:v>46730</x:v>
+      </x:c>
+      <x:c r="EY6" s="269" t="str">
+        <x:v>18-month anniversary calculated from final passage; extension or repeal not checked</x:v>
+      </x:c>
+      <x:c r="EZ6" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA6" s="269" t="str">
+        <x:v>McMinnville city limits</x:v>
+      </x:c>
+      <x:c r="FB6" s="269" t="str">
+        <x:v>new data centers and high-density computing/crypto-mining uses</x:v>
+      </x:c>
+      <x:c r="FC6" s="269" t="str">
+        <x:v>Ordinance 2026-09</x:v>
+      </x:c>
+      <x:c r="FD6" s="269" t="str">
+        <x:v>https://cms2.revize.com/revize/mcminnville/06%2009%202026%20BoMA%20Agenda%20Packet.pdf?t=202606051534130 | https://theucnow.com/2026/06/09/mcminnville-board-enacts-temporary-data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="FE6" s="269" t="str">
+        <x:v>June 3 was first reading; June 9 was final reading and immediate effective date. The &gt;250 W/sq ft or &gt;1 MW threshold defines high-density computing, not all data centers.</x:v>
+      </x:c>
+      <x:c r="FF6" s="269"/>
+      <x:c r="FG6" s="268"/>
+      <x:c r="FH6" s="268"/>
+      <x:c r="FI6" s="269" t="str">
+        <x:v>https://www.mtas.tennessee.edu/directories/cities/mcminnville</x:v>
+      </x:c>
+      <x:c r="FJ6" s="270" t="n">
+        <x:v>81.5987246641</x:v>
+      </x:c>
+      <x:c r="FK6" s="270" t="n">
+        <x:v>78.7599635618</x:v>
+      </x:c>
+      <x:c r="FL6" s="270" t="n">
+        <x:v>85.5488499203</x:v>
+      </x:c>
+      <x:c r="FM6" s="269" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="FN6" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO6" s="269" t="str">
+        <x:v>Priority 2</x:v>
+      </x:c>
+      <x:c r="FP6" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ6" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR6" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS6" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT6" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU6" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV6" s="269" t="str">
+        <x:v>linked_facility_context; reference_point_* describes policy jurisdiction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="101.25" customHeight="1">
+      <x:c r="A7" s="248" t="str">
+        <x:v>TNMOR-003</x:v>
+      </x:c>
+      <x:c r="B7" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C7" s="248" t="str">
+        <x:v>Cedar Hill</x:v>
+      </x:c>
+      <x:c r="D7" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E7" s="248" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="F7" s="249" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="G7" s="248" t="str">
+        <x:v>2 years</x:v>
+      </x:c>
+      <x:c r="H7" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I7" s="248" t="str">
+        <x:v>Two-year pause on data centers and cryptocurrency-mining facilities within Cedar Hill city limits.</x:v>
+      </x:c>
+      <x:c r="J7" s="248" t="str">
+        <x:v>The city cited potential electrical, water and wastewater, traffic and noise impacts and protection of rural character; reporting said no proposal was pending at adoption.</x:v>
+      </x:c>
+      <x:c r="K7" s="248" t="str">
+        <x:v>WSMV / Main Street Media</x:v>
+      </x:c>
+      <x:c r="L7" s="248" t="str">
+        <x:v>https://www.wsmv.com/2026/06/02/cedar-hill-imposes-two-year-moratorium-data-centers/ | https://www.cityofcedarhill.org/ws/media-library/e8c838795653fd4e0a9e648ee97d332b/commission-agenda-060126.pdf</x:v>
+      </x:c>
+      <x:c r="M7" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N7" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O7" s="248" t="str">
+        <x:v>interconnected-capital:tn:cedar-hill:2026-06-01</x:v>
+      </x:c>
+      <x:c r="P7" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q7" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R7" s="248" t="str">
+        <x:v>media-corroborated</x:v>
+      </x:c>
+      <x:c r="S7" s="257" t="n">
+        <x:v>36.5518</x:v>
+      </x:c>
+      <x:c r="T7" s="257" t="n">
+        <x:v>-87.00159</x:v>
+      </x:c>
+      <x:c r="U7" s="248" t="str">
+        <x:v>Cedar Hill municipal locality, Robertson County, TN</x:v>
+      </x:c>
+      <x:c r="V7" s="248" t="str">
+        <x:v>area_or_city</x:v>
+      </x:c>
+      <x:c r="W7" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Cedar%20Hill%2C%20Tennessee#map=15/36.55180/-87.00159</x:v>
+      </x:c>
+      <x:c r="X7" s="248" t="str">
+        <x:v>Municipal-area reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y7" s="248"/>
+      <x:c r="Z7" s="248"/>
+      <x:c r="AA7" s="248"/>
+      <x:c r="AB7" s="248"/>
+      <x:c r="AC7" s="248" t="str">
+        <x:v>Cedar Hill municipal locality, Robertson County, TN</x:v>
+      </x:c>
+      <x:c r="AD7" s="248" t="str">
+        <x:v>Cedar Hill</x:v>
+      </x:c>
+      <x:c r="AE7" s="248" t="str">
+        <x:v>Robertson</x:v>
+      </x:c>
+      <x:c r="AF7" s="248" t="str">
+        <x:v>37032</x:v>
+      </x:c>
+      <x:c r="AG7" s="248" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="AH7" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Cedar%20Hill%2C%20Tennessee#map=15/36.55180/-87.00159</x:v>
+      </x:c>
+      <x:c r="AI7" s="248"/>
+      <x:c r="AJ7" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK7" s="248"/>
+      <x:c r="AL7" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM7" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN7" s="248"/>
+      <x:c r="AO7" s="248"/>
+      <x:c r="AP7" s="248"/>
+      <x:c r="AQ7" s="248"/>
+      <x:c r="AR7" s="248"/>
+      <x:c r="AS7" s="248"/>
+      <x:c r="AT7" s="248"/>
+      <x:c r="AU7" s="248" t="str">
+        <x:v>interconnected_capital | wsmv.com | cityofcedarhill.org</x:v>
+      </x:c>
+      <x:c r="AV7" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW7" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX7" s="248" t="str">
+        <x:v>interconnected-capital:tn:cedar-hill:2026-06-01</x:v>
+      </x:c>
+      <x:c r="AY7" s="248" t="str">
+        <x:v>https://www.wsmv.com/2026/06/02/cedar-hill-imposes-two-year-moratorium-data-centers/ | https://www.cityofcedarhill.org/ws/media-library/e8c838795653fd4e0a9e648ee97d332b/commission-agenda-060126.pdf | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ7" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA7" s="248" t="str">
+        <x:v>reported_policy_action_corroborated</x:v>
+      </x:c>
+      <x:c r="BB7" s="248"/>
+      <x:c r="BC7" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD7" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE7" s="248"/>
+      <x:c r="BF7" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="BG7" s="248" t="str">
+        <x:v>Policy event, not a facility. media-corroborated. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH7" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI7" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ7" s="248"/>
+      <x:c r="BK7" s="248"/>
+      <x:c r="BL7" s="248" t="n">
+        <x:v>1.1524071801</x:v>
+      </x:c>
+      <x:c r="BM7" s="248" t="n">
+        <x:v>3.3353515807</x:v>
+      </x:c>
+      <x:c r="BN7" s="248" t="n">
+        <x:v>3.3446908334</x:v>
+      </x:c>
+      <x:c r="BO7" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP7" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ7" s="248" t="n">
+        <x:v>1.0203588232</x:v>
+      </x:c>
+      <x:c r="BR7" s="248" t="n">
+        <x:v>13.9458672925</x:v>
+      </x:c>
+      <x:c r="BS7" s="248" t="n">
+        <x:v>0.2076064974</x:v>
+      </x:c>
+      <x:c r="BT7" s="248" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="BU7" s="248" t="str">
+        <x:v>47147</x:v>
+      </x:c>
+      <x:c r="BV7" s="248" t="str">
+        <x:v>Robertson County</x:v>
+      </x:c>
+      <x:c r="BW7" s="248" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="BX7" s="248" t="n">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="BY7" s="248" t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="BZ7" s="248" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="CA7" s="248" t="n">
+        <x:v>1625</x:v>
+      </x:c>
+      <x:c r="CB7" s="248" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="CC7" s="248" t="n">
+        <x:v>21552</x:v>
+      </x:c>
+      <x:c r="CD7" s="248" t="n">
+        <x:v>1358</x:v>
+      </x:c>
+      <x:c r="CE7" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF7" s="248" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="CG7" s="248" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="CH7" s="248" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="CI7" s="248" t="n">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="CJ7" s="248" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="CK7" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL7" s="248"/>
+      <x:c r="CM7" s="248" t="str">
+        <x:v>TN5K-1792</x:v>
+      </x:c>
+      <x:c r="CN7" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO7" s="248"/>
+      <x:c r="CP7" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ7" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CR7" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CS7" s="248" t="n">
+        <x:v>0.6027814307</x:v>
+      </x:c>
+      <x:c r="CT7" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU7" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV7" s="248" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CW7" s="248"/>
+      <x:c r="CX7" s="248"/>
+      <x:c r="CY7" s="248"/>
+      <x:c r="CZ7" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA7" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB7" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC7" s="85" t="str">
+        <x:v>https://www.wsmv.com/2026/06/02/cedar-hill-imposes-two-year-moratorium-data-centers/ | https://www.cityofcedarhill.org/ws/media-library/e8c838795653fd4e0a9e648ee97d332b/commission-agenda-060126.pdf</x:v>
+      </x:c>
+      <x:c r="DD7" s="85" t="str">
+        <x:v>City agenda confirms the June 1 meeting; local reporting confirms approval and the two-year duration. No named project is identified.</x:v>
+      </x:c>
+      <x:c r="DE7" s="85"/>
+      <x:c r="DF7" s="85"/>
+      <x:c r="DG7" s="85"/>
+      <x:c r="DH7" s="85"/>
+      <x:c r="DI7" s="85" t="str">
+        <x:v>Cedar Hill</x:v>
+      </x:c>
+      <x:c r="DJ7" s="85" t="str">
+        <x:v>Robertson County</x:v>
+      </x:c>
+      <x:c r="DK7" s="85" t="str">
+        <x:v>47147</x:v>
+      </x:c>
+      <x:c r="DL7" s="85" t="str">
+        <x:v>Cedar Hill municipal locality, Robertson County, TN</x:v>
+      </x:c>
+      <x:c r="DM7" s="85" t="str">
+        <x:v>37032</x:v>
+      </x:c>
+      <x:c r="DN7" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO7" s="85" t="str">
+        <x:v>TN5K-1792</x:v>
+      </x:c>
+      <x:c r="DP7" s="85" t="n">
+        <x:v>1.014</x:v>
+      </x:c>
+      <x:c r="DQ7" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR7" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS7" s="85"/>
+      <x:c r="DT7" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU7" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV7" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DW7" s="85" t="n">
+        <x:v>0.6027814307</x:v>
+      </x:c>
+      <x:c r="DX7" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY7" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ7" s="85" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="EA7" s="85" t="n">
+        <x:v>1.1524071801</x:v>
+      </x:c>
+      <x:c r="EB7" s="85" t="n">
+        <x:v>3.3353515807</x:v>
+      </x:c>
+      <x:c r="EC7" s="85" t="n">
+        <x:v>3.3446908334</x:v>
+      </x:c>
+      <x:c r="ED7" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE7" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="EF7" s="85" t="n">
+        <x:v>1.0203588232</x:v>
+      </x:c>
+      <x:c r="EG7" s="85" t="n">
+        <x:v>13.9458672925</x:v>
+      </x:c>
+      <x:c r="EH7" s="85" t="n">
+        <x:v>0.2076064974</x:v>
+      </x:c>
+      <x:c r="EI7" s="85" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="EJ7" s="85" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="EK7" s="85" t="n">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="EL7" s="85" t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="EM7" s="85" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="EN7" s="85" t="n">
+        <x:v>1625</x:v>
+      </x:c>
+      <x:c r="EO7" s="85" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="EP7" s="85" t="n">
+        <x:v>21552</x:v>
+      </x:c>
+      <x:c r="EQ7" s="85" t="n">
+        <x:v>1358</x:v>
+      </x:c>
+      <x:c r="ER7" s="85" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="ES7" s="85" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="ET7" s="85" t="n">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="EU7" s="85" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="EV7" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW7" s="268" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="EX7" s="268" t="n">
+        <x:v>46905</x:v>
+      </x:c>
+      <x:c r="EY7" s="269" t="str">
+        <x:v>two-year anniversary calculated from reported adoption; exact sunset text not located</x:v>
+      </x:c>
+      <x:c r="EZ7" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA7" s="269" t="str">
+        <x:v>Cedar Hill city limits</x:v>
+      </x:c>
+      <x:c r="FB7" s="269" t="str">
+        <x:v>data centers; cryptocurrency-mining facilities</x:v>
+      </x:c>
+      <x:c r="FC7" s="269" t="str">
+        <x:v>city moratorium action, ordinance number unresolved</x:v>
+      </x:c>
+      <x:c r="FD7" s="269" t="str">
+        <x:v>https://www.cityofcedarhill.org/ws/media-library/e8c838795653fd4e0a9e648ee97d332b/commission-agenda-060126.pdf | https://www.wsmv.com/2026/06/02/cedar-hill-imposes-two-year-moratorium-data-centers/</x:v>
+      </x:c>
+      <x:c r="FE7" s="269"/>
+      <x:c r="FF7" s="269"/>
+      <x:c r="FG7" s="268"/>
+      <x:c r="FH7" s="268"/>
+      <x:c r="FI7" s="269" t="str">
+        <x:v>https://www.cityofcedarhill.org/government/</x:v>
+      </x:c>
+      <x:c r="FJ7" s="270" t="n">
+        <x:v>40.6513322706</x:v>
+      </x:c>
+      <x:c r="FK7" s="270" t="n">
+        <x:v>37.7431109087</x:v>
+      </x:c>
+      <x:c r="FL7" s="270" t="n">
+        <x:v>42.9196082897</x:v>
+      </x:c>
+      <x:c r="FM7" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN7" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO7" s="269" t="str">
+        <x:v>Lower empirical affinity</x:v>
+      </x:c>
+      <x:c r="FP7" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ7" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR7" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS7" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT7" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU7" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV7" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="101.25" customHeight="1">
+      <x:c r="A8" s="248" t="str">
+        <x:v>TNMOR-004</x:v>
+      </x:c>
+      <x:c r="B8" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C8" s="248" t="str">
+        <x:v>Paris</x:v>
+      </x:c>
+      <x:c r="D8" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E8" s="248" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="F8" s="249" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="G8" s="248" t="str">
+        <x:v>Until the revised zoning ordinance is completed, approved and effective; then terminates automatically</x:v>
+      </x:c>
+      <x:c r="H8" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I8" s="248" t="str">
+        <x:v>Pauses approval of development of computer/electronic data-processing centers within Paris city limits.</x:v>
+      </x:c>
+      <x:c r="J8" s="248" t="str">
+        <x:v>Temporary land-use control while the city completes and adopts revised zoning regulations.</x:v>
+      </x:c>
+      <x:c r="K8" s="248" t="str">
+        <x:v>Radio NWTN | City of Paris Commission minutes, Ordinance 1339; Radio NWTN</x:v>
+      </x:c>
+      <x:c r="L8" s="248" t="str">
+        <x:v>https://www.radionwtn.com/2026/07/01/city-commission-issues-temporary-moratorium-on-data-centers/ | https://paristn.gov/wp-content/uploads/2026/07/City-Commissioner-Minutes-06.04.2026.pdf | https://paristn.gov/wp-content/uploads/2026/08/City-Commissioner-Minutes-07.01.2026.pdf</x:v>
+      </x:c>
+      <x:c r="M8" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N8" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O8" s="248" t="str">
+        <x:v>interconnected-capital:tn:paris:2026-07-01</x:v>
+      </x:c>
+      <x:c r="P8" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q8" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R8" s="248" t="str">
+        <x:v>official-final-minutes-verified</x:v>
+      </x:c>
+      <x:c r="S8" s="257" t="n">
+        <x:v>36.302558</x:v>
+      </x:c>
+      <x:c r="T8" s="257" t="n">
+        <x:v>-88.328655</x:v>
+      </x:c>
+      <x:c r="U8" s="248" t="str">
+        <x:v>Paris City Hall, Paris, TN</x:v>
+      </x:c>
+      <x:c r="V8" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W8" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Paris%20City%20Hall%2C%20Tennessee#map=19/36.302558/-88.328655</x:v>
+      </x:c>
+      <x:c r="X8" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y8" s="248"/>
+      <x:c r="Z8" s="248"/>
+      <x:c r="AA8" s="248"/>
+      <x:c r="AB8" s="248"/>
+      <x:c r="AC8" s="248" t="str">
+        <x:v>Paris City Hall, 100 N Caldwell Street, Paris, TN 38242</x:v>
+      </x:c>
+      <x:c r="AD8" s="248" t="str">
+        <x:v>Paris</x:v>
+      </x:c>
+      <x:c r="AE8" s="248" t="str">
+        <x:v>Henry</x:v>
+      </x:c>
+      <x:c r="AF8" s="248" t="str">
+        <x:v>38242</x:v>
+      </x:c>
+      <x:c r="AG8" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH8" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Paris%20City%20Hall%2C%20Tennessee#map=19/36.302558/-88.328655</x:v>
+      </x:c>
+      <x:c r="AI8" s="248"/>
+      <x:c r="AJ8" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK8" s="248"/>
+      <x:c r="AL8" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM8" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN8" s="248"/>
+      <x:c r="AO8" s="248"/>
+      <x:c r="AP8" s="248"/>
+      <x:c r="AQ8" s="248"/>
+      <x:c r="AR8" s="248"/>
+      <x:c r="AS8" s="248"/>
+      <x:c r="AT8" s="248"/>
+      <x:c r="AU8" s="248" t="str">
+        <x:v>interconnected_capital | radionwtn.com | paristn.gov</x:v>
+      </x:c>
+      <x:c r="AV8" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW8" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX8" s="248" t="str">
+        <x:v>interconnected-capital:tn:paris:2026-07-01</x:v>
+      </x:c>
+      <x:c r="AY8" s="248" t="str">
+        <x:v>https://www.radionwtn.com/2026/07/01/city-commission-issues-temporary-moratorium-on-data-centers/ | https://paristn.gov/wp-content/uploads/2026/07/City-Commissioner-Minutes-06.04.2026.pdf | https://paristn.gov/wp-content/uploads/2026/08/City-Commissioner-Minutes-07.01.2026.pdf | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ8" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA8" s="248" t="str">
+        <x:v>official_policy_action_verified</x:v>
+      </x:c>
+      <x:c r="BB8" s="248"/>
+      <x:c r="BC8" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD8" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE8" s="248"/>
+      <x:c r="BF8" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="BG8" s="248" t="str">
+        <x:v>Policy event, not a facility. official-final-minutes-verified. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH8" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI8" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ8" s="248"/>
+      <x:c r="BK8" s="248"/>
+      <x:c r="BL8" s="248" t="n">
+        <x:v>2.242771886</x:v>
+      </x:c>
+      <x:c r="BM8" s="248" t="n">
+        <x:v>6.5173109592</x:v>
+      </x:c>
+      <x:c r="BN8" s="248" t="n">
+        <x:v>18.6641477203</x:v>
+      </x:c>
+      <x:c r="BO8" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP8" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ8" s="248" t="n">
+        <x:v>0.4888961211</x:v>
+      </x:c>
+      <x:c r="BR8" s="248" t="n">
+        <x:v>56.3021533807</x:v>
+      </x:c>
+      <x:c r="BS8" s="248" t="n">
+        <x:v>0.2247869188</x:v>
+      </x:c>
+      <x:c r="BT8" s="248" t="n">
+        <x:v>1267</x:v>
+      </x:c>
+      <x:c r="BU8" s="248" t="str">
+        <x:v>47079</x:v>
+      </x:c>
+      <x:c r="BV8" s="248" t="str">
+        <x:v>Henry County</x:v>
+      </x:c>
+      <x:c r="BW8" s="248" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BX8" s="248" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="BY8" s="248" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="BZ8" s="248" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="CA8" s="248" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="CB8" s="248" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="CC8" s="248" t="n">
+        <x:v>9513</x:v>
+      </x:c>
+      <x:c r="CD8" s="248" t="n">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="CE8" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF8" s="248" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="CG8" s="248" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="CH8" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CI8" s="248" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="CJ8" s="248" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="CK8" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL8" s="248"/>
+      <x:c r="CM8" s="248" t="str">
+        <x:v>TN5K-0946</x:v>
+      </x:c>
+      <x:c r="CN8" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO8" s="248"/>
+      <x:c r="CP8" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CQ8" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CR8" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS8" s="248" t="n">
+        <x:v>0.7329225507</x:v>
+      </x:c>
+      <x:c r="CT8" s="248" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CU8" s="248" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CV8" s="248" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="CW8" s="248"/>
+      <x:c r="CX8" s="248"/>
+      <x:c r="CY8" s="248"/>
+      <x:c r="CZ8" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA8" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB8" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC8" s="85" t="str">
+        <x:v>https://paristn.gov/wp-content/uploads/2026/07/City-Commissioner-Minutes-06.04.2026.pdf | https://www.radionwtn.com/2026/07/01/city-commission-issues-temporary-moratorium-on-data-centers/ | https://paristn.gov/wp-content/uploads/2026/08/City-Commissioner-Minutes-07.01.2026.pdf</x:v>
+      </x:c>
+      <x:c r="DD8" s="85" t="str">
+        <x:v>Official minutes establish adoption on June 4, 2026 (Ordinance 1339) and an end trigger tied to the revised zoning ordinance; this replaces the tracker-derived July 1 date and approximate one-year duration. | June 4 was first reading; July 1 was final passage and immediate effective date. End date depends on a revised zoning ordinance.</x:v>
+      </x:c>
+      <x:c r="DE8" s="85"/>
+      <x:c r="DF8" s="85"/>
+      <x:c r="DG8" s="85"/>
+      <x:c r="DH8" s="85"/>
+      <x:c r="DI8" s="85" t="str">
+        <x:v>Paris</x:v>
+      </x:c>
+      <x:c r="DJ8" s="85" t="str">
+        <x:v>Henry County</x:v>
+      </x:c>
+      <x:c r="DK8" s="85" t="str">
+        <x:v>47079</x:v>
+      </x:c>
+      <x:c r="DL8" s="85" t="str">
+        <x:v>Paris City Hall, 100 N Caldwell Street, Paris, TN 38242</x:v>
+      </x:c>
+      <x:c r="DM8" s="85" t="str">
+        <x:v>38242</x:v>
+      </x:c>
+      <x:c r="DN8" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO8" s="85" t="str">
+        <x:v>TN5K-0946</x:v>
+      </x:c>
+      <x:c r="DP8" s="85" t="n">
+        <x:v>2.409</x:v>
+      </x:c>
+      <x:c r="DQ8" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR8" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS8" s="85"/>
+      <x:c r="DT8" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DU8" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV8" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW8" s="85" t="n">
+        <x:v>0.7329225507</x:v>
+      </x:c>
+      <x:c r="DX8" s="85" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="DY8" s="85" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ8" s="85" t="str">
+        <x:v>west</x:v>
+      </x:c>
+      <x:c r="EA8" s="85" t="n">
+        <x:v>2.242771886</x:v>
+      </x:c>
+      <x:c r="EB8" s="85" t="n">
+        <x:v>6.5173109592</x:v>
+      </x:c>
+      <x:c r="EC8" s="85" t="n">
+        <x:v>18.6641477203</x:v>
+      </x:c>
+      <x:c r="ED8" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE8" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="EF8" s="85" t="n">
+        <x:v>0.4888961211</x:v>
+      </x:c>
+      <x:c r="EG8" s="85" t="n">
+        <x:v>56.3021533807</x:v>
+      </x:c>
+      <x:c r="EH8" s="85" t="n">
+        <x:v>0.2247869188</x:v>
+      </x:c>
+      <x:c r="EI8" s="85" t="n">
+        <x:v>1267</x:v>
+      </x:c>
+      <x:c r="EJ8" s="85" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="EK8" s="85" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="EL8" s="85" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="EM8" s="85" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="EN8" s="85" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="EO8" s="85" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="EP8" s="85" t="n">
+        <x:v>9513</x:v>
+      </x:c>
+      <x:c r="EQ8" s="85" t="n">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="ER8" s="85" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="ES8" s="85" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="ET8" s="85" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="EU8" s="85" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="EV8" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW8" s="268" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="EX8" s="268"/>
+      <x:c r="EY8" s="269" t="str">
+        <x:v>conditional: revised zoning ordinance becomes effective</x:v>
+      </x:c>
+      <x:c r="EZ8" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA8" s="269" t="str">
+        <x:v>Paris city limits</x:v>
+      </x:c>
+      <x:c r="FB8" s="269" t="str">
+        <x:v>computer/electronic data-processing centers</x:v>
+      </x:c>
+      <x:c r="FC8" s="269" t="str">
+        <x:v>Ordinance 1339</x:v>
+      </x:c>
+      <x:c r="FD8" s="269" t="str">
+        <x:v>https://paristn.gov/wp-content/uploads/2026/08/City-Commissioner-Minutes-07.01.2026.pdf</x:v>
+      </x:c>
+      <x:c r="FE8" s="269" t="str">
+        <x:v>June 4 was first reading; July 1 was final passage and immediate effective date. End date depends on a revised zoning ordinance.</x:v>
+      </x:c>
+      <x:c r="FF8" s="269"/>
+      <x:c r="FG8" s="268"/>
+      <x:c r="FH8" s="268"/>
+      <x:c r="FI8" s="269" t="str">
+        <x:v>https://paristn.gov/start-or-grow-a-business/</x:v>
+      </x:c>
+      <x:c r="FJ8" s="270" t="n">
+        <x:v>52.2887724892</x:v>
+      </x:c>
+      <x:c r="FK8" s="270" t="n">
+        <x:v>46.4620815304</x:v>
+      </x:c>
+      <x:c r="FL8" s="270" t="n">
+        <x:v>59.7904805284</x:v>
+      </x:c>
+      <x:c r="FM8" s="269" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="FN8" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO8" s="269" t="str">
+        <x:v>Watchlist</x:v>
+      </x:c>
+      <x:c r="FP8" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ8" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR8" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS8" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT8" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU8" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV8" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="101.25" customHeight="1">
+      <x:c r="A9" s="248" t="str">
+        <x:v>TNMOR-005</x:v>
+      </x:c>
+      <x:c r="B9" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C9" s="248" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="D9" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E9" s="248" t="str">
+        <x:v>County</x:v>
+      </x:c>
+      <x:c r="F9" s="249" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="G9" s="248" t="str">
+        <x:v>1 year</x:v>
+      </x:c>
+      <x:c r="H9" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I9" s="248" t="str">
+        <x:v>New data-center development in unincorporated Hamilton County; city jurisdictions are outside this county action.</x:v>
+      </x:c>
+      <x:c r="J9" s="248" t="str">
+        <x:v>One-year pause to let the planning department develop regulations amid energy and water concerns.</x:v>
+      </x:c>
+      <x:c r="K9" s="248" t="str">
+        <x:v>Chattanooga Times Free Press / WDEF</x:v>
+      </x:c>
+      <x:c r="L9" s="248" t="str">
+        <x:v>https://www.timesfreepress.com/news/2026/jul/15/hamilton-county-commission-approves-yearlong-data/ | https://www.hamiltontn.gov/MediaReleases/Mayor%20Wamp%20Proposes%20One-Year%20Moratorium%20on%20New%20Data%20Centers%20in%20Unincorporated%20Hamilton%20County.pdf</x:v>
+      </x:c>
+      <x:c r="M9" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N9" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O9" s="248" t="str">
+        <x:v>interconnected-capital:tn:hamilton-county:2026-07-15</x:v>
+      </x:c>
+      <x:c r="P9" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q9" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R9" s="248" t="str">
+        <x:v>media-corroborated; scope-context checked</x:v>
+      </x:c>
+      <x:c r="S9" s="257" t="n">
+        <x:v>35.049309</x:v>
+      </x:c>
+      <x:c r="T9" s="257" t="n">
+        <x:v>-85.306909</x:v>
+      </x:c>
+      <x:c r="U9" s="248" t="str">
+        <x:v>Hamilton County Courthouse, Chattanooga, TN</x:v>
+      </x:c>
+      <x:c r="V9" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W9" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Hamilton%20County%20Courthouse%2C%20Chattanooga%2C%20Tennessee#map=19/35.049309/-85.306909</x:v>
+      </x:c>
+      <x:c r="X9" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y9" s="248"/>
+      <x:c r="Z9" s="248"/>
+      <x:c r="AA9" s="248"/>
+      <x:c r="AB9" s="248"/>
+      <x:c r="AC9" s="248" t="str">
+        <x:v>Hamilton County Courthouse, 625 Georgia Avenue, Chattanooga, TN 37402</x:v>
+      </x:c>
+      <x:c r="AD9" s="248" t="str">
+        <x:v>Chattanooga</x:v>
+      </x:c>
+      <x:c r="AE9" s="248" t="str">
+        <x:v>Hamilton</x:v>
+      </x:c>
+      <x:c r="AF9" s="248" t="str">
+        <x:v>37402</x:v>
+      </x:c>
+      <x:c r="AG9" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH9" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Hamilton%20County%20Courthouse%2C%20Chattanooga%2C%20Tennessee#map=19/35.049309/-85.306909</x:v>
+      </x:c>
+      <x:c r="AI9" s="248"/>
+      <x:c r="AJ9" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK9" s="248"/>
+      <x:c r="AL9" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM9" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN9" s="248"/>
+      <x:c r="AO9" s="248"/>
+      <x:c r="AP9" s="248"/>
+      <x:c r="AQ9" s="248"/>
+      <x:c r="AR9" s="248"/>
+      <x:c r="AS9" s="248"/>
+      <x:c r="AT9" s="248"/>
+      <x:c r="AU9" s="248" t="str">
+        <x:v>interconnected_capital | timesfreepress.com | hamiltontn.gov</x:v>
+      </x:c>
+      <x:c r="AV9" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW9" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX9" s="248" t="str">
+        <x:v>interconnected-capital:tn:hamilton-county:2026-07-15</x:v>
+      </x:c>
+      <x:c r="AY9" s="248" t="str">
+        <x:v>https://www.timesfreepress.com/news/2026/jul/15/hamilton-county-commission-approves-yearlong-data/ | https://www.hamiltontn.gov/MediaReleases/Mayor%20Wamp%20Proposes%20One-Year%20Moratorium%20on%20New%20Data%20Centers%20in%20Unincorporated%20Hamilton%20County.pdf | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ9" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA9" s="248" t="str">
+        <x:v>reported_policy_action_corroborated</x:v>
+      </x:c>
+      <x:c r="BB9" s="248"/>
+      <x:c r="BC9" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD9" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE9" s="248"/>
+      <x:c r="BF9" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="BG9" s="248" t="str">
+        <x:v>Policy event, not a facility. media-corroborated; scope-context checked. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH9" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI9" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ9" s="248"/>
+      <x:c r="BK9" s="248"/>
+      <x:c r="BL9" s="248" t="n">
+        <x:v>3.264126973</x:v>
+      </x:c>
+      <x:c r="BM9" s="248" t="n">
+        <x:v>3.264126973</x:v>
+      </x:c>
+      <x:c r="BN9" s="248" t="n">
+        <x:v>8.4900454629</x:v>
+      </x:c>
+      <x:c r="BO9" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP9" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BQ9" s="248" t="n">
+        <x:v>0.2426543069</x:v>
+      </x:c>
+      <x:c r="BR9" s="248" t="n">
+        <x:v>3.7359647213</x:v>
+      </x:c>
+      <x:c r="BS9" s="248" t="n">
+        <x:v>0.1095350818</x:v>
+      </x:c>
+      <x:c r="BT9" s="248" t="n">
+        <x:v>1149</x:v>
+      </x:c>
+      <x:c r="BU9" s="248" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="BV9" s="248" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="BW9" s="248" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="BX9" s="248" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="BY9" s="248" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="BZ9" s="248" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="CA9" s="248" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="CB9" s="248" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="CC9" s="248" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="CD9" s="248" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="CE9" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF9" s="248" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="CG9" s="248" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="CH9" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CI9" s="248" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="CJ9" s="248" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="CK9" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL9" s="248"/>
+      <x:c r="CM9" s="248" t="str">
+        <x:v>TN5K-3028</x:v>
+      </x:c>
+      <x:c r="CN9" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO9" s="248"/>
+      <x:c r="CP9" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ9" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CR9" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS9" s="248" t="n">
+        <x:v>1.0866958482</x:v>
+      </x:c>
+      <x:c r="CT9" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU9" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV9" s="248" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CW9" s="248"/>
+      <x:c r="CX9" s="248"/>
+      <x:c r="CY9" s="248"/>
+      <x:c r="CZ9" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA9" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB9" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC9" s="85" t="str">
+        <x:v>https://www.timesfreepress.com/news/2026/jul/15/hamilton-county-commission-approves-yearlong-data/ | https://www.hamiltontn.gov/MediaReleases/Mayor%20Wamp%20Proposes%20One-Year%20Moratorium%20on%20New%20Data%20Centers%20in%20Unincorporated%20Hamilton%20County.pdf</x:v>
+      </x:c>
+      <x:c r="DD9" s="85" t="str">
+        <x:v>Coverage distinguishes the unincorporated-area pause from a small data center planned in the former Hamilton County Jail, which is within Chattanooga city limits. That facility is TNDC-004 and is not treated as subject to this moratorium.</x:v>
+      </x:c>
+      <x:c r="DE9" s="85"/>
+      <x:c r="DF9" s="85"/>
+      <x:c r="DG9" s="85" t="str">
+        <x:v>Former Hamilton County Jail data center, 601 Walnut St, Chattanooga (outside unincorporated county scope)</x:v>
+      </x:c>
+      <x:c r="DH9" s="85" t="str">
+        <x:v>TNDC-004</x:v>
+      </x:c>
+      <x:c r="DI9" s="85" t="str">
+        <x:v>Chattanooga</x:v>
+      </x:c>
+      <x:c r="DJ9" s="85" t="str">
+        <x:v>Hamilton County</x:v>
+      </x:c>
+      <x:c r="DK9" s="85" t="str">
+        <x:v>47065</x:v>
+      </x:c>
+      <x:c r="DL9" s="85" t="str">
+        <x:v>Hamilton County Courthouse, 625 Georgia Avenue, Chattanooga, TN 37402</x:v>
+      </x:c>
+      <x:c r="DM9" s="85" t="str">
+        <x:v>37402</x:v>
+      </x:c>
+      <x:c r="DN9" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO9" s="85" t="str">
+        <x:v>TN5K-3028</x:v>
+      </x:c>
+      <x:c r="DP9" s="85" t="n">
+        <x:v>2.41</x:v>
+      </x:c>
+      <x:c r="DQ9" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR9" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS9" s="85"/>
+      <x:c r="DT9" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU9" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV9" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW9" s="85" t="n">
+        <x:v>1.0866958482</x:v>
+      </x:c>
+      <x:c r="DX9" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY9" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ9" s="85" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="EA9" s="85" t="n">
+        <x:v>3.264126973</x:v>
+      </x:c>
+      <x:c r="EB9" s="85" t="n">
+        <x:v>3.264126973</x:v>
+      </x:c>
+      <x:c r="EC9" s="85" t="n">
+        <x:v>8.4900454629</x:v>
+      </x:c>
+      <x:c r="ED9" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE9" s="85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="EF9" s="85" t="n">
+        <x:v>0.2426543069</x:v>
+      </x:c>
+      <x:c r="EG9" s="85" t="n">
+        <x:v>3.7359647213</x:v>
+      </x:c>
+      <x:c r="EH9" s="85" t="n">
+        <x:v>0.1095350818</x:v>
+      </x:c>
+      <x:c r="EI9" s="85" t="n">
+        <x:v>1149</x:v>
+      </x:c>
+      <x:c r="EJ9" s="85" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="EK9" s="85" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="EL9" s="85" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="EM9" s="85" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="EN9" s="85" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="EO9" s="85" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="EP9" s="85" t="n">
+        <x:v>205761</x:v>
+      </x:c>
+      <x:c r="EQ9" s="85" t="n">
+        <x:v>9883</x:v>
+      </x:c>
+      <x:c r="ER9" s="85" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="ES9" s="85" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="ET9" s="85" t="n">
+        <x:v>10146</x:v>
+      </x:c>
+      <x:c r="EU9" s="85" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="EV9" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW9" s="268" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="EX9" s="268" t="n">
+        <x:v>46583</x:v>
+      </x:c>
+      <x:c r="EY9" s="269" t="str">
+        <x:v>one-year anniversary calculated from adoption; final resolution text not located</x:v>
+      </x:c>
+      <x:c r="EZ9" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA9" s="269" t="str">
+        <x:v>unincorporated Hamilton County</x:v>
+      </x:c>
+      <x:c r="FB9" s="269" t="str">
+        <x:v>new data-center development</x:v>
+      </x:c>
+      <x:c r="FC9" s="269" t="str">
+        <x:v>county commission moratorium action</x:v>
+      </x:c>
+      <x:c r="FD9" s="269" t="str">
+        <x:v>https://www.hamiltontn.gov/MediaReleases/Mayor%20Wamp%20Proposes%20One-Year%20Moratorium%20on%20New%20Data%20Centers%20in%20Unincorporated%20Hamilton%20County.pdf | https://www.timesfreepress.com/news/2026/jul/15/hamilton-county-commission-approves-yearlong-data/</x:v>
+      </x:c>
+      <x:c r="FE9" s="269"/>
+      <x:c r="FF9" s="269"/>
+      <x:c r="FG9" s="268"/>
+      <x:c r="FH9" s="268"/>
+      <x:c r="FI9" s="269" t="str">
+        <x:v>https://www.hamiltontn.gov/Directory.aspx</x:v>
+      </x:c>
+      <x:c r="FJ9" s="270" t="n">
+        <x:v>94.0560236848</x:v>
+      </x:c>
+      <x:c r="FK9" s="270" t="n">
+        <x:v>93.1553176953</x:v>
+      </x:c>
+      <x:c r="FL9" s="270" t="n">
+        <x:v>95.6217262583</x:v>
+      </x:c>
+      <x:c r="FM9" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN9" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO9" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP9" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ9" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR9" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS9" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT9" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU9" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV9" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="101.25" customHeight="1">
+      <x:c r="A10" s="248" t="str">
+        <x:v>TNMOR-006</x:v>
+      </x:c>
+      <x:c r="B10" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C10" s="248" t="str">
+        <x:v>Johnson City</x:v>
+      </x:c>
+      <x:c r="D10" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E10" s="248" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="F10" s="249" t="n">
+        <x:v>45813</x:v>
+      </x:c>
+      <x:c r="G10" s="248" t="str">
+        <x:v>Initial 12 months through June 5, 2026; extended six months through December 3, 2026</x:v>
+      </x:c>
+      <x:c r="H10" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I10" s="248" t="str">
+        <x:v>I-2 Heavy Industrial district: pauses acceptance of new industrial land-use applications and building permits for new construction; the city identifies data centers among the uses being studied.</x:v>
+      </x:c>
+      <x:c r="J10" s="248" t="str">
+        <x:v>The city extended the pause while staff study noise and vibration rules and data-center zoning standards, including noise limits and setbacks.</x:v>
+      </x:c>
+      <x:c r="K10" s="248" t="str">
+        <x:v>WJHL / Johnson City Press | Johnson City Commission May 21, 2026 agenda; WJHL / Johnson City Press</x:v>
+      </x:c>
+      <x:c r="L10" s="248" t="str">
+        <x:v>https://www.wjhl.com/news/local/johnson-city-commission-approves-moratorium-on-data-centers/ | https://johnsoncitytn.civicweb.net/document/336035/City%20Commission%20-%20May%2021%202026.pdf?handle=B1188EF2E7EF4197AB6B139B10832F6A | https://johnsoncitytn.civicweb.net/document/321248/City%20Commission%20-%20Jun%2005%202025.pdf?handle=9FC2E0B6FE394EFF81503C2D3139640E | https://www.supertalk929.com/2026/05/22/johnson-city-commission-votes-to-extend-data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="M10" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N10" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O10" s="248" t="str">
+        <x:v>interconnected-capital:tn:johnson-city:2025-06-05</x:v>
+      </x:c>
+      <x:c r="P10" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q10" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not establish a one-to-one link to a workbook facility or candidate.</x:v>
+      </x:c>
+      <x:c r="R10" s="248" t="str">
+        <x:v>official-agenda-verified + media-corroborated</x:v>
+      </x:c>
+      <x:c r="S10" s="257" t="n">
+        <x:v>36.321213</x:v>
+      </x:c>
+      <x:c r="T10" s="257" t="n">
+        <x:v>-82.342265</x:v>
+      </x:c>
+      <x:c r="U10" s="248" t="str">
+        <x:v>Johnson City City Hall, 601 E Main St, Johnson City, TN</x:v>
+      </x:c>
+      <x:c r="V10" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W10" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Johnson%20City%20City%20Hall%2C%20Tennessee#map=19/36.321213/-82.342265</x:v>
+      </x:c>
+      <x:c r="X10" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y10" s="248"/>
+      <x:c r="Z10" s="248"/>
+      <x:c r="AA10" s="248"/>
+      <x:c r="AB10" s="248"/>
+      <x:c r="AC10" s="248" t="str">
+        <x:v>Johnson City City Hall, 601 E Main Street, Johnson City, TN 37601</x:v>
+      </x:c>
+      <x:c r="AD10" s="248" t="str">
+        <x:v>Johnson City</x:v>
+      </x:c>
+      <x:c r="AE10" s="248" t="str">
+        <x:v>Washington</x:v>
+      </x:c>
+      <x:c r="AF10" s="248" t="str">
+        <x:v>37601</x:v>
+      </x:c>
+      <x:c r="AG10" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH10" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Johnson%20City%20City%20Hall%2C%20Tennessee#map=19/36.321213/-82.342265</x:v>
+      </x:c>
+      <x:c r="AI10" s="248"/>
+      <x:c r="AJ10" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK10" s="248"/>
+      <x:c r="AL10" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM10" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN10" s="248"/>
+      <x:c r="AO10" s="248"/>
+      <x:c r="AP10" s="248"/>
+      <x:c r="AQ10" s="248"/>
+      <x:c r="AR10" s="248"/>
+      <x:c r="AS10" s="248"/>
+      <x:c r="AT10" s="248"/>
+      <x:c r="AU10" s="248" t="str">
+        <x:v>interconnected_capital | wjhl.com | johnsoncitytn.civicweb.net | supertalk929.com</x:v>
+      </x:c>
+      <x:c r="AV10" s="248" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AW10" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX10" s="248" t="str">
+        <x:v>interconnected-capital:tn:johnson-city:2025-06-05</x:v>
+      </x:c>
+      <x:c r="AY10" s="248" t="str">
+        <x:v>https://www.wjhl.com/news/local/johnson-city-commission-approves-moratorium-on-data-centers/ | https://johnsoncitytn.civicweb.net/document/336035/City%20Commission%20-%20May%2021%202026.pdf?handle=B1188EF2E7EF4197AB6B139B10832F6A | https://johnsoncitytn.civicweb.net/document/321248/City%20Commission%20-%20Jun%2005%202025.pdf?handle=9FC2E0B6FE394EFF81503C2D3139640E | https://www.supertalk929.com/2026/05/22/johnson-city-commission-votes-to-extend-data-center-moratorium/ | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ10" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA10" s="248" t="str">
+        <x:v>official_policy_action_verified</x:v>
+      </x:c>
+      <x:c r="BB10" s="248"/>
+      <x:c r="BC10" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BD10" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE10" s="248"/>
+      <x:c r="BF10" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="BG10" s="248" t="str">
+        <x:v>Policy event, not a facility. official-agenda-verified + media-corroborated. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH10" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI10" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ10" s="248"/>
+      <x:c r="BK10" s="248"/>
+      <x:c r="BL10" s="248" t="n">
+        <x:v>0.8911535106</x:v>
+      </x:c>
+      <x:c r="BM10" s="248" t="n">
+        <x:v>0.8911535106</x:v>
+      </x:c>
+      <x:c r="BN10" s="248" t="n">
+        <x:v>9.9225781212</x:v>
+      </x:c>
+      <x:c r="BO10" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP10" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BQ10" s="248" t="n">
+        <x:v>0.118526493</x:v>
+      </x:c>
+      <x:c r="BR10" s="248" t="n">
+        <x:v>2.1302262685</x:v>
+      </x:c>
+      <x:c r="BS10" s="248" t="n">
+        <x:v>0.5791602898</x:v>
+      </x:c>
+      <x:c r="BT10" s="248" t="n">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="BU10" s="248" t="str">
+        <x:v>47179</x:v>
+      </x:c>
+      <x:c r="BV10" s="248" t="str">
+        <x:v>Washington County</x:v>
+      </x:c>
+      <x:c r="BW10" s="248" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="BX10" s="248" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="BY10" s="248" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="BZ10" s="248" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="CA10" s="248" t="n">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="CB10" s="248" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="CC10" s="248" t="n">
+        <x:v>56072</x:v>
+      </x:c>
+      <x:c r="CD10" s="248" t="n">
+        <x:v>3076</x:v>
+      </x:c>
+      <x:c r="CE10" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF10" s="248" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="CG10" s="248" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="CH10" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CI10" s="248" t="n">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="CJ10" s="248" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="CK10" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CL10" s="248"/>
+      <x:c r="CM10" s="248" t="str">
+        <x:v>TN5K-4388</x:v>
+      </x:c>
+      <x:c r="CN10" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO10" s="248"/>
+      <x:c r="CP10" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ10" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CR10" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS10" s="248" t="n">
+        <x:v>1.7036637664</x:v>
+      </x:c>
+      <x:c r="CT10" s="248" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="CU10" s="248" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="CV10" s="248" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CW10" s="248"/>
+      <x:c r="CX10" s="248"/>
+      <x:c r="CY10" s="248"/>
+      <x:c r="CZ10" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA10" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB10" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC10" s="85" t="str">
+        <x:v>https://johnsoncitytn.civicweb.net/document/336035/City%20Commission%20-%20May%2021%202026.pdf?handle=B1188EF2E7EF4197AB6B139B10832F6A | https://www.wjhl.com/news/local/johnson-city-commission-approves-moratorium-on-data-centers/ | https://johnsoncitytn.civicweb.net/document/321248/City%20Commission%20-%20Jun%2005%202025.pdf?handle=9FC2E0B6FE394EFF81503C2D3139640E | https://www.supertalk929.com/2026/05/22/johnson-city-commission-votes-to-extend-data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="DD10" s="85" t="str">
+        <x:v>The May 21, 2026 city agenda describes the approved item as extending the original 12-month I-2 moratorium by six months. The June 5, 2025 resolution sets the original end date; city planning materials cover data-center noise, vibration and zoning standards. | Data centers are a motivating use; the operative I-2 pause covers all new industrial uses.</x:v>
+      </x:c>
+      <x:c r="DE10" s="85"/>
+      <x:c r="DF10" s="85"/>
+      <x:c r="DG10" s="85"/>
+      <x:c r="DH10" s="85"/>
+      <x:c r="DI10" s="85" t="str">
+        <x:v>Johnson City</x:v>
+      </x:c>
+      <x:c r="DJ10" s="85" t="str">
+        <x:v>Washington County</x:v>
+      </x:c>
+      <x:c r="DK10" s="85" t="str">
+        <x:v>47179</x:v>
+      </x:c>
+      <x:c r="DL10" s="85" t="str">
+        <x:v>Johnson City City Hall, 601 E Main Street, Johnson City, TN 37601</x:v>
+      </x:c>
+      <x:c r="DM10" s="85" t="str">
+        <x:v>37601</x:v>
+      </x:c>
+      <x:c r="DN10" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO10" s="85" t="str">
+        <x:v>TN5K-4388</x:v>
+      </x:c>
+      <x:c r="DP10" s="85" t="n">
+        <x:v>1.802</x:v>
+      </x:c>
+      <x:c r="DQ10" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR10" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS10" s="85"/>
+      <x:c r="DT10" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU10" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DV10" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW10" s="85" t="n">
+        <x:v>1.7036637664</x:v>
+      </x:c>
+      <x:c r="DX10" s="85" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="DY10" s="85" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ10" s="85" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="EA10" s="85" t="n">
+        <x:v>0.8911535106</x:v>
+      </x:c>
+      <x:c r="EB10" s="85" t="n">
+        <x:v>0.8911535106</x:v>
+      </x:c>
+      <x:c r="EC10" s="85" t="n">
+        <x:v>9.9225781212</x:v>
+      </x:c>
+      <x:c r="ED10" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE10" s="85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="EF10" s="85" t="n">
+        <x:v>0.118526493</x:v>
+      </x:c>
+      <x:c r="EG10" s="85" t="n">
+        <x:v>2.1302262685</x:v>
+      </x:c>
+      <x:c r="EH10" s="85" t="n">
+        <x:v>0.5791602898</x:v>
+      </x:c>
+      <x:c r="EI10" s="85" t="n">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="EJ10" s="85" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="EK10" s="85" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="EL10" s="85" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="EM10" s="85" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="EN10" s="85" t="n">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="EO10" s="85" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="EP10" s="85" t="n">
+        <x:v>56072</x:v>
+      </x:c>
+      <x:c r="EQ10" s="85" t="n">
+        <x:v>3076</x:v>
+      </x:c>
+      <x:c r="ER10" s="85" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="ES10" s="85" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="ET10" s="85" t="n">
+        <x:v>1514</x:v>
+      </x:c>
+      <x:c r="EU10" s="85" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="EV10" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW10" s="268" t="n">
+        <x:v>45813</x:v>
+      </x:c>
+      <x:c r="EX10" s="268" t="n">
+        <x:v>46359</x:v>
+      </x:c>
+      <x:c r="EY10" s="269" t="str">
+        <x:v>extension reported and city agenda corroborated</x:v>
+      </x:c>
+      <x:c r="EZ10" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA10" s="269" t="str">
+        <x:v>Johnson City I-2 Heavy Industrial zoning district</x:v>
+      </x:c>
+      <x:c r="FB10" s="269" t="str">
+        <x:v>all new industrial land-use applications and new construction permits in I-2</x:v>
+      </x:c>
+      <x:c r="FC10" s="269" t="str">
+        <x:v>2025 I-2 moratorium resolution and 2026 extension</x:v>
+      </x:c>
+      <x:c r="FD10" s="269" t="str">
+        <x:v>https://johnsoncitytn.civicweb.net/document/321248/City%20Commission%20-%20Jun%2005%202025.pdf?handle=9FC2E0B6FE394EFF81503C2D3139640E | https://johnsoncitytn.civicweb.net/document/336035/City%20Commission%20-%20May%2021%202026.pdf?handle=B1188EF2E7EF4197AB6B139B10832F6A | https://www.supertalk929.com/2026/05/22/johnson-city-commission-votes-to-extend-data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="FE10" s="269" t="str">
+        <x:v>Data centers are a motivating use; the operative I-2 pause covers all new industrial uses.</x:v>
+      </x:c>
+      <x:c r="FF10" s="269"/>
+      <x:c r="FG10" s="268"/>
+      <x:c r="FH10" s="268"/>
+      <x:c r="FI10" s="269" t="str">
+        <x:v>https://johnsoncitytn.civicweb.net/portal/</x:v>
+      </x:c>
+      <x:c r="FJ10" s="270" t="n">
+        <x:v>98.9751764974</x:v>
+      </x:c>
+      <x:c r="FK10" s="270" t="n">
+        <x:v>98.6005465725</x:v>
+      </x:c>
+      <x:c r="FL10" s="270" t="n">
+        <x:v>99.3167843316</x:v>
+      </x:c>
+      <x:c r="FM10" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN10" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO10" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP10" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ10" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR10" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS10" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT10" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU10" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV10" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="101.25" customHeight="1">
+      <x:c r="A11" s="248" t="str">
+        <x:v>TNMOR-007</x:v>
+      </x:c>
+      <x:c r="B11" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C11" s="248" t="str">
+        <x:v>Anderson County</x:v>
+      </x:c>
+      <x:c r="D11" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E11" s="248" t="str">
+        <x:v>County</x:v>
+      </x:c>
+      <x:c r="F11" s="249" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="G11" s="248" t="str">
+        <x:v>2 years</x:v>
+      </x:c>
+      <x:c r="H11" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I11" s="248" t="str">
+        <x:v>Two-year county moratorium covering new data centers, cryptocurrency-mining facilities and large battery facilities; reporting describes thresholds of at least 20,000 sq ft or 5 MW.</x:v>
+      </x:c>
+      <x:c r="J11" s="248" t="str">
+        <x:v>Pause adopted while officials develop rules for land use and impacts including water, energy and noise; county reporting stated there were no applicants or planned projects in unincorporated areas at the time.</x:v>
+      </x:c>
+      <x:c r="K11" s="248" t="str">
+        <x:v>WBIR | WBIR; The Courier News</x:v>
+      </x:c>
+      <x:c r="L11" s="248" t="str">
+        <x:v>https://www.wbir.com/article/news/local/oak-ridge-anderson/anderson-county-commissioners-2-year-moratorium-data-center-zoning-regulations/51-6546cfdc-a6ca-4d82-8f87-4d01faea40b6 | https://www.mycouriernews.com/articles/2026/06/11193/no-data-centers-crypto-batteries-for-two-years | https://andersoncountytn.gov/county-commission-meeting-agendas/</x:v>
+      </x:c>
+      <x:c r="M11" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N11" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O11" s="248" t="str">
+        <x:v>interconnected-capital:tn:anderson-county:2026-06-15</x:v>
+      </x:c>
+      <x:c r="P11" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q11" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R11" s="248" t="str">
+        <x:v>media-corroborated</x:v>
+      </x:c>
+      <x:c r="S11" s="257" t="n">
+        <x:v>36.100382</x:v>
+      </x:c>
+      <x:c r="T11" s="257" t="n">
+        <x:v>-84.133889</x:v>
+      </x:c>
+      <x:c r="U11" s="248" t="str">
+        <x:v>Anderson County Courthouse, Clinton, TN</x:v>
+      </x:c>
+      <x:c r="V11" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W11" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Anderson%20County%20Courthouse%2C%20Clinton%2C%20Tennessee#map=19/36.100382/-84.133889</x:v>
+      </x:c>
+      <x:c r="X11" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y11" s="248"/>
+      <x:c r="Z11" s="248"/>
+      <x:c r="AA11" s="248"/>
+      <x:c r="AB11" s="248"/>
+      <x:c r="AC11" s="248" t="str">
+        <x:v>Anderson County Courthouse, 100 N Main Street, Clinton, TN 37716</x:v>
+      </x:c>
+      <x:c r="AD11" s="248" t="str">
+        <x:v>Clinton</x:v>
+      </x:c>
+      <x:c r="AE11" s="248" t="str">
+        <x:v>Anderson</x:v>
+      </x:c>
+      <x:c r="AF11" s="248" t="str">
+        <x:v>37716</x:v>
+      </x:c>
+      <x:c r="AG11" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH11" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Anderson%20County%20Courthouse%2C%20Clinton%2C%20Tennessee#map=19/36.100382/-84.133889</x:v>
+      </x:c>
+      <x:c r="AI11" s="248"/>
+      <x:c r="AJ11" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK11" s="248"/>
+      <x:c r="AL11" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM11" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN11" s="248"/>
+      <x:c r="AO11" s="248"/>
+      <x:c r="AP11" s="248"/>
+      <x:c r="AQ11" s="248"/>
+      <x:c r="AR11" s="248"/>
+      <x:c r="AS11" s="248"/>
+      <x:c r="AT11" s="248"/>
+      <x:c r="AU11" s="248" t="str">
+        <x:v>interconnected_capital | wbir.com | mycouriernews.com | andersoncountytn.gov</x:v>
+      </x:c>
+      <x:c r="AV11" s="248" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AW11" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX11" s="248" t="str">
+        <x:v>interconnected-capital:tn:anderson-county:2026-06-15</x:v>
+      </x:c>
+      <x:c r="AY11" s="248" t="str">
+        <x:v>https://www.wbir.com/article/news/local/oak-ridge-anderson/anderson-county-commissioners-2-year-moratorium-data-center-zoning-regulations/51-6546cfdc-a6ca-4d82-8f87-4d01faea40b6 | https://www.mycouriernews.com/articles/2026/06/11193/no-data-centers-crypto-batteries-for-two-years | https://andersoncountytn.gov/county-commission-meeting-agendas/ | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ11" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA11" s="248" t="str">
+        <x:v>reported_policy_action_corroborated</x:v>
+      </x:c>
+      <x:c r="BB11" s="248"/>
+      <x:c r="BC11" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BD11" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE11" s="248"/>
+      <x:c r="BF11" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="BG11" s="248" t="str">
+        <x:v>Policy event, not a facility. media-corroborated. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH11" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI11" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ11" s="248"/>
+      <x:c r="BK11" s="248"/>
+      <x:c r="BL11" s="248" t="n">
+        <x:v>0.0789438907</x:v>
+      </x:c>
+      <x:c r="BM11" s="248" t="n">
+        <x:v>0.0869040381</x:v>
+      </x:c>
+      <x:c r="BN11" s="248" t="n">
+        <x:v>7.5008185596</x:v>
+      </x:c>
+      <x:c r="BO11" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP11" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ11" s="248" t="n">
+        <x:v>0.6497247265</x:v>
+      </x:c>
+      <x:c r="BR11" s="248" t="n">
+        <x:v>6.1561244187</x:v>
+      </x:c>
+      <x:c r="BS11" s="248" t="n">
+        <x:v>0.7389578725</x:v>
+      </x:c>
+      <x:c r="BT11" s="248" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="BU11" s="248" t="str">
+        <x:v>47001</x:v>
+      </x:c>
+      <x:c r="BV11" s="248" t="str">
+        <x:v>Anderson County</x:v>
+      </x:c>
+      <x:c r="BW11" s="248" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="BX11" s="248" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="BY11" s="248" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BZ11" s="248" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="CA11" s="248" t="n">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="CB11" s="248" t="n">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="CC11" s="248" t="n">
+        <x:v>48104</x:v>
+      </x:c>
+      <x:c r="CD11" s="248" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="CE11" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF11" s="248" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="CG11" s="248" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="CH11" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CI11" s="248" t="n">
+        <x:v>9995</x:v>
+      </x:c>
+      <x:c r="CJ11" s="248" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="CK11" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL11" s="248"/>
+      <x:c r="CM11" s="248" t="str">
+        <x:v>TN5K-3717</x:v>
+      </x:c>
+      <x:c r="CN11" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO11" s="248"/>
+      <x:c r="CP11" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CQ11" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CR11" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CS11" s="248" t="n">
+        <x:v>1.7558251462</x:v>
+      </x:c>
+      <x:c r="CT11" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU11" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV11" s="248" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CW11" s="248"/>
+      <x:c r="CX11" s="248"/>
+      <x:c r="CY11" s="248"/>
+      <x:c r="CZ11" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA11" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB11" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC11" s="85" t="str">
+        <x:v>https://www.wbir.com/article/news/local/oak-ridge-anderson/anderson-county-commissioners-2-year-moratorium-data-center-zoning-regulations/51-6546cfdc-a6ca-4d82-8f87-4d01faea40b6 | https://www.mycouriernews.com/articles/2026/06/11193/no-data-centers-crypto-batteries-for-two-years | https://www.aol.com/articles/anderson-county-halts-data-center-152328000.html | https://andersoncountytn.gov/county-commission-meeting-agendas/</x:v>
+      </x:c>
+      <x:c r="DD11" s="85" t="str">
+        <x:v>Scope expanded from the abbreviated tracker entry to include crypto-mining and large battery facilities. Contemporary reporting says no data-center applications or planned projects were then in the unincorporated county; no Master facility link is inferred.</x:v>
+      </x:c>
+      <x:c r="DE11" s="85"/>
+      <x:c r="DF11" s="85"/>
+      <x:c r="DG11" s="85"/>
+      <x:c r="DH11" s="85"/>
+      <x:c r="DI11" s="85" t="str">
+        <x:v>Clinton</x:v>
+      </x:c>
+      <x:c r="DJ11" s="85" t="str">
+        <x:v>Anderson County</x:v>
+      </x:c>
+      <x:c r="DK11" s="85" t="str">
+        <x:v>47001</x:v>
+      </x:c>
+      <x:c r="DL11" s="85" t="str">
+        <x:v>Anderson County Courthouse, 100 N Main Street, Clinton, TN 37716</x:v>
+      </x:c>
+      <x:c r="DM11" s="85" t="str">
+        <x:v>37716</x:v>
+      </x:c>
+      <x:c r="DN11" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO11" s="85" t="str">
+        <x:v>TN5K-3717</x:v>
+      </x:c>
+      <x:c r="DP11" s="85" t="n">
+        <x:v>2.163</x:v>
+      </x:c>
+      <x:c r="DQ11" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR11" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS11" s="85"/>
+      <x:c r="DT11" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DU11" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DV11" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DW11" s="85" t="n">
+        <x:v>1.7558251462</x:v>
+      </x:c>
+      <x:c r="DX11" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY11" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ11" s="85" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="EA11" s="85" t="n">
+        <x:v>0.0789438907</x:v>
+      </x:c>
+      <x:c r="EB11" s="85" t="n">
+        <x:v>0.0869040381</x:v>
+      </x:c>
+      <x:c r="EC11" s="85" t="n">
+        <x:v>7.5008185596</x:v>
+      </x:c>
+      <x:c r="ED11" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE11" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="EF11" s="85" t="n">
+        <x:v>0.6497247265</x:v>
+      </x:c>
+      <x:c r="EG11" s="85" t="n">
+        <x:v>6.1561244187</x:v>
+      </x:c>
+      <x:c r="EH11" s="85" t="n">
+        <x:v>0.7389578725</x:v>
+      </x:c>
+      <x:c r="EI11" s="85" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="EJ11" s="85" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="EK11" s="85" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="EL11" s="85" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="EM11" s="85" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="EN11" s="85" t="n">
+        <x:v>1987</x:v>
+      </x:c>
+      <x:c r="EO11" s="85" t="n">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="EP11" s="85" t="n">
+        <x:v>48104</x:v>
+      </x:c>
+      <x:c r="EQ11" s="85" t="n">
+        <x:v>1599</x:v>
+      </x:c>
+      <x:c r="ER11" s="85" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="ES11" s="85" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="ET11" s="85" t="n">
+        <x:v>9995</x:v>
+      </x:c>
+      <x:c r="EU11" s="85" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="EV11" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW11" s="268" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="EX11" s="268" t="n">
+        <x:v>46919</x:v>
+      </x:c>
+      <x:c r="EY11" s="269" t="str">
+        <x:v>two-year anniversary calculated from reported adoption; final text not located</x:v>
+      </x:c>
+      <x:c r="EZ11" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA11" s="269" t="str">
+        <x:v>unincorporated Anderson County</x:v>
+      </x:c>
+      <x:c r="FB11" s="269" t="str">
+        <x:v>new data centers; cryptocurrency mining; large battery facilities</x:v>
+      </x:c>
+      <x:c r="FC11" s="269" t="str">
+        <x:v>county commission moratorium action</x:v>
+      </x:c>
+      <x:c r="FD11" s="269" t="str">
+        <x:v>https://andersoncountytn.gov/county-commission-meeting-agendas/ | https://www.mycouriernews.com/articles/2026/06/11193/no-data-centers-crypto-batteries-for-two-years</x:v>
+      </x:c>
+      <x:c r="FE11" s="269"/>
+      <x:c r="FF11" s="269"/>
+      <x:c r="FG11" s="268"/>
+      <x:c r="FH11" s="268"/>
+      <x:c r="FI11" s="269" t="str">
+        <x:v>https://andersoncountytn.gov/humanresources/currentjobopenings/</x:v>
+      </x:c>
+      <x:c r="FJ11" s="270" t="n">
+        <x:v>94.7620132088</x:v>
+      </x:c>
+      <x:c r="FK11" s="270" t="n">
+        <x:v>93.8601685265</x:v>
+      </x:c>
+      <x:c r="FL11" s="270" t="n">
+        <x:v>96.4290594398</x:v>
+      </x:c>
+      <x:c r="FM11" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN11" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO11" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP11" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ11" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR11" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS11" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT11" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU11" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV11" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="101.25" customHeight="1">
+      <x:c r="A12" s="248" t="str">
+        <x:v>TNMOR-008</x:v>
+      </x:c>
+      <x:c r="B12" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C12" s="248" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="D12" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E12" s="248" t="str">
+        <x:v>County</x:v>
+      </x:c>
+      <x:c r="F12" s="249" t="n">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="G12" s="248" t="str">
+        <x:v>1 year</x:v>
+      </x:c>
+      <x:c r="H12" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I12" s="248" t="str">
+        <x:v>Private, non-government data-center businesses projected at 5 MW peak demand or refusing to disclose demand; existing operating facilities are excepted by the posted amended resolution, but may not increase contracted peak power or replace grid supply with on-site generation.</x:v>
+      </x:c>
+      <x:c r="J12" s="248" t="str">
+        <x:v>Resolution cites electricity-grid strain, water use, continuous noise, fire hazards, limited job creation and time needed to study impacts and draft regulations.</x:v>
+      </x:c>
+      <x:c r="K12" s="248" t="str">
+        <x:v>WVLT | Knox County Commission proposed amended resolution; WVLT</x:v>
+      </x:c>
+      <x:c r="L12" s="248" t="str">
+        <x:v>https://www.wvlt.tv/2026/06/23/data-center-builds-one-year-delay-knox-county-votes-adopt-one-year-moratorium/ | https://commission.knoxcountytn.gov/forums/topic/data-center-moratorium/</x:v>
+      </x:c>
+      <x:c r="M12" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N12" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O12" s="248" t="str">
+        <x:v>interconnected-capital:tn:knox-county:2026-06-23</x:v>
+      </x:c>
+      <x:c r="P12" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q12" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R12" s="248" t="str">
+        <x:v>commission-posted-amended-text + adoption-media-corroborated</x:v>
+      </x:c>
+      <x:c r="S12" s="257" t="n">
+        <x:v>35.961126</x:v>
+      </x:c>
+      <x:c r="T12" s="257" t="n">
+        <x:v>-83.916534</x:v>
+      </x:c>
+      <x:c r="U12" s="248" t="str">
+        <x:v>Knox County Courthouse, Knoxville, TN</x:v>
+      </x:c>
+      <x:c r="V12" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W12" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Knox%20County%20Courthouse%2C%20Knoxville%2C%20Tennessee#map=19/35.961126/-83.916534</x:v>
+      </x:c>
+      <x:c r="X12" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y12" s="248"/>
+      <x:c r="Z12" s="248"/>
+      <x:c r="AA12" s="248"/>
+      <x:c r="AB12" s="248"/>
+      <x:c r="AC12" s="248" t="str">
+        <x:v>Old Knox County Courthouse, 300 W Main Avenue, Knoxville, TN 37902</x:v>
+      </x:c>
+      <x:c r="AD12" s="248" t="str">
+        <x:v>Knoxville</x:v>
+      </x:c>
+      <x:c r="AE12" s="248" t="str">
+        <x:v>Knox</x:v>
+      </x:c>
+      <x:c r="AF12" s="248" t="str">
+        <x:v>37902</x:v>
+      </x:c>
+      <x:c r="AG12" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH12" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Knox%20County%20Courthouse%2C%20Knoxville%2C%20Tennessee#map=19/35.961126/-83.916534</x:v>
+      </x:c>
+      <x:c r="AI12" s="248"/>
+      <x:c r="AJ12" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK12" s="248"/>
+      <x:c r="AL12" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM12" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN12" s="248"/>
+      <x:c r="AO12" s="248"/>
+      <x:c r="AP12" s="248"/>
+      <x:c r="AQ12" s="248"/>
+      <x:c r="AR12" s="248"/>
+      <x:c r="AS12" s="248"/>
+      <x:c r="AT12" s="248"/>
+      <x:c r="AU12" s="248" t="str">
+        <x:v>interconnected_capital | wvlt.tv | commission.knoxcountytn.gov</x:v>
+      </x:c>
+      <x:c r="AV12" s="248" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW12" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX12" s="248" t="str">
+        <x:v>interconnected-capital:tn:knox-county:2026-06-23</x:v>
+      </x:c>
+      <x:c r="AY12" s="248" t="str">
+        <x:v>https://www.wvlt.tv/2026/06/23/data-center-builds-one-year-delay-knox-county-votes-adopt-one-year-moratorium/ | https://commission.knoxcountytn.gov/forums/topic/data-center-moratorium/ | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ12" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA12" s="248" t="str">
+        <x:v>reported_policy_action_corroborated</x:v>
+      </x:c>
+      <x:c r="BB12" s="248"/>
+      <x:c r="BC12" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD12" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE12" s="248"/>
+      <x:c r="BF12" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="BG12" s="248" t="str">
+        <x:v>Policy event, not a facility. commission-posted-amended-text + adoption-media-corroborated. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH12" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI12" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ12" s="248"/>
+      <x:c r="BK12" s="248"/>
+      <x:c r="BL12" s="248" t="n">
+        <x:v>0.4238389727</x:v>
+      </x:c>
+      <x:c r="BM12" s="248" t="n">
+        <x:v>3.544038491</x:v>
+      </x:c>
+      <x:c r="BN12" s="248" t="n">
+        <x:v>14.0006594234</x:v>
+      </x:c>
+      <x:c r="BO12" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP12" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BQ12" s="248" t="n">
+        <x:v>0.356613296</x:v>
+      </x:c>
+      <x:c r="BR12" s="248" t="n">
+        <x:v>1.7795201937</x:v>
+      </x:c>
+      <x:c r="BS12" s="248" t="n">
+        <x:v>0.2000148662</x:v>
+      </x:c>
+      <x:c r="BT12" s="248" t="n">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="BU12" s="248" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BV12" s="248" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BW12" s="248" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BX12" s="248" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="BY12" s="248" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BZ12" s="248" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="CA12" s="248" t="n">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="CB12" s="248" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="CC12" s="248" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="CD12" s="248" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="CE12" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF12" s="248" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="CG12" s="248" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="CH12" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CI12" s="248" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="CJ12" s="248" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="CK12" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL12" s="248"/>
+      <x:c r="CM12" s="248" t="str">
+        <x:v>TN5K-3835</x:v>
+      </x:c>
+      <x:c r="CN12" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO12" s="248"/>
+      <x:c r="CP12" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ12" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CR12" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS12" s="248" t="n">
+        <x:v>1.6440967056</x:v>
+      </x:c>
+      <x:c r="CT12" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU12" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV12" s="248" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CW12" s="248"/>
+      <x:c r="CX12" s="248"/>
+      <x:c r="CY12" s="248"/>
+      <x:c r="CZ12" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA12" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB12" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC12" s="85" t="str">
+        <x:v>https://commission.knoxcountytn.gov/forums/topic/data-center-moratorium/ | https://www.wvlt.tv/2026/06/23/data-center-builds-one-year-delay-knox-county-votes-adopt-one-year-moratorium/</x:v>
+      </x:c>
+      <x:c r="DD12" s="85" t="str">
+        <x:v>The commission-posted amended text lists five existing operations as exceptions. Matched by name/address to TNDC-017, TNDC-048, TNDC-018, TNDC-047 and TNDC-049. The TenHats exception address is 500 Fort Summit Way while Master TNDC-047 records 550 Fort Summit Way; this discrepancy is retained for review. The approved text's final attachment was not located, so exemption mapping reflects the posted amended text. | Threshold, existing-facility exceptions, and June 30 sunset derive from commission-posted amended draft; final adopted attachment remains unresolved.</x:v>
+      </x:c>
+      <x:c r="DE12" s="85" t="str">
+        <x:v>Bitdeer Tennessee (5101 S National Dr) | Infinity Data Center (2575 Willow Point Way) | Scipio Technologies (500 W Summit Hill) | TenHats Knoxville (500 Fort Summit Way) | Windstream Knoxville (2333 Lovell Rd)</x:v>
+      </x:c>
+      <x:c r="DF12" s="85" t="str">
+        <x:v>TNDC-017 | TNDC-048 | TNDC-018 | TNDC-047 (address discrepancy: 500 vs 550 Fort Summit Way) | TNDC-049</x:v>
+      </x:c>
+      <x:c r="DG12" s="85"/>
+      <x:c r="DH12" s="85"/>
+      <x:c r="DI12" s="85" t="str">
+        <x:v>Knoxville</x:v>
+      </x:c>
+      <x:c r="DJ12" s="85" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="DK12" s="85" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="DL12" s="85" t="str">
+        <x:v>Old Knox County Courthouse, 300 W Main Avenue, Knoxville, TN 37902</x:v>
+      </x:c>
+      <x:c r="DM12" s="85" t="str">
+        <x:v>37902</x:v>
+      </x:c>
+      <x:c r="DN12" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO12" s="85" t="str">
+        <x:v>TN5K-3835</x:v>
+      </x:c>
+      <x:c r="DP12" s="85" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="DQ12" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR12" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS12" s="85"/>
+      <x:c r="DT12" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU12" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV12" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW12" s="85" t="n">
+        <x:v>1.6440967056</x:v>
+      </x:c>
+      <x:c r="DX12" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY12" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ12" s="85" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="EA12" s="85" t="n">
+        <x:v>0.4238389727</x:v>
+      </x:c>
+      <x:c r="EB12" s="85" t="n">
+        <x:v>3.544038491</x:v>
+      </x:c>
+      <x:c r="EC12" s="85" t="n">
+        <x:v>14.0006594234</x:v>
+      </x:c>
+      <x:c r="ED12" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE12" s="85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="EF12" s="85" t="n">
+        <x:v>0.356613296</x:v>
+      </x:c>
+      <x:c r="EG12" s="85" t="n">
+        <x:v>1.7795201937</x:v>
+      </x:c>
+      <x:c r="EH12" s="85" t="n">
+        <x:v>0.2000148662</x:v>
+      </x:c>
+      <x:c r="EI12" s="85" t="n">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="EJ12" s="85" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="EK12" s="85" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="EL12" s="85" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="EM12" s="85" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="EN12" s="85" t="n">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="EO12" s="85" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="EP12" s="85" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="EQ12" s="85" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="ER12" s="85" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="ES12" s="85" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="ET12" s="85" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="EU12" s="85" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="EV12" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW12" s="268" t="n">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="EX12" s="268" t="n">
+        <x:v>46568</x:v>
+      </x:c>
+      <x:c r="EY12" s="269" t="str">
+        <x:v>commission-posted amended draft sunset; final adopted text not located</x:v>
+      </x:c>
+      <x:c r="EZ12" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA12" s="269" t="str">
+        <x:v>unincorporated Knox County</x:v>
+      </x:c>
+      <x:c r="FB12" s="269" t="str">
+        <x:v>private non-government data centers at 5 MW peak demand or refusing disclosure, per amended draft</x:v>
+      </x:c>
+      <x:c r="FC12" s="269" t="str">
+        <x:v>Knox County Commission moratorium resolution, amended draft</x:v>
+      </x:c>
+      <x:c r="FD12" s="269" t="str">
+        <x:v>https://commission.knoxcountytn.gov/forums/topic/data-center-moratorium/ | https://www.wvlt.tv/2026/06/23/data-center-builds-one-year-delay-knox-county-votes-adopt-one-year-moratorium/</x:v>
+      </x:c>
+      <x:c r="FE12" s="269" t="str">
+        <x:v>Threshold, existing-facility exceptions, and June 30 sunset derive from commission-posted amended draft; final adopted attachment remains unresolved.</x:v>
+      </x:c>
+      <x:c r="FF12" s="269"/>
+      <x:c r="FG12" s="268"/>
+      <x:c r="FH12" s="268"/>
+      <x:c r="FI12" s="269" t="str">
+        <x:v>https://commission.knoxcountytn.gov/faqs/</x:v>
+      </x:c>
+      <x:c r="FJ12" s="270" t="n">
+        <x:v>99.0434980642</x:v>
+      </x:c>
+      <x:c r="FK12" s="270" t="n">
+        <x:v>98.6927806878</x:v>
+      </x:c>
+      <x:c r="FL12" s="270" t="n">
+        <x:v>99.2302436803</x:v>
+      </x:c>
+      <x:c r="FM12" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN12" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO12" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP12" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ12" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR12" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS12" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT12" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU12" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV12" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="101.25" customHeight="1">
+      <x:c r="A13" s="248" t="str">
+        <x:v>TNMOR-009</x:v>
+      </x:c>
+      <x:c r="B13" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C13" s="248" t="str">
+        <x:v>Knoxville</x:v>
+      </x:c>
+      <x:c r="D13" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E13" s="248" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="F13" s="249" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="G13" s="248" t="str">
+        <x:v>1 year (emergency ordinance)</x:v>
+      </x:c>
+      <x:c r="H13" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I13" s="248" t="str">
+        <x:v>One-year moratorium on large data centers within Knoxville city limits; official city materials reviewed do not establish a 10 MW threshold.</x:v>
+      </x:c>
+      <x:c r="J13" s="248" t="str">
+        <x:v>Temporary pause while Planning develops site-selection and operating safeguards, addressing potential effects on neighbors and the broader community.</x:v>
+      </x:c>
+      <x:c r="K13" s="248" t="str">
+        <x:v>City of Knoxville | City of Knoxville; WATE / local reporting</x:v>
+      </x:c>
+      <x:c r="L13" s="248" t="str">
+        <x:v>https://www.knoxvilletn.gov/news/2026/cc_approves_waterfront_plan_data_ctr_moratorium | https://www.knoxvilletn.gov/news/2026/mayor_seeks_unified_approach_on_data_centers</x:v>
+      </x:c>
+      <x:c r="M13" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N13" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O13" s="248" t="str">
+        <x:v>interconnected-capital:tn:knoxville:2026-07-07</x:v>
+      </x:c>
+      <x:c r="P13" s="248" t="str">
+        <x:v>not_linked</x:v>
+      </x:c>
+      <x:c r="Q13" s="248" t="str">
+        <x:v>Jurisdiction-wide policy record; tracker does not identify a single facility or candidate row.</x:v>
+      </x:c>
+      <x:c r="R13" s="248" t="str">
+        <x:v>official-city-action-verified; threshold-qualified</x:v>
+      </x:c>
+      <x:c r="S13" s="257" t="n">
+        <x:v>35.960052</x:v>
+      </x:c>
+      <x:c r="T13" s="257" t="n">
+        <x:v>-83.9165</x:v>
+      </x:c>
+      <x:c r="U13" s="248" t="str">
+        <x:v>City of Knoxville government communications office, 400 Main St, Knoxville, TN 37902</x:v>
+      </x:c>
+      <x:c r="V13" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W13" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=400%20Main%20Street%2C%20Knoxville%2C%20Tennessee#map=19/35.960052/-83.916500</x:v>
+      </x:c>
+      <x:c r="X13" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y13" s="248"/>
+      <x:c r="Z13" s="248"/>
+      <x:c r="AA13" s="248"/>
+      <x:c r="AB13" s="248"/>
+      <x:c r="AC13" s="248" t="str">
+        <x:v>City-County Building, 400 Main Street, Knoxville, TN 37902</x:v>
+      </x:c>
+      <x:c r="AD13" s="248" t="str">
+        <x:v>Knoxville</x:v>
+      </x:c>
+      <x:c r="AE13" s="248" t="str">
+        <x:v>Knox</x:v>
+      </x:c>
+      <x:c r="AF13" s="248" t="str">
+        <x:v>37902</x:v>
+      </x:c>
+      <x:c r="AG13" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH13" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=400%20Main%20Street%2C%20Knoxville%2C%20Tennessee#map=19/35.960052/-83.916500</x:v>
+      </x:c>
+      <x:c r="AI13" s="248"/>
+      <x:c r="AJ13" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK13" s="248"/>
+      <x:c r="AL13" s="248" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="AM13" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN13" s="248"/>
+      <x:c r="AO13" s="248"/>
+      <x:c r="AP13" s="248"/>
+      <x:c r="AQ13" s="248"/>
+      <x:c r="AR13" s="248"/>
+      <x:c r="AS13" s="248"/>
+      <x:c r="AT13" s="248"/>
+      <x:c r="AU13" s="248" t="str">
+        <x:v>interconnected_capital | knoxvilletn.gov</x:v>
+      </x:c>
+      <x:c r="AV13" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW13" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX13" s="248" t="str">
+        <x:v>interconnected-capital:tn:knoxville:2026-07-07</x:v>
+      </x:c>
+      <x:c r="AY13" s="248" t="str">
+        <x:v>https://www.knoxvilletn.gov/news/2026/cc_approves_waterfront_plan_data_ctr_moratorium | https://www.knoxvilletn.gov/news/2026/mayor_seeks_unified_approach_on_data_centers | https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="AZ13" s="248" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="BA13" s="248" t="str">
+        <x:v>official_policy_action_verified</x:v>
+      </x:c>
+      <x:c r="BB13" s="248"/>
+      <x:c r="BC13" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD13" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BE13" s="248"/>
+      <x:c r="BF13" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="BG13" s="248" t="str">
+        <x:v>Policy event, not a facility. official-city-action-verified; threshold-qualified. Linked facility identity and capacity remain blank unless independently established.</x:v>
+      </x:c>
+      <x:c r="BH13" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI13" s="248" t="str">
+        <x:v>derived_from_frozen_5km_grid; jurisdiction reference point</x:v>
+      </x:c>
+      <x:c r="BJ13" s="248"/>
+      <x:c r="BK13" s="248"/>
+      <x:c r="BL13" s="248" t="n">
+        <x:v>0.4238389727</x:v>
+      </x:c>
+      <x:c r="BM13" s="248" t="n">
+        <x:v>3.544038491</x:v>
+      </x:c>
+      <x:c r="BN13" s="248" t="n">
+        <x:v>14.0006594234</x:v>
+      </x:c>
+      <x:c r="BO13" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP13" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BQ13" s="248" t="n">
+        <x:v>0.356613296</x:v>
+      </x:c>
+      <x:c r="BR13" s="248" t="n">
+        <x:v>1.7795201937</x:v>
+      </x:c>
+      <x:c r="BS13" s="248" t="n">
+        <x:v>0.2000148662</x:v>
+      </x:c>
+      <x:c r="BT13" s="248" t="n">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="BU13" s="248" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="BV13" s="248" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="BW13" s="248" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="BX13" s="248" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="BY13" s="248" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="BZ13" s="248" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="CA13" s="248" t="n">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="CB13" s="248" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="CC13" s="248" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="CD13" s="248" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="CE13" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF13" s="248" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="CG13" s="248" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="CH13" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CI13" s="248" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="CJ13" s="248" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="CK13" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL13" s="248"/>
+      <x:c r="CM13" s="248" t="str">
+        <x:v>TN5K-3835</x:v>
+      </x:c>
+      <x:c r="CN13" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CO13" s="248"/>
+      <x:c r="CP13" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ13" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CR13" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS13" s="248" t="n">
+        <x:v>1.6440967056</x:v>
+      </x:c>
+      <x:c r="CT13" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU13" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV13" s="248" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="CW13" s="248"/>
+      <x:c r="CX13" s="248"/>
+      <x:c r="CY13" s="248"/>
+      <x:c r="CZ13" s="248" t="str">
+        <x:v>complete_reference_point_proxy</x:v>
+      </x:c>
+      <x:c r="DA13" s="248" t="str">
+        <x:v>../model/phase 2/dataset/phase2_model_dataset.xlsx; Domain_Cells</x:v>
+      </x:c>
+      <x:c r="DB13" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC13" s="85" t="str">
+        <x:v>https://www.knoxvilletn.gov/news/2026/mayor_seeks_unified_approach_on_data_centers | https://www.knoxvilletn.gov/news/2026/cc_approves_waterfront_plan_data_ctr_moratorium</x:v>
+      </x:c>
+      <x:c r="DD13" s="85" t="str">
+        <x:v>The city states the pause concerns large data centers for one year. The existing ≥10 MW claim could not be verified in official city material, so it was removed pending a resolution text that supports that threshold.</x:v>
+      </x:c>
+      <x:c r="DE13" s="85"/>
+      <x:c r="DF13" s="85"/>
+      <x:c r="DG13" s="85"/>
+      <x:c r="DH13" s="85"/>
+      <x:c r="DI13" s="85" t="str">
+        <x:v>Knoxville</x:v>
+      </x:c>
+      <x:c r="DJ13" s="85" t="str">
+        <x:v>Knox County</x:v>
+      </x:c>
+      <x:c r="DK13" s="85" t="str">
+        <x:v>47093</x:v>
+      </x:c>
+      <x:c r="DL13" s="85" t="str">
+        <x:v>City-County Building, 400 Main Street, Knoxville, TN 37902</x:v>
+      </x:c>
+      <x:c r="DM13" s="85" t="str">
+        <x:v>37902</x:v>
+      </x:c>
+      <x:c r="DN13" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO13" s="85" t="str">
+        <x:v>TN5K-3835</x:v>
+      </x:c>
+      <x:c r="DP13" s="85" t="n">
+        <x:v>0.457</x:v>
+      </x:c>
+      <x:c r="DQ13" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR13" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS13" s="85"/>
+      <x:c r="DT13" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DU13" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV13" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW13" s="85" t="n">
+        <x:v>1.6440967056</x:v>
+      </x:c>
+      <x:c r="DX13" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY13" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ13" s="85" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="EA13" s="85" t="n">
+        <x:v>0.4238389727</x:v>
+      </x:c>
+      <x:c r="EB13" s="85" t="n">
+        <x:v>3.544038491</x:v>
+      </x:c>
+      <x:c r="EC13" s="85" t="n">
+        <x:v>14.0006594234</x:v>
+      </x:c>
+      <x:c r="ED13" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE13" s="85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="EF13" s="85" t="n">
+        <x:v>0.356613296</x:v>
+      </x:c>
+      <x:c r="EG13" s="85" t="n">
+        <x:v>1.7795201937</x:v>
+      </x:c>
+      <x:c r="EH13" s="85" t="n">
+        <x:v>0.2000148662</x:v>
+      </x:c>
+      <x:c r="EI13" s="85" t="n">
+        <x:v>1211</x:v>
+      </x:c>
+      <x:c r="EJ13" s="85" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="EK13" s="85" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="EL13" s="85" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="EM13" s="85" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="EN13" s="85" t="n">
+        <x:v>1975</x:v>
+      </x:c>
+      <x:c r="EO13" s="85" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="EP13" s="85" t="n">
+        <x:v>242117</x:v>
+      </x:c>
+      <x:c r="EQ13" s="85" t="n">
+        <x:v>12519</x:v>
+      </x:c>
+      <x:c r="ER13" s="85" t="n">
+        <x:v>4993</x:v>
+      </x:c>
+      <x:c r="ES13" s="85" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="ET13" s="85" t="n">
+        <x:v>13096</x:v>
+      </x:c>
+      <x:c r="EU13" s="85" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="EV13" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW13" s="268" t="n">
+        <x:v>46210</x:v>
+      </x:c>
+      <x:c r="EX13" s="268" t="n">
+        <x:v>46575</x:v>
+      </x:c>
+      <x:c r="EY13" s="269" t="str">
+        <x:v>one-year anniversary calculated from reported passage; exact legal effective date not checked</x:v>
+      </x:c>
+      <x:c r="EZ13" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FA13" s="269" t="str">
+        <x:v>Knoxville city limits</x:v>
+      </x:c>
+      <x:c r="FB13" s="269" t="str">
+        <x:v>large data centers; MW threshold unverified</x:v>
+      </x:c>
+      <x:c r="FC13" s="269" t="str">
+        <x:v>city council moratorium action</x:v>
+      </x:c>
+      <x:c r="FD13" s="269" t="str">
+        <x:v>https://www.knoxvilletn.gov/news/2026/cc_approves_waterfront_plan_data_ctr_moratorium</x:v>
+      </x:c>
+      <x:c r="FE13" s="269"/>
+      <x:c r="FF13" s="269"/>
+      <x:c r="FG13" s="268"/>
+      <x:c r="FH13" s="268"/>
+      <x:c r="FI13" s="269" t="str">
+        <x:v>https://www.knoxvilletn.gov/contact</x:v>
+      </x:c>
+      <x:c r="FJ13" s="270" t="n">
+        <x:v>99.0434980642</x:v>
+      </x:c>
+      <x:c r="FK13" s="270" t="n">
+        <x:v>98.6927806878</x:v>
+      </x:c>
+      <x:c r="FL13" s="270" t="n">
+        <x:v>99.2302436803</x:v>
+      </x:c>
+      <x:c r="FM13" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN13" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO13" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP13" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ13" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR13" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS13" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT13" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU13" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV13" s="269" t="str">
+        <x:v>jurisdiction_reference_point; no facility inferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="101.25" customHeight="1">
+      <x:c r="A14" s="248" t="str">
+        <x:v>TNMOR-010</x:v>
+      </x:c>
+      <x:c r="B14" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C14" s="248" t="str">
+        <x:v>Nashville-Davidson</x:v>
+      </x:c>
+      <x:c r="D14" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E14" s="248" t="str">
+        <x:v>Metro Government</x:v>
+      </x:c>
+      <x:c r="F14" s="249" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="G14" s="248" t="str">
+        <x:v>Until November 1, 2026 or the effective date of BL2026-1391 and BL2026-1392, whichever occurs first</x:v>
+      </x:c>
+      <x:c r="H14" s="248" t="str">
+        <x:v>Expired</x:v>
+      </x:c>
+      <x:c r="I14" s="248" t="str">
+        <x:v>Pauses acceptance, processing, approval and issuance of zoning, building and grading permits for data-center developments in Nashville-Davidson County; the ordinance exempts server rooms and certain principal-use workstations.</x:v>
+      </x:c>
+      <x:c r="J14" s="248" t="str">
+        <x:v>Interim measure while Metro establishes data-center use definitions, size/power categories, siting and operating standards, and permit requirements.</x:v>
+      </x:c>
+      <x:c r="K14" s="248" t="str">
+        <x:v>Nashville Banner | Nashville Metro Council Legistar BL2026-1448; Nashville Banner</x:v>
+      </x:c>
+      <x:c r="L14" s="248" t="str">
+        <x:v>https://nashvillebanner.com/2026/07/21/nashville-data-center-regulations-moratorium/ | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=2A6E536A-95F6-46B9-993A-1F6E018DD389&amp;ID=8063111 | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=007B8704-62ED-46D1-9E9A-8B3F778229A8&amp;ID=8040869 | https://nashville.legistar.com/LegislationDetail.aspx?From=RSS&amp;GUID=ABD166B5-005A-400B-B447-1F81227D7B2C&amp;ID=8040870</x:v>
+      </x:c>
+      <x:c r="M14" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N14" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O14" s="248" t="str">
+        <x:v>interconnected-capital:tn:nashville-davidson:2026-07-21</x:v>
+      </x:c>
+      <x:c r="P14" s="248" t="str">
+        <x:v>TNDC-032</x:v>
+      </x:c>
+      <x:c r="Q14" s="248" t="str">
+        <x:v>Policy-context relationship. The Nashville moratorium is jurisdiction-wide; independently sourced coverage identifies the DC BLOX Grassmere Park proposal as a concurrent data-center policy context. This is not a claim that the moratorium is project-specific.</x:v>
+      </x:c>
+      <x:c r="R14" s="248" t="str">
+        <x:v>official-ordinance-sunset-inferred</x:v>
+      </x:c>
+      <x:c r="S14" s="257" t="n">
+        <x:v>36.1627</x:v>
+      </x:c>
+      <x:c r="T14" s="257" t="n">
+        <x:v>-86.7816</x:v>
+      </x:c>
+      <x:c r="U14" s="248" t="str">
+        <x:v>Nashville-Davidson municipal locality, TN</x:v>
+      </x:c>
+      <x:c r="V14" s="248" t="str">
+        <x:v>area_or_city</x:v>
+      </x:c>
+      <x:c r="W14" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Nashville%2C%20Tennessee#map=13/36.1627/-86.7816</x:v>
+      </x:c>
+      <x:c r="X14" s="248" t="str">
+        <x:v>Metro-government area reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y14" s="248" t="str">
+        <x:v>TNDC-032</x:v>
+      </x:c>
+      <x:c r="Z14" s="248" t="str">
+        <x:v>DC BLOX Nashville (Grassmere Park)</x:v>
+      </x:c>
+      <x:c r="AA14" s="248" t="str">
+        <x:v>DC BLOX</x:v>
+      </x:c>
+      <x:c r="AB14" s="248" t="str">
+        <x:v>DC BLOX</x:v>
+      </x:c>
+      <x:c r="AC14" s="248" t="str">
+        <x:v>648 Grassmere Park</x:v>
+      </x:c>
+      <x:c r="AD14" s="248" t="str">
+        <x:v>Nashville</x:v>
+      </x:c>
+      <x:c r="AE14" s="248" t="str">
+        <x:v>Davidson</x:v>
+      </x:c>
+      <x:c r="AF14" s="248" t="str">
+        <x:v>37211</x:v>
+      </x:c>
+      <x:c r="AG14" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="AH14" s="248" t="str">
+        <x:v>fractracker:1780860040054-4476</x:v>
+      </x:c>
+      <x:c r="AI14" s="248" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="AJ14" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AK14" s="248" t="str">
+        <x:v>proposed</x:v>
+      </x:c>
+      <x:c r="AL14" s="248" t="str">
+        <x:v>proposed</x:v>
+      </x:c>
+      <x:c r="AM14" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN14" s="248" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="AO14" s="248" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="AP14" s="248" t="str">
+        <x:v>core_data_center</x:v>
+      </x:c>
+      <x:c r="AQ14" s="248"/>
+      <x:c r="AR14" s="248" t="n">
+        <x:v>69220</x:v>
+      </x:c>
+      <x:c r="AS14" s="248"/>
+      <x:c r="AT14" s="248"/>
+      <x:c r="AU14" s="248" t="str">
+        <x:v>compute_atlas | fractracker</x:v>
+      </x:c>
+      <x:c r="AV14" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW14" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AX14" s="248" t="str">
+        <x:v>compute_atlas:dcblox-nashville-grassmere-tn | fractracker:1780860040054-4476</x:v>
+      </x:c>
+      <x:c r="AY14" s="248" t="str">
+        <x:v>https://williamsonsource.com/dc-blox-sues-metro-over-blocked-data-center-project-near-nashville-zoo/ | https://www.wsmv.com/2026/07/22/metro-council-passes-first-data-center-regulations-nashville-heres-what-changes/ | https://www.yahoo.com/news/us/articles/guide-data-centers-tennessee-could-081728521.html | https://www.datacenterdynamics.com/en/news/dc-bloxs-proposed-24-acre-data-center-near-nashville-zoo-could-be-blocked-by-moratorium/ | https://www.wkrn.com/news/local-news/nashville/160k-sign-petition-opposing-data-center-next-nashville-zoo/ | https://www.wsmv.com/2026/06/04/what-know-about-potential-data-center-next-nashville-zoo-facility-launches-petition-against-its-construction-feet-away-one-most-fragile-rare-collections-animals/</x:v>
+      </x:c>
+      <x:c r="AZ14" s="248" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="BA14" s="248" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="BB14" s="248" t="str">
+        <x:v>identified</x:v>
+      </x:c>
+      <x:c r="BC14" s="248" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BD14" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE14" s="248" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="BF14" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="BG14" s="248" t="str">
+        <x:v>Cross-verified facility record; unresolved values remain null rather than inferred.</x:v>
+      </x:c>
+      <x:c r="BH14" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI14" s="248" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="BJ14" s="248" t="n">
+        <x:v>1.5634296886992427</x:v>
+      </x:c>
+      <x:c r="BK14" s="248" t="str">
+        <x:v>C2 Nashville area</x:v>
+      </x:c>
+      <x:c r="BL14" s="248" t="n">
+        <x:v>0.115983122705762</x:v>
+      </x:c>
+      <x:c r="BM14" s="248" t="n">
+        <x:v>0.6606674404981177</x:v>
+      </x:c>
+      <x:c r="BN14" s="248" t="n">
+        <x:v>11.2366852000021</x:v>
+      </x:c>
+      <x:c r="BO14" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP14" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ14" s="248" t="n">
+        <x:v>1.0324548896531869</x:v>
+      </x:c>
+      <x:c r="BR14" s="248" t="n">
+        <x:v>1.3766893607197908</x:v>
+      </x:c>
+      <x:c r="BS14" s="248" t="n">
+        <x:v>0.5877614886412902</x:v>
+      </x:c>
+      <x:c r="BT14" s="248" t="n">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="BU14" s="248" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="BV14" s="248" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="BW14" s="248" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="BX14" s="248" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="BY14" s="248" t="n">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="BZ14" s="248" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="CA14" s="248" t="n">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="CB14" s="248" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="CC14" s="248" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="CD14" s="248" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="CE14" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF14" s="248" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="CG14" s="248" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="CH14" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CI14" s="248" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="CJ14" s="248" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="CK14" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL14" s="248" t="str">
+        <x:v>TNDC-032</x:v>
+      </x:c>
+      <x:c r="CM14" s="248" t="str">
+        <x:v>TN5K-1969</x:v>
+      </x:c>
+      <x:c r="CN14" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CO14" s="248" t="str">
+        <x:v>open_water;regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="CP14" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CQ14" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CR14" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS14" s="248" t="str">
+        <x:v>1.356198446618186</x:v>
+      </x:c>
+      <x:c r="CT14" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU14" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV14" s="248" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CW14" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CX14" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CY14" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CZ14" s="248" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="DA14" s="248" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
+      <x:c r="DB14" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC14" s="85" t="str">
+        <x:v>https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=2A6E536A-95F6-46B9-993A-1F6E018DD389&amp;ID=8063111 | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=007B8704-62ED-46D1-9E9A-8B3F778229A8&amp;ID=8040869 | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=ABD166B5-005A-400B-B447-1F81227D7B2C&amp;ID=8040870 | https://nashvillebanner.com/2026/07/21/nashville-data-center-regulations-moratorium/ | https://nashville.legistar.com/LegislationDetail.aspx?From=RSS&amp;GUID=ABD166B5-005A-400B-B447-1F81227D7B2C&amp;ID=8040870</x:v>
+      </x:c>
+      <x:c r="DD14" s="85" t="str">
+        <x:v>BL2026-1448 passed July 21 and took effect on publication; final text makes the sunset November 1 or the effective date of both zoning bills, whichever occurs first. BL2026-1391 and BL2026-1392 passed third reading July 21; the exact interaction of their effective dates with the moratorium sunset should be monitored. TNDC-032 is retained as policy context, not a one-to-one affected-site link. | BL2026-1391 and BL2026-1392 both became effective July 31; BL2026-1448 sunsets on their joint effective date or November 1, whichever occurs first.</x:v>
+      </x:c>
+      <x:c r="DE14" s="85"/>
+      <x:c r="DF14" s="85"/>
+      <x:c r="DG14" s="85"/>
+      <x:c r="DH14" s="85"/>
+      <x:c r="DI14" s="85" t="str">
+        <x:v>Nashville</x:v>
+      </x:c>
+      <x:c r="DJ14" s="85" t="str">
+        <x:v>Davidson County</x:v>
+      </x:c>
+      <x:c r="DK14" s="85" t="str">
+        <x:v>47037</x:v>
+      </x:c>
+      <x:c r="DL14" s="85" t="str">
+        <x:v>Nashville-Davidson municipal locality, TN</x:v>
+      </x:c>
+      <x:c r="DM14" s="85" t="str"/>
+      <x:c r="DN14" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO14" s="85" t="str">
+        <x:v>TN5K-1971</x:v>
+      </x:c>
+      <x:c r="DP14" s="85" t="n">
+        <x:v>2.128</x:v>
+      </x:c>
+      <x:c r="DQ14" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR14" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS14" s="85"/>
+      <x:c r="DT14" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DU14" s="86" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="DV14" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW14" s="85" t="n">
+        <x:v>0.9799223012</x:v>
+      </x:c>
+      <x:c r="DX14" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY14" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ14" s="85" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="EA14" s="85" t="n">
+        <x:v>0.664652563</x:v>
+      </x:c>
+      <x:c r="EB14" s="85" t="n">
+        <x:v>1.6100831572</x:v>
+      </x:c>
+      <x:c r="EC14" s="85" t="n">
+        <x:v>19.0156570415</x:v>
+      </x:c>
+      <x:c r="ED14" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE14" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="EF14" s="85" t="n">
+        <x:v>0.5087334748</x:v>
+      </x:c>
+      <x:c r="EG14" s="85" t="n">
+        <x:v>0.5087334748</x:v>
+      </x:c>
+      <x:c r="EH14" s="85" t="n">
+        <x:v>0.862252112</x:v>
+      </x:c>
+      <x:c r="EI14" s="85" t="n">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="EJ14" s="85" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="EK14" s="85" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="EL14" s="85" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="EM14" s="85" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="EN14" s="85" t="n">
+        <x:v>1609</x:v>
+      </x:c>
+      <x:c r="EO14" s="85" t="n">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="EP14" s="85" t="n">
+        <x:v>526927</x:v>
+      </x:c>
+      <x:c r="EQ14" s="85" t="n">
+        <x:v>22122</x:v>
+      </x:c>
+      <x:c r="ER14" s="85" t="n">
+        <x:v>16596</x:v>
+      </x:c>
+      <x:c r="ES14" s="85" t="n">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="ET14" s="85" t="n">
+        <x:v>33740</x:v>
+      </x:c>
+      <x:c r="EU14" s="85" t="n">
+        <x:v>2441</x:v>
+      </x:c>
+      <x:c r="EV14" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW14" s="268"/>
+      <x:c r="EX14" s="268" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="EY14" s="269" t="str">
+        <x:v>inferred from BL2026-1448 sunset clause and both companion ordinances effective July 31; no separate termination notice located</x:v>
+      </x:c>
+      <x:c r="EZ14" s="269" t="str">
+        <x:v>Expired</x:v>
+      </x:c>
+      <x:c r="FA14" s="269" t="str">
+        <x:v>Nashville and Davidson County jurisdiction</x:v>
+      </x:c>
+      <x:c r="FB14" s="269" t="str">
+        <x:v>data-center zoning, building, and grading permits</x:v>
+      </x:c>
+      <x:c r="FC14" s="269" t="str">
+        <x:v>BL2026-1448</x:v>
+      </x:c>
+      <x:c r="FD14" s="269" t="str">
+        <x:v>https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=2A6E536A-95F6-46B9-993A-1F6E018DD389&amp;ID=8063111 | https://nashville.legistar.com/LegislationDetail.aspx?FullText=1&amp;GUID=007B8704-62ED-46D1-9E9A-8B3F778229A8&amp;ID=8040869 | https://nashville.legistar.com/LegislationDetail.aspx?From=RSS&amp;GUID=ABD166B5-005A-400B-B447-1F81227D7B2C&amp;ID=8040870</x:v>
+      </x:c>
+      <x:c r="FE14" s="269" t="str">
+        <x:v>BL2026-1391 and BL2026-1392 both became effective July 31; BL2026-1448 sunsets on their joint effective date or November 1, whichever occurs first.</x:v>
+      </x:c>
+      <x:c r="FF14" s="269"/>
+      <x:c r="FG14" s="268"/>
+      <x:c r="FH14" s="268"/>
+      <x:c r="FI14" s="269"/>
+      <x:c r="FJ14" s="270" t="n">
+        <x:v>99.5672967433</x:v>
+      </x:c>
+      <x:c r="FK14" s="270" t="n">
+        <x:v>99.4488726941</x:v>
+      </x:c>
+      <x:c r="FL14" s="270" t="n">
+        <x:v>99.6151218401</x:v>
+      </x:c>
+      <x:c r="FM14" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN14" s="271" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="FO14" s="269" t="str">
+        <x:v>Priority 1</x:v>
+      </x:c>
+      <x:c r="FP14" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ14" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR14" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS14" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT14" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU14" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV14" s="269" t="str">
+        <x:v>linked_facility_context; reference_point_* describes policy jurisdiction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="101.25" customHeight="1">
+      <x:c r="A15" s="248" t="str">
+        <x:v>TNMOR-011</x:v>
+      </x:c>
+      <x:c r="B15" s="248" t="str">
+        <x:v>local_data_center_moratorium</x:v>
+      </x:c>
+      <x:c r="C15" s="248" t="str">
+        <x:v>Gallatin</x:v>
+      </x:c>
+      <x:c r="D15" s="248" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="E15" s="248" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="F15" s="249" t="n">
+        <x:v>46280</x:v>
+      </x:c>
+      <x:c r="G15" s="248" t="str">
+        <x:v>Six months proposed; passed first reading September 15, 2026; public hearing/final action scheduled October 20, 2026</x:v>
+      </x:c>
+      <x:c r="H15" s="248" t="str">
+        <x:v>In Process</x:v>
+      </x:c>
+      <x:c r="I15" s="248" t="str">
+        <x:v>Proposed citywide pause on new data-center applications; follows a separate 60-day application pause adopted July 28, 2026.</x:v>
+      </x:c>
+      <x:c r="J15" s="248" t="str">
+        <x:v>Council is considering a pause while developing standards for water and electricity demand, noise and facility types. The amended duration was shortened from 12 months to six months on first reading.</x:v>
+      </x:c>
+      <x:c r="K15" s="248" t="str">
+        <x:v>FOX 17 (WZTV) | Gallatin Agenda Center / Notices &amp; Meetings; Nashville Tennessean; FOX 17</x:v>
+      </x:c>
+      <x:c r="L15" s="248" t="str">
+        <x:v>https://fox17.com/news/local/gallatin-city-council-advances-12-month-data-center-moratorium-for-vote-next-week | https://gallatintn.gov/agendacenter | https://www.gallatintn.gov/AgendaCenter/ | https://www.wuot.org/2026-09-08/kentuckys-yet-to-see-a-hyperscale-data-center-come-online-but-gallatin-could-offer-a-glimpse-at-what-to-expect | https://www.aol.com/articles/gallatin-home-meta-campus-weighs-142756000.html</x:v>
+      </x:c>
+      <x:c r="M15" s="248" t="str">
+        <x:v>https://www.interconnectedcapital.com/research/data-center-moratoriums</x:v>
+      </x:c>
+      <x:c r="N15" s="249" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="O15" s="248" t="str">
+        <x:v>interconnected-capital:tn:gallatin:2026-09-08</x:v>
+      </x:c>
+      <x:c r="P15" s="248" t="str">
+        <x:v>TNDC-015</x:v>
+      </x:c>
+      <x:c r="Q15" s="248" t="str">
+        <x:v>Policy-context relationship. The tracker source states Gallatin is already home to a massive Meta data center; TNDC-015 is the existing full Master record for that campus. The proposed moratorium remains jurisdiction-wide, not a Meta-specific action.</x:v>
+      </x:c>
+      <x:c r="R15" s="248" t="str">
+        <x:v>first-reading-media-corroborated; final-action-pending</x:v>
+      </x:c>
+      <x:c r="S15" s="257" t="n">
+        <x:v>36.388184</x:v>
+      </x:c>
+      <x:c r="T15" s="257" t="n">
+        <x:v>-86.448109</x:v>
+      </x:c>
+      <x:c r="U15" s="248" t="str">
+        <x:v>Gallatin City Hall, Gallatin, TN</x:v>
+      </x:c>
+      <x:c r="V15" s="248" t="str">
+        <x:v>address_or_site</x:v>
+      </x:c>
+      <x:c r="W15" s="248" t="str">
+        <x:v>https://www.openstreetmap.org/search?query=Gallatin%20City%20Hall%2C%20Tennessee#map=19/36.388184/-86.448109</x:v>
+      </x:c>
+      <x:c r="X15" s="248" t="str">
+        <x:v>Jurisdiction-government reference point only; not a data-center site.</x:v>
+      </x:c>
+      <x:c r="Y15" s="248" t="str">
+        <x:v>TNDC-015</x:v>
+      </x:c>
+      <x:c r="Z15" s="248" t="str">
+        <x:v>Meta Gallatin Data Center Campus</x:v>
+      </x:c>
+      <x:c r="AA15" s="248" t="str">
+        <x:v>Meta</x:v>
+      </x:c>
+      <x:c r="AB15" s="248" t="str">
+        <x:v>Meta</x:v>
+      </x:c>
+      <x:c r="AC15" s="248" t="str">
+        <x:v>One Meta Lp</x:v>
+      </x:c>
+      <x:c r="AD15" s="248" t="str">
+        <x:v>Gallatin</x:v>
+      </x:c>
+      <x:c r="AE15" s="248" t="str">
+        <x:v>Sumner</x:v>
+      </x:c>
+      <x:c r="AF15" s="248" t="str">
+        <x:v>37066</x:v>
+      </x:c>
+      <x:c r="AG15" s="248" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="AH15" s="248" t="str">
+        <x:v>fractracker:496</x:v>
+      </x:c>
+      <x:c r="AI15" s="248" t="n">
+        <x:v>6.2572</x:v>
+      </x:c>
+      <x:c r="AJ15" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK15" s="248" t="str">
+        <x:v>operational</x:v>
+      </x:c>
+      <x:c r="AL15" s="248" t="str">
+        <x:v>operational</x:v>
+      </x:c>
+      <x:c r="AM15" s="267" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AN15" s="248" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="AO15" s="248" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="AP15" s="248" t="str">
+        <x:v>core_data_center</x:v>
+      </x:c>
+      <x:c r="AQ15" s="248"/>
+      <x:c r="AR15" s="248" t="n">
+        <x:v>1900000</x:v>
+      </x:c>
+      <x:c r="AS15" s="248" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="AT15" s="248" t="n">
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="AU15" s="248" t="str">
+        <x:v>compute_atlas | fractracker</x:v>
+      </x:c>
+      <x:c r="AV15" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW15" s="248" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AX15" s="248" t="str">
+        <x:v>compute_atlas:meta-gallatin-tn | fractracker:496</x:v>
+      </x:c>
+      <x:c r="AY15" s="248" t="str">
+        <x:v>https://datacenters.atmeta.com/2024/11/gallatin-we-are-online/ | https://ttc.tml1.org/2024/11/15/meta-data-center-begins-operations-gallatin | https://w.media/meta-expands-gallatin-data-center-with-nearly-1b-total-investment/ | https://www.datacenterdynamics.com/en/news/meta-brings-data-centers-in-tents-to-gallatin-tennessee/ | https://www.pascalforgallatin.com/post/why-is-gallatin-giving-woolhawk-a-tax-break-when-they-are-considering-raising-our-property-taxes | https://www.weku.org/amsn/2025-11-25/tennessee-has-60-data-centers-nashville-probably-has-more-than-you-think | https://www.datacenterdynamics.com/en/news/meta-to-expand-tennessee-data-center-campus/</x:v>
+      </x:c>
+      <x:c r="AZ15" s="248" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="BA15" s="248" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="BB15" s="248" t="str">
+        <x:v>identified</x:v>
+      </x:c>
+      <x:c r="BC15" s="248" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="BD15" s="267" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE15" s="248" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="BF15" s="248" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="BG15" s="248" t="str">
+        <x:v>Cross-verified facility record; unresolved values remain null rather than inferred.</x:v>
+      </x:c>
+      <x:c r="BH15" s="248" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="BI15" s="248" t="str">
+        <x:v>direct_site_features</x:v>
+      </x:c>
+      <x:c r="BJ15" s="248" t="n">
+        <x:v>2.3980314314913542</x:v>
+      </x:c>
+      <x:c r="BK15" s="248" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="BL15" s="248" t="n">
+        <x:v>3.91959956912533</x:v>
+      </x:c>
+      <x:c r="BM15" s="248" t="n">
+        <x:v>3.91959956912533</x:v>
+      </x:c>
+      <x:c r="BN15" s="248" t="n">
+        <x:v>14.790394818910544</x:v>
+      </x:c>
+      <x:c r="BO15" s="248" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="BP15" s="248" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ15" s="248" t="n">
+        <x:v>1.6581578932936945</x:v>
+      </x:c>
+      <x:c r="BR15" s="248" t="n">
+        <x:v>24.948091855395333</x:v>
+      </x:c>
+      <x:c r="BS15" s="248" t="n">
+        <x:v>0.4422402921235759</x:v>
+      </x:c>
+      <x:c r="BT15" s="248" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="BU15" s="248" t="str">
+        <x:v>47165</x:v>
+      </x:c>
+      <x:c r="BV15" s="248" t="str">
+        <x:v>Sumner County</x:v>
+      </x:c>
+      <x:c r="BW15" s="248" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="BX15" s="248" t="n">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="BY15" s="248" t="n">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="BZ15" s="248" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="CA15" s="248" t="n">
+        <x:v>1692</x:v>
+      </x:c>
+      <x:c r="CB15" s="248" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="CC15" s="248" t="n">
+        <x:v>56402</x:v>
+      </x:c>
+      <x:c r="CD15" s="248" t="n">
+        <x:v>3875</x:v>
+      </x:c>
+      <x:c r="CE15" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CF15" s="248" t="n">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="CG15" s="248" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="CH15" s="248" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="CI15" s="248" t="n">
+        <x:v>1911</x:v>
+      </x:c>
+      <x:c r="CJ15" s="248" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="CK15" s="248" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="CL15" s="248" t="str">
+        <x:v>TNDC-015</x:v>
+      </x:c>
+      <x:c r="CM15" s="248" t="str">
+        <x:v>TN5K-2199</x:v>
+      </x:c>
+      <x:c r="CN15" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CO15" s="248" t="str">
+        <x:v>regulatory_floodway</x:v>
+      </x:c>
+      <x:c r="CP15" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CQ15" s="248" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="CR15" s="248" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="CS15" s="248" t="str">
+        <x:v>0.827479319439994</x:v>
+      </x:c>
+      <x:c r="CT15" s="248" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="CU15" s="248" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="CV15" s="248" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="CW15" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CX15" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CY15" s="248" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="CZ15" s="248" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="DA15" s="248" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
+      </x:c>
+      <x:c r="DB15" s="85" t="str">
+        <x:v>2026-09-23</x:v>
+      </x:c>
+      <x:c r="DC15" s="85" t="str">
+        <x:v>https://gallatintn.gov/agendacenter | https://gallatintn.gov/2477/Notices-Meetings | https://www.aol.com/articles/gallatin-home-meta-campus-weighs-142756000.html | https://fox17.com/news/local/gallatin-city-council-advances-12-month-data-center-moratorium-for-vote-next-week | https://www.gallatintn.gov/AgendaCenter/ | https://www.wuot.org/2026-09-08/kentuckys-yet-to-see-a-hyperscale-data-center-come-online-but-gallatin-could-offer-a-glimpse-at-what-to-expect</x:v>
+      </x:c>
+      <x:c r="DD15" s="85" t="str">
+        <x:v>The Sept. 15 first reading amended the proposal from 12 months to six months. Gallatin's official notices list an Oct. 20 public hearing on O26-9-67, so as of Sept. 23 the action remained in process. TNDC-015 remains policy context only. | Six-month ordinance had first reading September 15 and was pending final action as of September 23. A separate 60-day application pause had passed July 28.</x:v>
+      </x:c>
+      <x:c r="DE15" s="85"/>
+      <x:c r="DF15" s="85"/>
+      <x:c r="DG15" s="85"/>
+      <x:c r="DH15" s="85"/>
+      <x:c r="DI15" s="85" t="str">
+        <x:v>Gallatin</x:v>
+      </x:c>
+      <x:c r="DJ15" s="85" t="str">
+        <x:v>Sumner County</x:v>
+      </x:c>
+      <x:c r="DK15" s="85" t="str">
+        <x:v>47165</x:v>
+      </x:c>
+      <x:c r="DL15" s="85" t="str">
+        <x:v>Gallatin City Hall, 132 W Main Street, Gallatin, TN 37066</x:v>
+      </x:c>
+      <x:c r="DM15" s="85" t="str">
+        <x:v>37066</x:v>
+      </x:c>
+      <x:c r="DN15" s="85" t="str">
+        <x:v>Nearest Phase 2 Domain_Cells 5-km equal-area cell centroid by haversine distance; regional proxy only</x:v>
+      </x:c>
+      <x:c r="DO15" s="85" t="str">
+        <x:v>TN5K-2161</x:v>
+      </x:c>
+      <x:c r="DP15" s="85" t="n">
+        <x:v>2.328</x:v>
+      </x:c>
+      <x:c r="DQ15" s="85" t="str">
+        <x:v>jurisdiction_reference_proxy; nearest 5-km Phase 2 domain cell; not a facility site, not a suitability score, and not a model presence record</x:v>
+      </x:c>
+      <x:c r="DR15" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DS15" s="85"/>
+      <x:c r="DT15" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DU15" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DV15" s="86" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="DW15" s="85" t="n">
+        <x:v>0.6482632053</x:v>
+      </x:c>
+      <x:c r="DX15" s="85" t="str">
+        <x:v>metro_50km</x:v>
+      </x:c>
+      <x:c r="DY15" s="85" t="str">
+        <x:v>metro_proxy</x:v>
+      </x:c>
+      <x:c r="DZ15" s="85" t="str">
+        <x:v>middle</x:v>
+      </x:c>
+      <x:c r="EA15" s="85" t="n">
+        <x:v>1.1141119436</x:v>
+      </x:c>
+      <x:c r="EB15" s="85" t="n">
+        <x:v>1.1141119436</x:v>
+      </x:c>
+      <x:c r="EC15" s="85" t="n">
+        <x:v>6.3992957698</x:v>
+      </x:c>
+      <x:c r="ED15" s="85" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="EE15" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="EF15" s="85" t="n">
+        <x:v>0.1435987599</x:v>
+      </x:c>
+      <x:c r="EG15" s="85" t="n">
+        <x:v>20.6441719818</x:v>
+      </x:c>
+      <x:c r="EH15" s="85" t="n">
+        <x:v>0.6053398728</x:v>
+      </x:c>
+      <x:c r="EI15" s="85" t="n">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="EJ15" s="85" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="EK15" s="85" t="n">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="EL15" s="85" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="EM15" s="85" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="EN15" s="85" t="n">
+        <x:v>1717</x:v>
+      </x:c>
+      <x:c r="EO15" s="85" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="EP15" s="85" t="n">
+        <x:v>56402</x:v>
+      </x:c>
+      <x:c r="EQ15" s="85" t="n">
+        <x:v>3875</x:v>
+      </x:c>
+      <x:c r="ER15" s="85" t="n">
+        <x:v>754</x:v>
+      </x:c>
+      <x:c r="ES15" s="85" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="ET15" s="85" t="n">
+        <x:v>1911</x:v>
+      </x:c>
+      <x:c r="EU15" s="85" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="EV15" s="268" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="EW15" s="268"/>
+      <x:c r="EX15" s="268"/>
+      <x:c r="EY15" s="269"/>
+      <x:c r="EZ15" s="269" t="str">
+        <x:v>In Process</x:v>
+      </x:c>
+      <x:c r="FA15" s="269" t="str">
+        <x:v>Gallatin city limits</x:v>
+      </x:c>
+      <x:c r="FB15" s="269" t="str">
+        <x:v>proposed new data-center applications</x:v>
+      </x:c>
+      <x:c r="FC15" s="269" t="str">
+        <x:v>O26-9-67, first reading only</x:v>
+      </x:c>
+      <x:c r="FD15" s="269" t="str">
+        <x:v>https://www.gallatintn.gov/AgendaCenter/ | https://www.wuot.org/2026-09-08/kentuckys-yet-to-see-a-hyperscale-data-center-come-online-but-gallatin-could-offer-a-glimpse-at-what-to-expect | https://www.aol.com/articles/gallatin-home-meta-campus-weighs-142756000.html</x:v>
+      </x:c>
+      <x:c r="FE15" s="269" t="str">
+        <x:v>Six-month ordinance had first reading September 15 and was pending final action as of September 23. A separate 60-day application pause had passed July 28.</x:v>
+      </x:c>
+      <x:c r="FF15" s="269" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="FG15" s="268" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="FH15" s="268" t="n">
+        <x:v>46291</x:v>
+      </x:c>
+      <x:c r="FI15" s="269" t="str">
+        <x:v>https://www.gallatintn.gov/27/Departments</x:v>
+      </x:c>
+      <x:c r="FJ15" s="270" t="n">
+        <x:v>78.068777044</x:v>
+      </x:c>
+      <x:c r="FK15" s="270" t="n">
+        <x:v>75.4805283535</x:v>
+      </x:c>
+      <x:c r="FL15" s="270" t="n">
+        <x:v>80.4919152813</x:v>
+      </x:c>
+      <x:c r="FM15" s="269" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="FN15" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FO15" s="269" t="str">
+        <x:v>Priority 2</x:v>
+      </x:c>
+      <x:c r="FP15" s="269" t="str">
+        <x:v>TN-DC-1.0.0</x:v>
+      </x:c>
+      <x:c r="FQ15" s="269" t="str">
+        <x:v>../model/phase 4/results/TN-DC-1.0.0_statewide_scores.csv</x:v>
+      </x:c>
+      <x:c r="FR15" s="269" t="str">
+        <x:v>D1-relative empirical-affinity percentile of nearest 5-km grid cell; jurisdiction reference context only; not construction or permit probability</x:v>
+      </x:c>
+      <x:c r="FS15" s="269" t="str">
+        <x:v>jurisdiction_reference_point</x:v>
+      </x:c>
+      <x:c r="FT15" s="269" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="FU15" s="271" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="FV15" s="269" t="str">
+        <x:v>linked_facility_context; reference_point_* describes policy jurisdiction</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e84555b28f04ce9"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -8914,11 +15627,10 @@
         <x:v>Raw source records</x:v>
       </x:c>
       <x:c r="B5" s="131" t="n">
-        <x:f>COUNTA(Raw_Aligned!B2:B1000)</x:f>
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C5" s="67" t="str">
-        <x:v>All source records, including appended public verification rows.</x:v>
+        <x:v>All source records, including the 2026-09-22 Project River candidate discovery row.</x:v>
       </x:c>
       <x:c r="D5" s="71"/>
       <x:c r="E5" s="67" t="str">
@@ -24661,7 +31373,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93c813e2fcf143ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1781b639dcd4443e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45496,6 +52208,106 @@
       </x:c>
       <x:c r="AR217"/>
     </x:row>
+    <x:row r="218">
+      <x:c r="A218" t="str">
+        <x:v>project_river</x:v>
+      </x:c>
+      <x:c r="B218" t="str">
+        <x:v>project-river-2026-08-26</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>Project River Industrial Energy and Data Center Campus</x:v>
+      </x:c>
+      <x:c r="D218" t="str">
+        <x:v>Project River</x:v>
+      </x:c>
+      <x:c r="E218" t="str">
+        <x:v>Wright family / Wright Industrial Group</x:v>
+      </x:c>
+      <x:c r="F218"/>
+      <x:c r="G218" t="str">
+        <x:v>Lower River Road area</x:v>
+      </x:c>
+      <x:c r="H218"/>
+      <x:c r="I218"/>
+      <x:c r="J218" t="str">
+        <x:v>Bradley</x:v>
+      </x:c>
+      <x:c r="K218" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="L218"/>
+      <x:c r="M218"/>
+      <x:c r="N218"/>
+      <x:c r="O218" t="str">
+        <x:v>area_or_city</x:v>
+      </x:c>
+      <x:c r="P218" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="Q218" t="str">
+        <x:v>Public sources identify Cleveland/Bradley County and the Lower River Road area; no defensible facility-point coordinate is published.</x:v>
+      </x:c>
+      <x:c r="R218" t="str">
+        <x:v>proposed</x:v>
+      </x:c>
+      <x:c r="S218" t="str">
+        <x:v>proposed</x:v>
+      </x:c>
+      <x:c r="T218" t="str">
+        <x:v>data_center</x:v>
+      </x:c>
+      <x:c r="U218" t="str">
+        <x:v>Proposed industrial campus described by sponsor as including a large data center with on-site generation.</x:v>
+      </x:c>
+      <x:c r="V218"/>
+      <x:c r="W218"/>
+      <x:c r="X218"/>
+      <x:c r="Y218"/>
+      <x:c r="Z218"/>
+      <x:c r="AA218"/>
+      <x:c r="AB218"/>
+      <x:c r="AC218"/>
+      <x:c r="AD218" t="str">
+        <x:v>Natural gas and biomass generation described by sponsor; do not record generation capacity as data-center capacity.</x:v>
+      </x:c>
+      <x:c r="AE218"/>
+      <x:c r="AF218"/>
+      <x:c r="AG218"/>
+      <x:c r="AH218" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="AI218" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="AJ218" t="str">
+        <x:v>https://projectriver.energy/project-river-a-new-kind-of-industrial-energy-campus/ | https://clevelandtn.gov/m/newsflash/home/detail/577</x:v>
+      </x:c>
+      <x:c r="AK218" t="str">
+        <x:v>https://projectriver.energy/project-river-a-new-kind-of-industrial-energy-campus/</x:v>
+      </x:c>
+      <x:c r="AL218" t="str">
+        <x:v>https://projectriver.energy/project-river-a-new-kind-of-industrial-energy-campus/</x:v>
+      </x:c>
+      <x:c r="AM218" t="str">
+        <x:v>Government notice dated 2026-09-18 confirms Project River proceedings are ongoing but suspended pending independent engineering review. No tenant, exact facility coordinate, or final approval is publicly established.</x:v>
+      </x:c>
+      <x:c r="AN218" t="str">
+        <x:v>core_data_center</x:v>
+      </x:c>
+      <x:c r="AO218" s="76" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AP218" t="str">
+        <x:v>wright family wright industrial group</x:v>
+      </x:c>
+      <x:c r="AQ218" t="str">
+        <x:v>project river industrial energy and data center campus</x:v>
+      </x:c>
+      <x:c r="AR218" t="str">
+        <x:v>lower river road area</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="7">
     <x:dataValidation type="list" sqref="K2:K5000">
@@ -45524,7 +52336,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cd57382c1b4424f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a495922925e4ff6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47566,7 +54378,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2f7eb29274f4c41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b115ba976e04d63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47746,7 +54558,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R382e68194b2f4993"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1241b10fca5c4f30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48122,7 +54934,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb98e9fcef35f4beb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38befa4e7eec4d3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48307,7 +55119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R898d95e465624112"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43d851be480244a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51666,6 +58478,199 @@
         <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>TNCAND-018</x:v>
+      </x:c>
+      <x:c r="B18"/>
+      <x:c r="C18" t="str">
+        <x:v>Project River Industrial Energy and Data Center Campus</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>proposed_data_center_energy_campus</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>707 Lower River Road NW</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Charleston</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Bradley</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>TN</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>37310</x:v>
+      </x:c>
+      <x:c r="K18" t="n">
+        <x:v>35.3314</x:v>
+      </x:c>
+      <x:c r="L18" t="n">
+        <x:v>-84.8686</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>Project sponsor describes a proposed Cleveland/Bradley County data-center and energy campus. City of Cleveland annexation materials identify Wright Brothers Construction land on Lower River Road (Tax Map 009 Parcel 012.00). The public registry coordinate is an approximate Lower River Road NW geocode, not a parcel centroid; it is used only for grid-aligned screening fields.</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>project_river | city_of_cleveland | compute_atlas</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>https://projectriver.energy/project-river-a-new-kind-of-industrial-energy-campus/ | https://clevelandtn.gov/DocumentCenter/View/3080 | https://suedatacenters.org/data-centers/project-river-data-center-bradley-county-tn</x:v>
+      </x:c>
+      <x:c r="P18" t="str">
+        <x:v>2026-09-22</x:v>
+      </x:c>
+      <x:c r="Q18" t="str">
+        <x:v>Approximate Lower River Road NW coordinate (35.3314, -84.8686) is a public road geocode, not a surveyed site point. The spatial attributes below are from nearest frozen 5 km cell TN5K-3295, 1.565 km from that coordinate. Do not promote to Master until a tenant, final approval, and site-level facility evidence are public.</x:v>
+      </x:c>
+      <x:c r="R18" t="str">
+        <x:v>approximate</x:v>
+      </x:c>
+      <x:c r="S18" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="T18" t="str">
+        <x:v>Compute Atlas-derived Lower River Road NW geocode reported by Sue Data Centers; corroborated geographic context by City of Cleveland annexation plan.</x:v>
+      </x:c>
+      <x:c r="U18" t="str">
+        <x:v>derived_from_frozen_5km_grid</x:v>
+      </x:c>
+      <x:c r="V18" t="n">
+        <x:v>21.597746449</x:v>
+      </x:c>
+      <x:c r="W18" t="str">
+        <x:v>Noise / isolated</x:v>
+      </x:c>
+      <x:c r="X18" t="n">
+        <x:v>2.1997392221</x:v>
+      </x:c>
+      <x:c r="Y18" t="n">
+        <x:v>2.1997392221</x:v>
+      </x:c>
+      <x:c r="Z18" t="n">
+        <x:v>2.1997392221</x:v>
+      </x:c>
+      <x:c r="AA18" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="AB18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC18" t="n">
+        <x:v>2.4424678494</x:v>
+      </x:c>
+      <x:c r="AD18" t="n">
+        <x:v>5.0752916477</x:v>
+      </x:c>
+      <x:c r="AE18" t="n">
+        <x:v>0.4557985082</x:v>
+      </x:c>
+      <x:c r="AF18" t="n">
+        <x:v>1241</x:v>
+      </x:c>
+      <x:c r="AG18" t="n">
+        <x:v>47011</x:v>
+      </x:c>
+      <x:c r="AH18" t="str">
+        <x:v>Bradley County</x:v>
+      </x:c>
+      <x:c r="AI18" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AJ18" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="AK18" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="AL18" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AM18" t="n">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="AN18" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AO18" t="n">
+        <x:v>42835</x:v>
+      </x:c>
+      <x:c r="AP18" t="n">
+        <x:v>2074</x:v>
+      </x:c>
+      <x:c r="AQ18" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="AR18" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="AS18" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AT18" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="AU18" t="n">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="AV18" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="AW18" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="AX18" t="str">
+        <x:v>TNCAND-018</x:v>
+      </x:c>
+      <x:c r="AY18" t="str">
+        <x:v>TN5K-3295</x:v>
+      </x:c>
+      <x:c r="AZ18" s="76" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA18"/>
+      <x:c r="BB18" s="76" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC18" s="76" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD18" s="76" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE18" t="n">
+        <x:v>1.7647514409</x:v>
+      </x:c>
+      <x:c r="BF18" t="str">
+        <x:v>nonmetro</x:v>
+      </x:c>
+      <x:c r="BG18" t="str">
+        <x:v>nonmetro_proxy</x:v>
+      </x:c>
+      <x:c r="BH18" t="str">
+        <x:v>east</x:v>
+      </x:c>
+      <x:c r="BI18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="BJ18" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BK18" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="BL18" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="BM18" t="str">
+        <x:v>USGS 3DEP; USGS PAD-US; Tennessee DFIRM; USGS NHD; TN-DC frozen 5 km feature grid</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="E2:E2000">
@@ -51691,7 +58696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec46d6693e164d2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa87e389651c412f"/>
   </x:tableParts>
 </x:worksheet>
 </file>